--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -18,7 +18,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">밤과다람쥐!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이고이스트!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">피난민!$A$1:$J$30</definedName>
   </definedNames>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="556">
   <si>
     <t>guild_name</t>
   </si>
@@ -254,7 +254,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 1221억 9952만</t>
+    <t>15조 2195억 3666만</t>
   </si>
   <si>
     <t>2</t>
@@ -272,57 +272,57 @@
     <t>신궁</t>
   </si>
   <si>
+    <t>14조 951억 2182만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>12조 6365억 3160만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>10조 7888억 6150만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
     <t>102</t>
   </si>
   <si>
-    <t>14조 951억 2182만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>12조 6365억 3160만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>10조 6714억 9011만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>9조 4831억 8007만</t>
   </si>
   <si>
@@ -335,7 +335,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>7조 3899억 9567만</t>
+    <t>8조 3534억 4319만</t>
   </si>
   <si>
     <t>7</t>
@@ -377,7 +377,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>5조 1472억 5810만</t>
+    <t>5조 1592억 3651만</t>
   </si>
   <si>
     <t>10</t>
@@ -407,7 +407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>3조 8750억 1931만</t>
+    <t>4조 2089억 9652만</t>
   </si>
   <si>
     <t>12</t>
@@ -449,6 +449,21 @@
     <t>15</t>
   </si>
   <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>2조 5943억 9545만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -461,18 +476,6 @@
     <t>2조 5940억 8239만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>2조 5711억 1705만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
@@ -488,30 +491,27 @@
     <t>18</t>
   </si>
   <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 5359억 851만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>꾸르꾸르</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>2조 3765억 8123만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 3302억 2720만</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -578,6 +578,18 @@
     <t>25</t>
   </si>
   <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 8260억 5446만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
     <t>여눈</t>
   </si>
   <si>
@@ -587,7 +599,7 @@
     <t>1조 7856억 5439만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -599,18 +611,6 @@
     <t>1조 6923억 5834만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 6435억 7464만</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -626,282 +626,270 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
+    <t>증권보이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>20조 4898억 61만</t>
+  </si>
+  <si>
+    <t>둥둥콩이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>19조 9942억 330만</t>
+  </si>
+  <si>
+    <t>가온스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>17조 4585억 7977만</t>
+  </si>
+  <si>
+    <t>Canary</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Canary</t>
+  </si>
+  <si>
+    <t>15조 8193억 825만</t>
+  </si>
+  <si>
+    <t>처히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
+  </si>
+  <si>
+    <t>13조 2156억 7422만</t>
+  </si>
+  <si>
+    <t>환생의불꼬츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>10조 9549억 8302만</t>
+  </si>
+  <si>
+    <t>밍진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8조 9166억 6911만</t>
+  </si>
+  <si>
+    <t>Naco</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Naco</t>
+  </si>
+  <si>
+    <t>6조 9849억 7135만</t>
+  </si>
+  <si>
+    <t>AKPS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
+  </si>
+  <si>
+    <t>6조 5629억 7412만</t>
+  </si>
+  <si>
+    <t>사나이기백황</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
+  </si>
+  <si>
+    <t>3조 8303억 3845만</t>
+  </si>
+  <si>
+    <t>토미오카상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
+  </si>
+  <si>
+    <t>3조 3002억 4541만</t>
+  </si>
+  <si>
+    <t>평평이형</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
+  </si>
+  <si>
+    <t>3조 906억 3513만</t>
+  </si>
+  <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>2조 6702억 2482만</t>
+  </si>
+  <si>
+    <t>토니워터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 6162억 1545만</t>
+  </si>
+  <si>
+    <t>펑풀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
+  </si>
+  <si>
+    <t>2조 4885억 7115만</t>
+  </si>
+  <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 4258억 6186만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 4177억 8071만</t>
+  </si>
+  <si>
+    <t>피어난</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
+  </si>
+  <si>
+    <t>2조 305억 8537만</t>
+  </si>
+  <si>
+    <t>샤스찌에</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
+  </si>
+  <si>
+    <t>1조 4976억 9640만</t>
+  </si>
+  <si>
+    <t>보동핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
+  </si>
+  <si>
+    <t>1조 1820억 5434만</t>
+  </si>
+  <si>
+    <t>싸토루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 1480억 9108만</t>
+  </si>
+  <si>
+    <t>지니좋아요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>1조 666억 9786만</t>
+  </si>
+  <si>
+    <t>2026년1월30일</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
+  </si>
+  <si>
+    <t>1조 129억 4198만</t>
+  </si>
+  <si>
+    <t>찐곽정근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>1조 24억 1640만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>8747억 2403만</t>
+  </si>
+  <si>
+    <t>Targa</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Targa</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>5665억 5826만</t>
+  </si>
+  <si>
+    <t>애둘이에요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>5424억 3794만</t>
+  </si>
+  <si>
+    <t>짱창훈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
+  </si>
+  <si>
+    <t>3382억 604만</t>
+  </si>
+  <si>
     <t>29</t>
   </si>
   <si>
-    <t>혜영인기도1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%9C%EC%98%81%EC%9D%B8%EA%B8%B0%EB%8F%841</t>
-  </si>
-  <si>
-    <t>76</t>
-  </si>
-  <si>
-    <t>11억 9359만</t>
-  </si>
-  <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>20조 4898억 61만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19조 9942억 330만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 4585억 7977만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>15조 8193억 825만</t>
-  </si>
-  <si>
-    <t>처히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
-  </si>
-  <si>
-    <t>13조 2156억 7422만</t>
-  </si>
-  <si>
-    <t>환생의불꼬츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>10조 9549억 8302만</t>
-  </si>
-  <si>
-    <t>밍진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8조 9166억 6911만</t>
-  </si>
-  <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 9849억 7135만</t>
-  </si>
-  <si>
-    <t>AKPS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AKPS</t>
-  </si>
-  <si>
-    <t>6조 5629억 7412만</t>
-  </si>
-  <si>
-    <t>사나이기백황</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
-  </si>
-  <si>
-    <t>3조 8303억 3845만</t>
-  </si>
-  <si>
-    <t>토미오카상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%AF%B8%EC%98%A4%EC%B9%B4%EC%83%81</t>
-  </si>
-  <si>
-    <t>3조 3002억 4541만</t>
-  </si>
-  <si>
-    <t>평평이형</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
-  </si>
-  <si>
-    <t>3조 906억 3513만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>2조 6702억 2482만</t>
-  </si>
-  <si>
-    <t>토니워터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>2조 6162억 1545만</t>
-  </si>
-  <si>
-    <t>펑풀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
-  </si>
-  <si>
-    <t>2조 4885억 7115만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 4258억 6186만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 4177억 8071만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>2조 305억 8537만</t>
-  </si>
-  <si>
-    <t>샤스찌에</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
-  </si>
-  <si>
-    <t>1조 4976억 9640만</t>
-  </si>
-  <si>
-    <t>보동핑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
-  </si>
-  <si>
-    <t>1조 1820억 5434만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 1480억 9108만</t>
-  </si>
-  <si>
-    <t>지니좋아요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
-  </si>
-  <si>
-    <t>1조 666억 9786만</t>
-  </si>
-  <si>
-    <t>2026년1월30일</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=2026%EB%85%841%EC%9B%9430%EC%9D%BC</t>
-  </si>
-  <si>
-    <t>1조 129억 4198만</t>
-  </si>
-  <si>
-    <t>찐곽정근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EA%B3%BD%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>1조 24억 1640만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>8747억 2403만</t>
-  </si>
-  <si>
-    <t>Targa</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Targa</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>5665억 5826만</t>
-  </si>
-  <si>
-    <t>애둘이에요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>5424억 3794만</t>
-  </si>
-  <si>
-    <t>짱창훈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
-  </si>
-  <si>
-    <t>3382억 604만</t>
-  </si>
-  <si>
     <t>구리구리뽕리</t>
   </si>
   <si>
@@ -1472,7 +1460,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
   </si>
   <si>
-    <t>12조 8020억 1758만</t>
+    <t>13조 4832억 9129만</t>
   </si>
   <si>
     <t>세계챔피언</t>
@@ -1490,7 +1478,16 @@
     <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
   </si>
   <si>
-    <t>3조 3361억 4225만</t>
+    <t>3조 3854억 4624만</t>
+  </si>
+  <si>
+    <t>찐썽잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 5906억 6272만</t>
   </si>
   <si>
     <t>건야웅</t>
@@ -1502,15 +1499,6 @@
     <t>2조 4543억 8797만</t>
   </si>
   <si>
-    <t>찐썽잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 2859억 6115만</t>
-  </si>
-  <si>
     <t>보꿍</t>
   </si>
   <si>
@@ -1544,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
   </si>
   <si>
-    <t>9440억 8488만</t>
+    <t>9811억 2977만</t>
   </si>
   <si>
     <t>묨밍</t>
@@ -1625,7 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
   </si>
   <si>
-    <t>4366억 6830만</t>
+    <t>4484억 5846만</t>
   </si>
   <si>
     <t>깝용잉</t>
@@ -1643,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
   </si>
   <si>
-    <t>3876억 9482만</t>
+    <t>4161억 969만</t>
   </si>
   <si>
     <t>모몬쌍</t>
@@ -1652,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
   </si>
   <si>
-    <t>2497억 5284만</t>
+    <t>2679억 4512만</t>
   </si>
   <si>
     <t>우주강아지</t>
@@ -1673,7 +1661,16 @@
     <t>92</t>
   </si>
   <si>
-    <t>1787억 2037만</t>
+    <t>1801억 3527만</t>
+  </si>
+  <si>
+    <t>이진니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>970억 5432만</t>
   </si>
   <si>
     <t>봉오리</t>
@@ -1685,16 +1682,7 @@
     <t>87</t>
   </si>
   <si>
-    <t>919억 4970만</t>
-  </si>
-  <si>
-    <t>이진니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>902억 7225만</t>
+    <t>921억 1003만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -1703,10 +1691,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%85%84%EC%84%A4%EB%94%B8%EA%B8%B0</t>
   </si>
   <si>
-    <t>84</t>
-  </si>
-  <si>
-    <t>230억 2754만</t>
+    <t>85</t>
+  </si>
+  <si>
+    <t>248억 7797만</t>
   </si>
 </sst>
 </file>
@@ -2346,7 +2334,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2446,10 +2434,10 @@
         <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>81</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>82</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2460,28 +2448,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>87</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>88</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2492,28 +2480,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2524,25 +2512,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>98</v>
@@ -2571,10 +2559,10 @@
         <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>102</v>
@@ -2603,7 +2591,7 @@
         <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>106</v>
@@ -2638,7 +2626,7 @@
         <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>112</v>
@@ -2670,7 +2658,7 @@
         <v>73</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>116</v>
@@ -2731,10 +2719,10 @@
         <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>126</v>
@@ -2798,7 +2786,7 @@
         <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>134</v>
@@ -2894,10 +2882,10 @@
         <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2908,16 +2896,16 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -2929,7 +2917,7 @@
         <v>121</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2940,25 +2928,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>155</v>
+        <v>86</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>156</v>
@@ -2987,10 +2975,10 @@
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>87</v>
+        <v>142</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>160</v>
@@ -3022,7 +3010,7 @@
         <v>73</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>164</v>
@@ -3054,7 +3042,7 @@
         <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>168</v>
@@ -3086,7 +3074,7 @@
         <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>172</v>
@@ -3118,7 +3106,7 @@
         <v>80</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>176</v>
@@ -3150,7 +3138,7 @@
         <v>180</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>181</v>
@@ -3179,10 +3167,10 @@
         <v>79</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>142</v>
+        <v>86</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>185</v>
@@ -3211,10 +3199,10 @@
         <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>189</v>
@@ -3243,10 +3231,10 @@
         <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>96</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>193</v>
@@ -3287,40 +3275,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3350,7 +3306,6 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3411,13 +3366,13 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -3429,7 +3384,7 @@
         <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -3443,25 +3398,25 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -3472,16 +3427,16 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -3493,7 +3448,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>212</v>
+        <v>207</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -3504,16 +3459,16 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>208</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>209</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -3525,7 +3480,7 @@
         <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>210</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -3536,16 +3491,16 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>211</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>217</v>
+        <v>212</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -3554,10 +3509,10 @@
         <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>218</v>
+        <v>213</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -3571,13 +3526,13 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>219</v>
+        <v>214</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>215</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
@@ -3586,10 +3541,10 @@
         <v>73</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>216</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -3603,13 +3558,13 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>222</v>
+        <v>217</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>79</v>
@@ -3618,10 +3573,10 @@
         <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>219</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -3635,13 +3590,13 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>225</v>
+        <v>220</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
@@ -3650,10 +3605,10 @@
         <v>111</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>222</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -3667,25 +3622,25 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>223</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>224</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H10" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>225</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -3699,25 +3654,25 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>226</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>227</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>228</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -3731,13 +3686,13 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>229</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>235</v>
+        <v>230</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
@@ -3746,10 +3701,10 @@
         <v>80</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>236</v>
+        <v>231</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -3763,13 +3718,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>232</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -3778,10 +3733,10 @@
         <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -3795,25 +3750,25 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>243</v>
+        <v>238</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -3827,13 +3782,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -3842,10 +3797,10 @@
         <v>73</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>246</v>
+        <v>241</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -3859,13 +3814,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>247</v>
+        <v>242</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -3874,10 +3829,10 @@
         <v>80</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>249</v>
+        <v>244</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -3891,25 +3846,25 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>250</v>
+        <v>245</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>251</v>
+        <v>246</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>252</v>
+        <v>247</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -3920,16 +3875,16 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -3941,7 +3896,7 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>255</v>
+        <v>250</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -3952,28 +3907,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>257</v>
+        <v>252</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -3987,13 +3942,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>260</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
@@ -4005,7 +3960,7 @@
         <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -4019,25 +3974,25 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -4051,25 +4006,25 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>266</v>
+        <v>261</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>268</v>
+        <v>263</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -4083,13 +4038,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>269</v>
+        <v>264</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>270</v>
+        <v>265</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
@@ -4101,7 +4056,7 @@
         <v>197</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -4115,13 +4070,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -4133,7 +4088,7 @@
         <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -4147,25 +4102,25 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -4185,7 +4140,7 @@
         <v>33</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>72</v>
@@ -4194,10 +4149,10 @@
         <v>120</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -4211,13 +4166,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -4226,10 +4181,10 @@
         <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -4243,13 +4198,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -4258,10 +4213,10 @@
         <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -4275,13 +4230,13 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
@@ -4290,10 +4245,10 @@
         <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -4304,28 +4259,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -4423,25 +4378,25 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -4455,13 +4410,13 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>79</v>
@@ -4470,10 +4425,10 @@
         <v>80</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>300</v>
+        <v>296</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -4484,16 +4439,16 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -4505,7 +4460,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>303</v>
+        <v>299</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -4516,16 +4471,16 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -4537,7 +4492,7 @@
         <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -4548,16 +4503,16 @@
         <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -4569,7 +4524,7 @@
         <v>106</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -4583,13 +4538,13 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
@@ -4601,7 +4556,7 @@
         <v>106</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -4615,25 +4570,25 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>106</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -4647,25 +4602,25 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -4679,13 +4634,13 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -4697,7 +4652,7 @@
         <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -4711,13 +4666,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -4729,7 +4684,7 @@
         <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -4743,25 +4698,25 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H12" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -4775,13 +4730,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -4790,10 +4745,10 @@
         <v>73</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -4813,19 +4768,19 @@
         <v>42</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>72</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4839,13 +4794,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -4857,7 +4812,7 @@
         <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -4871,25 +4826,25 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>337</v>
+        <v>333</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H16" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I16" s="2" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -4903,13 +4858,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -4921,7 +4876,7 @@
         <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -4932,16 +4887,16 @@
         <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -4950,10 +4905,10 @@
         <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -4964,16 +4919,16 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
@@ -4985,7 +4940,7 @@
         <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -4999,13 +4954,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
@@ -5017,7 +4972,7 @@
         <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -5031,13 +4986,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
@@ -5049,7 +5004,7 @@
         <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -5063,13 +5018,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
@@ -5078,10 +5033,10 @@
         <v>80</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -5095,25 +5050,25 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -5127,13 +5082,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -5142,10 +5097,10 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -5159,13 +5114,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -5174,10 +5129,10 @@
         <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -5191,13 +5146,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>79</v>
@@ -5206,10 +5161,10 @@
         <v>73</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -5223,13 +5178,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>369</v>
+        <v>365</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -5238,10 +5193,10 @@
         <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -5255,13 +5210,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -5270,10 +5225,10 @@
         <v>73</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -5287,25 +5242,25 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -5316,28 +5271,28 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>380</v>
+        <v>376</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>381</v>
+        <v>377</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>382</v>
+        <v>378</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -5435,25 +5390,25 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>383</v>
+        <v>379</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>384</v>
+        <v>380</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>74</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -5467,13 +5422,13 @@
         <v>76</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>79</v>
@@ -5482,10 +5437,10 @@
         <v>73</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>388</v>
+        <v>384</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5496,28 +5451,28 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>389</v>
+        <v>385</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>390</v>
+        <v>386</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>81</v>
+        <v>97</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>391</v>
+        <v>387</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5528,28 +5483,28 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>392</v>
+        <v>388</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>393</v>
+        <v>389</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>394</v>
+        <v>390</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5560,28 +5515,28 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>395</v>
+        <v>391</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>396</v>
+        <v>392</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>87</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>397</v>
+        <v>393</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5595,25 +5550,25 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>398</v>
+        <v>394</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>399</v>
+        <v>395</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>400</v>
+        <v>396</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5633,7 +5588,7 @@
         <v>52</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>401</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>72</v>
@@ -5642,10 +5597,10 @@
         <v>73</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>402</v>
+        <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5659,25 +5614,25 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>403</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>404</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>405</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5691,13 +5646,13 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>406</v>
+        <v>402</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>407</v>
+        <v>403</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -5709,7 +5664,7 @@
         <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>408</v>
+        <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -5723,13 +5678,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>409</v>
+        <v>405</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>410</v>
+        <v>406</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -5738,10 +5693,10 @@
         <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>411</v>
+        <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -5755,13 +5710,13 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>412</v>
+        <v>408</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>413</v>
+        <v>409</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
@@ -5773,7 +5728,7 @@
         <v>197</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>414</v>
+        <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -5787,13 +5742,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>415</v>
+        <v>411</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>416</v>
+        <v>412</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -5805,7 +5760,7 @@
         <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>417</v>
+        <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -5819,13 +5774,13 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>418</v>
+        <v>414</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
@@ -5837,7 +5792,7 @@
         <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>420</v>
+        <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -5851,13 +5806,13 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>421</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>422</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
@@ -5869,7 +5824,7 @@
         <v>197</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>423</v>
+        <v>419</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -5883,13 +5838,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>424</v>
+        <v>420</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>425</v>
+        <v>421</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -5901,7 +5856,7 @@
         <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>426</v>
+        <v>422</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -5915,13 +5870,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>427</v>
+        <v>423</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>428</v>
+        <v>424</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -5933,7 +5888,7 @@
         <v>197</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>429</v>
+        <v>425</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -5944,16 +5899,16 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>430</v>
+        <v>426</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>431</v>
+        <v>427</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -5965,7 +5920,7 @@
         <v>197</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>432</v>
+        <v>428</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -5976,16 +5931,16 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>433</v>
+        <v>429</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>434</v>
+        <v>430</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
@@ -5994,10 +5949,10 @@
         <v>80</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>435</v>
+        <v>431</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6011,13 +5966,13 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>436</v>
+        <v>432</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>437</v>
+        <v>433</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
@@ -6029,7 +5984,7 @@
         <v>197</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>438</v>
+        <v>434</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6043,13 +5998,13 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>439</v>
+        <v>435</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>440</v>
+        <v>436</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
@@ -6061,7 +6016,7 @@
         <v>197</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>441</v>
+        <v>437</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6075,13 +6030,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>442</v>
+        <v>438</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
@@ -6090,10 +6045,10 @@
         <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>444</v>
+        <v>440</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6107,13 +6062,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>445</v>
+        <v>441</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>446</v>
+        <v>442</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
@@ -6122,10 +6077,10 @@
         <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>447</v>
+        <v>443</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6139,13 +6094,13 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>448</v>
+        <v>444</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
@@ -6154,10 +6109,10 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>450</v>
+        <v>446</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6171,13 +6126,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>451</v>
+        <v>447</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>452</v>
+        <v>448</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -6189,7 +6144,7 @@
         <v>197</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6203,13 +6158,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>454</v>
+        <v>450</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>455</v>
+        <v>451</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>79</v>
@@ -6218,10 +6173,10 @@
         <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>456</v>
+        <v>452</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6235,13 +6190,13 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>457</v>
+        <v>453</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>458</v>
+        <v>454</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
@@ -6250,10 +6205,10 @@
         <v>73</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>459</v>
+        <v>455</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6267,13 +6222,13 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
@@ -6282,10 +6237,10 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>462</v>
+        <v>458</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6299,25 +6254,25 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -6328,28 +6283,28 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>199</v>
+        <v>286</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>466</v>
+        <v>462</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>467</v>
+        <v>463</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>468</v>
+        <v>464</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -6360,16 +6315,16 @@
         <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>469</v>
+        <v>465</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>470</v>
+        <v>466</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>471</v>
+        <v>467</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>79</v>
@@ -6378,10 +6333,10 @@
         <v>73</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>
@@ -6480,13 +6435,13 @@
         <v>70</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>79</v>
@@ -6495,10 +6450,10 @@
         <v>73</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6518,7 +6473,7 @@
         <v>61</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>72</v>
@@ -6530,7 +6485,7 @@
         <v>74</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6541,16 +6496,16 @@
         <v>53</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>79</v>
@@ -6562,7 +6517,7 @@
         <v>106</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6573,16 +6528,16 @@
         <v>53</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>79</v>
@@ -6594,7 +6549,7 @@
         <v>106</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6605,16 +6560,16 @@
         <v>53</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>79</v>
@@ -6626,7 +6581,7 @@
         <v>121</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6640,25 +6595,25 @@
         <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>378</v>
+        <v>237</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6672,25 +6627,25 @@
         <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>242</v>
+        <v>374</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6704,13 +6659,13 @@
         <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>79</v>
@@ -6719,10 +6674,10 @@
         <v>73</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6736,13 +6691,13 @@
         <v>113</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>79</v>
@@ -6751,10 +6706,10 @@
         <v>120</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6768,13 +6723,13 @@
         <v>117</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>79</v>
@@ -6783,10 +6738,10 @@
         <v>73</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6800,13 +6755,13 @@
         <v>123</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>79</v>
@@ -6815,10 +6770,10 @@
         <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>142</v>
+        <v>147</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6832,13 +6787,13 @@
         <v>127</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>79</v>
@@ -6850,7 +6805,7 @@
         <v>197</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6864,13 +6819,13 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>79</v>
@@ -6882,7 +6837,7 @@
         <v>197</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6896,25 +6851,25 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6928,13 +6883,13 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>79</v>
@@ -6946,7 +6901,7 @@
         <v>197</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6960,13 +6915,13 @@
         <v>144</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>518</v>
+        <v>514</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>519</v>
+        <v>515</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>79</v>
@@ -6975,10 +6930,10 @@
         <v>80</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>520</v>
+        <v>516</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6989,16 +6944,16 @@
         <v>53</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>521</v>
+        <v>517</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>79</v>
@@ -7007,10 +6962,10 @@
         <v>73</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7021,28 +6976,28 @@
         <v>53</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7056,25 +7011,25 @@
         <v>157</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7088,25 +7043,25 @@
         <v>161</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7120,13 +7075,13 @@
         <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>79</v>
@@ -7135,10 +7090,10 @@
         <v>73</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7152,13 +7107,13 @@
         <v>169</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>79</v>
@@ -7167,10 +7122,10 @@
         <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>538</v>
+        <v>534</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7184,25 +7139,25 @@
         <v>173</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>539</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>540</v>
+        <v>536</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>541</v>
+        <v>537</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7216,13 +7171,13 @@
         <v>177</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>542</v>
+        <v>538</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>543</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>79</v>
@@ -7231,10 +7186,10 @@
         <v>73</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>544</v>
+        <v>540</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7248,13 +7203,13 @@
         <v>182</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>79</v>
@@ -7263,10 +7218,10 @@
         <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>548</v>
+        <v>544</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7280,25 +7235,25 @@
         <v>186</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>80</v>
+        <v>374</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>551</v>
+        <v>370</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7312,25 +7267,25 @@
         <v>190</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>553</v>
+        <v>548</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>554</v>
+        <v>549</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>378</v>
+        <v>80</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>374</v>
+        <v>550</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>555</v>
+        <v>551</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7344,25 +7299,25 @@
         <v>194</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>556</v>
+        <v>552</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>557</v>
+        <v>553</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>79</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>558</v>
+        <v>554</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>559</v>
+        <v>555</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -980,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 2574억 6994만</t>
+    <t>4조 5668억 4770만</t>
   </si>
   <si>
     <t>소방담요</t>
@@ -998,7 +998,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
   </si>
   <si>
-    <t>3조 1638억 2823만</t>
+    <t>3조 2567억 9335만</t>
   </si>
   <si>
     <t>샾프심</t>
@@ -1010,6 +1010,15 @@
     <t>2조 6800억 1132만</t>
   </si>
   <si>
+    <t>김퍽퍽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
+  </si>
+  <si>
+    <t>2조 4319억 7939만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
   </si>
   <si>
@@ -1025,22 +1034,13 @@
     <t>2조 3342억 6132만</t>
   </si>
   <si>
-    <t>김퍽퍽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
-  </si>
-  <si>
-    <t>2조 1388억 1231만</t>
-  </si>
-  <si>
     <t>샾오프</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
   </si>
   <si>
-    <t>1조 6634억 6181만</t>
+    <t>2조 2853억 136만</t>
   </si>
   <si>
     <t>샾감자</t>
@@ -1112,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
   </si>
   <si>
-    <t>2316억 2601만</t>
+    <t>2467억 4454만</t>
   </si>
   <si>
     <t>긩섷</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
   </si>
   <si>
-    <t>1864억 9941만</t>
+    <t>1902억 6187만</t>
   </si>
   <si>
     <t>샾갈배</t>
@@ -1142,7 +1142,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1544억 6027만</t>
+    <t>1595억 1874만</t>
   </si>
   <si>
     <t>샾사니서리당</t>
@@ -1172,7 +1172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
   </si>
   <si>
-    <t>45조 8042억 2273만</t>
+    <t>47조 1661억 6718만</t>
   </si>
   <si>
     <t>라면에계란탁</t>
@@ -1181,7 +1181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
   </si>
   <si>
-    <t>32조 9314억 2581만</t>
+    <t>34조 2412억 9802만</t>
   </si>
   <si>
     <t>에이비숍</t>
@@ -1190,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>18조 8542억 5406만</t>
+    <t>19조 1150억 3370만</t>
   </si>
   <si>
     <t>환불카드</t>
@@ -1199,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>10조 6115억 767만</t>
+    <t>11조 2858억 9176만</t>
   </si>
   <si>
     <t>아빠카드</t>
@@ -1208,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>7조 2480억 6688만</t>
+    <t>7조 2849억 8496만</t>
   </si>
   <si>
     <t>시글</t>
@@ -1286,7 +1286,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
   </si>
   <si>
-    <t>1조 3063억 1657만</t>
+    <t>1조 3204억 8722만</t>
   </si>
   <si>
     <t>돌격대원</t>
@@ -1307,13 +1307,22 @@
     <t>1조 1455억 4997만</t>
   </si>
   <si>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>1조 985억 8507만</t>
+  </si>
+  <si>
     <t>호츠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
   </si>
   <si>
-    <t>1조 389억 721만</t>
+    <t>1조 967억 8189만</t>
   </si>
   <si>
     <t>회원카드</t>
@@ -1352,13 +1361,13 @@
     <t>9221억 2396만</t>
   </si>
   <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>9200억 3546만</t>
+    <t>오보기다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>7694억 6713만</t>
   </si>
   <si>
     <t>떼링</t>
@@ -1370,22 +1379,13 @@
     <t>7499억 5629만</t>
   </si>
   <si>
-    <t>오보기다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>6741억 7723만</t>
-  </si>
-  <si>
     <t>로우머</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
   </si>
   <si>
-    <t>6583억 4222만</t>
+    <t>6645억 6088만</t>
   </si>
   <si>
     <t>RIMS</t>
@@ -1394,7 +1394,7 @@
     <t>https://mgf.gg/contents/character.php?n=RIMS</t>
   </si>
   <si>
-    <t>6512억 5748만</t>
+    <t>6625억 2854만</t>
   </si>
   <si>
     <t>떵헤</t>
@@ -1403,7 +1403,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
   </si>
   <si>
-    <t>6144억 6753만</t>
+    <t>6293억 7369만</t>
   </si>
   <si>
     <t>오말랑</t>
@@ -1412,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
   </si>
   <si>
-    <t>5601억 9209만</t>
+    <t>5652억 1941만</t>
   </si>
   <si>
     <t>직불카드</t>
@@ -4762,25 +4762,25 @@
         <v>131</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>327</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>42</v>
+        <v>327</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>147</v>
+        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -4794,22 +4794,22 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>329</v>
+        <v>42</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>329</v>
+        <v>42</v>
       </c>
       <c r="E15" s="2" t="s">
         <v>330</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>73</v>
+        <v>91</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>147</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>331</v>
@@ -4838,10 +4838,10 @@
         <v>79</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>85</v>
+        <v>73</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>86</v>
+        <v>121</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>334</v>
@@ -5469,7 +5469,7 @@
         <v>374</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>97</v>
+        <v>74</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>387</v>
@@ -5789,7 +5789,7 @@
         <v>73</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>416</v>
@@ -5914,10 +5914,10 @@
         <v>79</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>197</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>428</v>
@@ -5946,10 +5946,10 @@
         <v>79</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>262</v>
+        <v>197</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>431</v>
@@ -5978,10 +5978,10 @@
         <v>79</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>73</v>
+        <v>80</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>197</v>
+        <v>262</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>434</v>
@@ -6010,7 +6010,7 @@
         <v>79</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>197</v>
@@ -6042,10 +6042,10 @@
         <v>79</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>147</v>
+        <v>197</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>440</v>
@@ -6074,7 +6074,7 @@
         <v>79</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>147</v>
@@ -6106,10 +6106,10 @@
         <v>79</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>197</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>446</v>
@@ -6138,10 +6138,10 @@
         <v>79</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>73</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>197</v>
+        <v>277</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>449</v>
@@ -6237,7 +6237,7 @@
         <v>111</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>277</v>
+        <v>262</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>458</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="부계둘" sheetId="3" r:id="rId3"/>
-    <sheet name="피난민" sheetId="4" r:id="rId4"/>
-    <sheet name="이고이스트" sheetId="5" r:id="rId5"/>
-    <sheet name="밤과다람쥐" sheetId="6" r:id="rId6"/>
+    <sheet name="피난민" sheetId="3" r:id="rId3"/>
+    <sheet name="이고이스트" sheetId="4" r:id="rId4"/>
+    <sheet name="밤과다람쥐" sheetId="5" r:id="rId5"/>
+    <sheet name="부계둘" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">밤과다람쥐!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">부계둘!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">이고이스트!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">피난민!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">밤과다람쥐!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">부계둘!$A$1:$J$23</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">이고이스트!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">피난민!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1568" uniqueCount="556">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1518" uniqueCount="540">
   <si>
     <t>guild_name</t>
   </si>
@@ -104,6 +104,90 @@
     <t>2026.04.11</t>
   </si>
   <si>
+    <t>피난민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>364</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>137조 4077억 2612만</t>
+  </si>
+  <si>
+    <t>피난 오신 여러분 반갑습니다.</t>
+  </si>
+  <si>
+    <t>주방화</t>
+  </si>
+  <si>
+    <t>2026.04.10</t>
+  </si>
+  <si>
+    <t>이고이스트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>30위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>135조 5251억 2923만</t>
+  </si>
+  <si>
+    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
+  </si>
+  <si>
+    <t>한도카드</t>
+  </si>
+  <si>
+    <t>밤과다람쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>326</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>171조 6333억 5023만</t>
+  </si>
+  <si>
+    <t>자유가입 길드입니다 1d 길컨 미참 스펙상승에 따른 길컨 점수 미상향 추방컷 관리로 이루어지고 있습니다</t>
+  </si>
+  <si>
+    <t>매미형</t>
+  </si>
+  <si>
     <t>부계둘</t>
   </si>
   <si>
@@ -119,9 +203,6 @@
     <t>10위</t>
   </si>
   <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
     <t>124조 4701억 3596만</t>
   </si>
   <si>
@@ -131,90 +212,6 @@
     <t>홍춘삼</t>
   </si>
   <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>피난민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>17위</t>
-  </si>
-  <si>
-    <t>137조 4077억 2612만</t>
-  </si>
-  <si>
-    <t>피난 오신 여러분 반갑습니다.</t>
-  </si>
-  <si>
-    <t>주방화</t>
-  </si>
-  <si>
-    <t>이고이스트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>135조 5251억 2923만</t>
-  </si>
-  <si>
-    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
-  </si>
-  <si>
-    <t>한도카드</t>
-  </si>
-  <si>
-    <t>밤과다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>171조 6333억 5023만</t>
-  </si>
-  <si>
-    <t>자유가입 길드입니다 1d 길컨 미참 스펙상승에 따른 길컨 점수 미상향 추방컷 관리로 이루어지고 있습니다</t>
-  </si>
-  <si>
-    <t>매미형</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -254,7 +251,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>15조 2195억 3666만</t>
+    <t>17조 1695억 4531만</t>
   </si>
   <si>
     <t>2</t>
@@ -305,7 +302,7 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>10조 7888억 6150만</t>
+    <t>10조 8080억 1797만</t>
   </si>
   <si>
     <t>5</t>
@@ -323,7 +320,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>9조 4831억 8007만</t>
+    <t>9조 7862억 1841만</t>
   </si>
   <si>
     <t>6</t>
@@ -335,7 +332,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>8조 3534억 4319만</t>
+    <t>8조 3610억 5502만</t>
   </si>
   <si>
     <t>7</t>
@@ -365,7 +362,7 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>5조 1968억 8766만</t>
+    <t>6조 140억 9399만</t>
   </si>
   <si>
     <t>9</t>
@@ -392,37 +389,52 @@
     <t>나이트로드</t>
   </si>
   <si>
+    <t>4조 5676억 7592만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>4조 2993억 5963만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 6676억 5224만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
     <t>99</t>
   </si>
   <si>
-    <t>4조 4313억 1006만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>4조 2089억 9652만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
     <t>3조 3846억 5890만</t>
   </si>
   <si>
-    <t>13</t>
+    <t>14</t>
   </si>
   <si>
     <t>므고</t>
@@ -431,10 +443,34 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>3조 175억 79만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>3조 2011억 997만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>2조 8180억 4925만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>2조 7171억 6721만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -446,7 +482,22 @@
     <t>2조 6747억 6521만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 6008억 7148만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -455,28 +506,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>98</t>
-  </si>
-  <si>
     <t>2조 5943억 9545만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>2조 5940억 8239만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>20</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -488,31 +521,7 @@
     <t>2조 5595억 2만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>2조 5359억 851만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>2조 3765억 8123만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -521,10 +530,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 2480억 2119만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>2조 3068억 391만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>겨울바다</t>
@@ -533,10 +542,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>2조 1038억 6635만</t>
-  </si>
-  <si>
-    <t>22</t>
+    <t>2조 3067억 6242만</t>
+  </si>
+  <si>
+    <t>23</t>
   </si>
   <si>
     <t>여븨</t>
@@ -548,7 +557,7 @@
     <t>2조 737억 3833만</t>
   </si>
   <si>
-    <t>23</t>
+    <t>24</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -560,7 +569,7 @@
     <t>1조 9311억 8518만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>25</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -575,7 +584,7 @@
     <t>1조 9171억 4797만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -587,7 +596,7 @@
     <t>1조 8260억 5446만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>여눈</t>
@@ -599,7 +608,7 @@
     <t>1조 7856억 5439만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -608,10 +617,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
   </si>
   <si>
-    <t>1조 6923억 5834만</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>1조 7536억 1673만</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>욤지</t>
@@ -626,40 +635,820 @@
     <t>1조 2381억 1362만</t>
   </si>
   <si>
-    <t>증권보이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A6%9D%EA%B6%8C%EB%B3%B4%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>20조 4898억 61만</t>
-  </si>
-  <si>
-    <t>둥둥콩이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%91%A5%EB%91%A5%EC%BD%A9%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>19조 9942억 330만</t>
-  </si>
-  <si>
-    <t>가온스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%98%A8%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>17조 4585억 7977만</t>
-  </si>
-  <si>
-    <t>Canary</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Canary</t>
-  </si>
-  <si>
-    <t>15조 8193억 825만</t>
+    <t>샾온</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
+  </si>
+  <si>
+    <t>35조 551억 5969만</t>
+  </si>
+  <si>
+    <t>샾한궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%9C%EA%B6%81</t>
+  </si>
+  <si>
+    <t>28조 740억 9066만</t>
+  </si>
+  <si>
+    <t>샾샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%83%B7</t>
+  </si>
+  <si>
+    <t>20조 8124억 1059만</t>
+  </si>
+  <si>
+    <t>샾살개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%B4%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>17조 3578억 3768만</t>
+  </si>
+  <si>
+    <t>고생했어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%83%9D%ED%96%88%EC%96%B4</t>
+  </si>
+  <si>
+    <t>11조 6683억 8284만</t>
+  </si>
+  <si>
+    <t>샾브샤브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>9조 6513억 9267만</t>
+  </si>
+  <si>
+    <t>샾밉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>8조 7980억 5102만</t>
+  </si>
+  <si>
+    <t>샾꾸붕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%BE%B8%EB%B6%95</t>
+  </si>
+  <si>
+    <t>6조 455억 5131만</t>
+  </si>
+  <si>
+    <t>쩡미니지후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
+  </si>
+  <si>
+    <t>4조 5686억 1316만</t>
+  </si>
+  <si>
+    <t>소방담요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
+  </si>
+  <si>
+    <t>3조 4276억 8898만</t>
+  </si>
+  <si>
+    <t>상산의조자룡</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
+  </si>
+  <si>
+    <t>3조 2567억 9335만</t>
+  </si>
+  <si>
+    <t>샾프심</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
+  </si>
+  <si>
+    <t>2조 9255억 9764만</t>
+  </si>
+  <si>
+    <t>샾오산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
+  </si>
+  <si>
+    <t>2조 4451억 748만</t>
+  </si>
+  <si>
+    <t>김퍽퍽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
+  </si>
+  <si>
+    <t>2조 4418억 9894만</t>
+  </si>
+  <si>
+    <t>샾오프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 3827억 3541만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
+  </si>
+  <si>
+    <t>2조 3814억 4063만</t>
+  </si>
+  <si>
+    <t>샾감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1조 6116억 2745만</t>
+  </si>
+  <si>
+    <t>무진미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>1조 5577억 7193만</t>
+  </si>
+  <si>
+    <t>oEMPo</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
+  </si>
+  <si>
+    <t>1조 3704억 7106만</t>
+  </si>
+  <si>
+    <t>샾햇살</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
+  </si>
+  <si>
+    <t>1조 1825억 6907만</t>
+  </si>
+  <si>
+    <t>이지아지콩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%95%84%EC%A7%80%EC%BD%A9</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>9592억 7414만</t>
+  </si>
+  <si>
+    <t>백수돼지로성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
+  </si>
+  <si>
+    <t>5433억 4764만</t>
+  </si>
+  <si>
+    <t>딱지냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
+  </si>
+  <si>
+    <t>4713억 5012만</t>
+  </si>
+  <si>
+    <t>샾앤플랫</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>2467억 4454만</t>
+  </si>
+  <si>
+    <t>긩섷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
+  </si>
+  <si>
+    <t>2057억 4658만</t>
+  </si>
+  <si>
+    <t>샾갈배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>1872억 2636만</t>
+  </si>
+  <si>
+    <t>최훈석개멋져</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1613억 4146만</t>
+  </si>
+  <si>
+    <t>샾사니서리당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>1346억 4398만</t>
+  </si>
+  <si>
+    <t>커피둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
+  </si>
+  <si>
+    <t>1200억 9858만</t>
+  </si>
+  <si>
+    <t>마퀸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
+  </si>
+  <si>
+    <t>47조 1661억 6718만</t>
+  </si>
+  <si>
+    <t>라면에계란탁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
+  </si>
+  <si>
+    <t>34조 4115억 6254만</t>
+  </si>
+  <si>
+    <t>에이비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>19조 1150억 3370만</t>
+  </si>
+  <si>
+    <t>환불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>11조 2858억 9176만</t>
+  </si>
+  <si>
+    <t>아빠카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>7조 2849억 8496만</t>
+  </si>
+  <si>
+    <t>시글</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
+  </si>
+  <si>
+    <t>6조 5681억 7800만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>4조 9474억 2059만</t>
+  </si>
+  <si>
+    <t>공사과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2조 4059억 2866만</t>
+  </si>
+  <si>
+    <t>사과닷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
+  </si>
+  <si>
+    <t>2조 3790억 6194만</t>
+  </si>
+  <si>
+    <t>뽀뾰해봄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%BE%B0%ED%95%B4%EB%B4%84</t>
+  </si>
+  <si>
+    <t>2조 1792억 5639만</t>
+  </si>
+  <si>
+    <t>Eddy0825</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
+  </si>
+  <si>
+    <t>1조 5159억 8227만</t>
+  </si>
+  <si>
+    <t>망치전문</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
+  </si>
+  <si>
+    <t>1조 4484억 1233만</t>
+  </si>
+  <si>
+    <t>히히맘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
+  </si>
+  <si>
+    <t>1조 3706억 670만</t>
+  </si>
+  <si>
+    <t>토이감자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1조 3297억 1328만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>1조 3179억 5406만</t>
+  </si>
+  <si>
+    <t>돌격대원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 1790억 5697만</t>
+  </si>
+  <si>
+    <t>비숍덩구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>1조 985억 8507만</t>
+  </si>
+  <si>
+    <t>호츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1조 967억 8189만</t>
+  </si>
+  <si>
+    <t>핑와스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>9855억 7893만</t>
+  </si>
+  <si>
+    <t>회원카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>9586억 327만</t>
+  </si>
+  <si>
+    <t>단풍a</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
+  </si>
+  <si>
+    <t>9581억 3672만</t>
+  </si>
+  <si>
+    <t>문뚱식</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
+  </si>
+  <si>
+    <t>9221억 2396만</t>
+  </si>
+  <si>
+    <t>오보기다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>7794억 7560만</t>
+  </si>
+  <si>
+    <t>떼링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>7499억 5629만</t>
+  </si>
+  <si>
+    <t>떵헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
+  </si>
+  <si>
+    <t>6808억 2793만</t>
+  </si>
+  <si>
+    <t>로우머</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
+  </si>
+  <si>
+    <t>6740억 4975만</t>
+  </si>
+  <si>
+    <t>RIMS</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
+  </si>
+  <si>
+    <t>6625억 2854만</t>
+  </si>
+  <si>
+    <t>오말랑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
+  </si>
+  <si>
+    <t>5652억 1941만</t>
+  </si>
+  <si>
+    <t>직불카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>2713억 109만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>채채자매</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
+  </si>
+  <si>
+    <t>1544억 6246만</t>
+  </si>
+  <si>
+    <t>MAKTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>113조 6505억 8775만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
+  </si>
+  <si>
+    <t>52조 8422억 5943만</t>
+  </si>
+  <si>
+    <t>민헤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
+  </si>
+  <si>
+    <t>13조 4832억 9129만</t>
+  </si>
+  <si>
+    <t>세계챔피언</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
+  </si>
+  <si>
+    <t>11조 2225억 3682만</t>
+  </si>
+  <si>
+    <t>I라헬I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
+  </si>
+  <si>
+    <t>3조 4648억 7843만</t>
+  </si>
+  <si>
+    <t>건야웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
+  </si>
+  <si>
+    <t>2조 9755억 5188만</t>
+  </si>
+  <si>
+    <t>찐썽잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 5906억 6272만</t>
+  </si>
+  <si>
+    <t>치킨v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
+  </si>
+  <si>
+    <t>2조 303억 9270만</t>
+  </si>
+  <si>
+    <t>보꿍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%BF%8D</t>
+  </si>
+  <si>
+    <t>1조 7252억 2671만</t>
+  </si>
+  <si>
+    <t>썰렁포</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%B0%EB%A0%81%ED%8F%AC</t>
+  </si>
+  <si>
+    <t>1조 2131억 8650만</t>
+  </si>
+  <si>
+    <t>레제내꺼야</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
+  </si>
+  <si>
+    <t>9811억 2977만</t>
+  </si>
+  <si>
+    <t>S2지존</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=S2%EC%A7%80%EC%A1%B4</t>
+  </si>
+  <si>
+    <t>9193억 6581만</t>
+  </si>
+  <si>
+    <t>키죠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%A3%A0</t>
+  </si>
+  <si>
+    <t>8948억 8533만</t>
+  </si>
+  <si>
+    <t>묨밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>8657억 5632만</t>
+  </si>
+  <si>
+    <t>하얀물개</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
+  </si>
+  <si>
+    <t>7680억 3260만</t>
+  </si>
+  <si>
+    <t>비숍둑이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%91%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7379억 2392만</t>
+  </si>
+  <si>
+    <t>초코냥부하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
+  </si>
+  <si>
+    <t>6544억 5291만</t>
+  </si>
+  <si>
+    <t>장빵구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>5600억 447만</t>
+  </si>
+  <si>
+    <t>환불냠냠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
+  </si>
+  <si>
+    <t>5115억 5105만</t>
+  </si>
+  <si>
+    <t>레피스나2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
+  </si>
+  <si>
+    <t>5053억 2083만</t>
+  </si>
+  <si>
+    <t>혼자가최고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>4847억 4441만</t>
+  </si>
+  <si>
+    <t>깝용잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%9A%A9%EC%9E%89</t>
+  </si>
+  <si>
+    <t>4702억 4731만</t>
+  </si>
+  <si>
+    <t>망복복</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
+  </si>
+  <si>
+    <t>4161억 969만</t>
+  </si>
+  <si>
+    <t>모몬쌍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
+  </si>
+  <si>
+    <t>2823억 7454만</t>
+  </si>
+  <si>
+    <t>우주강아지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%EA%B0%95%EC%95%84%EC%A7%80</t>
+  </si>
+  <si>
+    <t>1954억 3029만</t>
+  </si>
+  <si>
+    <t>화가난꽝섭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1801억 3527만</t>
+  </si>
+  <si>
+    <t>이진니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
+  </si>
+  <si>
+    <t>1002억 7173만</t>
+  </si>
+  <si>
+    <t>봉오리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%98%A4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>87</t>
+  </si>
+  <si>
+    <t>921억 1003만</t>
+  </si>
+  <si>
+    <t>만년설딸기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%85%84%EC%84%A4%EB%94%B8%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>85</t>
+  </si>
+  <si>
+    <t>312억 3253만</t>
   </si>
   <si>
     <t>처히</t>
@@ -668,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
   </si>
   <si>
-    <t>13조 2156억 7422만</t>
+    <t>13조 5574억 3249만</t>
   </si>
   <si>
     <t>환생의불꼬츠</t>
@@ -689,15 +1478,6 @@
     <t>8조 9166억 6911만</t>
   </si>
   <si>
-    <t>Naco</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Naco</t>
-  </si>
-  <si>
-    <t>6조 9849억 7135만</t>
-  </si>
-  <si>
     <t>AKPS</t>
   </si>
   <si>
@@ -713,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%82%98%EC%9D%B4%EA%B8%B0%EB%B0%B1%ED%99%A9</t>
   </si>
   <si>
-    <t>3조 8303억 3845만</t>
+    <t>3조 9540억 9597만</t>
   </si>
   <si>
     <t>토미오카상</t>
@@ -731,7 +1511,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%89%ED%8F%89%EC%9D%B4%ED%98%95</t>
   </si>
   <si>
-    <t>3조 906억 3513만</t>
+    <t>3조 2987억 2385만</t>
+  </si>
+  <si>
+    <t>런닝래빗</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
+  </si>
+  <si>
+    <t>2조 6773억 6238만</t>
   </si>
   <si>
     <t>천칠</t>
@@ -740,12 +1529,18 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
     <t>2조 6702억 2482만</t>
   </si>
   <si>
+    <t>화살대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>2조 6342억 2078만</t>
+  </si>
+  <si>
     <t>토니워터</t>
   </si>
   <si>
@@ -761,34 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
   </si>
   <si>
-    <t>2조 4885억 7115만</t>
-  </si>
-  <si>
-    <t>화살대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>2조 4258억 6186만</t>
-  </si>
-  <si>
-    <t>런닝래빗</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
-  </si>
-  <si>
-    <t>2조 4177억 8071만</t>
-  </si>
-  <si>
-    <t>피어난</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BC%EC%96%B4%EB%82%9C</t>
-  </si>
-  <si>
-    <t>2조 305억 8537만</t>
+    <t>2조 4991억 587만</t>
   </si>
   <si>
     <t>샤스찌에</t>
@@ -797,7 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
   </si>
   <si>
-    <t>1조 4976억 9640만</t>
+    <t>1조 5997억 4972만</t>
   </si>
   <si>
     <t>보동핑</t>
@@ -806,19 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 1820억 5434만</t>
-  </si>
-  <si>
-    <t>싸토루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%B8%ED%86%A0%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 1480억 9108만</t>
+    <t>1조 3542억 7780만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -851,7 +1607,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
   </si>
   <si>
-    <t>8747억 2403만</t>
+    <t>8969억 3132만</t>
   </si>
   <si>
     <t>Targa</t>
@@ -860,9 +1616,6 @@
     <t>https://mgf.gg/contents/character.php?n=Targa</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>5665억 5826만</t>
   </si>
   <si>
@@ -872,10 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>5424억 3794만</t>
+    <t>5504억 9405만</t>
   </si>
   <si>
     <t>짱창훈</t>
@@ -887,9 +1637,6 @@
     <t>3382억 604만</t>
   </si>
   <si>
-    <t>29</t>
-  </si>
-  <si>
     <t>구리구리뽕리</t>
   </si>
   <si>
@@ -900,801 +1647,6 @@
   </si>
   <si>
     <t>55억 5534만</t>
-  </si>
-  <si>
-    <t>샾온</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A8</t>
-  </si>
-  <si>
-    <t>35조 551억 5969만</t>
-  </si>
-  <si>
-    <t>샾한궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%95%9C%EA%B6%81</t>
-  </si>
-  <si>
-    <t>28조 740억 9066만</t>
-  </si>
-  <si>
-    <t>샾살개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%B4%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>17조 3578억 3768만</t>
-  </si>
-  <si>
-    <t>샾샷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%83%B7</t>
-  </si>
-  <si>
-    <t>14조 7510억 2730만</t>
-  </si>
-  <si>
-    <t>고생했어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%83%9D%ED%96%88%EC%96%B4</t>
-  </si>
-  <si>
-    <t>11조 6683억 8284만</t>
-  </si>
-  <si>
-    <t>샾브샤브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>9조 4038억 7114만</t>
-  </si>
-  <si>
-    <t>샾밉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>8조 5617억 8638만</t>
-  </si>
-  <si>
-    <t>샾꾸붕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%BE%B8%EB%B6%95</t>
-  </si>
-  <si>
-    <t>6조 355억 4707만</t>
-  </si>
-  <si>
-    <t>쩡미니지후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
-  </si>
-  <si>
-    <t>4조 5668억 4770만</t>
-  </si>
-  <si>
-    <t>소방담요</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
-  </si>
-  <si>
-    <t>3조 4276억 8898만</t>
-  </si>
-  <si>
-    <t>상산의조자룡</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
-  </si>
-  <si>
-    <t>3조 2567억 9335만</t>
-  </si>
-  <si>
-    <t>샾프심</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
-  </si>
-  <si>
-    <t>2조 6800억 1132만</t>
-  </si>
-  <si>
-    <t>김퍽퍽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
-  </si>
-  <si>
-    <t>2조 4319억 7939만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
-  </si>
-  <si>
-    <t>2조 3354억 9574만</t>
-  </si>
-  <si>
-    <t>샾오산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
-  </si>
-  <si>
-    <t>2조 3342억 6132만</t>
-  </si>
-  <si>
-    <t>샾오프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 2853억 136만</t>
-  </si>
-  <si>
-    <t>샾감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 6116억 2745만</t>
-  </si>
-  <si>
-    <t>무진미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 5577억 7193만</t>
-  </si>
-  <si>
-    <t>oEMPo</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
-  </si>
-  <si>
-    <t>1조 3704억 7106만</t>
-  </si>
-  <si>
-    <t>샾햇살</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
-  </si>
-  <si>
-    <t>1조 833억 4380만</t>
-  </si>
-  <si>
-    <t>이지아지콩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%80%EC%95%84%EC%A7%80%EC%BD%A9</t>
-  </si>
-  <si>
-    <t>9566억 7217만</t>
-  </si>
-  <si>
-    <t>백수돼지로성</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B1%EC%88%98%EB%8F%BC%EC%A7%80%EB%A1%9C%EC%84%B1</t>
-  </si>
-  <si>
-    <t>5265억 7331만</t>
-  </si>
-  <si>
-    <t>딱지냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4672억 6247만</t>
-  </si>
-  <si>
-    <t>샾앤플랫</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%95%A4%ED%94%8C%EB%9E%AB</t>
-  </si>
-  <si>
-    <t>2467억 4454만</t>
-  </si>
-  <si>
-    <t>긩섷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
-  </si>
-  <si>
-    <t>1902억 6187만</t>
-  </si>
-  <si>
-    <t>샾갈배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>1862억 1727만</t>
-  </si>
-  <si>
-    <t>최훈석개멋져</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%9B%88%EC%84%9D%EA%B0%9C%EB%A9%8B%EC%A0%B8</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1595억 1874만</t>
-  </si>
-  <si>
-    <t>샾사니서리당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%82%AC%EB%8B%88%EC%84%9C%EB%A6%AC%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>1346억 4398만</t>
-  </si>
-  <si>
-    <t>커피둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
-  </si>
-  <si>
-    <t>1200억 9858만</t>
-  </si>
-  <si>
-    <t>마퀸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%ED%80%B8</t>
-  </si>
-  <si>
-    <t>47조 1661억 6718만</t>
-  </si>
-  <si>
-    <t>라면에계란탁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
-  </si>
-  <si>
-    <t>34조 2412억 9802만</t>
-  </si>
-  <si>
-    <t>에이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>19조 1150억 3370만</t>
-  </si>
-  <si>
-    <t>환불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>11조 2858억 9176만</t>
-  </si>
-  <si>
-    <t>아빠카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>7조 2849억 8496만</t>
-  </si>
-  <si>
-    <t>시글</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
-  </si>
-  <si>
-    <t>6조 5681억 7800만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>4조 9365억 4349만</t>
-  </si>
-  <si>
-    <t>공사과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EC%82%AC%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 4059억 2866만</t>
-  </si>
-  <si>
-    <t>사과닷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
-  </si>
-  <si>
-    <t>2조 3266억 8637만</t>
-  </si>
-  <si>
-    <t>뽀뾰해봄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%BE%B0%ED%95%B4%EB%B4%84</t>
-  </si>
-  <si>
-    <t>2조 690억 7726만</t>
-  </si>
-  <si>
-    <t>Eddy0825</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
-  </si>
-  <si>
-    <t>1조 5159억 8227만</t>
-  </si>
-  <si>
-    <t>히히맘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
-  </si>
-  <si>
-    <t>1조 3663억 941만</t>
-  </si>
-  <si>
-    <t>토이감자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EC%9D%B4%EA%B0%90%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 3297억 1328만</t>
-  </si>
-  <si>
-    <t>망치전문</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
-  </si>
-  <si>
-    <t>1조 3204억 8722만</t>
-  </si>
-  <si>
-    <t>돌격대원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 1548억 8804만</t>
-  </si>
-  <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>1조 1455억 4997만</t>
-  </si>
-  <si>
-    <t>비숍덩구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>1조 985억 8507만</t>
-  </si>
-  <si>
-    <t>호츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1조 967억 8189만</t>
-  </si>
-  <si>
-    <t>회원카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>9586억 327만</t>
-  </si>
-  <si>
-    <t>핑와스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>9422억 3151만</t>
-  </si>
-  <si>
-    <t>단풍a</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
-  </si>
-  <si>
-    <t>9328억 34만</t>
-  </si>
-  <si>
-    <t>문뚱식</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
-  </si>
-  <si>
-    <t>9221억 2396만</t>
-  </si>
-  <si>
-    <t>오보기다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>7694억 6713만</t>
-  </si>
-  <si>
-    <t>떼링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>7499억 5629만</t>
-  </si>
-  <si>
-    <t>로우머</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
-  </si>
-  <si>
-    <t>6645억 6088만</t>
-  </si>
-  <si>
-    <t>RIMS</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=RIMS</t>
-  </si>
-  <si>
-    <t>6625억 2854만</t>
-  </si>
-  <si>
-    <t>떵헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
-  </si>
-  <si>
-    <t>6293억 7369만</t>
-  </si>
-  <si>
-    <t>오말랑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
-  </si>
-  <si>
-    <t>5652억 1941만</t>
-  </si>
-  <si>
-    <t>직불카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>2615억 5649만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>채채자매</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
-  </si>
-  <si>
-    <t>1433억 9734만</t>
-  </si>
-  <si>
-    <t>MAKTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=MAKTO</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>113조 6505억 8775만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
-  </si>
-  <si>
-    <t>50조 6875억 1260만</t>
-  </si>
-  <si>
-    <t>민헤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
-  </si>
-  <si>
-    <t>13조 4832억 9129만</t>
-  </si>
-  <si>
-    <t>세계챔피언</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
-  </si>
-  <si>
-    <t>10조 3718억 3648만</t>
-  </si>
-  <si>
-    <t>I라헬I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
-  </si>
-  <si>
-    <t>3조 3854억 4624만</t>
-  </si>
-  <si>
-    <t>찐썽잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B0%90%EC%8D%BD%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 5906억 6272만</t>
-  </si>
-  <si>
-    <t>건야웅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
-  </si>
-  <si>
-    <t>2조 4543억 8797만</t>
-  </si>
-  <si>
-    <t>보꿍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EA%BF%8D</t>
-  </si>
-  <si>
-    <t>1조 7252억 2671만</t>
-  </si>
-  <si>
-    <t>소년가장원딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%85%84%EA%B0%80%EC%9E%A5%EC%9B%90%EB%94%9C</t>
-  </si>
-  <si>
-    <t>1조 3553억 3451만</t>
-  </si>
-  <si>
-    <t>치킨v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%98%ED%82%A8v</t>
-  </si>
-  <si>
-    <t>1조 2546억 5507만</t>
-  </si>
-  <si>
-    <t>레제내꺼야</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
-  </si>
-  <si>
-    <t>9811억 2977만</t>
-  </si>
-  <si>
-    <t>묨밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>8657억 5632만</t>
-  </si>
-  <si>
-    <t>키죠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%A4%EC%A3%A0</t>
-  </si>
-  <si>
-    <t>8583억 9432만</t>
-  </si>
-  <si>
-    <t>S2지존</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=S2%EC%A7%80%EC%A1%B4</t>
-  </si>
-  <si>
-    <t>8260억 7822만</t>
-  </si>
-  <si>
-    <t>하얀물개</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
-  </si>
-  <si>
-    <t>7680억 3260만</t>
-  </si>
-  <si>
-    <t>초코냥부하</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
-  </si>
-  <si>
-    <t>6544억 5291만</t>
-  </si>
-  <si>
-    <t>장빵구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>5600억 447만</t>
-  </si>
-  <si>
-    <t>레피스나2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
-  </si>
-  <si>
-    <t>5053억 2083만</t>
-  </si>
-  <si>
-    <t>환불냠냠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
-  </si>
-  <si>
-    <t>5025억 7617만</t>
-  </si>
-  <si>
-    <t>혼자가최고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%BC%EC%9E%90%EA%B0%80%EC%B5%9C%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4484억 5846만</t>
-  </si>
-  <si>
-    <t>깝용잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%9D%EC%9A%A9%EC%9E%89</t>
-  </si>
-  <si>
-    <t>4268억 6235만</t>
-  </si>
-  <si>
-    <t>망복복</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
-  </si>
-  <si>
-    <t>4161억 969만</t>
-  </si>
-  <si>
-    <t>모몬쌍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
-  </si>
-  <si>
-    <t>2679억 4512만</t>
-  </si>
-  <si>
-    <t>우주강아지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%A3%BC%EA%B0%95%EC%95%84%EC%A7%80</t>
-  </si>
-  <si>
-    <t>1874억 3020만</t>
-  </si>
-  <si>
-    <t>화가난꽝섭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>1801억 3527만</t>
-  </si>
-  <si>
-    <t>이진니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
-  </si>
-  <si>
-    <t>970억 5432만</t>
-  </si>
-  <si>
-    <t>봉오리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%98%A4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>87</t>
-  </si>
-  <si>
-    <t>921억 1003만</t>
-  </si>
-  <si>
-    <t>만년설딸기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%85%84%EC%84%A4%EB%94%B8%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>248억 7797만</t>
   </si>
 </sst>
 </file>
@@ -2178,89 +2130,89 @@
         <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
-      </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>36</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="H4" s="2" t="s">
-        <v>19</v>
-      </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>44</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>43</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>49</v>
@@ -2275,7 +2227,7 @@
         <v>52</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2301,22 +2253,22 @@
         <v>57</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>48</v>
+        <v>39</v>
       </c>
       <c r="I6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J6" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="L6" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -2334,7 +2286,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2352,28 +2304,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2384,7 +2336,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2393,19 +2345,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>74</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>75</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2416,28 +2368,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>78</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>80</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>81</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2448,28 +2400,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2480,28 +2432,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2512,28 +2464,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="H6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>97</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>98</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2544,28 +2496,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>102</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2576,28 +2528,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H8" s="2" t="s">
+      <c r="I8" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2608,28 +2560,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
+      <c r="H9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2640,28 +2592,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>114</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2672,28 +2624,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="2" t="s">
+      <c r="H11" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2704,28 +2656,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>124</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>126</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2736,28 +2688,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="I13" s="2" t="s">
         <v>129</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2768,25 +2720,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>134</v>
@@ -2812,13 +2764,13 @@
         <v>137</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>138</v>
@@ -2844,16 +2796,16 @@
         <v>141</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2864,28 +2816,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2896,28 +2848,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>150</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>152</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2928,28 +2880,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>153</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="I19" s="2" t="s">
         <v>155</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>156</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2960,28 +2912,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>159</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>160</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2992,28 +2944,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>163</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>164</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3024,28 +2976,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>167</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>168</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3056,28 +3008,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>171</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>172</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3088,28 +3040,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>175</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>176</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3120,28 +3072,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>179</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3152,28 +3104,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="H26" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3184,28 +3136,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3216,28 +3168,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3248,35 +3200,67 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3306,6 +3290,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3331,28 +3316,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3363,31 +3348,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3395,31 +3380,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G3" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="H3" s="2" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3427,31 +3412,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3459,31 +3444,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3491,31 +3476,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3523,31 +3508,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3555,31 +3540,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>105</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3587,31 +3572,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>111</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3619,31 +3604,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>86</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3651,31 +3636,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3683,31 +3668,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3715,31 +3700,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3747,31 +3732,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>237</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3782,28 +3767,28 @@
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>147</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3814,28 +3799,28 @@
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>80</v>
+        <v>110</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3843,31 +3828,31 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3875,31 +3860,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3907,31 +3892,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>142</v>
+        <v>200</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3939,31 +3924,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3971,31 +3956,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4003,31 +3988,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="F22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G22" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="H22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4035,31 +4020,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>264</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>197</v>
-      </c>
       <c r="I23" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4067,31 +4052,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>197</v>
+        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4099,31 +4084,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>262</v>
+        <v>274</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4131,31 +4116,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>33</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="F26" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G26" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G26" s="2" t="s">
-        <v>120</v>
-      </c>
       <c r="H26" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4163,31 +4148,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4195,31 +4180,31 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4227,31 +4212,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>281</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4259,31 +4244,31 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -4325,1018 +4310,6 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>306</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>309</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>237</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>339</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>368</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>371</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>374</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>377</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5355,28 +4328,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5384,962 +4357,962 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>293</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>380</v>
+        <v>294</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>381</v>
+        <v>295</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>382</v>
+        <v>296</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>383</v>
+        <v>297</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>384</v>
+        <v>298</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>299</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>385</v>
+        <v>299</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>386</v>
+        <v>300</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>387</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>388</v>
+        <v>302</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>389</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>390</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>391</v>
+        <v>305</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>391</v>
+        <v>305</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>392</v>
+        <v>306</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>86</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>393</v>
+        <v>307</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>394</v>
+        <v>308</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>395</v>
+        <v>309</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>396</v>
+        <v>310</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="D8" s="2" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H8" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>398</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>401</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>402</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>404</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>405</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>406</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>407</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>408</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G12" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>410</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>411</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G13" s="2" t="s">
-        <v>111</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>413</v>
+        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>414</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>147</v>
+        <v>200</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>416</v>
+        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>417</v>
+        <v>331</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>332</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>419</v>
+        <v>333</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>420</v>
+        <v>334</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>420</v>
+        <v>334</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>421</v>
+        <v>335</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>422</v>
+        <v>336</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>423</v>
+        <v>337</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>423</v>
+        <v>337</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>424</v>
+        <v>338</v>
       </c>
       <c r="F17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G17" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H17" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>425</v>
+        <v>339</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>426</v>
+        <v>340</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>426</v>
+        <v>340</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>427</v>
+        <v>341</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>428</v>
+        <v>342</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>429</v>
+        <v>343</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>429</v>
+        <v>343</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>430</v>
+        <v>344</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>197</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>431</v>
+        <v>345</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>432</v>
+        <v>346</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>432</v>
+        <v>346</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>433</v>
+        <v>347</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>434</v>
+        <v>348</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>435</v>
+        <v>349</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>436</v>
+        <v>350</v>
       </c>
       <c r="F21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G21" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H21" s="2" t="s">
-        <v>197</v>
+        <v>351</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>437</v>
+        <v>352</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>438</v>
+        <v>353</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>438</v>
+        <v>353</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>439</v>
+        <v>354</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>440</v>
+        <v>355</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>441</v>
+        <v>356</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>441</v>
+        <v>356</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>442</v>
+        <v>357</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>443</v>
+        <v>358</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>444</v>
+        <v>359</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>444</v>
+        <v>359</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>445</v>
+        <v>360</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>446</v>
+        <v>361</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>447</v>
+        <v>362</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>448</v>
+        <v>363</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>449</v>
+        <v>364</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>450</v>
+        <v>365</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>450</v>
+        <v>365</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>451</v>
+        <v>366</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>351</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>452</v>
+        <v>367</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>453</v>
+        <v>368</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>453</v>
+        <v>368</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>454</v>
+        <v>369</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>262</v>
+        <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>455</v>
+        <v>370</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>456</v>
+        <v>371</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>457</v>
+        <v>372</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>458</v>
+        <v>373</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>459</v>
+        <v>374</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>460</v>
+        <v>375</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>461</v>
+        <v>376</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>286</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>462</v>
+        <v>377</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>462</v>
+        <v>377</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>463</v>
+        <v>378</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>374</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>464</v>
+        <v>379</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>465</v>
+        <v>380</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>466</v>
+        <v>381</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>466</v>
+        <v>381</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>467</v>
+        <v>382</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>468</v>
+        <v>383</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -6380,9 +5353,9 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6400,28 +5373,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>68</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>69</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6429,902 +5402,934 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>469</v>
+        <v>384</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>470</v>
+        <v>385</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>471</v>
+        <v>386</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>472</v>
+        <v>387</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>473</v>
+        <v>388</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>74</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>474</v>
+        <v>389</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>475</v>
+        <v>390</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>475</v>
+        <v>390</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>476</v>
+        <v>391</v>
       </c>
       <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G4" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>477</v>
+        <v>392</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>478</v>
+        <v>393</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>478</v>
+        <v>393</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>479</v>
+        <v>394</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>480</v>
+        <v>395</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>481</v>
+        <v>396</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>481</v>
+        <v>396</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>482</v>
+        <v>397</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>80</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>121</v>
+        <v>133</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>483</v>
+        <v>398</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>484</v>
+        <v>399</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>485</v>
+        <v>400</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>486</v>
+        <v>401</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>487</v>
+        <v>402</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>488</v>
+        <v>403</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>374</v>
+        <v>222</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>142</v>
+        <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>489</v>
+        <v>404</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>490</v>
+        <v>405</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>490</v>
+        <v>405</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>491</v>
+        <v>406</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>142</v>
+        <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>492</v>
+        <v>407</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>493</v>
+        <v>408</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>494</v>
+        <v>409</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>120</v>
+        <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>147</v>
+        <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>495</v>
+        <v>410</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>496</v>
+        <v>411</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>497</v>
+        <v>412</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>73</v>
+        <v>110</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>147</v>
+        <v>351</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>498</v>
+        <v>413</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>499</v>
+        <v>414</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>499</v>
+        <v>414</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>500</v>
+        <v>415</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>147</v>
+        <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>501</v>
+        <v>416</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>417</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>502</v>
+        <v>417</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>503</v>
+        <v>418</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>197</v>
+        <v>351</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>504</v>
+        <v>419</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>505</v>
+        <v>420</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>506</v>
+        <v>421</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>507</v>
+        <v>422</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>508</v>
+        <v>423</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>508</v>
+        <v>423</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>509</v>
+        <v>424</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>85</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>262</v>
+        <v>200</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>510</v>
+        <v>425</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>139</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>511</v>
+        <v>426</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>512</v>
+        <v>427</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>513</v>
+        <v>428</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>514</v>
+        <v>429</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>515</v>
+        <v>430</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>516</v>
+        <v>431</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>517</v>
+        <v>432</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>518</v>
+        <v>433</v>
       </c>
       <c r="F18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G18" s="2" t="s">
-        <v>73</v>
-      </c>
       <c r="H18" s="2" t="s">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>519</v>
+        <v>434</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>520</v>
+        <v>435</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>521</v>
+        <v>436</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>374</v>
+        <v>72</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>522</v>
+        <v>437</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>523</v>
+        <v>438</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>523</v>
+        <v>438</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>524</v>
+        <v>439</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>525</v>
+        <v>440</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>526</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>526</v>
+        <v>441</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>527</v>
+        <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>237</v>
+        <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>262</v>
+        <v>351</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>528</v>
+        <v>443</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>529</v>
+        <v>444</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>529</v>
+        <v>444</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>530</v>
+        <v>445</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>73</v>
+        <v>222</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>277</v>
+        <v>351</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>531</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>532</v>
+        <v>447</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>532</v>
+        <v>447</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>533</v>
+        <v>448</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>534</v>
+        <v>449</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>535</v>
+        <v>450</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>535</v>
+        <v>450</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>536</v>
+        <v>451</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>277</v>
+        <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>537</v>
+        <v>452</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>538</v>
+        <v>453</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>539</v>
+        <v>454</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>73</v>
+        <v>84</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>281</v>
+        <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>540</v>
+        <v>455</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>541</v>
+        <v>456</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>541</v>
+        <v>456</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>542</v>
+        <v>457</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>72</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>543</v>
+        <v>274</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>544</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>545</v>
+        <v>459</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>545</v>
+        <v>459</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>546</v>
+        <v>460</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>374</v>
+        <v>110</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>370</v>
+        <v>461</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>547</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>548</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>548</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>549</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>80</v>
+        <v>288</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>550</v>
+        <v>284</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>551</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>552</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>552</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>553</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="G29" s="2" t="s">
-        <v>85</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>554</v>
+        <v>468</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>555</v>
+        <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7354,6 +6359,788 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>495</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>160</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J23"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -80,130 +80,130 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>377</t>
+    <t>383</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>151조 6709억 8177만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.14</t>
+  </si>
+  <si>
+    <t>피난민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>Scania 26</t>
+  </si>
+  <si>
+    <t>373</t>
+  </si>
+  <si>
+    <t>17위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>161조 6412억 5566만</t>
+  </si>
+  <si>
+    <t>피난 오신 여러분 반갑습니다.</t>
+  </si>
+  <si>
+    <t>주방화</t>
+  </si>
+  <si>
+    <t>2026.04.15</t>
+  </si>
+  <si>
+    <t>이고이스트</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>31위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>30명</t>
+  </si>
+  <si>
+    <t>162조 405억 5019만</t>
+  </si>
+  <si>
+    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
+  </si>
+  <si>
+    <t>한도카드</t>
+  </si>
+  <si>
+    <t>밤과다람쥐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>323</t>
+  </si>
+  <si>
+    <t>218조 876억 5313만</t>
+  </si>
+  <si>
+    <t>자유가입 길드입니다 1d 길컨 미참 스펙상승에 따른 길컨 점수 미상향 추방컷 관리로 이루어지고 있습니다</t>
+  </si>
+  <si>
+    <t>매미형</t>
+  </si>
+  <si>
+    <t>부계둘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>556</t>
   </si>
   <si>
     <t>14위</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>127조 3213억 5790만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.11</t>
-  </si>
-  <si>
-    <t>피난민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%94%BC%EB%82%9C%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>Scania 26</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>17위</t>
-  </si>
-  <si>
-    <t>137조 4077억 2612만</t>
-  </si>
-  <si>
-    <t>피난 오신 여러분 반갑습니다.</t>
-  </si>
-  <si>
-    <t>주방화</t>
-  </si>
-  <si>
-    <t>2026.04.10</t>
-  </si>
-  <si>
-    <t>이고이스트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9D%B4%EA%B3%A0%EC%9D%B4%EC%8A%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>30위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>30명</t>
-  </si>
-  <si>
-    <t>135조 5251억 2923만</t>
-  </si>
-  <si>
-    <t>가입문의 &amp;gt;&amp;gt; [ 에이비숍 , Eddy0825 ] &amp;lt;&amp;lt; 귓 1조 이상 :)</t>
-  </si>
-  <si>
-    <t>한도카드</t>
-  </si>
-  <si>
-    <t>밤과다람쥐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B0%A4%EA%B3%BC%EB%8B%A4%EB%9E%8C%EC%A5%90</t>
-  </si>
-  <si>
-    <t>Scania 5</t>
-  </si>
-  <si>
-    <t>326</t>
-  </si>
-  <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>28명</t>
-  </si>
-  <si>
-    <t>171조 6333억 5023만</t>
-  </si>
-  <si>
-    <t>자유가입 길드입니다 1d 길컨 미참 스펙상승에 따른 길컨 점수 미상향 추방컷 관리로 이루어지고 있습니다</t>
-  </si>
-  <si>
-    <t>매미형</t>
-  </si>
-  <si>
-    <t>부계둘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B6%80%EA%B3%84%EB%91%98</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>381</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>124조 4701억 3596만</t>
+    <t>22명</t>
+  </si>
+  <si>
+    <t>77조 1270억 4589만</t>
   </si>
   <si>
     <t>부계들 + 부계둘</t>
@@ -251,7 +251,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>17조 1695억 4531만</t>
+    <t>17조 7749억 2348만</t>
   </si>
   <si>
     <t>2</t>
@@ -269,7 +269,7 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>14조 951억 2182만</t>
+    <t>17조 4717억 6864만</t>
   </si>
   <si>
     <t>3</t>
@@ -284,43 +284,46 @@
     <t>다크나이트</t>
   </si>
   <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 6365억 3160만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>12조 629억 6271만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
     <t>100</t>
   </si>
   <si>
-    <t>12조 6365억 3160만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>10조 8080억 1797만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>9조 7862억 1841만</t>
+    <t>10조 9567억 7396만</t>
   </si>
   <si>
     <t>6</t>
@@ -332,39 +335,36 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>8조 3610억 5502만</t>
+    <t>9조 8332억 7293만</t>
   </si>
   <si>
     <t>7</t>
   </si>
   <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>6조 3436억 8307만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
     <t>아르미느</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>6조 468억 64만</t>
   </si>
   <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6조 140억 9399만</t>
-  </si>
-  <si>
     <t>9</t>
   </si>
   <si>
@@ -374,7 +374,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>5조 1592억 3651만</t>
+    <t>5조 2150억 6407만</t>
   </si>
   <si>
     <t>10</t>
@@ -389,7 +389,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>4조 5676억 7592만</t>
+    <t>4조 7691억 8012만</t>
   </si>
   <si>
     <t>11</t>
@@ -401,7 +401,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 2993억 5963만</t>
+    <t>4조 3794억 3430만</t>
   </si>
   <si>
     <t>12</t>
@@ -416,49 +416,88 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 6676억 5224만</t>
+    <t>3조 6709억 3521만</t>
   </si>
   <si>
     <t>13</t>
   </si>
   <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>3조 5242억 2736만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>흑두부</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
+    <t>3조 3846억 5890만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>3조 2452억 8664만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
     <t>99</t>
   </si>
   <si>
-    <t>3조 3846억 5890만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>3조 2011억 997만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>2조 8180억 4925만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>3조 247억 827만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 8428억 9825만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>2조 8112억 4149만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -467,46 +506,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>2조 7171억 6721만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 6747억 6521만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>2조 6008억 7148만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>2조 5943억 9545만</t>
+    <t>2조 7458억 6839만</t>
   </si>
   <si>
     <t>20</t>
@@ -530,7 +530,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 3068억 391만</t>
+    <t>2조 5125억 5820만</t>
   </si>
   <si>
     <t>22</t>
@@ -542,7 +542,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
   </si>
   <si>
-    <t>2조 3067억 6242만</t>
+    <t>2조 3898억 659만</t>
   </si>
   <si>
     <t>23</t>
@@ -659,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%83%B7</t>
   </si>
   <si>
-    <t>20조 8124억 1059만</t>
+    <t>27조 3333억 40만</t>
   </si>
   <si>
     <t>샾살개</t>
@@ -680,25 +680,25 @@
     <t>11조 6683억 8284만</t>
   </si>
   <si>
+    <t>샾밉당</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>10조 8651억 4898만</t>
+  </si>
+  <si>
     <t>샾브샤브</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B8%8C%EC%83%A4%EB%B8%8C</t>
   </si>
   <si>
-    <t>9조 6513억 9267만</t>
-  </si>
-  <si>
-    <t>샾밉당</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EB%B0%89%EB%8B%B9</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>8조 7980억 5102만</t>
+    <t>9조 7560억 1197만</t>
   </si>
   <si>
     <t>샾꾸붕</t>
@@ -716,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A9%A1%EB%AF%B8%EB%8B%88%EC%A7%80%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 5686억 1316만</t>
+    <t>4조 8038억 7054만</t>
   </si>
   <si>
     <t>소방담요</t>
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
   </si>
   <si>
-    <t>3조 4276억 8898만</t>
+    <t>4조 154억 1336만</t>
   </si>
   <si>
     <t>상산의조자룡</t>
@@ -734,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%81%EC%82%B0%EC%9D%98%EC%A1%B0%EC%9E%90%EB%A3%A1</t>
   </si>
   <si>
-    <t>3조 2567억 9335만</t>
+    <t>3조 5621억 118만</t>
   </si>
   <si>
     <t>샾프심</t>
@@ -743,7 +743,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
   </si>
   <si>
-    <t>2조 9255억 9764만</t>
+    <t>2조 9608억 3032만</t>
+  </si>
+  <si>
+    <t>샾오프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 5156억 7222만</t>
   </si>
   <si>
     <t>샾오산</t>
@@ -752,7 +761,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%EC%82%B0</t>
   </si>
   <si>
-    <t>2조 4451억 748만</t>
+    <t>2조 5067억 6250만</t>
   </si>
   <si>
     <t>김퍽퍽</t>
@@ -761,16 +770,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%80%ED%8D%BD%ED%8D%BD</t>
   </si>
   <si>
-    <t>2조 4418억 9894만</t>
-  </si>
-  <si>
-    <t>샾오프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EC%98%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 3827억 3541만</t>
+    <t>2조 4899억 8851만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EB%B0%A9%ED%99%94</t>
@@ -779,22 +779,22 @@
     <t>2조 3814억 4063만</t>
   </si>
   <si>
+    <t>무진미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>2조 533억 5756만</t>
+  </si>
+  <si>
     <t>샾감자</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%90%EC%9E%90</t>
   </si>
   <si>
-    <t>1조 6116억 2745만</t>
-  </si>
-  <si>
-    <t>무진미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%A7%84%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>1조 5577억 7193만</t>
+    <t>1조 7329억 8725만</t>
   </si>
   <si>
     <t>oEMPo</t>
@@ -803,7 +803,7 @@
     <t>https://mgf.gg/contents/character.php?n=oEMPo</t>
   </si>
   <si>
-    <t>1조 3704억 7106만</t>
+    <t>1조 4601억 6912만</t>
   </si>
   <si>
     <t>샾햇살</t>
@@ -812,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%96%87%EC%82%B4</t>
   </si>
   <si>
-    <t>1조 1825억 6907만</t>
+    <t>1조 2268억 6595만</t>
   </si>
   <si>
     <t>이지아지콩</t>
@@ -827,6 +827,15 @@
     <t>9592억 7414만</t>
   </si>
   <si>
+    <t>딱지냥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
+  </si>
+  <si>
+    <t>5612억 6313만</t>
+  </si>
+  <si>
     <t>백수돼지로성</t>
   </si>
   <si>
@@ -836,15 +845,6 @@
     <t>5433억 4764만</t>
   </si>
   <si>
-    <t>딱지냥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%94%B1%EC%A7%80%EB%83%A5</t>
-  </si>
-  <si>
-    <t>4713억 5012만</t>
-  </si>
-  <si>
     <t>샾앤플랫</t>
   </si>
   <si>
@@ -863,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%A9%EC%84%B7</t>
   </si>
   <si>
-    <t>2057억 4658만</t>
+    <t>2246억 9058만</t>
   </si>
   <si>
     <t>샾갈배</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%EA%B0%88%EB%B0%B0</t>
   </si>
   <si>
-    <t>1872억 2636만</t>
+    <t>2084억 3410만</t>
   </si>
   <si>
     <t>최훈석개멋져</t>
@@ -884,7 +884,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1613억 4146만</t>
+    <t>1663억 5682만</t>
   </si>
   <si>
     <t>샾사니서리당</t>
@@ -896,7 +896,10 @@
     <t>비숍</t>
   </si>
   <si>
-    <t>1346억 4398만</t>
+    <t>92</t>
+  </si>
+  <si>
+    <t>1550억 8284만</t>
   </si>
   <si>
     <t>커피둥</t>
@@ -905,7 +908,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BB%A4%ED%94%BC%EB%91%A5</t>
   </si>
   <si>
-    <t>1200억 9858만</t>
+    <t>1407억 6881만</t>
   </si>
   <si>
     <t>마퀸</t>
@@ -923,7 +926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A9%B4%EC%97%90%EA%B3%84%EB%9E%80%ED%83%81</t>
   </si>
   <si>
-    <t>34조 4115억 6254만</t>
+    <t>34조 5712억 8430만</t>
   </si>
   <si>
     <t>에이비숍</t>
@@ -932,7 +935,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%90%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>19조 1150억 3370만</t>
+    <t>20조 3804억 8074만</t>
   </si>
   <si>
     <t>환불카드</t>
@@ -941,7 +944,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>11조 2858억 9176만</t>
+    <t>12조 9547억 5564만</t>
   </si>
   <si>
     <t>아빠카드</t>
@@ -950,7 +953,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%B9%A0%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>7조 2849억 8496만</t>
+    <t>7조 5501억 3642만</t>
   </si>
   <si>
     <t>시글</t>
@@ -959,13 +962,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EA%B8%80</t>
   </si>
   <si>
-    <t>6조 5681억 7800만</t>
+    <t>6조 7561억 7684만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%8F%84%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>4조 9474억 2059만</t>
+    <t>5조 2844억 8811만</t>
+  </si>
+  <si>
+    <t>사과닷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
+  </si>
+  <si>
+    <t>2조 4695억 3778만</t>
   </si>
   <si>
     <t>공사과장</t>
@@ -977,22 +989,13 @@
     <t>2조 4059억 2866만</t>
   </si>
   <si>
-    <t>사과닷</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EA%B3%BC%EB%8B%B7</t>
-  </si>
-  <si>
-    <t>2조 3790억 6194만</t>
-  </si>
-  <si>
     <t>뽀뾰해봄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BD%80%EB%BE%B0%ED%95%B4%EB%B4%84</t>
   </si>
   <si>
-    <t>2조 1792억 5639만</t>
+    <t>2조 1919억 275만</t>
   </si>
   <si>
     <t>Eddy0825</t>
@@ -1001,7 +1004,25 @@
     <t>https://mgf.gg/contents/character.php?n=Eddy0825</t>
   </si>
   <si>
-    <t>1조 5159억 8227만</t>
+    <t>1조 8635억 9379만</t>
+  </si>
+  <si>
+    <t>닉커</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
+  </si>
+  <si>
+    <t>1조 7008억 4774만</t>
+  </si>
+  <si>
+    <t>돌격대원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 6591억 4304만</t>
   </si>
   <si>
     <t>망치전문</t>
@@ -1010,7 +1031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EC%A0%84%EB%AC%B8</t>
   </si>
   <si>
-    <t>1조 4484억 1233만</t>
+    <t>1조 5648억 7841만</t>
   </si>
   <si>
     <t>히히맘</t>
@@ -1019,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%ED%9E%88%EB%A7%98</t>
   </si>
   <si>
-    <t>1조 3706억 670만</t>
+    <t>1조 4032억 2065만</t>
   </si>
   <si>
     <t>토이감자</t>
@@ -1031,22 +1052,13 @@
     <t>1조 3297억 1328만</t>
   </si>
   <si>
-    <t>닉커</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%89%EC%BB%A4</t>
-  </si>
-  <si>
-    <t>1조 3179억 5406만</t>
-  </si>
-  <si>
-    <t>돌격대원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%8C%EA%B2%A9%EB%8C%80%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 1790억 5697만</t>
+    <t>호츠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
+  </si>
+  <si>
+    <t>1조 2018억 6742만</t>
   </si>
   <si>
     <t>비숍덩구</t>
@@ -1055,16 +1067,19 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%88%8D%EB%8D%A9%EA%B5%AC</t>
   </si>
   <si>
-    <t>1조 985억 8507만</t>
-  </si>
-  <si>
-    <t>호츠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EC%B8%A0</t>
-  </si>
-  <si>
-    <t>1조 967억 8189만</t>
+    <t>1조 1743억 6070만</t>
+  </si>
+  <si>
+    <t>회원카드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 755억 7415만</t>
   </si>
   <si>
     <t>핑와스</t>
@@ -1073,19 +1088,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%91%EC%99%80%EC%8A%A4</t>
   </si>
   <si>
-    <t>9855억 7893만</t>
-  </si>
-  <si>
-    <t>회원카드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%8C%EC%9B%90%EC%B9%B4%EB%93%9C</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>9586억 327만</t>
+    <t>1조 569억 5370만</t>
   </si>
   <si>
     <t>단풍a</t>
@@ -1094,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8Da</t>
   </si>
   <si>
-    <t>9581억 3672만</t>
+    <t>9929억 6615만</t>
   </si>
   <si>
     <t>문뚱식</t>
@@ -1103,7 +1106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%9A%B1%EC%8B%9D</t>
   </si>
   <si>
-    <t>9221억 2396만</t>
+    <t>9594억 537만</t>
   </si>
   <si>
     <t>오보기다</t>
@@ -1112,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%B3%B4%EA%B8%B0%EB%8B%A4</t>
   </si>
   <si>
-    <t>7794억 7560만</t>
+    <t>9505억 1644만</t>
   </si>
   <si>
     <t>떼링</t>
@@ -1121,7 +1124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%BC%EB%A7%81</t>
   </si>
   <si>
-    <t>7499억 5629만</t>
+    <t>8216억 9233만</t>
   </si>
   <si>
     <t>떵헤</t>
@@ -1130,7 +1133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%96%B5%ED%97%A4</t>
   </si>
   <si>
-    <t>6808억 2793만</t>
+    <t>7236억 9194만</t>
   </si>
   <si>
     <t>로우머</t>
@@ -1139,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%9C%EC%9A%B0%EB%A8%B8</t>
   </si>
   <si>
-    <t>6740억 4975만</t>
+    <t>6984억 8158만</t>
   </si>
   <si>
     <t>RIMS</t>
@@ -1148,7 +1151,7 @@
     <t>https://mgf.gg/contents/character.php?n=RIMS</t>
   </si>
   <si>
-    <t>6625억 2854만</t>
+    <t>6891억 1958만</t>
   </si>
   <si>
     <t>오말랑</t>
@@ -1157,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A7%90%EB%9E%91</t>
   </si>
   <si>
-    <t>5652억 1941만</t>
+    <t>6170억 1113만</t>
   </si>
   <si>
     <t>직불카드</t>
@@ -1166,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%81%EB%B6%88%EC%B9%B4%EB%93%9C</t>
   </si>
   <si>
-    <t>2713억 109만</t>
+    <t>2889억 9343만</t>
   </si>
   <si>
     <t>30</t>
@@ -1178,7 +1181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EC%B1%84%EC%9E%90%EB%A7%A4</t>
   </si>
   <si>
-    <t>1544억 6246만</t>
+    <t>1737억 306만</t>
   </si>
   <si>
     <t>MAKTO</t>
@@ -1196,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%AF%B8%ED%98%95</t>
   </si>
   <si>
-    <t>52조 8422억 5943만</t>
+    <t>53조 233억 7789만</t>
   </si>
   <si>
     <t>민헤</t>
@@ -1205,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%ED%97%A4</t>
   </si>
   <si>
-    <t>13조 4832억 9129만</t>
+    <t>14조 4469억 7634만</t>
   </si>
   <si>
     <t>세계챔피언</t>
@@ -1214,7 +1217,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EA%B3%84%EC%B1%94%ED%94%BC%EC%96%B8</t>
   </si>
   <si>
-    <t>11조 2225억 3682만</t>
+    <t>12조 4884억 2860만</t>
   </si>
   <si>
     <t>I라헬I</t>
@@ -1223,7 +1226,7 @@
     <t>https://mgf.gg/contents/character.php?n=I%EB%9D%BC%ED%97%ACI</t>
   </si>
   <si>
-    <t>3조 4648억 7843만</t>
+    <t>3조 6959억 7439만</t>
   </si>
   <si>
     <t>건야웅</t>
@@ -1232,7 +1235,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EC%95%BC%EC%9B%85</t>
   </si>
   <si>
-    <t>2조 9755억 5188만</t>
+    <t>3조 1423억 222만</t>
   </si>
   <si>
     <t>찐썽잉</t>
@@ -1268,7 +1271,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8D%B0%EB%A0%81%ED%8F%AC</t>
   </si>
   <si>
-    <t>1조 2131억 8650만</t>
+    <t>1조 2142억 4318만</t>
   </si>
   <si>
     <t>레제내꺼야</t>
@@ -1277,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%EC%A0%9C%EB%82%B4%EA%BA%BC%EC%95%BC</t>
   </si>
   <si>
-    <t>9811억 2977만</t>
+    <t>1조 1042억 9983만</t>
   </si>
   <si>
     <t>S2지존</t>
@@ -1304,7 +1307,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%A8%EB%B0%8D</t>
   </si>
   <si>
-    <t>8657억 5632만</t>
+    <t>8670억 6486만</t>
+  </si>
+  <si>
+    <t>이치마루김</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%B9%98%EB%A7%88%EB%A3%A8%EA%B9%80</t>
+  </si>
+  <si>
+    <t>7865억 6669만</t>
   </si>
   <si>
     <t>하얀물개</t>
@@ -1313,7 +1325,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%96%80%EB%AC%BC%EA%B0%9C</t>
   </si>
   <si>
-    <t>7680억 3260만</t>
+    <t>7845억 5838만</t>
   </si>
   <si>
     <t>비숍둑이</t>
@@ -1331,16 +1343,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EC%BD%94%EB%83%A5%EB%B6%80%ED%95%98</t>
   </si>
   <si>
-    <t>6544억 5291만</t>
-  </si>
-  <si>
-    <t>장빵구</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EB%B9%B5%EA%B5%AC</t>
-  </si>
-  <si>
-    <t>5600억 447만</t>
+    <t>6892억 944만</t>
   </si>
   <si>
     <t>환불냠냠</t>
@@ -1349,7 +1352,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EB%B6%88%EB%83%A0%EB%83%A0</t>
   </si>
   <si>
-    <t>5115억 5105만</t>
+    <t>6180억 600만</t>
   </si>
   <si>
     <t>레피스나2</t>
@@ -1358,7 +1361,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A0%88%ED%94%BC%EC%8A%A4%EB%82%982</t>
   </si>
   <si>
-    <t>5053억 2083만</t>
+    <t>5611억 1871만</t>
   </si>
   <si>
     <t>혼자가최고</t>
@@ -1385,7 +1388,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%B3%B5%EB%B3%B5</t>
   </si>
   <si>
-    <t>4161억 969만</t>
+    <t>4558억 3369만</t>
   </si>
   <si>
     <t>모몬쌍</t>
@@ -1394,7 +1397,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%AA%AC%EC%8C%8D</t>
   </si>
   <si>
-    <t>2823억 7454만</t>
+    <t>2896억 4112만</t>
   </si>
   <si>
     <t>우주강아지</t>
@@ -1412,9 +1415,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EA%B0%80%EB%82%9C%EA%BD%9D%EC%84%AD%EC%9D%B4</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
     <t>1801억 3527만</t>
   </si>
   <si>
@@ -1424,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%A7%84%EB%8B%88</t>
   </si>
   <si>
-    <t>1002억 7173만</t>
+    <t>1055억 1449만</t>
   </si>
   <si>
     <t>봉오리</t>
@@ -1436,7 +1436,7 @@
     <t>87</t>
   </si>
   <si>
-    <t>921억 1003만</t>
+    <t>1006억 4557만</t>
   </si>
   <si>
     <t>만년설딸기</t>
@@ -1445,10 +1445,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%85%84%EC%84%A4%EB%94%B8%EA%B8%B0</t>
   </si>
   <si>
-    <t>85</t>
-  </si>
-  <si>
-    <t>312억 3253만</t>
+    <t>86</t>
+  </si>
+  <si>
+    <t>326억 6738만</t>
   </si>
   <si>
     <t>처히</t>
@@ -1457,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%98%ED%9E%88</t>
   </si>
   <si>
-    <t>13조 5574억 3249만</t>
+    <t>14조 7855억 3870만</t>
   </si>
   <si>
     <t>환생의불꼬츠</t>
@@ -1466,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%98%EC%83%9D%EC%9D%98%EB%B6%88%EA%BC%AC%EC%B8%A0</t>
   </si>
   <si>
-    <t>10조 9549억 8302만</t>
+    <t>11조 5497억 9854만</t>
   </si>
   <si>
     <t>밍진</t>
@@ -1475,7 +1475,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%A7%84</t>
   </si>
   <si>
-    <t>8조 9166억 6911만</t>
+    <t>10조 6082억 1924만</t>
   </si>
   <si>
     <t>AKPS</t>
@@ -1496,6 +1496,15 @@
     <t>3조 9540억 9597만</t>
   </si>
   <si>
+    <t>천칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>3조 3198억 5397만</t>
+  </si>
+  <si>
     <t>토미오카상</t>
   </si>
   <si>
@@ -1520,16 +1529,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9F%B0%EB%8B%9D%EB%9E%98%EB%B9%97</t>
   </si>
   <si>
-    <t>2조 6773억 6238만</t>
-  </si>
-  <si>
-    <t>천칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 6702억 2482만</t>
+    <t>3조 936억 8016만</t>
   </si>
   <si>
     <t>화살대</t>
@@ -1538,7 +1538,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%94%EC%82%B4%EB%8C%80</t>
   </si>
   <si>
-    <t>2조 6342억 2078만</t>
+    <t>2조 8470억 3764만</t>
   </si>
   <si>
     <t>토니워터</t>
@@ -1547,7 +1547,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%8B%88%EC%9B%8C%ED%84%B0</t>
   </si>
   <si>
-    <t>2조 6162억 1545만</t>
+    <t>2조 7791억 8260만</t>
   </si>
   <si>
     <t>펑풀</t>
@@ -1556,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8E%91%ED%92%80</t>
   </si>
   <si>
-    <t>2조 4991억 587만</t>
+    <t>2조 7515억 9768만</t>
   </si>
   <si>
     <t>샤스찌에</t>
@@ -1565,7 +1565,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EC%8A%A4%EC%B0%8C%EC%97%90</t>
   </si>
   <si>
-    <t>1조 5997억 4972만</t>
+    <t>2조 1842억 9550만</t>
   </si>
   <si>
     <t>보동핑</t>
@@ -1574,7 +1574,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%8F%99%ED%95%91</t>
   </si>
   <si>
-    <t>1조 3542억 7780만</t>
+    <t>1조 3859억 2131만</t>
   </si>
   <si>
     <t>지니좋아요</t>
@@ -1583,7 +1583,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EB%8B%88%EC%A2%8B%EC%95%84%EC%9A%94</t>
   </si>
   <si>
-    <t>1조 666억 9786만</t>
+    <t>1조 3132억 7342만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
+  </si>
+  <si>
+    <t>1조 620억 1277만</t>
   </si>
   <si>
     <t>2026년1월30일</t>
@@ -1604,19 +1610,13 @@
     <t>1조 24억 1640만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%B6%98%EC%82%BC</t>
-  </si>
-  <si>
-    <t>8969억 3132만</t>
-  </si>
-  <si>
     <t>Targa</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Targa</t>
   </si>
   <si>
-    <t>5665억 5826만</t>
+    <t>5903억 2749만</t>
   </si>
   <si>
     <t>애둘이에요</t>
@@ -1625,7 +1625,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EB%91%98%EC%9D%B4%EC%97%90%EC%9A%94</t>
   </si>
   <si>
-    <t>5504억 9405만</t>
+    <t>5820억 7009만</t>
   </si>
   <si>
     <t>짱창훈</t>
@@ -1634,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EC%B0%BD%ED%9B%88</t>
   </si>
   <si>
-    <t>3382억 604만</t>
+    <t>3558억 439만</t>
   </si>
   <si>
     <t>구리구리뽕리</t>
@@ -1643,10 +1643,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%AC%EB%A6%AC%EA%B5%AC%EB%A6%AC%EB%BD%95%EB%A6%AC</t>
   </si>
   <si>
-    <t>80</t>
-  </si>
-  <si>
-    <t>55억 5534만</t>
+    <t>81</t>
+  </si>
+  <si>
+    <t>57억 3736만</t>
   </si>
 </sst>
 </file>
@@ -2133,130 +2133,130 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>45</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>44</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>48</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="J5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="L5" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="M5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>54</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>20</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>58</v>
@@ -2268,7 +2268,7 @@
         <v>60</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2450,10 +2450,10 @@
         <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2464,28 +2464,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2496,16 +2496,16 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>78</v>
@@ -2514,10 +2514,10 @@
         <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>96</v>
+        <v>73</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2528,28 +2528,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>90</v>
+        <v>106</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2560,22 +2560,22 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>85</v>
@@ -2610,7 +2610,7 @@
         <v>72</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>115</v>
@@ -2642,7 +2642,7 @@
         <v>119</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>120</v>
@@ -2671,10 +2671,10 @@
         <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>124</v>
@@ -2735,13 +2735,13 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>133</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2752,28 +2752,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>137</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>138</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2784,28 +2784,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>139</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>141</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>128</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2816,25 +2816,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>146</v>
@@ -2866,7 +2866,7 @@
         <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>150</v>
@@ -2895,7 +2895,7 @@
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>154</v>
@@ -2927,10 +2927,10 @@
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>128</v>
+        <v>97</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>159</v>
@@ -2962,7 +2962,7 @@
         <v>119</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>163</v>
@@ -3023,7 +3023,7 @@
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>128</v>
@@ -3058,7 +3058,7 @@
         <v>72</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>175</v>
@@ -3154,7 +3154,7 @@
         <v>79</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>188</v>
@@ -3215,10 +3215,10 @@
         <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>196</v>
@@ -3363,16 +3363,16 @@
         <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>204</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3398,13 +3398,13 @@
         <v>79</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>207</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3430,13 +3430,13 @@
         <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>210</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3462,13 +3462,13 @@
         <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>213</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3476,7 +3476,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>214</v>
@@ -3491,16 +3491,16 @@
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>216</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3508,7 +3508,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>217</v>
@@ -3523,16 +3523,16 @@
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>110</v>
+        <v>219</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3540,31 +3540,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3572,7 +3572,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>224</v>
@@ -3587,16 +3587,16 @@
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3619,16 +3619,16 @@
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3654,13 +3654,13 @@
         <v>72</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3686,13 +3686,13 @@
         <v>84</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3718,13 +3718,13 @@
         <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3747,16 +3747,16 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3764,7 +3764,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>242</v>
@@ -3779,16 +3779,16 @@
         <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>84</v>
+        <v>72</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>85</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3796,7 +3796,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3811,16 +3811,16 @@
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3828,13 +3828,13 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>248</v>
@@ -3843,7 +3843,7 @@
         <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>154</v>
@@ -3852,7 +3852,7 @@
         <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3875,7 +3875,7 @@
         <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>154</v>
@@ -3884,7 +3884,7 @@
         <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3907,16 +3907,16 @@
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3939,7 +3939,7 @@
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>200</v>
@@ -3948,7 +3948,7 @@
         <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -3971,7 +3971,7 @@
         <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>154</v>
@@ -3980,7 +3980,7 @@
         <v>261</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4012,7 +4012,7 @@
         <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4035,7 +4035,7 @@
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>84</v>
+        <v>106</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>264</v>
@@ -4044,7 +4044,7 @@
         <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4067,7 +4067,7 @@
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>264</v>
@@ -4076,7 +4076,7 @@
         <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4108,7 +4108,7 @@
         <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4140,7 +4140,7 @@
         <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4163,7 +4163,7 @@
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>274</v>
@@ -4172,7 +4172,7 @@
         <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4204,7 +4204,7 @@
         <v>285</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4230,13 +4230,13 @@
         <v>288</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -4247,28 +4247,28 @@
         <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>284</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4357,19 +4357,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
@@ -4381,27 +4381,27 @@
         <v>73</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>78</v>
@@ -4410,30 +4410,30 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
@@ -4445,59 +4445,59 @@
         <v>73</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>78</v>
@@ -4506,30 +4506,30 @@
         <v>84</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>78</v>
@@ -4538,30 +4538,30 @@
         <v>288</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>71</v>
@@ -4570,126 +4570,126 @@
         <v>72</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>288</v>
+        <v>79</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>78</v>
@@ -4701,347 +4701,347 @@
         <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>106</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>110</v>
+        <v>119</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>106</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>200</v>
+        <v>349</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>200</v>
+        <v>154</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>78</v>
@@ -5053,27 +5053,27 @@
         <v>154</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>78</v>
@@ -5085,123 +5085,123 @@
         <v>200</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>264</v>
+        <v>349</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>78</v>
@@ -5210,62 +5210,62 @@
         <v>72</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>78</v>
@@ -5277,27 +5277,27 @@
         <v>264</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>78</v>
@@ -5309,10 +5309,10 @@
         <v>274</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -5402,19 +5402,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>78</v>
@@ -5423,30 +5423,30 @@
         <v>72</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>71</v>
@@ -5458,27 +5458,27 @@
         <v>73</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>78</v>
@@ -5487,30 +5487,30 @@
         <v>79</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>78</v>
@@ -5519,30 +5519,30 @@
         <v>72</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>105</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>78</v>
@@ -5551,30 +5551,30 @@
         <v>79</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>78</v>
@@ -5586,59 +5586,59 @@
         <v>128</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>128</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>78</v>
@@ -5650,27 +5650,27 @@
         <v>154</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>112</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>78</v>
@@ -5682,91 +5682,91 @@
         <v>128</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>154</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>78</v>
@@ -5775,30 +5775,30 @@
         <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>130</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>78</v>
@@ -5810,27 +5810,27 @@
         <v>200</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>78</v>
@@ -5842,155 +5842,155 @@
         <v>200</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>200</v>
+        <v>264</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>288</v>
+        <v>72</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>79</v>
+        <v>288</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>264</v>
+        <v>349</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>78</v>
@@ -6002,27 +6002,27 @@
         <v>264</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>78</v>
@@ -6031,62 +6031,62 @@
         <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>351</v>
+        <v>200</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>78</v>
@@ -6098,59 +6098,59 @@
         <v>264</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>172</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>264</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>176</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>78</v>
@@ -6162,27 +6162,27 @@
         <v>264</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>78</v>
@@ -6194,47 +6194,47 @@
         <v>274</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>185</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>78</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>461</v>
+        <v>274</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>189</v>
@@ -6255,18 +6255,18 @@
         <v>288</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>193</v>
@@ -6293,12 +6293,12 @@
         <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>197</v>
@@ -6325,7 +6325,7 @@
         <v>473</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -6414,7 +6414,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>69</v>
@@ -6432,21 +6432,21 @@
         <v>78</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>75</v>
@@ -6467,18 +6467,18 @@
         <v>72</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>81</v>
@@ -6505,12 +6505,12 @@
         <v>482</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>87</v>
@@ -6531,21 +6531,21 @@
         <v>84</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>85</v>
+        <v>97</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>486</v>
@@ -6560,24 +6560,24 @@
         <v>78</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>133</v>
+        <v>145</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>489</v>
@@ -6592,24 +6592,24 @@
         <v>78</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>79</v>
+        <v>219</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>491</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>492</v>
@@ -6624,7 +6624,7 @@
         <v>78</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>154</v>
@@ -6633,15 +6633,15 @@
         <v>494</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>495</v>
@@ -6656,7 +6656,7 @@
         <v>78</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>110</v>
+        <v>72</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>154</v>
@@ -6665,12 +6665,12 @@
         <v>497</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>112</v>
@@ -6688,21 +6688,21 @@
         <v>78</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>222</v>
+        <v>106</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>500</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>116</v>
@@ -6720,21 +6720,21 @@
         <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>503</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>121</v>
@@ -6755,18 +6755,18 @@
         <v>72</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>154</v>
+        <v>128</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>506</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>125</v>
@@ -6793,12 +6793,12 @@
         <v>509</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>130</v>
@@ -6816,7 +6816,7 @@
         <v>78</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>200</v>
@@ -6825,15 +6825,15 @@
         <v>512</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>513</v>
@@ -6857,15 +6857,15 @@
         <v>515</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>516</v>
@@ -6889,108 +6889,108 @@
         <v>518</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>519</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="J17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>524</v>
-      </c>
       <c r="J18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>60</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>60</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
         <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>119</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>156</v>
@@ -7011,18 +7011,18 @@
         <v>72</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>264</v>
+        <v>349</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>160</v>
@@ -7049,12 +7049,12 @@
         <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>164</v>
@@ -7072,21 +7072,21 @@
         <v>78</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>168</v>
@@ -7104,7 +7104,7 @@
         <v>78</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>538</v>
@@ -7113,7 +7113,7 @@
         <v>539</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -725,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%B0%A9%EB%8B%B4%EC%9A%94</t>
   </si>
   <si>
-    <t>4조 154억 1336만</t>
+    <t>4조 3012억 1168만</t>
   </si>
   <si>
     <t>상산의조자룡</t>
@@ -743,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%83%BE%ED%94%84%EC%8B%AC</t>
   </si>
   <si>
-    <t>2조 9608억 3032만</t>
+    <t>3조 5501억 637만</t>
   </si>
   <si>
     <t>샾오프</t>
@@ -1646,7 +1646,7 @@
     <t>81</t>
   </si>
   <si>
-    <t>57억 3736만</t>
+    <t>68억 654만</t>
   </si>
 </sst>
 </file>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>380</t>
+    <t>381</t>
   </si>
   <si>
     <t>12위</t>
@@ -137,7 +137,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
   </si>
   <si>
-    <t>389</t>
+    <t>390</t>
   </si>
   <si>
     <t>13위</t>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -11,16 +11,16 @@
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="Kali" sheetId="3" r:id="rId3"/>
     <sheet name="숑숑" sheetId="4" r:id="rId4"/>
-    <sheet name="채금" sheetId="5" r:id="rId5"/>
-    <sheet name="쌈뽕" sheetId="6" r:id="rId6"/>
+    <sheet name="쌈뽕" sheetId="5" r:id="rId5"/>
+    <sheet name="채금" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$27</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">쌈뽕!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">채금!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">채금!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>171조 6820억 7377만</t>
+    <t>171조 8825억 4334만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -137,13 +137,13 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
   </si>
   <si>
-    <t>390</t>
+    <t>389</t>
   </si>
   <si>
     <t>13위</t>
   </si>
   <si>
-    <t>165조 7814억 6486만</t>
+    <t>166조 473억 3111만</t>
   </si>
   <si>
     <t>소통 잘하시는분들 환영! 투력1조이상! 가입 전 꼭 귓문의 부탁드려용 문의는(강린)</t>
@@ -152,6 +152,33 @@
     <t>숑이</t>
   </si>
   <si>
+    <t>쌈뽕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8C%88%EB%BD%95</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>366</t>
+  </si>
+  <si>
+    <t>32위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>181조 9602억 7867만</t>
+  </si>
+  <si>
+    <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
+  </si>
+  <si>
+    <t>장정근</t>
+  </si>
+  <si>
     <t>채금</t>
   </si>
   <si>
@@ -179,33 +206,6 @@
     <t>역뢰</t>
   </si>
   <si>
-    <t>쌈뽕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8C%88%EB%BD%95</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>32위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>181조 9602억 7867만</t>
-  </si>
-  <si>
-    <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
-  </si>
-  <si>
-    <t>장정근</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -245,7 +245,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>22조 5686억 1996만</t>
+    <t>22조 7699억 4133만</t>
   </si>
   <si>
     <t>2</t>
@@ -338,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>6조 9065억 9844만</t>
+    <t>6조 9158억 4470만</t>
   </si>
   <si>
     <t>8</t>
@@ -362,6 +362,21 @@
     <t>9</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>5조 7798억 2930만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -371,21 +386,6 @@
     <t>5조 5324억 9799만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>5조 3916억 4603만</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -395,12 +395,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 5125억 6849만</t>
+    <t>4조 9239억 3208만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>4조 3189억 8200만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -410,10 +422,10 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 2010억 1283만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>4조 2090억 334만</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>므고</t>
@@ -422,10 +434,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 1502억 5010만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>4조 1855억 6129만</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -437,10 +449,10 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 6989억 1308만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>3조 7011억 1668만</t>
+  </si>
+  <si>
+    <t>16</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -455,21 +467,21 @@
     <t>3조 6112억 850만</t>
   </si>
   <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>3조 5215억 9190만</t>
-  </si>
-  <si>
     <t>17</t>
   </si>
   <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>3조 5006억 2017만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>쭌파파</t>
   </si>
   <si>
@@ -479,18 +491,6 @@
     <t>3조 3744억 7808만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>3조 2687억 7234만</t>
-  </si>
-  <si>
     <t>19</t>
   </si>
   <si>
@@ -500,31 +500,31 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>2조 8414억 2069만</t>
+    <t>2조 8438억 7638만</t>
   </si>
   <si>
     <t>20</t>
   </si>
   <si>
-    <t>겨울바다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EC%9A%B8%EB%B0%94%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>2조 7544억 9536만</t>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 7646억 9816만</t>
   </si>
   <si>
     <t>21</t>
   </si>
   <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 7199억 9178만</t>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 5691억 3500만</t>
   </si>
   <si>
     <t>22</t>
@@ -542,18 +542,30 @@
     <t>23</t>
   </si>
   <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 3162억 528만</t>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2조 2322억 7931만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 2114억 104만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>여눈</t>
   </si>
   <si>
@@ -563,18 +575,6 @@
     <t>2조 1697억 686만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
-    <t>2조 689억 590만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -599,540 +599,540 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>1조 9531억 7029만</t>
+    <t>2조 123억 3425만</t>
   </si>
   <si>
     <t>28</t>
   </si>
   <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 9311억 8518만</t>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>1조 8260억 5446만</t>
   </si>
   <si>
     <t>29</t>
   </si>
   <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>1조 8260억 5446만</t>
+    <t>욤지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 2511억 5308만</t>
+  </si>
+  <si>
+    <t>윤기종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
+  </si>
+  <si>
+    <t>39조 2810억 3527만</t>
+  </si>
+  <si>
+    <t>니니니닉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
+  </si>
+  <si>
+    <t>14조 3084억 1761만</t>
+  </si>
+  <si>
+    <t>뤄드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
+  </si>
+  <si>
+    <t>9조 2003억 1997만</t>
+  </si>
+  <si>
+    <t>태태아방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>8조 4957억 2889만</t>
+  </si>
+  <si>
+    <t>롱노즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
+  </si>
+  <si>
+    <t>7조 7367억 9818만</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>6조 9130억 7586만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>6조 7975억 2029만</t>
+  </si>
+  <si>
+    <t>삼치김치찜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%EA%B9%80%EC%B9%98%EC%B0%9C</t>
+  </si>
+  <si>
+    <t>6조 6403억 9033만</t>
+  </si>
+  <si>
+    <t>뱀맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>5조 5509억 2697만</t>
+  </si>
+  <si>
+    <t>약한디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EB%94%94</t>
+  </si>
+  <si>
+    <t>5조 4820억 4885만</t>
+  </si>
+  <si>
+    <t>IMABORNHATER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
+  </si>
+  <si>
+    <t>5조 3482억 55만</t>
+  </si>
+  <si>
+    <t>조지선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5조 1623억 2192만</t>
+  </si>
+  <si>
+    <t>AI루미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 818억 5256만</t>
+  </si>
+  <si>
+    <t>사당행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
+  </si>
+  <si>
+    <t>4조 9701억 4878만</t>
+  </si>
+  <si>
+    <t>지안히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%88%ED%9E%88</t>
+  </si>
+  <si>
+    <t>4조 4179억 3072만</t>
+  </si>
+  <si>
+    <t>올망건빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%A7%9D%EA%B1%B4%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>4조 2661억 9603만</t>
+  </si>
+  <si>
+    <t>거푸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
+  </si>
+  <si>
+    <t>3조 9897억 2659만</t>
+  </si>
+  <si>
+    <t>석종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
+  </si>
+  <si>
+    <t>3조 2905억 1139만</t>
+  </si>
+  <si>
+    <t>Pixy</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pixy</t>
+  </si>
+  <si>
+    <t>3조 376억 9729만</t>
+  </si>
+  <si>
+    <t>채빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>2조 4663억 2375만</t>
+  </si>
+  <si>
+    <t>겨농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
+  </si>
+  <si>
+    <t>2조 3597억 3925만</t>
+  </si>
+  <si>
+    <t>히미노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 3013억 13만</t>
+  </si>
+  <si>
+    <t>코코호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2조 2396억 7990만</t>
+  </si>
+  <si>
+    <t>킴머웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%A8%B8%EC%9B%85</t>
+  </si>
+  <si>
+    <t>2조 755억 5068만</t>
+  </si>
+  <si>
+    <t>홍이수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
+  </si>
+  <si>
+    <t>1조 8193억 3141만</t>
+  </si>
+  <si>
+    <t>kingsister</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=kingsister</t>
+  </si>
+  <si>
+    <t>1조 8130억 5412만</t>
+  </si>
+  <si>
+    <t>반음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>1조 3764억 3946만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>39조 4651억 8162만</t>
+  </si>
+  <si>
+    <t>소독약</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
+  </si>
+  <si>
+    <t>15조 1317억 316만</t>
+  </si>
+  <si>
+    <t>주존사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>14조 310억 5090만</t>
+  </si>
+  <si>
+    <t>휘정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
+  </si>
+  <si>
+    <t>8조 6331억 9927만</t>
+  </si>
+  <si>
+    <t>무피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
+  </si>
+  <si>
+    <t>7조 8201억 9257만</t>
+  </si>
+  <si>
+    <t>캐서린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>6조 7426억 1980만</t>
+  </si>
+  <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>6조 479억 7569만</t>
+  </si>
+  <si>
+    <t>슈웃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
+  </si>
+  <si>
+    <t>5조 9520억 8440만</t>
+  </si>
+  <si>
+    <t>빡박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 4044억 7879만</t>
+  </si>
+  <si>
+    <t>임나연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
+  </si>
+  <si>
+    <t>5조 2628억 1749만</t>
+  </si>
+  <si>
+    <t>강린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>5조 52억 9592만</t>
+  </si>
+  <si>
+    <t>졸귀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
+  </si>
+  <si>
+    <t>4조 4792억 5669만</t>
+  </si>
+  <si>
+    <t>스파토이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 240억 3613만</t>
+  </si>
+  <si>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>3조 5728억 1195만</t>
+  </si>
+  <si>
+    <t>픽홀로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3조 4727억 2206만</t>
+  </si>
+  <si>
+    <t>Rania</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rania</t>
+  </si>
+  <si>
+    <t>3조 4486억 9673만</t>
+  </si>
+  <si>
+    <t>쟈라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>3조 2195억 1007만</t>
+  </si>
+  <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>2조 9519억 3003만</t>
+  </si>
+  <si>
+    <t>Uhani</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
+  </si>
+  <si>
+    <t>2조 8490억 4859만</t>
+  </si>
+  <si>
+    <t>베르1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
+  </si>
+  <si>
+    <t>2조 8254억 9759만</t>
+  </si>
+  <si>
+    <t>바세린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>2조 8084억 6646만</t>
+  </si>
+  <si>
+    <t>쟁반짜장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>2조 5842억 993만</t>
+  </si>
+  <si>
+    <t>별렉스b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
+  </si>
+  <si>
+    <t>2조 5328억 6439만</t>
+  </si>
+  <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>2조 3781억 3063만</t>
+  </si>
+  <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 878억 617만</t>
+  </si>
+  <si>
+    <t>하숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
+  </si>
+  <si>
+    <t>2조 367억 9637만</t>
+  </si>
+  <si>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 8281억 425만</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=potato</t>
+  </si>
+  <si>
+    <t>1조 4832억 5664만</t>
+  </si>
+  <si>
+    <t>양산호수공원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 3890억 1669만</t>
   </si>
   <si>
     <t>30</t>
   </si>
   <si>
-    <t>욤지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 2511억 5308만</t>
-  </si>
-  <si>
-    <t>윤기종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
-  </si>
-  <si>
-    <t>39조 2810억 3527만</t>
-  </si>
-  <si>
-    <t>니니니닉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
-  </si>
-  <si>
-    <t>14조 3084억 1761만</t>
-  </si>
-  <si>
-    <t>뤄드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
-  </si>
-  <si>
-    <t>8조 5205억 3108만</t>
-  </si>
-  <si>
-    <t>태태아방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>8조 4957억 2889만</t>
-  </si>
-  <si>
-    <t>삼치김치찜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%EA%B9%80%EC%B9%98%EC%B0%9C</t>
-  </si>
-  <si>
-    <t>6조 6403억 9033만</t>
-  </si>
-  <si>
-    <t>롱노즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
-  </si>
-  <si>
-    <t>6조 4812억 989만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>6조 4506억 8954만</t>
-  </si>
-  <si>
-    <t>뱀맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>5조 5509억 2697만</t>
-  </si>
-  <si>
-    <t>약한디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EB%94%94</t>
-  </si>
-  <si>
-    <t>5조 4820억 4885만</t>
-  </si>
-  <si>
-    <t>IMABORNHATER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
-  </si>
-  <si>
-    <t>5조 476억 4906만</t>
-  </si>
-  <si>
-    <t>AI루미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>4조 5050억 1781만</t>
-  </si>
-  <si>
-    <t>올망건빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%A7%9D%EA%B1%B4%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>4조 2661억 9603만</t>
-  </si>
-  <si>
-    <t>사당행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
-  </si>
-  <si>
-    <t>4조 2460억 3771만</t>
-  </si>
-  <si>
-    <t>지안히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%88%ED%9E%88</t>
-  </si>
-  <si>
-    <t>4조 2226억 6581만</t>
-  </si>
-  <si>
-    <t>거푸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
-  </si>
-  <si>
-    <t>3조 7262억 4497만</t>
-  </si>
-  <si>
-    <t>조지선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>3조 6759억 5540만</t>
-  </si>
-  <si>
-    <t>석종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
-  </si>
-  <si>
-    <t>3조 2688억 1322만</t>
-  </si>
-  <si>
-    <t>전통한우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%86%B5%ED%95%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>2조 8377억 608만</t>
-  </si>
-  <si>
-    <t>Pixy</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pixy</t>
-  </si>
-  <si>
-    <t>2조 6219억 2992만</t>
-  </si>
-  <si>
-    <t>채빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>2조 4033억 8268만</t>
-  </si>
-  <si>
-    <t>겨농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
-  </si>
-  <si>
-    <t>2조 3597억 3925만</t>
-  </si>
-  <si>
-    <t>히미노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 3013억 13만</t>
-  </si>
-  <si>
-    <t>킴머웅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%A8%B8%EC%9B%85</t>
-  </si>
-  <si>
-    <t>2조 755억 5068만</t>
-  </si>
-  <si>
-    <t>홍이수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
-  </si>
-  <si>
-    <t>1조 8193억 3141만</t>
-  </si>
-  <si>
-    <t>kingsister</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=kingsister</t>
-  </si>
-  <si>
-    <t>1조 6892억 1926만</t>
-  </si>
-  <si>
-    <t>반음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>1조 3764억 3946만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>36조 7285억 9551만</t>
-  </si>
-  <si>
-    <t>소독약</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
-  </si>
-  <si>
-    <t>14조 6115억 5118만</t>
-  </si>
-  <si>
-    <t>주존사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>13조 8904억 3743만</t>
-  </si>
-  <si>
-    <t>휘정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
-  </si>
-  <si>
-    <t>8조 3451억 6979만</t>
-  </si>
-  <si>
-    <t>무피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
-  </si>
-  <si>
-    <t>7조 3950억 3835만</t>
-  </si>
-  <si>
-    <t>캐서린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>6조 3805억 9354만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>6조 479억 7569만</t>
-  </si>
-  <si>
-    <t>슈웃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
-  </si>
-  <si>
-    <t>5조 8443억 6332만</t>
-  </si>
-  <si>
-    <t>임나연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
-  </si>
-  <si>
-    <t>5조 2364억 8418만</t>
-  </si>
-  <si>
-    <t>빡박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 5873억 1265만</t>
-  </si>
-  <si>
-    <t>졸귀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
-  </si>
-  <si>
-    <t>4조 4792억 5669만</t>
-  </si>
-  <si>
-    <t>강린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>4조 4116억 2751만</t>
-  </si>
-  <si>
-    <t>스파토이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 240억 3613만</t>
-  </si>
-  <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>3조 3825억 9331만</t>
-  </si>
-  <si>
-    <t>Rania</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rania</t>
-  </si>
-  <si>
-    <t>3조 2727억 7752만</t>
-  </si>
-  <si>
-    <t>픽홀로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3조 2374억 3323만</t>
-  </si>
-  <si>
-    <t>쟈라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>3조 2195억 1007만</t>
-  </si>
-  <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>2조 9486억 8418만</t>
-  </si>
-  <si>
-    <t>Uhani</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
-  </si>
-  <si>
-    <t>2조 8490억 4859만</t>
-  </si>
-  <si>
-    <t>베르1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
-  </si>
-  <si>
-    <t>2조 8208억 2045만</t>
-  </si>
-  <si>
-    <t>바세린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>2조 8084억 6646만</t>
-  </si>
-  <si>
-    <t>쟁반짜장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 5842억 993만</t>
-  </si>
-  <si>
-    <t>별렉스b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
-  </si>
-  <si>
-    <t>2조 3850억 5203만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>2조 1935억 9827만</t>
-  </si>
-  <si>
-    <t>하숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
-  </si>
-  <si>
-    <t>2조 367억 9637만</t>
-  </si>
-  <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 74억 73만</t>
-  </si>
-  <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 7507억 2465만</t>
-  </si>
-  <si>
-    <t>potato</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=potato</t>
-  </si>
-  <si>
-    <t>1조 4832억 5664만</t>
-  </si>
-  <si>
-    <t>양산호수공원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 3330억 2595만</t>
-  </si>
-  <si>
     <t>도레스</t>
   </si>
   <si>
@@ -1142,12 +1142,285 @@
     <t>1조 1839억 1961만</t>
   </si>
   <si>
+    <t>깔개73호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>78조 8073억 1735만</t>
+  </si>
+  <si>
+    <t>다정파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>49조 5207억 6718만</t>
+  </si>
+  <si>
+    <t>천상의빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>11조 3490억 4725만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>5조 9561억 7364만</t>
+  </si>
+  <si>
+    <t>남과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>5조 7457억 4288만</t>
+  </si>
+  <si>
+    <t>분함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
+  </si>
+  <si>
+    <t>3조 6371억 6189만</t>
+  </si>
+  <si>
+    <t>숭이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 9166억 6057만</t>
+  </si>
+  <si>
+    <t>기초수급좌파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 6547억 3128만</t>
+  </si>
+  <si>
+    <t>춘봉박2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
+  </si>
+  <si>
+    <t>1조 5673억 4102만</t>
+  </si>
+  <si>
+    <t>갓라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>1조 5405억 7815만</t>
+  </si>
+  <si>
+    <t>나폴리맛동산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1조 3291억 2549만</t>
+  </si>
+  <si>
+    <t>건브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>1조 3226억 6401만</t>
+  </si>
+  <si>
+    <t>망치든여자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>1조 2622억 9485만</t>
+  </si>
+  <si>
+    <t>독고패</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
+  </si>
+  <si>
+    <t>1조 1914억 3083만</t>
+  </si>
+  <si>
+    <t>마도훈이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 794억 4396만</t>
+  </si>
+  <si>
+    <t>선빵쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
+  </si>
+  <si>
+    <t>1조 209억 940만</t>
+  </si>
+  <si>
+    <t>어허오빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 58억 6815만</t>
+  </si>
+  <si>
+    <t>고지혈증</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
+  </si>
+  <si>
+    <t>9486억 7273만</t>
+  </si>
+  <si>
+    <t>I비숍I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
+  </si>
+  <si>
+    <t>9331억 5903만</t>
+  </si>
+  <si>
+    <t>힐링완이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8817억 6822만</t>
+  </si>
+  <si>
+    <t>남편이니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>7514억 7367만</t>
+  </si>
+  <si>
+    <t>왕구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>7021억 603만</t>
+  </si>
+  <si>
+    <t>만능도끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
+  </si>
+  <si>
+    <t>6698억 7563만</t>
+  </si>
+  <si>
+    <t>망치균이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6641억 2479만</t>
+  </si>
+  <si>
+    <t>후돌돌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
+  </si>
+  <si>
+    <t>3392억 3791만</t>
+  </si>
+  <si>
+    <t>이선호에용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>3263억 2615만</t>
+  </si>
+  <si>
+    <t>우유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>2925억 9662만</t>
+  </si>
+  <si>
+    <t>제육아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>2854억 8020만</t>
+  </si>
+  <si>
+    <t>굴화주민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2813억 8310만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
     <t>80조 1485억 4555만</t>
   </si>
   <si>
@@ -1229,9 +1502,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
     <t>1조 3170억 3660만</t>
   </si>
   <si>
@@ -1295,9 +1565,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
     <t>4260억 6750만</t>
   </si>
   <si>
@@ -1325,9 +1592,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
     <t>3871억 7997만</t>
   </si>
   <si>
@@ -1349,9 +1613,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
     <t>2860억 3607만</t>
   </si>
   <si>
@@ -1406,9 +1667,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
     <t>90</t>
   </si>
   <si>
@@ -1431,264 +1689,6 @@
   </si>
   <si>
     <t>1448억 449만</t>
-  </si>
-  <si>
-    <t>깔개73호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
-  </si>
-  <si>
-    <t>78조 8073억 1735만</t>
-  </si>
-  <si>
-    <t>다정파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>49조 5207억 6718만</t>
-  </si>
-  <si>
-    <t>천상의빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>11조 3490억 4725만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>5조 9561억 7364만</t>
-  </si>
-  <si>
-    <t>남과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>5조 7457억 4288만</t>
-  </si>
-  <si>
-    <t>분함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
-  </si>
-  <si>
-    <t>3조 6371억 6189만</t>
-  </si>
-  <si>
-    <t>숭이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 9166억 6057만</t>
-  </si>
-  <si>
-    <t>기초수급좌파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 6547억 3128만</t>
-  </si>
-  <si>
-    <t>춘봉박2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
-  </si>
-  <si>
-    <t>1조 5673억 4102만</t>
-  </si>
-  <si>
-    <t>갓라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>1조 5405억 7815만</t>
-  </si>
-  <si>
-    <t>나폴리맛동산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1조 3291억 2549만</t>
-  </si>
-  <si>
-    <t>건브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>1조 3226억 6401만</t>
-  </si>
-  <si>
-    <t>망치든여자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 2622억 9485만</t>
-  </si>
-  <si>
-    <t>독고패</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
-  </si>
-  <si>
-    <t>1조 1914억 3083만</t>
-  </si>
-  <si>
-    <t>마도훈이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 794억 4396만</t>
-  </si>
-  <si>
-    <t>선빵쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
-  </si>
-  <si>
-    <t>1조 209억 940만</t>
-  </si>
-  <si>
-    <t>어허오빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>1조 58억 6815만</t>
-  </si>
-  <si>
-    <t>고지혈증</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
-  </si>
-  <si>
-    <t>9486억 7273만</t>
-  </si>
-  <si>
-    <t>I비숍I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
-  </si>
-  <si>
-    <t>9331억 5903만</t>
-  </si>
-  <si>
-    <t>힐링완이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8817억 6822만</t>
-  </si>
-  <si>
-    <t>남편이니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>7514억 7367만</t>
-  </si>
-  <si>
-    <t>왕구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>7021억 603만</t>
-  </si>
-  <si>
-    <t>만능도끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
-  </si>
-  <si>
-    <t>6698억 7563만</t>
-  </si>
-  <si>
-    <t>망치균이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6641억 2479만</t>
-  </si>
-  <si>
-    <t>후돌돌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
-  </si>
-  <si>
-    <t>3392억 3791만</t>
-  </si>
-  <si>
-    <t>이선호에용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>3263억 2615만</t>
-  </si>
-  <si>
-    <t>우유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>2925억 9662만</t>
-  </si>
-  <si>
-    <t>제육아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>2854억 8020만</t>
-  </si>
-  <si>
-    <t>굴화주민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>2813억 8310만</t>
   </si>
 </sst>
 </file>
@@ -2328,7 +2328,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -2649,13 +2649,13 @@
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2666,22 +2666,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>108</v>
@@ -2745,13 +2745,13 @@
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2762,25 +2762,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -2809,13 +2809,13 @@
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2826,16 +2826,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
@@ -2844,10 +2844,10 @@
         <v>107</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2858,16 +2858,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -2876,7 +2876,7 @@
         <v>107</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>145</v>
@@ -2908,7 +2908,7 @@
         <v>70</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>149</v>
@@ -2940,7 +2940,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -3001,10 +3001,10 @@
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>126</v>
+        <v>144</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>161</v>
@@ -3036,7 +3036,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>140</v>
+        <v>108</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>165</v>
@@ -3065,10 +3065,10 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>169</v>
@@ -3100,7 +3100,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>108</v>
+        <v>139</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>173</v>
@@ -3129,10 +3129,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>177</v>
@@ -3164,7 +3164,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>181</v>
@@ -3196,7 +3196,7 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>185</v>
@@ -3228,7 +3228,7 @@
         <v>189</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>190</v>
@@ -3260,7 +3260,7 @@
         <v>77</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>135</v>
+        <v>108</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3289,52 +3289,20 @@
         <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>108</v>
+        <v>198</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3365,7 +3333,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3373,7 +3340,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J27"/>
+  <dimension ref="A1:J28"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3426,13 +3393,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>76</v>
@@ -3444,7 +3411,7 @@
         <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>206</v>
+        <v>202</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3458,13 +3425,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>207</v>
+        <v>203</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>208</v>
+        <v>204</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
@@ -3476,7 +3443,7 @@
         <v>108</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>209</v>
+        <v>205</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3490,13 +3457,13 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>210</v>
+        <v>206</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -3505,10 +3472,10 @@
         <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3522,13 +3489,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -3540,7 +3507,7 @@
         <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>215</v>
+        <v>211</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3554,25 +3521,25 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3586,25 +3553,25 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>113</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3624,19 +3591,19 @@
         <v>33</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3650,25 +3617,25 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3682,25 +3649,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3711,28 +3678,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3746,25 +3713,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3778,13 +3745,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -3796,7 +3763,7 @@
         <v>108</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3807,28 +3774,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3842,25 +3809,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3871,28 +3838,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3903,16 +3870,16 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -3921,10 +3888,10 @@
         <v>107</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3938,25 +3905,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>254</v>
+        <v>250</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3970,25 +3937,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>255</v>
+        <v>251</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>126</v>
+        <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4002,13 +3969,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
@@ -4017,10 +3984,10 @@
         <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4034,13 +4001,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>261</v>
+        <v>257</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>262</v>
+        <v>258</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
@@ -4052,7 +4019,7 @@
         <v>108</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4066,13 +4033,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>265</v>
+        <v>261</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -4081,10 +4048,10 @@
         <v>88</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4098,13 +4065,13 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>267</v>
+        <v>263</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>268</v>
+        <v>264</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
@@ -4116,7 +4083,7 @@
         <v>108</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4130,25 +4097,25 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>189</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4162,13 +4129,13 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>273</v>
+        <v>269</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>274</v>
+        <v>270</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
@@ -4177,10 +4144,10 @@
         <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4194,25 +4161,25 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>276</v>
+        <v>272</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>277</v>
+        <v>273</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4226,13 +4193,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -4241,17 +4208,49 @@
         <v>189</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>202</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J27"/>
+  <autoFilter ref="A1:J28"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4279,6 +4278,7 @@
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4345,7 +4345,7 @@
         <v>40</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4357,7 +4357,7 @@
         <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4371,13 +4371,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
@@ -4389,7 +4389,7 @@
         <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4403,13 +4403,13 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>287</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>287</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>288</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -4421,7 +4421,7 @@
         <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4435,13 +4435,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -4450,10 +4450,10 @@
         <v>77</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4467,13 +4467,13 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
@@ -4485,7 +4485,7 @@
         <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4499,13 +4499,13 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
@@ -4517,7 +4517,7 @@
         <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4531,13 +4531,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
@@ -4549,7 +4549,7 @@
         <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4563,13 +4563,13 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -4578,10 +4578,10 @@
         <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4595,25 +4595,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4624,28 +4624,28 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4659,25 +4659,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>311</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>312</v>
-      </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4691,25 +4691,25 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>314</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>315</v>
-      </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4720,16 +4720,16 @@
         <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>317</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
@@ -4738,10 +4738,10 @@
         <v>77</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4755,13 +4755,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
@@ -4773,7 +4773,7 @@
         <v>108</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4784,28 +4784,28 @@
         <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>324</v>
-      </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4816,28 +4816,28 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>326</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>117</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4851,25 +4851,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4883,13 +4883,13 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
@@ -4901,7 +4901,7 @@
         <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4915,13 +4915,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
@@ -4930,10 +4930,10 @@
         <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4947,13 +4947,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
@@ -4965,7 +4965,7 @@
         <v>108</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4979,13 +4979,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>341</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -4997,7 +4997,7 @@
         <v>108</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5011,25 +5011,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>344</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5043,13 +5043,13 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -5061,7 +5061,7 @@
         <v>108</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5075,13 +5075,13 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>350</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
@@ -5090,10 +5090,10 @@
         <v>107</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5107,13 +5107,13 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>353</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
@@ -5122,10 +5122,10 @@
         <v>82</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5139,13 +5139,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -5154,10 +5154,10 @@
         <v>82</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5171,13 +5171,13 @@
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>359</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
@@ -5186,10 +5186,10 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5203,13 +5203,13 @@
         <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
@@ -5218,10 +5218,10 @@
         <v>107</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5235,13 +5235,13 @@
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>364</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>365</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
@@ -5250,10 +5250,10 @@
         <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5264,7 +5264,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>367</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>368</v>
@@ -5282,7 +5282,7 @@
         <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>370</v>
@@ -5331,6 +5331,1018 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J30"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.7109375" customWidth="1"/>
+    <col min="2" max="2" width="22.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="5" max="5" width="50.7109375" customWidth="1"/>
+    <col min="6" max="8" width="12.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="10" max="10" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
+      <c r="A2" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
+      <c r="A3" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
+      <c r="A4" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>380</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="I7" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I8" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>399</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
+      <c r="A15" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I17" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="J17" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I18" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="J18" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I19" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="J19" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I20" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="J20" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I21" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I22" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="J22" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I23" s="2" t="s">
+        <v>438</v>
+      </c>
+      <c r="J23" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I24" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="J24" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I25" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="A26" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I28" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="J28" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J30"/>
+  <hyperlinks>
+    <hyperlink ref="E2" r:id="rId1"/>
+    <hyperlink ref="E3" r:id="rId2"/>
+    <hyperlink ref="E4" r:id="rId3"/>
+    <hyperlink ref="E5" r:id="rId4"/>
+    <hyperlink ref="E6" r:id="rId5"/>
+    <hyperlink ref="E7" r:id="rId6"/>
+    <hyperlink ref="E8" r:id="rId7"/>
+    <hyperlink ref="E9" r:id="rId8"/>
+    <hyperlink ref="E10" r:id="rId9"/>
+    <hyperlink ref="E11" r:id="rId10"/>
+    <hyperlink ref="E12" r:id="rId11"/>
+    <hyperlink ref="E13" r:id="rId12"/>
+    <hyperlink ref="E14" r:id="rId13"/>
+    <hyperlink ref="E15" r:id="rId14"/>
+    <hyperlink ref="E16" r:id="rId15"/>
+    <hyperlink ref="E17" r:id="rId16"/>
+    <hyperlink ref="E18" r:id="rId17"/>
+    <hyperlink ref="E19" r:id="rId18"/>
+    <hyperlink ref="E20" r:id="rId19"/>
+    <hyperlink ref="E21" r:id="rId20"/>
+    <hyperlink ref="E22" r:id="rId21"/>
+    <hyperlink ref="E23" r:id="rId22"/>
+    <hyperlink ref="E24" r:id="rId23"/>
+    <hyperlink ref="E25" r:id="rId24"/>
+    <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
+    <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
@@ -5378,19 +6390,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>371</v>
+        <v>463</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -5399,10 +6411,10 @@
         <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>373</v>
+        <v>464</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5410,19 +6422,19 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>374</v>
+        <v>465</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>374</v>
+        <v>465</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>375</v>
+        <v>466</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
@@ -5434,7 +6446,7 @@
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>376</v>
+        <v>467</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5442,19 +6454,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>377</v>
+        <v>468</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>377</v>
+        <v>468</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>378</v>
+        <v>469</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -5466,7 +6478,7 @@
         <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>379</v>
+        <v>470</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5474,19 +6486,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>380</v>
+        <v>471</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>472</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -5498,7 +6510,7 @@
         <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>382</v>
+        <v>473</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5506,19 +6518,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>474</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>383</v>
+        <v>474</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>384</v>
+        <v>475</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
@@ -5527,10 +6539,10 @@
         <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>385</v>
+        <v>476</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5538,19 +6550,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>386</v>
+        <v>477</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>387</v>
+        <v>478</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
@@ -5559,10 +6571,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>388</v>
+        <v>479</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5570,19 +6582,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>389</v>
+        <v>480</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>389</v>
+        <v>480</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>390</v>
+        <v>481</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
@@ -5591,10 +6603,10 @@
         <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>391</v>
+        <v>482</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5602,19 +6614,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>392</v>
+        <v>483</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>392</v>
+        <v>483</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>393</v>
+        <v>484</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -5623,10 +6635,10 @@
         <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>394</v>
+        <v>485</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5634,31 +6646,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>395</v>
+        <v>486</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>395</v>
+        <v>486</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>396</v>
+        <v>487</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>397</v>
+        <v>488</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5666,19 +6678,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>489</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>399</v>
+        <v>490</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
@@ -5687,10 +6699,10 @@
         <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>401</v>
+        <v>491</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5698,19 +6710,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>402</v>
+        <v>492</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>402</v>
+        <v>492</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>403</v>
+        <v>493</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
@@ -5719,10 +6731,10 @@
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>404</v>
+        <v>494</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5730,19 +6742,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>405</v>
+        <v>495</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>406</v>
+        <v>496</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -5751,10 +6763,10 @@
         <v>94</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>407</v>
+        <v>497</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5762,19 +6774,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>408</v>
+        <v>498</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>408</v>
+        <v>498</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>409</v>
+        <v>499</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
@@ -5783,10 +6795,10 @@
         <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>410</v>
+        <v>500</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5794,19 +6806,19 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>411</v>
+        <v>501</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>412</v>
+        <v>502</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
@@ -5815,10 +6827,10 @@
         <v>88</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>413</v>
+        <v>503</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5826,31 +6838,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>414</v>
+        <v>504</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>414</v>
+        <v>504</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>415</v>
+        <v>505</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>416</v>
+        <v>506</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5858,19 +6870,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>417</v>
+        <v>507</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>417</v>
+        <v>507</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>418</v>
+        <v>508</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -5879,10 +6891,10 @@
         <v>77</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>419</v>
+        <v>509</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5890,19 +6902,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>420</v>
+        <v>510</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>421</v>
+        <v>511</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
@@ -5911,10 +6923,10 @@
         <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>423</v>
+        <v>512</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5922,19 +6934,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>424</v>
+        <v>513</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>425</v>
+        <v>514</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
@@ -5943,10 +6955,10 @@
         <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>400</v>
+        <v>422</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>426</v>
+        <v>515</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5954,19 +6966,19 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>427</v>
+        <v>516</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>427</v>
+        <v>516</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>428</v>
+        <v>517</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
@@ -5975,10 +6987,10 @@
         <v>107</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>429</v>
+        <v>518</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5986,19 +6998,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>430</v>
+        <v>519</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>430</v>
+        <v>519</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>431</v>
+        <v>520</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
@@ -6007,10 +7019,10 @@
         <v>107</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>433</v>
+        <v>521</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6018,31 +7030,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>434</v>
+        <v>522</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>434</v>
+        <v>522</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>435</v>
+        <v>523</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>437</v>
+        <v>525</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6050,19 +7062,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>438</v>
+        <v>526</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>438</v>
+        <v>526</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>439</v>
+        <v>527</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
@@ -6071,10 +7083,10 @@
         <v>88</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>440</v>
+        <v>461</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>441</v>
+        <v>528</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6082,19 +7094,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>442</v>
+        <v>529</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>442</v>
+        <v>529</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>443</v>
+        <v>530</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -6103,10 +7115,10 @@
         <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>422</v>
+        <v>409</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>444</v>
+        <v>531</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6114,19 +7126,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>445</v>
+        <v>532</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>445</v>
+        <v>532</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>446</v>
+        <v>533</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
@@ -6135,10 +7147,10 @@
         <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>447</v>
+        <v>534</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6146,19 +7158,19 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>448</v>
+        <v>535</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>449</v>
+        <v>536</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
@@ -6167,10 +7179,10 @@
         <v>77</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>450</v>
+        <v>537</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6178,19 +7190,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>451</v>
+        <v>538</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>452</v>
+        <v>539</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -6199,10 +7211,10 @@
         <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>453</v>
+        <v>540</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6210,19 +7222,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>454</v>
+        <v>541</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>454</v>
+        <v>541</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>455</v>
+        <v>542</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
@@ -6231,10 +7243,10 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>456</v>
+        <v>543</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6242,31 +7254,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="H29" s="2" t="s">
-        <v>460</v>
+        <v>546</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>461</v>
+        <v>547</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6274,19 +7286,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>462</v>
+        <v>548</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>462</v>
+        <v>548</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>463</v>
+        <v>549</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
@@ -6295,10 +7307,10 @@
         <v>107</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>436</v>
+        <v>524</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>464</v>
+        <v>550</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6306,19 +7318,19 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>367</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>465</v>
+        <v>551</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>466</v>
+        <v>552</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>76</v>
@@ -6327,10 +7339,10 @@
         <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>432</v>
+        <v>450</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>467</v>
+        <v>553</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6372,1016 +7384,4 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="12.7109375" customWidth="1"/>
-    <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
-    <col min="5" max="5" width="50.7109375" customWidth="1"/>
-    <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:10">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
-      <c r="A2" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
-      <c r="A3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3" s="2" t="s">
-        <v>73</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
-      <c r="A4" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="J4" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
-      <c r="A5" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>481</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
-      <c r="A7" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="J7" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
-      <c r="A8" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B8" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
-      <c r="A9" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
-      <c r="A10" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>493</v>
-      </c>
-      <c r="J10" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B11" s="2" t="s">
-        <v>114</v>
-      </c>
-      <c r="C11" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>496</v>
-      </c>
-      <c r="J11" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="J12" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>501</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>502</v>
-      </c>
-      <c r="J13" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>504</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="J14" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>507</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>508</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>511</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="J17" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>517</v>
-      </c>
-      <c r="J18" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>520</v>
-      </c>
-      <c r="J19" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>522</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="J20" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>525</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>529</v>
-      </c>
-      <c r="J22" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>531</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="J23" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>174</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>538</v>
-      </c>
-      <c r="J25" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>540</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>400</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>541</v>
-      </c>
-      <c r="J26" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>182</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>543</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>546</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>547</v>
-      </c>
-      <c r="J28" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>549</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>550</v>
-      </c>
-      <c r="J29" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>552</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-  </sheetData>
-  <autoFilter ref="A1:J30"/>
-  <hyperlinks>
-    <hyperlink ref="E2" r:id="rId1"/>
-    <hyperlink ref="E3" r:id="rId2"/>
-    <hyperlink ref="E4" r:id="rId3"/>
-    <hyperlink ref="E5" r:id="rId4"/>
-    <hyperlink ref="E6" r:id="rId5"/>
-    <hyperlink ref="E7" r:id="rId6"/>
-    <hyperlink ref="E8" r:id="rId7"/>
-    <hyperlink ref="E9" r:id="rId8"/>
-    <hyperlink ref="E10" r:id="rId9"/>
-    <hyperlink ref="E11" r:id="rId10"/>
-    <hyperlink ref="E12" r:id="rId11"/>
-    <hyperlink ref="E13" r:id="rId12"/>
-    <hyperlink ref="E14" r:id="rId13"/>
-    <hyperlink ref="E15" r:id="rId14"/>
-    <hyperlink ref="E16" r:id="rId15"/>
-    <hyperlink ref="E17" r:id="rId16"/>
-    <hyperlink ref="E18" r:id="rId17"/>
-    <hyperlink ref="E19" r:id="rId18"/>
-    <hyperlink ref="E20" r:id="rId19"/>
-    <hyperlink ref="E21" r:id="rId20"/>
-    <hyperlink ref="E22" r:id="rId21"/>
-    <hyperlink ref="E23" r:id="rId22"/>
-    <hyperlink ref="E24" r:id="rId23"/>
-    <hyperlink ref="E25" r:id="rId24"/>
-    <hyperlink ref="E26" r:id="rId25"/>
-    <hyperlink ref="E27" r:id="rId26"/>
-    <hyperlink ref="E28" r:id="rId27"/>
-    <hyperlink ref="E29" r:id="rId28"/>
-    <hyperlink ref="E30" r:id="rId29"/>
-  </hyperlinks>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -11,23 +11,23 @@
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="Kali" sheetId="3" r:id="rId3"/>
     <sheet name="숑숑" sheetId="4" r:id="rId4"/>
-    <sheet name="쌈뽕" sheetId="5" r:id="rId5"/>
-    <sheet name="채금" sheetId="6" r:id="rId6"/>
+    <sheet name="채금" sheetId="5" r:id="rId5"/>
+    <sheet name="쌈뽕" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$30</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">채금!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">쌈뽕!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">채금!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1578" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="559">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,70 +80,73 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>381</t>
+    <t>390</t>
+  </si>
+  <si>
+    <t>13위</t>
+  </si>
+  <si>
+    <t>Lv.8</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>172조 8970억 7998만</t>
+  </si>
+  <si>
+    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
+  </si>
+  <si>
+    <t>망겜감별사</t>
+  </si>
+  <si>
+    <t>2026.04.19</t>
+  </si>
+  <si>
+    <t>Kali</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=Kali</t>
+  </si>
+  <si>
+    <t>Scania 13</t>
+  </si>
+  <si>
+    <t>361</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>28명</t>
+  </si>
+  <si>
+    <t>196조 1458억 5121만</t>
+  </si>
+  <si>
+    <t>토벌전 4위 kali 칼리길드 2조이상 함께 성장하실 신규인원 모집합니다 많은 관심 부탁드립니</t>
+  </si>
+  <si>
+    <t>마삐아</t>
+  </si>
+  <si>
+    <t>숑숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
+  </si>
+  <si>
+    <t>387</t>
   </si>
   <si>
     <t>12위</t>
   </si>
   <si>
-    <t>Lv.8</t>
-  </si>
-  <si>
     <t>30명</t>
   </si>
   <si>
-    <t>171조 8825억 4334만</t>
-  </si>
-  <si>
-    <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
-  </si>
-  <si>
-    <t>망겜감별사</t>
-  </si>
-  <si>
-    <t>2026.04.17</t>
-  </si>
-  <si>
-    <t>Kali</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=Kali</t>
-  </si>
-  <si>
-    <t>Scania 13</t>
-  </si>
-  <si>
-    <t>364</t>
-  </si>
-  <si>
-    <t>14위</t>
-  </si>
-  <si>
-    <t>27명</t>
-  </si>
-  <si>
-    <t>185조 938억 8372만</t>
-  </si>
-  <si>
-    <t>토벌전 4위 kali 칼리길드 2조이상 함께 성장하실 신규인원 모집합니다 많은 관심 부탁드립니</t>
-  </si>
-  <si>
-    <t>마삐아</t>
-  </si>
-  <si>
-    <t>숑숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
-  </si>
-  <si>
-    <t>389</t>
-  </si>
-  <si>
-    <t>13위</t>
-  </si>
-  <si>
-    <t>166조 473억 3111만</t>
+    <t>176조 5464억 5925만</t>
   </si>
   <si>
     <t>소통 잘하시는분들 환영! 투력1조이상! 가입 전 꼭 귓문의 부탁드려용 문의는(강린)</t>
@@ -152,6 +155,33 @@
     <t>숑이</t>
   </si>
   <si>
+    <t>채금</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B1%84%EA%B8%88</t>
+  </si>
+  <si>
+    <t>Scania 29</t>
+  </si>
+  <si>
+    <t>369</t>
+  </si>
+  <si>
+    <t>10위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>185조 3031억 5251만</t>
+  </si>
+  <si>
+    <t>안녕하세요 채금길드입니다. 공지사항 꼭 필수로 지켜주세요!</t>
+  </si>
+  <si>
+    <t>역뢰</t>
+  </si>
+  <si>
     <t>쌈뽕</t>
   </si>
   <si>
@@ -161,16 +191,13 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>32위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>181조 9602억 7867만</t>
+    <t>372</t>
+  </si>
+  <si>
+    <t>31위</t>
+  </si>
+  <si>
+    <t>183조 7878억 5998만</t>
   </si>
   <si>
     <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
@@ -179,33 +206,6 @@
     <t>장정근</t>
   </si>
   <si>
-    <t>채금</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B1%84%EA%B8%88</t>
-  </si>
-  <si>
-    <t>Scania 29</t>
-  </si>
-  <si>
-    <t>371</t>
-  </si>
-  <si>
-    <t>10위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>179조 9543억 1541만</t>
-  </si>
-  <si>
-    <t>안녕하세요 채금길드입니다. 공지사항 꼭 필수로 지켜주세요!</t>
-  </si>
-  <si>
-    <t>역뢰</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -245,7 +245,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>22조 7699억 4133만</t>
+    <t>23조 641억 4651만</t>
   </si>
   <si>
     <t>2</t>
@@ -287,6 +287,24 @@
     <t>4</t>
   </si>
   <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>12조 8368억 6384만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>킹몬</t>
   </si>
   <si>
@@ -296,27 +314,9 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>12조 6365억 3160만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>12조 251억 6196만</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -338,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>6조 9158억 4470만</t>
+    <t>7조 1232억 2869만</t>
   </si>
   <si>
     <t>8</t>
@@ -362,6 +362,18 @@
     <t>9</t>
   </si>
   <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>6조 1164억 6608만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>반도</t>
   </si>
   <si>
@@ -371,19 +383,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>5조 7798억 2930만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>5조 5324억 9799만</t>
+    <t>5조 9591억 5169만</t>
   </si>
   <si>
     <t>11</t>
@@ -395,7 +395,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 9239억 3208만</t>
+    <t>4조 9286억 68만</t>
   </si>
   <si>
     <t>12</t>
@@ -407,7 +407,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 3189억 8200만</t>
+    <t>4조 4114억 7192만</t>
   </si>
   <si>
     <t>13</t>
@@ -422,7 +422,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 2090억 334만</t>
+    <t>4조 2568억 4863만</t>
   </si>
   <si>
     <t>14</t>
@@ -449,12 +449,24 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 7011억 1668만</t>
+    <t>3조 7219억 6524만</t>
   </si>
   <si>
     <t>16</t>
   </si>
   <si>
+    <t>강철고튠데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>3조 6838억 5909만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
@@ -464,10 +476,10 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 6112억 850만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>3조 6572억 2213만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -479,7 +491,7 @@
     <t>3조 5006억 2017만</t>
   </si>
   <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -491,7 +503,7 @@
     <t>3조 3744억 7808만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -500,10 +512,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>2조 8438억 7638만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>3조 316억 6665만</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -515,7 +527,7 @@
     <t>2조 7646억 9816만</t>
   </si>
   <si>
-    <t>21</t>
+    <t>22</t>
   </si>
   <si>
     <t>여븨</t>
@@ -524,19 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 5691억 3500만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>2조 5595억 2만</t>
+    <t>2조 6571억 479만</t>
   </si>
   <si>
     <t>23</t>
@@ -548,7 +548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2조 2322억 7931만</t>
+    <t>2조 2590억 8270만</t>
   </si>
   <si>
     <t>24</t>
@@ -578,6 +578,21 @@
     <t>26</t>
   </si>
   <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>2조 721억 7045만</t>
+  </si>
+  <si>
+    <t>27</t>
+  </si>
+  <si>
     <t>플로우00</t>
   </si>
   <si>
@@ -587,21 +602,6 @@
     <t>2조 663억 1201만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>2조 123억 3425만</t>
-  </si>
-  <si>
     <t>28</t>
   </si>
   <si>
@@ -611,7 +611,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>1조 8260억 5446만</t>
+    <t>1조 8338억 6575만</t>
   </si>
   <si>
     <t>29</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
   </si>
   <si>
-    <t>39조 2810억 3527만</t>
+    <t>54조 4254억 6928만</t>
   </si>
   <si>
     <t>니니니닉</t>
@@ -644,7 +644,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
   </si>
   <si>
-    <t>14조 3084억 1761만</t>
+    <t>17조 9330억 2509만</t>
+  </si>
+  <si>
+    <t>태태아방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>10조 9987억 69만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>10조 411억 1296만</t>
   </si>
   <si>
     <t>뤄드</t>
@@ -656,22 +674,13 @@
     <t>9조 2003억 1997만</t>
   </si>
   <si>
-    <t>태태아방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>8조 4957억 2889만</t>
-  </si>
-  <si>
     <t>롱노즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
   </si>
   <si>
-    <t>7조 7367억 9818만</t>
+    <t>7조 8027억 3811만</t>
   </si>
   <si>
     <t>주요엘농산</t>
@@ -680,16 +689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
   </si>
   <si>
-    <t>6조 9130억 7586만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>6조 7975억 2029만</t>
+    <t>6조 9792억 5346만</t>
   </si>
   <si>
     <t>삼치김치찜</t>
@@ -707,7 +707,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
   </si>
   <si>
-    <t>5조 5509억 2697만</t>
+    <t>6조 2855억 9823만</t>
+  </si>
+  <si>
+    <t>AI루미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>5조 5427억 5727만</t>
   </si>
   <si>
     <t>약한디</t>
@@ -725,7 +734,7 @@
     <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
   </si>
   <si>
-    <t>5조 3482억 55만</t>
+    <t>5조 3686억 6294만</t>
   </si>
   <si>
     <t>조지선</t>
@@ -737,15 +746,6 @@
     <t>5조 1623억 2192만</t>
   </si>
   <si>
-    <t>AI루미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>5조 818억 5256만</t>
-  </si>
-  <si>
     <t>사당행</t>
   </si>
   <si>
@@ -779,7 +779,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
   </si>
   <si>
-    <t>3조 9897억 2659만</t>
+    <t>4조 152억 1170만</t>
+  </si>
+  <si>
+    <t>전통한우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%86%B5%ED%95%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>3조 8267억 3011만</t>
   </si>
   <si>
     <t>석종</t>
@@ -788,7 +797,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
   </si>
   <si>
-    <t>3조 2905억 1139만</t>
+    <t>3조 3604억 7751만</t>
   </si>
   <si>
     <t>Pixy</t>
@@ -800,22 +809,22 @@
     <t>3조 376억 9729만</t>
   </si>
   <si>
+    <t>겨농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
+  </si>
+  <si>
+    <t>2조 7618억 6020만</t>
+  </si>
+  <si>
     <t>채빛</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
   </si>
   <si>
-    <t>2조 4663억 2375만</t>
-  </si>
-  <si>
-    <t>겨농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
-  </si>
-  <si>
-    <t>2조 3597억 3925만</t>
+    <t>2조 6949억 5357만</t>
   </si>
   <si>
     <t>히미노</t>
@@ -833,7 +842,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
   </si>
   <si>
-    <t>2조 2396억 7990만</t>
+    <t>2조 2439억 5677만</t>
   </si>
   <si>
     <t>킴머웅</t>
@@ -875,7 +884,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
   </si>
   <si>
-    <t>39조 4651억 8162만</t>
+    <t>104</t>
+  </si>
+  <si>
+    <t>40조 2505억 462만</t>
   </si>
   <si>
     <t>소독약</t>
@@ -884,7 +896,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
   </si>
   <si>
-    <t>15조 1317억 316만</t>
+    <t>15조 2296억 9794만</t>
   </si>
   <si>
     <t>주존사</t>
@@ -902,7 +914,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
   </si>
   <si>
-    <t>8조 6331억 9927만</t>
+    <t>9조 2382억 9399만</t>
   </si>
   <si>
     <t>무피</t>
@@ -911,7 +923,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
   </si>
   <si>
-    <t>7조 8201억 9257만</t>
+    <t>8조 9505억 9058만</t>
   </si>
   <si>
     <t>캐서린</t>
@@ -929,7 +941,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
   </si>
   <si>
-    <t>6조 479억 7569만</t>
+    <t>6조 4068억 7161만</t>
   </si>
   <si>
     <t>슈웃</t>
@@ -938,7 +950,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
   </si>
   <si>
-    <t>5조 9520억 8440만</t>
+    <t>5조 9822억 3121만</t>
   </si>
   <si>
     <t>빡박이</t>
@@ -947,7 +959,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 4044억 7879만</t>
+    <t>5조 6913억 7437만</t>
   </si>
   <si>
     <t>임나연</t>
@@ -956,7 +968,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
   </si>
   <si>
-    <t>5조 2628억 1749만</t>
+    <t>5조 2733억 7581만</t>
   </si>
   <si>
     <t>강린</t>
@@ -974,7 +986,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
   </si>
   <si>
-    <t>4조 4792억 5669만</t>
+    <t>4조 8438억 9104만</t>
   </si>
   <si>
     <t>스파토이</t>
@@ -992,7 +1004,7 @@
     <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
   </si>
   <si>
-    <t>3조 5728억 1195만</t>
+    <t>3조 5862억 5239만</t>
   </si>
   <si>
     <t>픽홀로</t>
@@ -1001,7 +1013,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
   </si>
   <si>
-    <t>3조 4727억 2206만</t>
+    <t>3조 5343억 2166만</t>
   </si>
   <si>
     <t>Rania</t>
@@ -1013,13 +1025,22 @@
     <t>3조 4486억 9673만</t>
   </si>
   <si>
+    <t>베르1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
+  </si>
+  <si>
+    <t>3조 2821억 7435만</t>
+  </si>
+  <si>
     <t>쟈라</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
   </si>
   <si>
-    <t>3조 2195억 1007만</t>
+    <t>3조 2359억 4543만</t>
   </si>
   <si>
     <t>미진생</t>
@@ -1028,7 +1049,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
   </si>
   <si>
-    <t>2조 9519억 3003만</t>
+    <t>3조 1216억 9132만</t>
+  </si>
+  <si>
+    <t>쟁반짜장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3조 431억 2870만</t>
   </si>
   <si>
     <t>Uhani</t>
@@ -1040,31 +1070,22 @@
     <t>2조 8490억 4859만</t>
   </si>
   <si>
-    <t>베르1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
-  </si>
-  <si>
-    <t>2조 8254억 9759만</t>
-  </si>
-  <si>
     <t>바세린</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
   </si>
   <si>
-    <t>2조 8084억 6646만</t>
-  </si>
-  <si>
-    <t>쟁반짜장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>2조 5842억 993만</t>
+    <t>2조 8267억 4354만</t>
+  </si>
+  <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 6656억 6767만</t>
   </si>
   <si>
     <t>별렉스b</t>
@@ -1073,7 +1094,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
   </si>
   <si>
-    <t>2조 5328억 6439만</t>
+    <t>2조 6092억 6019만</t>
   </si>
   <si>
     <t>깅궁둥</t>
@@ -1082,16 +1103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
   </si>
   <si>
-    <t>2조 3781억 3063만</t>
-  </si>
-  <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 878억 617만</t>
+    <t>2조 5912억 5139만</t>
   </si>
   <si>
     <t>하숑</t>
@@ -1109,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 8281억 425만</t>
+    <t>1조 8386억 8160만</t>
   </si>
   <si>
     <t>potato</t>
@@ -1127,7 +1139,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
   </si>
   <si>
-    <t>1조 3890억 1669만</t>
+    <t>1조 4062억 4984만</t>
   </si>
   <si>
     <t>30</t>
@@ -1139,7 +1151,292 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
   </si>
   <si>
-    <t>1조 1839억 1961만</t>
+    <t>1조 3209억 8583만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
+  </si>
+  <si>
+    <t>80조 1485억 4555만</t>
+  </si>
+  <si>
+    <t>쭈딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
+  </si>
+  <si>
+    <t>44조 9583억 1185만</t>
+  </si>
+  <si>
+    <t>퀸이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>22조 4976억 7059만</t>
+  </si>
+  <si>
+    <t>나는숭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EC%88%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>12조 1238억 4073만</t>
+  </si>
+  <si>
+    <t>으캬앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
+  </si>
+  <si>
+    <t>5조 802억 2326만</t>
+  </si>
+  <si>
+    <t>용두산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
+  </si>
+  <si>
+    <t>3조 4741억 1825만</t>
+  </si>
+  <si>
+    <t>형뱁새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
+  </si>
+  <si>
+    <t>3조 4135억 4059만</t>
+  </si>
+  <si>
+    <t>수컹수컹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
+  </si>
+  <si>
+    <t>1조 5561억 8483만</t>
+  </si>
+  <si>
+    <t>팽됴리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%BD%EB%90%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1조 5492억 5497만</t>
+  </si>
+  <si>
+    <t>꾜뀨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
+  </si>
+  <si>
+    <t>1조 4825억 9042만</t>
+  </si>
+  <si>
+    <t>점검중임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1조 751억 130만</t>
+  </si>
+  <si>
+    <t>비비보람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>1조 535억 532만</t>
+  </si>
+  <si>
+    <t>장헌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
+  </si>
+  <si>
+    <t>8474억 6346만</t>
+  </si>
+  <si>
+    <t>메쓰가키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%93%B0%EA%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>8295억 3279만</t>
+  </si>
+  <si>
+    <t>뿌뿝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>5215억 1110만</t>
+  </si>
+  <si>
+    <t>다시스타투</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
+  </si>
+  <si>
+    <t>5116억 4071만</t>
+  </si>
+  <si>
+    <t>곰굼곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>4799억 5631만</t>
+  </si>
+  <si>
+    <t>쉬누2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EB%88%842</t>
+  </si>
+  <si>
+    <t>4755억 4148만</t>
+  </si>
+  <si>
+    <t>신똥은원딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
+  </si>
+  <si>
+    <t>4713억 3098만</t>
+  </si>
+  <si>
+    <t>난뭉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%AD%89</t>
+  </si>
+  <si>
+    <t>4063억 6955만</t>
+  </si>
+  <si>
+    <t>만칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>3989억 2356만</t>
+  </si>
+  <si>
+    <t>박오팔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%A4%ED%8C%94</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>3345억 3597만</t>
+  </si>
+  <si>
+    <t>해피킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>3151억 2021만</t>
+  </si>
+  <si>
+    <t>쌀유건</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2769억 4945만</t>
+  </si>
+  <si>
+    <t>문현준2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%ED%98%84%EC%A4%802</t>
+  </si>
+  <si>
+    <t>2637억 6649만</t>
+  </si>
+  <si>
+    <t>정다몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>2151억 6189만</t>
+  </si>
+  <si>
+    <t>쌀코볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>1966억 5195만</t>
+  </si>
+  <si>
+    <t>팔라완</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>1824억 1756만</t>
+  </si>
+  <si>
+    <t>해피퀸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
+  </si>
+  <si>
+    <t>1814억 8997만</t>
+  </si>
+  <si>
+    <t>왕필</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%95%84</t>
+  </si>
+  <si>
+    <t>1688억 9471만</t>
   </si>
   <si>
     <t>깔개73호</t>
@@ -1148,10 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>78조 8073억 1735만</t>
+    <t>79조 646억 6977만</t>
   </si>
   <si>
     <t>다정파파</t>
@@ -1169,13 +1463,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
   </si>
   <si>
-    <t>11조 3490억 4725만</t>
+    <t>11조 7274억 5785만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
   </si>
   <si>
-    <t>5조 9561억 7364만</t>
+    <t>6조 1081억 6659만</t>
   </si>
   <si>
     <t>남과장</t>
@@ -1184,7 +1478,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
   </si>
   <si>
-    <t>5조 7457억 4288만</t>
+    <t>5조 7760억 8358만</t>
   </si>
   <si>
     <t>분함</t>
@@ -1202,7 +1496,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
   </si>
   <si>
-    <t>2조 9166억 6057만</t>
+    <t>2조 9582억 1913만</t>
   </si>
   <si>
     <t>기초수급좌파</t>
@@ -1214,13 +1508,22 @@
     <t>2조 6547억 3128만</t>
   </si>
   <si>
+    <t>늑멍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
+  </si>
+  <si>
+    <t>2조 6062억 690만</t>
+  </si>
+  <si>
     <t>춘봉박2</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
   </si>
   <si>
-    <t>1조 5673억 4102만</t>
+    <t>1조 6837억 1388만</t>
   </si>
   <si>
     <t>갓라딘</t>
@@ -1232,22 +1535,22 @@
     <t>1조 5405억 7815만</t>
   </si>
   <si>
+    <t>건브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>1조 4667억 2641만</t>
+  </si>
+  <si>
     <t>나폴리맛동산</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
   </si>
   <si>
-    <t>1조 3291억 2549만</t>
-  </si>
-  <si>
-    <t>건브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>1조 3226억 6401만</t>
+    <t>1조 4184억 8397만</t>
   </si>
   <si>
     <t>망치든여자</t>
@@ -1256,10 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
   </si>
   <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>1조 2622억 9485만</t>
+    <t>1조 3391억 6610만</t>
   </si>
   <si>
     <t>독고패</t>
@@ -1268,7 +1568,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
   </si>
   <si>
-    <t>1조 1914억 3083만</t>
+    <t>1조 2421억 1576만</t>
+  </si>
+  <si>
+    <t>I비숍I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
+  </si>
+  <si>
+    <t>1조 1523억 9005만</t>
+  </si>
+  <si>
+    <t>힐링완이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 1510억 7576만</t>
   </si>
   <si>
     <t>마도훈이</t>
@@ -1277,7 +1595,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 794억 4396만</t>
+    <t>1조 877억 886만</t>
   </si>
   <si>
     <t>선빵쳐</t>
@@ -1286,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
   </si>
   <si>
-    <t>1조 209억 940만</t>
+    <t>1조 525억 5220만</t>
   </si>
   <si>
     <t>어허오빠</t>
@@ -1295,10 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>1조 58억 6815만</t>
+    <t>1조 75억 6364만</t>
   </si>
   <si>
     <t>고지혈증</t>
@@ -1307,25 +1622,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
   </si>
   <si>
-    <t>9486억 7273만</t>
-  </si>
-  <si>
-    <t>I비숍I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
-  </si>
-  <si>
-    <t>9331억 5903만</t>
-  </si>
-  <si>
-    <t>힐링완이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8817억 6822만</t>
+    <t>9749억 734만</t>
+  </si>
+  <si>
+    <t>왕구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>8755억 696만</t>
   </si>
   <si>
     <t>남편이니</t>
@@ -1334,16 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
   </si>
   <si>
-    <t>7514억 7367만</t>
-  </si>
-  <si>
-    <t>왕구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>7021억 603만</t>
+    <t>7538억 292만</t>
   </si>
   <si>
     <t>만능도끼</t>
@@ -1352,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
   </si>
   <si>
-    <t>6698억 7563만</t>
+    <t>6776억 5098만</t>
   </si>
   <si>
     <t>망치균이</t>
@@ -1370,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
   </si>
   <si>
-    <t>3392억 3791만</t>
+    <t>4906억 1481만</t>
   </si>
   <si>
     <t>이선호에용</t>
@@ -1379,10 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
   </si>
   <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>3263억 2615만</t>
+    <t>3280억 8417만</t>
   </si>
   <si>
     <t>우유나</t>
@@ -1391,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
   </si>
   <si>
-    <t>2925억 9662만</t>
+    <t>2955억 4772만</t>
   </si>
   <si>
     <t>제육아저씨</t>
@@ -1400,10 +1694,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
   </si>
   <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>2854억 8020만</t>
+    <t>2898억 6575만</t>
   </si>
   <si>
     <t>굴화주민</t>
@@ -1412,283 +1703,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
     <t>2813억 8310만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
-  </si>
-  <si>
-    <t>80조 1485억 4555만</t>
-  </si>
-  <si>
-    <t>쭈딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
-  </si>
-  <si>
-    <t>41조 5529억 3436만</t>
-  </si>
-  <si>
-    <t>퀸이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>22조 4976억 7059만</t>
-  </si>
-  <si>
-    <t>나는숭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EC%88%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 1238억 4073만</t>
-  </si>
-  <si>
-    <t>으캬앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
-  </si>
-  <si>
-    <t>4조 2793억 333만</t>
-  </si>
-  <si>
-    <t>용두산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
-  </si>
-  <si>
-    <t>3조 4741억 1825만</t>
-  </si>
-  <si>
-    <t>형뱁새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
-  </si>
-  <si>
-    <t>3조 1098억 4897만</t>
-  </si>
-  <si>
-    <t>팽됴리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%BD%EB%90%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 5492억 5497만</t>
-  </si>
-  <si>
-    <t>수컹수컹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
-  </si>
-  <si>
-    <t>1조 4464억 2만</t>
-  </si>
-  <si>
-    <t>꾜뀨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
-  </si>
-  <si>
-    <t>1조 3170억 3660만</t>
-  </si>
-  <si>
-    <t>점검중임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
-  </si>
-  <si>
-    <t>9251억 9712만</t>
-  </si>
-  <si>
-    <t>비비보람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>9249억 7328만</t>
-  </si>
-  <si>
-    <t>장헌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
-  </si>
-  <si>
-    <t>8474억 6346만</t>
-  </si>
-  <si>
-    <t>메쓰가키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%93%B0%EA%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>6016억 1844만</t>
-  </si>
-  <si>
-    <t>뿌뿝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
-  </si>
-  <si>
-    <t>5139억 1251만</t>
-  </si>
-  <si>
-    <t>신똥은원딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
-  </si>
-  <si>
-    <t>4638억 4380만</t>
-  </si>
-  <si>
-    <t>다시스타투</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
-  </si>
-  <si>
-    <t>4260억 6750만</t>
-  </si>
-  <si>
-    <t>난뭉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%AD%89</t>
-  </si>
-  <si>
-    <t>4063억 6955만</t>
-  </si>
-  <si>
-    <t>만칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>3887억 7987만</t>
-  </si>
-  <si>
-    <t>곰굼곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>3871억 7997만</t>
-  </si>
-  <si>
-    <t>박오팔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%A4%ED%8C%94</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>3240억 2807만</t>
-  </si>
-  <si>
-    <t>해피킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
-  </si>
-  <si>
-    <t>2860억 3607만</t>
-  </si>
-  <si>
-    <t>쉬누2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EB%88%842</t>
-  </si>
-  <si>
-    <t>2711억 90만</t>
-  </si>
-  <si>
-    <t>문현준2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%ED%98%84%EC%A4%802</t>
-  </si>
-  <si>
-    <t>2637억 6649만</t>
-  </si>
-  <si>
-    <t>쌀유건</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
-  </si>
-  <si>
-    <t>2322억 2832만</t>
-  </si>
-  <si>
-    <t>정다몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>2037억 8277만</t>
-  </si>
-  <si>
-    <t>쌀코볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>1769억 2747만</t>
-  </si>
-  <si>
-    <t>팔라완</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1672억 9392만</t>
-  </si>
-  <si>
-    <t>왕필</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%95%84</t>
-  </si>
-  <si>
-    <t>1659억 9282만</t>
-  </si>
-  <si>
-    <t>해피퀸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
-  </si>
-  <si>
-    <t>1448억 449만</t>
   </si>
 </sst>
 </file>
@@ -2216,16 +2231,16 @@
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2233,40 +2248,40 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>42</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>41</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2274,31 +2289,31 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>51</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>20</v>
+        <v>38</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>56</v>
@@ -2553,7 +2568,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>71</v>
@@ -2585,7 +2600,7 @@
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>89</v>
@@ -2649,13 +2664,13 @@
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2666,22 +2681,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>108</v>
@@ -2713,7 +2728,7 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>108</v>
@@ -2873,13 +2888,13 @@
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2890,25 +2905,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>130</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>149</v>
@@ -2940,7 +2955,7 @@
         <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -2969,7 +2984,7 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>108</v>
@@ -3001,10 +3016,10 @@
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>161</v>
@@ -3036,7 +3051,7 @@
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>165</v>
@@ -3065,10 +3080,10 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>130</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>169</v>
@@ -3193,13 +3208,13 @@
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>185</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3210,25 +3225,25 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>190</v>
@@ -3340,7 +3355,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J28"/>
+  <dimension ref="A1:J29"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3408,7 +3423,7 @@
         <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>202</v>
@@ -3440,7 +3455,7 @@
         <v>107</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>205</v>
@@ -3472,7 +3487,7 @@
         <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>208</v>
@@ -3489,22 +3504,22 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>211</v>
@@ -3533,10 +3548,10 @@
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>214</v>
@@ -3565,7 +3580,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>113</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>108</v>
@@ -3585,19 +3600,19 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>33</v>
+        <v>218</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>219</v>
+        <v>117</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>108</v>
@@ -3632,7 +3647,7 @@
         <v>107</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>223</v>
@@ -3664,7 +3679,7 @@
         <v>77</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>226</v>
@@ -3678,7 +3693,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>227</v>
@@ -3693,7 +3708,7 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>108</v>
@@ -3725,7 +3740,7 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>108</v>
@@ -3789,10 +3804,10 @@
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>238</v>
@@ -3902,7 +3917,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>248</v>
@@ -3917,7 +3932,7 @@
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>130</v>
@@ -3949,10 +3964,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>253</v>
@@ -3981,10 +3996,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>256</v>
@@ -4016,7 +4031,7 @@
         <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>259</v>
@@ -4045,10 +4060,10 @@
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>262</v>
@@ -4077,7 +4092,7 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>82</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>108</v>
@@ -4109,10 +4124,10 @@
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>189</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>139</v>
+        <v>108</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>268</v>
@@ -4141,10 +4156,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>185</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>271</v>
@@ -4176,7 +4191,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>274</v>
@@ -4205,10 +4220,10 @@
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>189</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>277</v>
@@ -4222,7 +4237,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>278</v>
@@ -4237,10 +4252,10 @@
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>280</v>
@@ -4249,8 +4264,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="I29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="J29" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J28"/>
+  <autoFilter ref="A1:J29"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4279,6 +4326,7 @@
     <hyperlink ref="E26" r:id="rId25"/>
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
+    <hyperlink ref="E29" r:id="rId28"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4339,13 +4387,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -4354,10 +4402,10 @@
         <v>107</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4371,13 +4419,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
@@ -4389,7 +4437,7 @@
         <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4403,25 +4451,25 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4435,13 +4483,13 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -4453,7 +4501,7 @@
         <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4467,13 +4515,13 @@
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
@@ -4485,7 +4533,7 @@
         <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4499,25 +4547,25 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4531,13 +4579,13 @@
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
@@ -4549,7 +4597,7 @@
         <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4563,13 +4611,13 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -4581,7 +4629,7 @@
         <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4595,25 +4643,25 @@
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4624,16 +4672,16 @@
         <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
@@ -4645,7 +4693,7 @@
         <v>89</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4659,25 +4707,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4691,13 +4739,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -4709,7 +4757,7 @@
         <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4723,13 +4771,13 @@
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
@@ -4741,7 +4789,7 @@
         <v>130</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4755,13 +4803,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
@@ -4773,7 +4821,7 @@
         <v>108</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4787,25 +4835,25 @@
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4819,13 +4867,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -4837,7 +4885,7 @@
         <v>108</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4848,28 +4896,28 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>113</v>
+        <v>94</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4883,25 +4931,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>107</v>
+        <v>117</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4915,25 +4963,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4947,25 +4995,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>88</v>
+        <v>117</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4979,25 +5027,25 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>108</v>
+        <v>148</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5011,25 +5059,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>113</v>
+        <v>107</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5043,25 +5091,25 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>82</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>108</v>
+        <v>130</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5075,25 +5123,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>107</v>
+        <v>88</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5107,25 +5155,25 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5139,13 +5187,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -5157,7 +5205,7 @@
         <v>130</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5168,16 +5216,16 @@
         <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
@@ -5189,7 +5237,7 @@
         <v>139</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5203,13 +5251,13 @@
         <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
@@ -5218,10 +5266,10 @@
         <v>107</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5235,13 +5283,13 @@
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
@@ -5250,10 +5298,10 @@
         <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5264,16 +5312,16 @@
         <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>76</v>
@@ -5282,10 +5330,10 @@
         <v>70</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5331,7 +5379,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5378,31 +5426,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>371</v>
+        <v>50</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>371</v>
+        <v>50</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>94</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5410,31 +5458,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5442,31 +5490,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5474,31 +5522,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>49</v>
+        <v>383</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>49</v>
+        <v>383</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>219</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5506,31 +5554,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5538,31 +5586,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>130</v>
+        <v>148</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5570,31 +5618,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5602,31 +5650,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5634,31 +5682,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>107</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5666,31 +5714,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5698,31 +5746,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>139</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5730,19 +5778,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -5751,10 +5799,10 @@
         <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5762,31 +5810,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>409</v>
+        <v>198</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5794,31 +5842,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
+        <v>94</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>139</v>
+        <v>198</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5826,31 +5874,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>198</v>
+        <v>418</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5858,31 +5906,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E17" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>198</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5890,31 +5938,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5922,31 +5970,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="E19" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="I19" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5954,31 +6002,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5986,31 +6034,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>198</v>
+        <v>418</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6018,19 +6066,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -6039,10 +6087,10 @@
         <v>107</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>198</v>
+        <v>418</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6050,31 +6098,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>441</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6082,31 +6130,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>445</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>441</v>
+        <v>446</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6114,31 +6162,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>442</v>
+        <v>447</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>443</v>
+        <v>448</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>422</v>
+        <v>449</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>444</v>
+        <v>450</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6146,31 +6194,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>445</v>
+        <v>451</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>446</v>
+        <v>452</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>447</v>
+        <v>453</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6178,31 +6226,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>448</v>
+        <v>454</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>449</v>
+        <v>455</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6210,31 +6258,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>219</v>
+        <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6242,31 +6290,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6274,38 +6322,70 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>461</v>
+        <v>445</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6336,6 +6416,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6390,31 +6471,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>58</v>
+        <v>470</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>58</v>
+        <v>470</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>463</v>
+        <v>471</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>373</v>
+        <v>285</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6422,31 +6503,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>465</v>
+        <v>473</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>466</v>
+        <v>474</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>94</v>
+        <v>70</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>467</v>
+        <v>475</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6454,31 +6535,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>468</v>
+        <v>476</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>469</v>
+        <v>477</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>470</v>
+        <v>478</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6486,31 +6567,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>471</v>
+        <v>58</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>471</v>
+        <v>58</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>472</v>
+        <v>479</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>108</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>473</v>
+        <v>480</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6518,31 +6599,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>474</v>
+        <v>481</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>475</v>
+        <v>482</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>476</v>
+        <v>483</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6550,31 +6631,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>477</v>
+        <v>484</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>478</v>
+        <v>485</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>144</v>
+        <v>108</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>479</v>
+        <v>486</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6582,31 +6663,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>130</v>
+        <v>108</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>482</v>
+        <v>489</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6614,31 +6695,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>483</v>
+        <v>490</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>484</v>
+        <v>491</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>210</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>485</v>
+        <v>492</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6646,31 +6727,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>486</v>
+        <v>493</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>487</v>
+        <v>494</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>488</v>
+        <v>495</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6678,19 +6759,19 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>489</v>
+        <v>496</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>490</v>
+        <v>497</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
@@ -6699,10 +6780,10 @@
         <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>422</v>
+        <v>130</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>491</v>
+        <v>498</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6710,31 +6791,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>492</v>
+        <v>499</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>493</v>
+        <v>500</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>117</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>494</v>
+        <v>501</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6742,19 +6823,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>495</v>
+        <v>502</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>496</v>
+        <v>503</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -6766,7 +6847,7 @@
         <v>198</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>497</v>
+        <v>504</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6774,31 +6855,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>498</v>
+        <v>505</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>499</v>
+        <v>506</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>88</v>
+        <v>107</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>148</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>500</v>
+        <v>507</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6806,31 +6887,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>501</v>
+        <v>508</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>502</v>
+        <v>509</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>503</v>
+        <v>510</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6838,31 +6919,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>504</v>
+        <v>511</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>505</v>
+        <v>512</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>219</v>
+        <v>107</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>422</v>
+        <v>148</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>506</v>
+        <v>513</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6870,31 +6951,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>507</v>
+        <v>514</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>508</v>
+        <v>515</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>210</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>198</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>509</v>
+        <v>516</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6902,31 +6983,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>510</v>
+        <v>517</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>511</v>
+        <v>518</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>107</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>409</v>
+        <v>198</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>512</v>
+        <v>519</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6934,31 +7015,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>513</v>
+        <v>520</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>514</v>
+        <v>521</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>422</v>
+        <v>198</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>515</v>
+        <v>522</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6966,31 +7047,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>516</v>
+        <v>523</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>517</v>
+        <v>524</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>409</v>
+        <v>198</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6998,31 +7079,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>520</v>
+        <v>527</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>450</v>
+        <v>418</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7030,31 +7111,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>522</v>
+        <v>529</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>523</v>
+        <v>530</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>524</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>525</v>
+        <v>531</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7062,31 +7143,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>526</v>
+        <v>532</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>527</v>
+        <v>533</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>88</v>
+        <v>210</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>461</v>
+        <v>198</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>528</v>
+        <v>534</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7094,31 +7175,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>529</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>530</v>
+        <v>536</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>107</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>409</v>
+        <v>198</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>531</v>
+        <v>537</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7126,31 +7207,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>532</v>
+        <v>538</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>533</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>450</v>
+        <v>198</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>534</v>
+        <v>540</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7158,31 +7239,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>535</v>
+        <v>541</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>536</v>
+        <v>542</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>524</v>
+        <v>418</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>537</v>
+        <v>543</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7190,31 +7271,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>538</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>539</v>
+        <v>545</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>70</v>
+        <v>210</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>524</v>
+        <v>198</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>540</v>
+        <v>546</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7222,19 +7303,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>541</v>
+        <v>547</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>542</v>
+        <v>548</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
@@ -7243,10 +7324,10 @@
         <v>77</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>524</v>
+        <v>445</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>543</v>
+        <v>549</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7254,31 +7335,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>191</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>544</v>
+        <v>550</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>545</v>
+        <v>551</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>457</v>
+        <v>210</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>546</v>
+        <v>445</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>547</v>
+        <v>552</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7286,31 +7367,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>548</v>
+        <v>553</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>549</v>
+        <v>554</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>107</v>
+        <v>462</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>524</v>
+        <v>425</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>550</v>
+        <v>555</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7318,31 +7399,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>551</v>
+        <v>556</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>552</v>
+        <v>557</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>553</v>
+        <v>558</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -11,23 +11,23 @@
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="Kali" sheetId="3" r:id="rId3"/>
     <sheet name="숑숑" sheetId="4" r:id="rId4"/>
-    <sheet name="채금" sheetId="5" r:id="rId5"/>
-    <sheet name="쌈뽕" sheetId="6" r:id="rId6"/>
+    <sheet name="쌈뽕" sheetId="5" r:id="rId5"/>
+    <sheet name="채금" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$29</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">쌈뽕!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">채금!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">채금!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="559">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="563">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>390</t>
+    <t>389</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>172조 8970억 7998만</t>
+    <t>173조 9352억 9390만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>361</t>
+    <t>353</t>
   </si>
   <si>
     <t>14위</t>
@@ -122,7 +122,7 @@
     <t>28명</t>
   </si>
   <si>
-    <t>196조 1458억 5121만</t>
+    <t>204조 4538억 7680만</t>
   </si>
   <si>
     <t>토벌전 4위 kali 칼리길드 2조이상 함께 성장하실 신규인원 모집합니다 많은 관심 부탁드립니</t>
@@ -131,6 +131,9 @@
     <t>마삐아</t>
   </si>
   <si>
+    <t>2026.04.20</t>
+  </si>
+  <si>
     <t>숑숑</t>
   </si>
   <si>
@@ -146,7 +149,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>176조 5464억 5925만</t>
+    <t>176조 5634억 4488만</t>
   </si>
   <si>
     <t>소통 잘하시는분들 환영! 투력1조이상! 가입 전 꼭 귓문의 부탁드려용 문의는(강린)</t>
@@ -155,6 +158,33 @@
     <t>숑이</t>
   </si>
   <si>
+    <t>쌈뽕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8C%88%EB%BD%95</t>
+  </si>
+  <si>
+    <t>Scania 27</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>31위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>183조 7878억 5998만</t>
+  </si>
+  <si>
+    <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
+  </si>
+  <si>
+    <t>장정근</t>
+  </si>
+  <si>
     <t>채금</t>
   </si>
   <si>
@@ -164,15 +194,12 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>369</t>
+    <t>370</t>
   </si>
   <si>
     <t>10위</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
     <t>185조 3031억 5251만</t>
   </si>
   <si>
@@ -182,30 +209,6 @@
     <t>역뢰</t>
   </si>
   <si>
-    <t>쌈뽕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%8C%88%EB%BD%95</t>
-  </si>
-  <si>
-    <t>Scania 27</t>
-  </si>
-  <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>31위</t>
-  </si>
-  <si>
-    <t>183조 7878억 5998만</t>
-  </si>
-  <si>
-    <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
-  </si>
-  <si>
-    <t>장정근</t>
-  </si>
-  <si>
     <t>member_rank_in_guild</t>
   </si>
   <si>
@@ -245,7 +248,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>23조 641억 4651만</t>
+    <t>26조 7249억 1381만</t>
   </si>
   <si>
     <t>2</t>
@@ -299,7 +302,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>12조 8368억 6384만</t>
+    <t>13조 1760억 5067만</t>
   </si>
   <si>
     <t>5</t>
@@ -314,7 +317,7 @@
     <t>다크나이트</t>
   </si>
   <si>
-    <t>12조 6365억 3160만</t>
+    <t>12조 9053억 3941만</t>
   </si>
   <si>
     <t>6</t>
@@ -338,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 1232억 2869만</t>
+    <t>7조 2859억 1203만</t>
   </si>
   <si>
     <t>8</t>
@@ -383,7 +386,7 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>5조 9591억 5169만</t>
+    <t>6조 623억 4209만</t>
   </si>
   <si>
     <t>11</t>
@@ -395,7 +398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>4조 9286억 68만</t>
+    <t>5조 3840억 4662만</t>
   </si>
   <si>
     <t>12</t>
@@ -407,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 4114억 7192만</t>
+    <t>4조 7044억 9896만</t>
   </si>
   <si>
     <t>13</t>
@@ -434,12 +437,39 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 1855억 6129만</t>
+    <t>4조 1902억 7508만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>3조 9403억 5517만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 7580억 1099만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
@@ -449,10 +479,10 @@
     <t>97</t>
   </si>
   <si>
-    <t>3조 7219억 6524만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>3조 7369억 5836만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>강철고튠데</t>
@@ -464,22 +494,7 @@
     <t>3조 6838억 5909만</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 6572억 2213만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>19</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -491,7 +506,7 @@
     <t>3조 5006억 2017만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -503,7 +518,7 @@
     <t>3조 3744억 7808만</t>
   </si>
   <si>
-    <t>20</t>
+    <t>21</t>
   </si>
   <si>
     <t>민들레꽃</t>
@@ -512,10 +527,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 316억 6665만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>3조 897억 1185만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -527,7 +542,7 @@
     <t>2조 7646억 9816만</t>
   </si>
   <si>
-    <t>22</t>
+    <t>23</t>
   </si>
   <si>
     <t>여븨</t>
@@ -536,10 +551,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 6571억 479만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>2조 6956억 5390만</t>
+  </si>
+  <si>
+    <t>24</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -548,10 +563,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2조 2590억 8270만</t>
-  </si>
-  <si>
-    <t>24</t>
+    <t>2조 3877억 7093만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -563,7 +578,7 @@
     <t>2조 2114억 104만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>여눈</t>
@@ -575,7 +590,7 @@
     <t>2조 1697억 686만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -590,7 +605,7 @@
     <t>2조 721억 7045만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -602,7 +617,7 @@
     <t>2조 663억 1201만</t>
   </si>
   <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -611,10 +626,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>1조 8338억 6575만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>2조 131억 6518만</t>
+  </si>
+  <si>
+    <t>30</t>
   </si>
   <si>
     <t>욤지</t>
@@ -635,7 +650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
   </si>
   <si>
-    <t>54조 4254억 6928만</t>
+    <t>56조 4336억 1427만</t>
   </si>
   <si>
     <t>니니니닉</t>
@@ -644,7 +659,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
   </si>
   <si>
-    <t>17조 9330억 2509만</t>
+    <t>19조 1873억 9519만</t>
   </si>
   <si>
     <t>태태아방</t>
@@ -653,7 +668,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
   </si>
   <si>
-    <t>10조 9987억 69만</t>
+    <t>11조 7591억 2701만</t>
+  </si>
+  <si>
+    <t>뤄드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
+  </si>
+  <si>
+    <t>10조 5089억 5342만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
@@ -665,22 +689,13 @@
     <t>10조 411억 1296만</t>
   </si>
   <si>
-    <t>뤄드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
-  </si>
-  <si>
-    <t>9조 2003억 1997만</t>
-  </si>
-  <si>
     <t>롱노즈</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
   </si>
   <si>
-    <t>7조 8027억 3811만</t>
+    <t>8조 8023억 7275만</t>
   </si>
   <si>
     <t>주요엘농산</t>
@@ -689,7 +704,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
   </si>
   <si>
-    <t>6조 9792억 5346만</t>
+    <t>7조 5088억 6473만</t>
+  </si>
+  <si>
+    <t>뱀맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>6조 6808억 2457만</t>
   </si>
   <si>
     <t>삼치김치찜</t>
@@ -701,22 +725,31 @@
     <t>6조 6403억 9033만</t>
   </si>
   <si>
-    <t>뱀맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>6조 2855억 9823만</t>
-  </si>
-  <si>
     <t>AI루미</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 5427억 5727만</t>
+    <t>5조 8372억 9176만</t>
+  </si>
+  <si>
+    <t>IMABORNHATER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
+  </si>
+  <si>
+    <t>5조 6292억 9178만</t>
+  </si>
+  <si>
+    <t>조지선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5조 6263억 8504만</t>
   </si>
   <si>
     <t>약한디</t>
@@ -728,31 +761,13 @@
     <t>5조 4820억 4885만</t>
   </si>
   <si>
-    <t>IMABORNHATER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
-  </si>
-  <si>
-    <t>5조 3686억 6294만</t>
-  </si>
-  <si>
-    <t>조지선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>5조 1623억 2192만</t>
-  </si>
-  <si>
     <t>사당행</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
   </si>
   <si>
-    <t>4조 9701억 4878만</t>
+    <t>5조 997억 2848만</t>
   </si>
   <si>
     <t>지안히</t>
@@ -761,7 +776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%88%ED%9E%88</t>
   </si>
   <si>
-    <t>4조 4179억 3072만</t>
+    <t>4조 4230억 6755만</t>
   </si>
   <si>
     <t>올망건빵</t>
@@ -770,7 +785,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%A7%9D%EA%B1%B4%EB%B9%B5</t>
   </si>
   <si>
-    <t>4조 2661억 9603만</t>
+    <t>4조 3253억 2975만</t>
   </si>
   <si>
     <t>거푸</t>
@@ -779,7 +794,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
   </si>
   <si>
-    <t>4조 152억 1170만</t>
+    <t>4조 251억 5009만</t>
   </si>
   <si>
     <t>전통한우</t>
@@ -797,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
   </si>
   <si>
-    <t>3조 3604억 7751만</t>
+    <t>3조 4298억 7488만</t>
   </si>
   <si>
     <t>Pixy</t>
@@ -806,7 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=Pixy</t>
   </si>
   <si>
-    <t>3조 376억 9729만</t>
+    <t>3조 435억 6193만</t>
   </si>
   <si>
     <t>겨농</t>
@@ -815,7 +830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
   </si>
   <si>
-    <t>2조 7618억 6020만</t>
+    <t>2조 9572억 5139만</t>
   </si>
   <si>
     <t>채빛</t>
@@ -824,7 +839,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
   </si>
   <si>
-    <t>2조 6949억 5357만</t>
+    <t>2조 7334억 7694만</t>
+  </si>
+  <si>
+    <t>코코호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2조 4775억 7747만</t>
   </si>
   <si>
     <t>히미노</t>
@@ -836,13 +860,13 @@
     <t>2조 3013억 13만</t>
   </si>
   <si>
-    <t>코코호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
-  </si>
-  <si>
-    <t>2조 2439억 5677만</t>
+    <t>홍이수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
+  </si>
+  <si>
+    <t>2조 1363억 5566만</t>
   </si>
   <si>
     <t>킴머웅</t>
@@ -854,22 +878,13 @@
     <t>2조 755억 5068만</t>
   </si>
   <si>
-    <t>홍이수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
-  </si>
-  <si>
-    <t>1조 8193억 3141만</t>
-  </si>
-  <si>
     <t>kingsister</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=kingsister</t>
   </si>
   <si>
-    <t>1조 8130억 5412만</t>
+    <t>2조 382억 7025만</t>
   </si>
   <si>
     <t>반음</t>
@@ -887,7 +902,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>40조 2505억 462만</t>
+    <t>41조 5368억 1284만</t>
   </si>
   <si>
     <t>소독약</t>
@@ -896,7 +911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
   </si>
   <si>
-    <t>15조 2296억 9794만</t>
+    <t>17조 6120억 3459만</t>
   </si>
   <si>
     <t>주존사</t>
@@ -905,7 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>14조 310억 5090만</t>
+    <t>14조 9077억 7078만</t>
   </si>
   <si>
     <t>휘정</t>
@@ -914,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
   </si>
   <si>
-    <t>9조 2382억 9399만</t>
+    <t>9조 6125억 3694만</t>
   </si>
   <si>
     <t>무피</t>
@@ -932,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
   </si>
   <si>
-    <t>6조 7426억 1980만</t>
+    <t>6조 8863억 8744만</t>
   </si>
   <si>
     <t>파산</t>
@@ -950,7 +965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
   </si>
   <si>
-    <t>5조 9822억 3121만</t>
+    <t>6조 125억 9034만</t>
   </si>
   <si>
     <t>빡박이</t>
@@ -959,7 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
   </si>
   <si>
-    <t>5조 6913억 7437만</t>
+    <t>5조 7053억 1061만</t>
   </si>
   <si>
     <t>임나연</t>
@@ -968,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
   </si>
   <si>
-    <t>5조 2733억 7581만</t>
+    <t>5조 3772억 2631만</t>
   </si>
   <si>
     <t>강린</t>
@@ -1004,7 +1019,7 @@
     <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
   </si>
   <si>
-    <t>3조 5862억 5239만</t>
+    <t>3조 6098억 2513만</t>
   </si>
   <si>
     <t>픽홀로</t>
@@ -1013,7 +1028,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
   </si>
   <si>
-    <t>3조 5343억 2166만</t>
+    <t>3조 5392억 5846만</t>
+  </si>
+  <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>3조 5115억 5642만</t>
   </si>
   <si>
     <t>Rania</t>
@@ -1043,15 +1067,6 @@
     <t>3조 2359억 4543만</t>
   </si>
   <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>3조 1216억 9132만</t>
-  </si>
-  <si>
     <t>쟁반짜장</t>
   </si>
   <si>
@@ -1061,6 +1076,15 @@
     <t>3조 431억 2870만</t>
   </si>
   <si>
+    <t>바세린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>2조 8856억 8846만</t>
+  </si>
+  <si>
     <t>Uhani</t>
   </si>
   <si>
@@ -1070,22 +1094,22 @@
     <t>2조 8490억 4859만</t>
   </si>
   <si>
-    <t>바세린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>2조 8267억 4354만</t>
-  </si>
-  <si>
     <t>가이아의격노</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 6656억 6767만</t>
+    <t>2조 7333억 8809만</t>
+  </si>
+  <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>2조 7002억 9323만</t>
   </si>
   <si>
     <t>별렉스b</t>
@@ -1094,16 +1118,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
   </si>
   <si>
-    <t>2조 6092억 6019만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>2조 5912억 5139만</t>
+    <t>2조 6151억 9678만</t>
   </si>
   <si>
     <t>하숑</t>
@@ -1121,7 +1136,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 8386억 8160만</t>
+    <t>1조 8426억 7540만</t>
   </si>
   <si>
     <t>potato</t>
@@ -1139,10 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
   </si>
   <si>
-    <t>1조 4062억 4984만</t>
-  </si>
-  <si>
-    <t>30</t>
+    <t>1조 4185억 250만</t>
   </si>
   <si>
     <t>도레스</t>
@@ -1154,10 +1166,289 @@
     <t>1조 3209억 8583만</t>
   </si>
   <si>
+    <t>깔개73호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
+  </si>
+  <si>
+    <t>81조 6541억 8669만</t>
+  </si>
+  <si>
+    <t>다정파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>49조 5207억 6718만</t>
+  </si>
+  <si>
+    <t>천상의빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>12조 3733억 7725만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>6조 7713억 5577만</t>
+  </si>
+  <si>
+    <t>남과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>5조 7995억 13만</t>
+  </si>
+  <si>
+    <t>분함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
+  </si>
+  <si>
+    <t>3조 7213억 2312만</t>
+  </si>
+  <si>
+    <t>숭이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>2조 9582억 1913만</t>
+  </si>
+  <si>
+    <t>기초수급좌파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 6547억 3128만</t>
+  </si>
+  <si>
+    <t>늑멍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
+  </si>
+  <si>
+    <t>2조 6062억 690만</t>
+  </si>
+  <si>
+    <t>갓라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>1조 7674억 4038만</t>
+  </si>
+  <si>
+    <t>춘봉박2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
+  </si>
+  <si>
+    <t>1조 6857억 4180만</t>
+  </si>
+  <si>
+    <t>건브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>1조 4692억 7043만</t>
+  </si>
+  <si>
+    <t>나폴리맛동산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1조 4355억 7514만</t>
+  </si>
+  <si>
+    <t>망치든여자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
+  </si>
+  <si>
+    <t>94</t>
+  </si>
+  <si>
+    <t>1조 3828억 2857만</t>
+  </si>
+  <si>
+    <t>독고패</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
+  </si>
+  <si>
+    <t>1조 2671억 4754만</t>
+  </si>
+  <si>
+    <t>힐링완이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 1855억 5213만</t>
+  </si>
+  <si>
+    <t>I비숍I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
+  </si>
+  <si>
+    <t>1조 1523억 9005만</t>
+  </si>
+  <si>
+    <t>마도훈이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 1059억 1590만</t>
+  </si>
+  <si>
+    <t>어허오빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>1조 568억 2998만</t>
+  </si>
+  <si>
+    <t>선빵쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
+  </si>
+  <si>
+    <t>1조 525억 5220만</t>
+  </si>
+  <si>
+    <t>고지혈증</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
+  </si>
+  <si>
+    <t>1조 2316만</t>
+  </si>
+  <si>
+    <t>왕구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>8755억 696만</t>
+  </si>
+  <si>
+    <t>남편이니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>7787억 8004만</t>
+  </si>
+  <si>
+    <t>만능도끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
+  </si>
+  <si>
+    <t>7521억 8497만</t>
+  </si>
+  <si>
+    <t>망치균이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6847억 7382만</t>
+  </si>
+  <si>
+    <t>후돌돌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
+  </si>
+  <si>
+    <t>5122억 4355만</t>
+  </si>
+  <si>
+    <t>이선호에용</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>3471억 1403만</t>
+  </si>
+  <si>
+    <t>제육아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>3368억 8534만</t>
+  </si>
+  <si>
+    <t>우유나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
+  </si>
+  <si>
+    <t>2986억 7312만</t>
+  </si>
+  <si>
+    <t>굴화주민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2813억 8310만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
   </si>
   <si>
-    <t>80조 1485억 4555만</t>
+    <t>81조 4222억 6140만</t>
   </si>
   <si>
     <t>쭈딘</t>
@@ -1166,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
   </si>
   <si>
-    <t>44조 9583억 1185만</t>
+    <t>45조 2123억 4090만</t>
   </si>
   <si>
     <t>퀸이</t>
@@ -1175,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
   </si>
   <si>
-    <t>22조 4976억 7059만</t>
+    <t>27조 5175억 5855만</t>
   </si>
   <si>
     <t>나는숭이</t>
@@ -1193,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
   </si>
   <si>
-    <t>5조 802억 2326만</t>
+    <t>5조 3057억 4157만</t>
   </si>
   <si>
     <t>용두산</t>
@@ -1202,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
   </si>
   <si>
-    <t>3조 4741억 1825만</t>
+    <t>3조 8492억 7706만</t>
   </si>
   <si>
     <t>형뱁새</t>
@@ -1211,7 +1502,16 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3조 4135억 4059만</t>
+    <t>3조 5791억 7535만</t>
+  </si>
+  <si>
+    <t>꾜뀨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
+  </si>
+  <si>
+    <t>1조 7824억 4059만</t>
   </si>
   <si>
     <t>수컹수컹</t>
@@ -1220,7 +1520,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
   </si>
   <si>
-    <t>1조 5561억 8483만</t>
+    <t>1조 6026억 5550만</t>
   </si>
   <si>
     <t>팽됴리</t>
@@ -1232,22 +1532,13 @@
     <t>1조 5492억 5497만</t>
   </si>
   <si>
-    <t>꾜뀨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
-  </si>
-  <si>
-    <t>1조 4825억 9042만</t>
-  </si>
-  <si>
     <t>점검중임</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
   </si>
   <si>
-    <t>1조 751억 130만</t>
+    <t>1조 798억 2267만</t>
   </si>
   <si>
     <t>비비보람</t>
@@ -1256,7 +1547,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
   </si>
   <si>
-    <t>1조 535억 532만</t>
+    <t>1조 613억 1229만</t>
   </si>
   <si>
     <t>장헌</t>
@@ -1265,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
   </si>
   <si>
-    <t>8474억 6346만</t>
+    <t>8663억 5781만</t>
   </si>
   <si>
     <t>메쓰가키</t>
@@ -1277,6 +1568,15 @@
     <t>8295억 3279만</t>
   </si>
   <si>
+    <t>신똥은원딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
+  </si>
+  <si>
+    <t>6609억 5361만</t>
+  </si>
+  <si>
     <t>뿌뿝</t>
   </si>
   <si>
@@ -1286,7 +1586,16 @@
     <t>95</t>
   </si>
   <si>
-    <t>5215억 1110만</t>
+    <t>5370억 6459만</t>
+  </si>
+  <si>
+    <t>곰굼곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>5347억 88만</t>
   </si>
   <si>
     <t>다시스타투</t>
@@ -1295,19 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
   </si>
   <si>
-    <t>5116억 4071만</t>
-  </si>
-  <si>
-    <t>곰굼곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>4799억 5631만</t>
+    <t>5304억 699만</t>
   </si>
   <si>
     <t>쉬누2</t>
@@ -1319,22 +1616,13 @@
     <t>4755억 4148만</t>
   </si>
   <si>
-    <t>신똥은원딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
-  </si>
-  <si>
-    <t>4713억 3098만</t>
-  </si>
-  <si>
     <t>난뭉</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%AD%89</t>
   </si>
   <si>
-    <t>4063억 6955만</t>
+    <t>4651억 9020만</t>
   </si>
   <si>
     <t>만칠</t>
@@ -1343,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
   </si>
   <si>
-    <t>3989억 2356만</t>
+    <t>4224억 6620만</t>
   </si>
   <si>
     <t>박오팔</t>
@@ -1352,82 +1640,73 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%A4%ED%8C%94</t>
   </si>
   <si>
+    <t>3568억 9779만</t>
+  </si>
+  <si>
+    <t>해피킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
+  </si>
+  <si>
+    <t>3164억 2985만</t>
+  </si>
+  <si>
+    <t>쌀유건</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
+  </si>
+  <si>
+    <t>2876억 5455만</t>
+  </si>
+  <si>
+    <t>문현준2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%ED%98%84%EC%A4%802</t>
+  </si>
+  <si>
+    <t>2637억 6649만</t>
+  </si>
+  <si>
+    <t>정다몽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
+  </si>
+  <si>
+    <t>2333억 7104만</t>
+  </si>
+  <si>
+    <t>쌀코볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>2134억 8190만</t>
+  </si>
+  <si>
+    <t>해피퀸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
+  </si>
+  <si>
+    <t>2083억 487만</t>
+  </si>
+  <si>
+    <t>팔라완</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
+  </si>
+  <si>
     <t>91</t>
   </si>
   <si>
-    <t>3345억 3597만</t>
-  </si>
-  <si>
-    <t>해피킹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>3151억 2021만</t>
-  </si>
-  <si>
-    <t>쌀유건</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
-  </si>
-  <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>2769억 4945만</t>
-  </si>
-  <si>
-    <t>문현준2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%ED%98%84%EC%A4%802</t>
-  </si>
-  <si>
-    <t>2637억 6649만</t>
-  </si>
-  <si>
-    <t>정다몽</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
-  </si>
-  <si>
-    <t>2151억 6189만</t>
-  </si>
-  <si>
-    <t>쌀코볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>1966억 5195만</t>
-  </si>
-  <si>
-    <t>팔라완</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>1824억 1756만</t>
-  </si>
-  <si>
-    <t>해피퀸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
-  </si>
-  <si>
-    <t>1814억 8997만</t>
+    <t>1842억 8286만</t>
   </si>
   <si>
     <t>왕필</t>
@@ -1436,274 +1715,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%95%84</t>
   </si>
   <si>
-    <t>1688억 9471만</t>
-  </si>
-  <si>
-    <t>깔개73호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
-  </si>
-  <si>
-    <t>79조 646억 6977만</t>
-  </si>
-  <si>
-    <t>다정파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>49조 5207억 6718만</t>
-  </si>
-  <si>
-    <t>천상의빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>11조 7274억 5785만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>6조 1081억 6659만</t>
-  </si>
-  <si>
-    <t>남과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>5조 7760억 8358만</t>
-  </si>
-  <si>
-    <t>분함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
-  </si>
-  <si>
-    <t>3조 6371억 6189만</t>
-  </si>
-  <si>
-    <t>숭이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>2조 9582억 1913만</t>
-  </si>
-  <si>
-    <t>기초수급좌파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 6547억 3128만</t>
-  </si>
-  <si>
-    <t>늑멍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
-  </si>
-  <si>
-    <t>2조 6062억 690만</t>
-  </si>
-  <si>
-    <t>춘봉박2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
-  </si>
-  <si>
-    <t>1조 6837억 1388만</t>
-  </si>
-  <si>
-    <t>갓라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>1조 5405억 7815만</t>
-  </si>
-  <si>
-    <t>건브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>1조 4667억 2641만</t>
-  </si>
-  <si>
-    <t>나폴리맛동산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1조 4184억 8397만</t>
-  </si>
-  <si>
-    <t>망치든여자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
-  </si>
-  <si>
-    <t>1조 3391억 6610만</t>
-  </si>
-  <si>
-    <t>독고패</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
-  </si>
-  <si>
-    <t>1조 2421억 1576만</t>
-  </si>
-  <si>
-    <t>I비숍I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
-  </si>
-  <si>
-    <t>1조 1523억 9005만</t>
-  </si>
-  <si>
-    <t>힐링완이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 1510억 7576만</t>
-  </si>
-  <si>
-    <t>마도훈이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 877억 886만</t>
-  </si>
-  <si>
-    <t>선빵쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
-  </si>
-  <si>
-    <t>1조 525억 5220만</t>
-  </si>
-  <si>
-    <t>어허오빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>1조 75억 6364만</t>
-  </si>
-  <si>
-    <t>고지혈증</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
-  </si>
-  <si>
-    <t>9749억 734만</t>
-  </si>
-  <si>
-    <t>왕구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>8755억 696만</t>
-  </si>
-  <si>
-    <t>남편이니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>7538억 292만</t>
-  </si>
-  <si>
-    <t>만능도끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
-  </si>
-  <si>
-    <t>6776억 5098만</t>
-  </si>
-  <si>
-    <t>망치균이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6641억 2479만</t>
-  </si>
-  <si>
-    <t>후돌돌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
-  </si>
-  <si>
-    <t>4906억 1481만</t>
-  </si>
-  <si>
-    <t>이선호에용</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
-  </si>
-  <si>
-    <t>3280억 8417만</t>
-  </si>
-  <si>
-    <t>우유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>2955억 4772만</t>
-  </si>
-  <si>
-    <t>제육아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>2898억 6575만</t>
-  </si>
-  <si>
-    <t>굴화주민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
-  </si>
-  <si>
-    <t>2813억 8310만</t>
+    <t>1694억 261만</t>
   </si>
 </sst>
 </file>
@@ -2202,18 +2214,18 @@
         <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>35</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
@@ -2222,25 +2234,25 @@
         <v>16</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2248,40 +2260,40 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2289,40 +2301,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2343,13 +2355,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
@@ -2361,28 +2372,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2393,7 +2404,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2402,19 +2413,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2425,28 +2436,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2457,28 +2468,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2489,28 +2500,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2521,28 +2532,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2553,28 +2564,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2585,28 +2596,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2617,28 +2628,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2649,28 +2660,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2681,28 +2692,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2713,28 +2724,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2745,28 +2756,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2777,28 +2788,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2809,28 +2820,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2841,25 +2852,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2885,16 +2896,16 @@
         <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2905,28 +2916,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2937,28 +2948,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
+        <v>109</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2969,28 +2980,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -3001,28 +3012,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3033,28 +3044,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3065,28 +3076,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>89</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3097,28 +3108,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>139</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3129,28 +3140,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3161,28 +3172,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3193,25 +3204,25 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>185</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>186</v>
@@ -3237,16 +3248,16 @@
         <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3257,28 +3268,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3289,25 +3300,25 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>198</v>
+        <v>109</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>199</v>
@@ -3316,8 +3327,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -3348,6 +3391,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -3373,28 +3417,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3405,31 +3449,31 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>202</v>
+        <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3437,31 +3481,31 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>204</v>
+        <v>209</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>205</v>
+        <v>210</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3469,31 +3513,31 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>206</v>
+        <v>211</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3501,31 +3545,31 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>33</v>
+        <v>214</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3533,31 +3577,31 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>212</v>
+        <v>33</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>214</v>
+        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3565,31 +3609,31 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>215</v>
+        <v>220</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>216</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3597,31 +3641,31 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>219</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3629,31 +3673,31 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3661,31 +3705,31 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3693,31 +3737,31 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>227</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>228</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>229</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3725,31 +3769,31 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>230</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>231</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>232</v>
+        <v>237</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3757,31 +3801,31 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>233</v>
+        <v>238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>234</v>
+        <v>239</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>235</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3789,31 +3833,31 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>236</v>
+        <v>241</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>237</v>
+        <v>242</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>238</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3821,31 +3865,31 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>241</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3853,31 +3897,31 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>243</v>
+        <v>248</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>244</v>
+        <v>249</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -3888,28 +3932,28 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>245</v>
+        <v>250</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>246</v>
+        <v>251</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>247</v>
+        <v>252</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -3917,31 +3961,31 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>249</v>
+        <v>254</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>250</v>
+        <v>255</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -3949,31 +3993,31 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -3981,31 +4025,31 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>254</v>
+        <v>259</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -4013,31 +4057,31 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -4045,31 +4089,31 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>262</v>
+        <v>267</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -4077,31 +4121,31 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>263</v>
+        <v>268</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>264</v>
+        <v>269</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -4109,31 +4153,31 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>266</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>190</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>108</v>
+        <v>149</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -4141,31 +4185,31 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>185</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>139</v>
+        <v>109</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>271</v>
+        <v>276</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -4173,31 +4217,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -4205,31 +4249,31 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -4240,28 +4284,28 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -4269,31 +4313,31 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -4352,28 +4396,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4381,31 +4425,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4413,31 +4457,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4445,31 +4489,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>292</v>
+        <v>297</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4477,31 +4521,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>293</v>
+        <v>298</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>294</v>
+        <v>299</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>295</v>
+        <v>300</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4509,31 +4553,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>296</v>
+        <v>301</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>297</v>
+        <v>302</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4541,31 +4585,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>299</v>
+        <v>304</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>300</v>
+        <v>305</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>301</v>
+        <v>306</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4573,31 +4617,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4605,31 +4649,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>306</v>
+        <v>311</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>307</v>
+        <v>312</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4637,31 +4681,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>308</v>
+        <v>313</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>309</v>
+        <v>314</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>185</v>
+        <v>190</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>310</v>
+        <v>315</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4669,31 +4713,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>311</v>
+        <v>316</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>312</v>
+        <v>317</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>313</v>
+        <v>318</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4701,31 +4745,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>314</v>
+        <v>319</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>315</v>
+        <v>320</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>316</v>
+        <v>321</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4733,31 +4777,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>317</v>
+        <v>322</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>318</v>
+        <v>323</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>319</v>
+        <v>324</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4765,31 +4809,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>320</v>
+        <v>325</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>321</v>
+        <v>326</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>322</v>
+        <v>327</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4797,31 +4841,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>323</v>
+        <v>328</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>324</v>
+        <v>329</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>325</v>
+        <v>330</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4829,31 +4873,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>326</v>
+        <v>331</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>327</v>
+        <v>332</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>328</v>
+        <v>333</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4861,31 +4905,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>329</v>
+        <v>334</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>330</v>
+        <v>335</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>331</v>
+        <v>336</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4893,31 +4937,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>332</v>
+        <v>337</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>333</v>
+        <v>338</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>334</v>
+        <v>339</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4925,31 +4969,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>335</v>
+        <v>340</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>336</v>
+        <v>341</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>117</v>
+        <v>95</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>337</v>
+        <v>342</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4957,31 +5001,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>338</v>
+        <v>343</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>339</v>
+        <v>344</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>107</v>
+        <v>118</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4989,31 +5033,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>341</v>
+        <v>346</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5021,31 +5065,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>344</v>
+        <v>349</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5053,31 +5097,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>348</v>
+        <v>353</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5085,31 +5129,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>352</v>
+        <v>357</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5117,31 +5161,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>108</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5149,31 +5193,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>356</v>
+        <v>361</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>357</v>
+        <v>362</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>358</v>
+        <v>363</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5181,31 +5225,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>359</v>
+        <v>364</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>360</v>
+        <v>365</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>361</v>
+        <v>366</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5213,31 +5257,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>362</v>
+        <v>367</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>363</v>
+        <v>368</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>364</v>
+        <v>369</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5245,31 +5289,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>365</v>
+        <v>370</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>366</v>
+        <v>371</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>131</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>367</v>
+        <v>372</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5277,31 +5321,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>368</v>
+        <v>373</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>369</v>
+        <v>374</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>370</v>
+        <v>375</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5309,31 +5353,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5397,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5426,31 +5470,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>50</v>
+        <v>379</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>50</v>
+        <v>379</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>375</v>
+        <v>380</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>376</v>
+        <v>381</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5458,31 +5502,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>377</v>
+        <v>382</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>378</v>
+        <v>383</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>379</v>
+        <v>384</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5490,31 +5534,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>381</v>
+        <v>386</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>382</v>
+        <v>387</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5522,31 +5566,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>383</v>
+        <v>51</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>383</v>
+        <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>109</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5554,31 +5598,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5586,31 +5630,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>148</v>
+        <v>109</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5618,31 +5662,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>94</v>
+        <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5650,31 +5694,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5682,31 +5726,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>139</v>
+        <v>144</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5714,31 +5758,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5746,31 +5790,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5778,31 +5822,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5810,31 +5854,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>198</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5842,31 +5886,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>198</v>
+        <v>419</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5874,31 +5918,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>418</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5906,31 +5950,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>77</v>
+        <v>108</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>418</v>
+        <v>203</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5938,31 +5982,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>425</v>
+        <v>149</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5970,31 +6014,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>425</v>
+        <v>203</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6002,31 +6046,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>139</v>
+        <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6034,31 +6078,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>418</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6066,31 +6110,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>418</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6098,31 +6142,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>441</v>
+        <v>149</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6130,31 +6174,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>94</v>
+        <v>108</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>445</v>
+        <v>149</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6162,28 +6206,28 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>449</v>
+        <v>149</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>450</v>
@@ -6194,10 +6238,10 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
         <v>451</v>
@@ -6209,13 +6253,13 @@
         <v>452</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>425</v>
+        <v>203</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>453</v>
@@ -6226,10 +6270,10 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>454</v>
@@ -6241,13 +6285,13 @@
         <v>455</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>441</v>
+        <v>203</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>456</v>
@@ -6258,7 +6302,7 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>187</v>
@@ -6273,16 +6317,16 @@
         <v>458</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>449</v>
+        <v>459</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6290,31 +6334,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>441</v>
+        <v>419</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6322,31 +6366,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>70</v>
+        <v>218</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6354,31 +6398,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>107</v>
+        <v>89</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>441</v>
+        <v>470</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6442,28 +6486,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6471,31 +6515,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>470</v>
+        <v>59</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>470</v>
+        <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6503,31 +6547,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6535,31 +6579,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6567,31 +6611,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>58</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>58</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6599,31 +6643,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6631,31 +6675,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>108</v>
+        <v>131</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6663,31 +6707,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>77</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6695,31 +6739,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6727,31 +6771,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>107</v>
+        <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6759,31 +6803,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>70</v>
+        <v>108</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>130</v>
+        <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6791,31 +6835,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>117</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6823,31 +6867,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>198</v>
+        <v>149</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6855,31 +6899,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>203</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6887,31 +6931,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>425</v>
+        <v>203</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6919,31 +6963,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>107</v>
+        <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6951,31 +6995,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>139</v>
+        <v>518</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6983,31 +7027,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>198</v>
+        <v>419</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7015,31 +7059,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>198</v>
+        <v>518</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7047,31 +7091,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>198</v>
+        <v>419</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7079,31 +7123,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>77</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>418</v>
+        <v>203</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7111,31 +7155,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>210</v>
+        <v>108</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>139</v>
+        <v>518</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7143,31 +7187,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>198</v>
+        <v>470</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7175,31 +7219,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>107</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>198</v>
+        <v>459</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7207,31 +7251,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>198</v>
+        <v>470</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7239,31 +7283,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7271,31 +7315,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>198</v>
+        <v>470</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -7303,31 +7347,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>445</v>
+        <v>470</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -7335,31 +7379,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>210</v>
+        <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>445</v>
+        <v>459</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -7367,31 +7411,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>425</v>
+        <v>558</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -7399,31 +7443,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>371</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>88</v>
+        <v>108</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>449</v>
+        <v>558</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -19,7 +19,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$29</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">채금!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="563">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="560">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>389</t>
+    <t>400</t>
   </si>
   <si>
     <t>13위</t>
@@ -113,7 +113,7 @@
     <t>Scania 13</t>
   </si>
   <si>
-    <t>353</t>
+    <t>363</t>
   </si>
   <si>
     <t>14위</t>
@@ -125,7 +125,7 @@
     <t>204조 4538억 7680만</t>
   </si>
   <si>
-    <t>토벌전 4위 kali 칼리길드 2조이상 함께 성장하실 신규인원 모집합니다 많은 관심 부탁드립니</t>
+    <t>소통 좋아하고 길드컨텐츠 진심이신 3조이상 메키인 모십니다^0^</t>
   </si>
   <si>
     <t>마삐아</t>
@@ -140,7 +140,7 @@
     <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%88%91%EC%88%91</t>
   </si>
   <si>
-    <t>387</t>
+    <t>398</t>
   </si>
   <si>
     <t>12위</t>
@@ -167,16 +167,16 @@
     <t>Scania 27</t>
   </si>
   <si>
-    <t>372</t>
-  </si>
-  <si>
-    <t>31위</t>
+    <t>383</t>
+  </si>
+  <si>
+    <t>32위</t>
   </si>
   <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>183조 7878억 5998만</t>
+    <t>188조 4295억 3108만</t>
   </si>
   <si>
     <t>투력7000억이상-미접 자동추방-컨텐츠적극참여-일일무료업글필수-오픈챗필수-대항전1위길드</t>
@@ -194,13 +194,13 @@
     <t>Scania 29</t>
   </si>
   <si>
-    <t>370</t>
+    <t>377</t>
   </si>
   <si>
     <t>10위</t>
   </si>
   <si>
-    <t>185조 3031억 5251만</t>
+    <t>194조 281억 9392만</t>
   </si>
   <si>
     <t>안녕하세요 채금길드입니다. 공지사항 꼭 필수로 지켜주세요!</t>
@@ -248,7 +248,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>26조 7249억 1381만</t>
+    <t>26조 8075억 1513만</t>
   </si>
   <si>
     <t>2</t>
@@ -266,12 +266,30 @@
     <t>신궁</t>
   </si>
   <si>
-    <t>17조 4717억 6864만</t>
+    <t>20조 8772억 7416만</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>17조 4194억 2235만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -287,7 +305,7 @@
     <t>13조 2229억 5022만</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -299,27 +317,9 @@
     <t>히어로</t>
   </si>
   <si>
-    <t>101</t>
-  </si>
-  <si>
     <t>13조 1760억 5067만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>12조 9053억 3941만</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 1227억 1470만</t>
+    <t>11조 1815억 3519만</t>
   </si>
   <si>
     <t>7</t>
@@ -347,6 +347,24 @@
     <t>8</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 3772억 4815만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -356,13 +374,10 @@
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>6조 3436억 8307만</t>
   </si>
   <si>
-    <t>9</t>
+    <t>10</t>
   </si>
   <si>
     <t>포스코퓨처엠</t>
@@ -374,21 +389,6 @@
     <t>6조 1164억 6608만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>6조 623억 4209만</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -398,7 +398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>5조 3840억 4662만</t>
+    <t>5조 3918억 8444만</t>
   </si>
   <si>
     <t>12</t>
@@ -410,7 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 7044억 9896만</t>
+    <t>4조 7515억 6288만</t>
   </si>
   <si>
     <t>13</t>
@@ -425,7 +425,7 @@
     <t>99</t>
   </si>
   <si>
-    <t>4조 2568억 4863만</t>
+    <t>4조 3985억 226만</t>
   </si>
   <si>
     <t>14</t>
@@ -455,6 +455,21 @@
     <t>16</t>
   </si>
   <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>3조 7729억 7800만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
@@ -464,22 +479,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 7580억 1099만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>3조 7369억 5836만</t>
+    <t>3조 7652억 4400만</t>
   </si>
   <si>
     <t>18</t>
@@ -527,7 +527,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 897억 1185만</t>
+    <t>3조 1414억 4138만</t>
   </si>
   <si>
     <t>22</t>
@@ -539,7 +539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 7646억 9816만</t>
+    <t>2조 7711억 1811만</t>
   </si>
   <si>
     <t>23</t>
@@ -551,7 +551,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 6956억 5390만</t>
+    <t>2조 7026억 5570만</t>
   </si>
   <si>
     <t>24</t>
@@ -602,7 +602,7 @@
     <t>아크메이지(불,독)</t>
   </si>
   <si>
-    <t>2조 721억 7045만</t>
+    <t>2조 1168억 8492만</t>
   </si>
   <si>
     <t>28</t>
@@ -626,7 +626,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 131억 6518만</t>
+    <t>2조 200억 173만</t>
   </si>
   <si>
     <t>30</t>
@@ -650,7 +650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
   </si>
   <si>
-    <t>56조 4336억 1427만</t>
+    <t>56조 9456억 9229만</t>
   </si>
   <si>
     <t>니니니닉</t>
@@ -668,7 +668,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
   </si>
   <si>
-    <t>11조 7591억 2701만</t>
+    <t>13조 4687억 3647만</t>
   </si>
   <si>
     <t>뤄드</t>
@@ -695,7 +695,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
   </si>
   <si>
-    <t>8조 8023억 7275만</t>
+    <t>9조 3375억 9613만</t>
   </si>
   <si>
     <t>주요엘농산</t>
@@ -704,7 +704,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
   </si>
   <si>
-    <t>7조 5088억 6473만</t>
+    <t>7조 6065억 9341만</t>
   </si>
   <si>
     <t>뱀맹</t>
@@ -713,7 +713,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
   </si>
   <si>
-    <t>6조 6808억 2457만</t>
+    <t>6조 7803억 2245만</t>
   </si>
   <si>
     <t>삼치김치찜</t>
@@ -731,7 +731,16 @@
     <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
   </si>
   <si>
-    <t>5조 8372억 9176만</t>
+    <t>6조 143억 8054만</t>
+  </si>
+  <si>
+    <t>조지선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5조 8459억 2046만</t>
   </si>
   <si>
     <t>IMABORNHATER</t>
@@ -743,13 +752,13 @@
     <t>5조 6292억 9178만</t>
   </si>
   <si>
-    <t>조지선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>5조 6263억 8504만</t>
+    <t>사당행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
+  </si>
+  <si>
+    <t>5조 5692억 1059만</t>
   </si>
   <si>
     <t>약한디</t>
@@ -761,15 +770,6 @@
     <t>5조 4820억 4885만</t>
   </si>
   <si>
-    <t>사당행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
-  </si>
-  <si>
-    <t>5조 997억 2848만</t>
-  </si>
-  <si>
     <t>지안히</t>
   </si>
   <si>
@@ -794,7 +794,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
   </si>
   <si>
-    <t>4조 251억 5009만</t>
+    <t>4조 843억 3028만</t>
+  </si>
+  <si>
+    <t>겨농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
+  </si>
+  <si>
+    <t>3조 9000억 3764만</t>
   </si>
   <si>
     <t>전통한우</t>
@@ -812,7 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
   </si>
   <si>
-    <t>3조 4298억 7488만</t>
+    <t>3조 4662억 3545만</t>
   </si>
   <si>
     <t>Pixy</t>
@@ -824,22 +833,22 @@
     <t>3조 435억 6193만</t>
   </si>
   <si>
-    <t>겨농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
-  </si>
-  <si>
-    <t>2조 9572억 5139만</t>
-  </si>
-  <si>
     <t>채빛</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
   </si>
   <si>
-    <t>2조 7334억 7694만</t>
+    <t>2조 8616억 7425만</t>
+  </si>
+  <si>
+    <t>히미노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 6103억 6339만</t>
   </si>
   <si>
     <t>코코호</t>
@@ -848,16 +857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
   </si>
   <si>
-    <t>2조 4775억 7747만</t>
-  </si>
-  <si>
-    <t>히미노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 3013억 13만</t>
+    <t>2조 5001억 7365만</t>
   </si>
   <si>
     <t>홍이수</t>
@@ -866,7 +866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
   </si>
   <si>
-    <t>2조 1363억 5566만</t>
+    <t>2조 2068억 3894만</t>
   </si>
   <si>
     <t>킴머웅</t>
@@ -902,7 +902,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>41조 5368억 1284만</t>
+    <t>41조 7037억 5060만</t>
   </si>
   <si>
     <t>소독약</t>
@@ -911,7 +911,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
   </si>
   <si>
-    <t>17조 6120억 3459만</t>
+    <t>18조 1571억 312만</t>
   </si>
   <si>
     <t>주존사</t>
@@ -920,7 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
   </si>
   <si>
-    <t>14조 9077억 7078만</t>
+    <t>16조 2347억 4300만</t>
   </si>
   <si>
     <t>휘정</t>
@@ -929,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
   </si>
   <si>
-    <t>9조 6125억 3694만</t>
+    <t>9조 8695억 5615만</t>
   </si>
   <si>
     <t>무피</t>
@@ -947,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
   </si>
   <si>
-    <t>6조 8863억 8744만</t>
+    <t>6조 9080억 4196만</t>
   </si>
   <si>
     <t>파산</t>
@@ -956,7 +956,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
   </si>
   <si>
-    <t>6조 4068억 7161만</t>
+    <t>6조 7437억 3524만</t>
   </si>
   <si>
     <t>슈웃</t>
@@ -986,6 +986,15 @@
     <t>5조 3772억 2631만</t>
   </si>
   <si>
+    <t>졸귀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
+  </si>
+  <si>
+    <t>5조 890억 5092만</t>
+  </si>
+  <si>
     <t>강린</t>
   </si>
   <si>
@@ -995,13 +1004,13 @@
     <t>5조 52억 9592만</t>
   </si>
   <si>
-    <t>졸귀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
-  </si>
-  <si>
-    <t>4조 8438억 9104만</t>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>4조 2509억 6170만</t>
   </si>
   <si>
     <t>스파토이</t>
@@ -1010,16 +1019,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 240억 3613만</t>
-  </si>
-  <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>3조 6098억 2513만</t>
+    <t>4조 891억 6456만</t>
+  </si>
+  <si>
+    <t>Rania</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rania</t>
+  </si>
+  <si>
+    <t>3조 9985억 2480만</t>
   </si>
   <si>
     <t>픽홀로</t>
@@ -1040,15 +1049,6 @@
     <t>3조 5115억 5642만</t>
   </si>
   <si>
-    <t>Rania</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rania</t>
-  </si>
-  <si>
-    <t>3조 4486억 9673만</t>
-  </si>
-  <si>
     <t>베르1</t>
   </si>
   <si>
@@ -1082,7 +1082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
   </si>
   <si>
-    <t>2조 8856억 8846만</t>
+    <t>2조 9237억 864만</t>
   </si>
   <si>
     <t>Uhani</t>
@@ -1094,22 +1094,22 @@
     <t>2조 8490억 4859만</t>
   </si>
   <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>2조 7659억 4400만</t>
+  </si>
+  <si>
     <t>가이아의격노</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
   </si>
   <si>
-    <t>2조 7333억 8809만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>2조 7002억 9323만</t>
+    <t>2조 7515억 4604만</t>
   </si>
   <si>
     <t>별렉스b</t>
@@ -1121,6 +1121,15 @@
     <t>2조 6151억 9678만</t>
   </si>
   <si>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>2조 384억 459만</t>
+  </si>
+  <si>
     <t>하숑</t>
   </si>
   <si>
@@ -1130,15 +1139,6 @@
     <t>2조 367억 9637만</t>
   </si>
   <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 8426억 7540만</t>
-  </si>
-  <si>
     <t>potato</t>
   </si>
   <si>
@@ -1154,7 +1154,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
   </si>
   <si>
-    <t>1조 4185억 250만</t>
+    <t>1조 4231억 8184만</t>
   </si>
   <si>
     <t>도레스</t>
@@ -1172,7 +1172,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
   </si>
   <si>
-    <t>81조 6541억 8669만</t>
+    <t>85조 3099억 6271만</t>
   </si>
   <si>
     <t>다정파파</t>
@@ -1181,7 +1181,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>49조 5207억 6718만</t>
+    <t>50조 1289억 7645만</t>
   </si>
   <si>
     <t>천상의빛</t>
@@ -1190,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
   </si>
   <si>
-    <t>12조 3733억 7725만</t>
+    <t>12조 4236억 3512만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
@@ -1205,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
   </si>
   <si>
-    <t>5조 7995억 13만</t>
+    <t>5조 9233억 2118만</t>
   </si>
   <si>
     <t>분함</t>
@@ -1223,7 +1223,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
   </si>
   <si>
-    <t>2조 9582억 1913만</t>
+    <t>3조 1138억 667만</t>
+  </si>
+  <si>
+    <t>늑멍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
+  </si>
+  <si>
+    <t>2조 7760억 1995만</t>
   </si>
   <si>
     <t>기초수급좌파</t>
@@ -1235,13 +1244,13 @@
     <t>2조 6547억 3128만</t>
   </si>
   <si>
-    <t>늑멍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
-  </si>
-  <si>
-    <t>2조 6062억 690만</t>
+    <t>춘봉박2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
+  </si>
+  <si>
+    <t>1조 7858억 5017만</t>
   </si>
   <si>
     <t>갓라딘</t>
@@ -1253,22 +1262,13 @@
     <t>1조 7674억 4038만</t>
   </si>
   <si>
-    <t>춘봉박2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
-  </si>
-  <si>
-    <t>1조 6857억 4180만</t>
-  </si>
-  <si>
     <t>건브</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
   </si>
   <si>
-    <t>1조 4692억 7043만</t>
+    <t>1조 5546억 3661만</t>
   </si>
   <si>
     <t>나폴리맛동산</t>
@@ -1277,7 +1277,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
   </si>
   <si>
-    <t>1조 4355억 7514만</t>
+    <t>1조 4816억 777만</t>
   </si>
   <si>
     <t>망치든여자</t>
@@ -1301,6 +1301,15 @@
     <t>1조 2671억 4754만</t>
   </si>
   <si>
+    <t>선빵쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
+  </si>
+  <si>
+    <t>1조 2334억 7944만</t>
+  </si>
+  <si>
     <t>힐링완이</t>
   </si>
   <si>
@@ -1325,7 +1334,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
   </si>
   <si>
-    <t>1조 1059억 1590만</t>
+    <t>1조 1260억 4093만</t>
   </si>
   <si>
     <t>어허오빠</t>
@@ -1337,22 +1346,13 @@
     <t>1조 568억 2998만</t>
   </si>
   <si>
-    <t>선빵쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
-  </si>
-  <si>
-    <t>1조 525억 5220만</t>
-  </si>
-  <si>
     <t>고지혈증</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
   </si>
   <si>
-    <t>1조 2316만</t>
+    <t>1조 28억 9591만</t>
   </si>
   <si>
     <t>왕구링</t>
@@ -1370,7 +1370,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
   </si>
   <si>
-    <t>7787억 8004만</t>
+    <t>8720억 7180만</t>
+  </si>
+  <si>
+    <t>망치균이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8492억 8216만</t>
   </si>
   <si>
     <t>만능도끼</t>
@@ -1382,22 +1391,13 @@
     <t>7521억 8497만</t>
   </si>
   <si>
-    <t>망치균이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6847억 7382만</t>
-  </si>
-  <si>
     <t>후돌돌</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
   </si>
   <si>
-    <t>5122억 4355만</t>
+    <t>5587억 2994만</t>
   </si>
   <si>
     <t>이선호에용</t>
@@ -1409,7 +1409,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>3471억 1403만</t>
+    <t>3552억 3651만</t>
   </si>
   <si>
     <t>제육아저씨</t>
@@ -1421,16 +1421,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>3368억 8534만</t>
-  </si>
-  <si>
-    <t>우유나</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%EC%9C%A0%EB%82%98</t>
-  </si>
-  <si>
-    <t>2986억 7312만</t>
+    <t>3416억 9933만</t>
   </si>
   <si>
     <t>굴화주민</t>
@@ -1439,207 +1430,207 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
   </si>
   <si>
+    <t>2813억 8310만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
+  </si>
+  <si>
+    <t>81조 4222억 6140만</t>
+  </si>
+  <si>
+    <t>쭈딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
+  </si>
+  <si>
+    <t>45조 2123억 4090만</t>
+  </si>
+  <si>
+    <t>퀸이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>27조 5175억 5855만</t>
+  </si>
+  <si>
+    <t>나는숭이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EC%88%AD%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>12조 1238억 4073만</t>
+  </si>
+  <si>
+    <t>으캬앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
+  </si>
+  <si>
+    <t>5조 4765억 1534만</t>
+  </si>
+  <si>
+    <t>용두산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
+  </si>
+  <si>
+    <t>3조 8492억 7706만</t>
+  </si>
+  <si>
+    <t>형뱁새</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
+  </si>
+  <si>
+    <t>3조 6596억 204만</t>
+  </si>
+  <si>
+    <t>꾜뀨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
+  </si>
+  <si>
+    <t>1조 7824억 4059만</t>
+  </si>
+  <si>
+    <t>팽됴리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%BD%EB%90%B4%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>1조 7090억 4670만</t>
+  </si>
+  <si>
+    <t>수컹수컹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
+  </si>
+  <si>
+    <t>1조 6673억 9108만</t>
+  </si>
+  <si>
+    <t>비비보람</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
+  </si>
+  <si>
+    <t>1조 1038억 8919만</t>
+  </si>
+  <si>
+    <t>점검중임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1조 798억 2267만</t>
+  </si>
+  <si>
+    <t>장헌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
+  </si>
+  <si>
+    <t>9049억 6777만</t>
+  </si>
+  <si>
+    <t>메쓰가키</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%93%B0%EA%B0%80%ED%82%A4</t>
+  </si>
+  <si>
+    <t>8295억 3279만</t>
+  </si>
+  <si>
+    <t>신똥은원딜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
+  </si>
+  <si>
+    <t>6609억 5361만</t>
+  </si>
+  <si>
+    <t>곰굼곰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
+  </si>
+  <si>
+    <t>5587억 3185만</t>
+  </si>
+  <si>
+    <t>다시스타투</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>5571억 6081만</t>
+  </si>
+  <si>
+    <t>뿌뿝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
+  </si>
+  <si>
+    <t>5406억 10만</t>
+  </si>
+  <si>
+    <t>난뭉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%AD%89</t>
+  </si>
+  <si>
+    <t>4935억 4526만</t>
+  </si>
+  <si>
+    <t>쉬누2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EB%88%842</t>
+  </si>
+  <si>
+    <t>4755억 4148만</t>
+  </si>
+  <si>
+    <t>만칠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
+  </si>
+  <si>
+    <t>4224억 6620만</t>
+  </si>
+  <si>
+    <t>박오팔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%A4%ED%8C%94</t>
+  </si>
+  <si>
     <t>92</t>
   </si>
   <si>
-    <t>2813억 8310만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
-  </si>
-  <si>
-    <t>81조 4222억 6140만</t>
-  </si>
-  <si>
-    <t>쭈딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
-  </si>
-  <si>
-    <t>45조 2123억 4090만</t>
-  </si>
-  <si>
-    <t>퀸이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>27조 5175억 5855만</t>
-  </si>
-  <si>
-    <t>나는숭이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%EB%8A%94%EC%88%AD%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>12조 1238억 4073만</t>
-  </si>
-  <si>
-    <t>으캬앙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
-  </si>
-  <si>
-    <t>5조 3057억 4157만</t>
-  </si>
-  <si>
-    <t>용두산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
-  </si>
-  <si>
-    <t>3조 8492억 7706만</t>
-  </si>
-  <si>
-    <t>형뱁새</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
-  </si>
-  <si>
-    <t>3조 5791억 7535만</t>
-  </si>
-  <si>
-    <t>꾜뀨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
-  </si>
-  <si>
-    <t>1조 7824억 4059만</t>
-  </si>
-  <si>
-    <t>수컹수컹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
-  </si>
-  <si>
-    <t>1조 6026억 5550만</t>
-  </si>
-  <si>
-    <t>팽됴리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%BD%EB%90%B4%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>1조 5492억 5497만</t>
-  </si>
-  <si>
-    <t>점검중임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1조 798억 2267만</t>
-  </si>
-  <si>
-    <t>비비보람</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
-  </si>
-  <si>
-    <t>1조 613억 1229만</t>
-  </si>
-  <si>
-    <t>장헌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
-  </si>
-  <si>
-    <t>8663억 5781만</t>
-  </si>
-  <si>
-    <t>메쓰가키</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%93%B0%EA%B0%80%ED%82%A4</t>
-  </si>
-  <si>
-    <t>8295억 3279만</t>
-  </si>
-  <si>
-    <t>신똥은원딜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EB%98%A5%EC%9D%80%EC%9B%90%EB%94%9C</t>
-  </si>
-  <si>
-    <t>6609억 5361만</t>
-  </si>
-  <si>
-    <t>뿌뿝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>5370억 6459만</t>
-  </si>
-  <si>
-    <t>곰굼곰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B0%EA%B5%BC%EA%B3%B0</t>
-  </si>
-  <si>
-    <t>5347억 88만</t>
-  </si>
-  <si>
-    <t>다시스타투</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
-  </si>
-  <si>
-    <t>5304억 699만</t>
-  </si>
-  <si>
-    <t>쉬누2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%89%AC%EB%88%842</t>
-  </si>
-  <si>
-    <t>4755억 4148만</t>
-  </si>
-  <si>
-    <t>난뭉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%9C%EB%AD%89</t>
-  </si>
-  <si>
-    <t>4651억 9020만</t>
-  </si>
-  <si>
-    <t>만칠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
-  </si>
-  <si>
-    <t>4224억 6620만</t>
-  </si>
-  <si>
-    <t>박오팔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EC%98%A4%ED%8C%94</t>
-  </si>
-  <si>
     <t>3568억 9779만</t>
   </si>
   <si>
@@ -1649,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
   </si>
   <si>
-    <t>3164억 2985만</t>
+    <t>3286억 7173만</t>
   </si>
   <si>
     <t>쌀유건</t>
@@ -1658,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
   </si>
   <si>
-    <t>2876억 5455만</t>
+    <t>3069억 4515만</t>
   </si>
   <si>
     <t>문현준2</t>
@@ -1676,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
   </si>
   <si>
-    <t>2333억 7104만</t>
+    <t>2379억 9792만</t>
   </si>
   <si>
     <t>쌀코볼</t>
@@ -1685,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
   </si>
   <si>
-    <t>2134억 8190만</t>
+    <t>2240억 760만</t>
   </si>
   <si>
     <t>해피퀸</t>
@@ -1694,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
   </si>
   <si>
-    <t>2083억 487만</t>
+    <t>2152억 5744만</t>
   </si>
   <si>
     <t>팔라완</t>
@@ -1706,7 +1697,7 @@
     <t>91</t>
   </si>
   <si>
-    <t>1842억 8286만</t>
+    <t>1898억 5109만</t>
   </si>
   <si>
     <t>왕필</t>
@@ -1715,7 +1706,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%95%84</t>
   </si>
   <si>
-    <t>1694억 261만</t>
+    <t>1845억 8958만</t>
   </si>
 </sst>
 </file>
@@ -2284,7 +2275,7 @@
         <v>48</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>39</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>49</v>
@@ -2296,7 +2287,7 @@
         <v>51</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:13">
@@ -2337,7 +2328,7 @@
         <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -2550,7 +2541,7 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>96</v>
@@ -2579,7 +2570,7 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>72</v>
@@ -2611,10 +2602,10 @@
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>104</v>
@@ -2675,13 +2666,13 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2692,22 +2683,22 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>109</v>
@@ -2739,7 +2730,7 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>109</v>
@@ -2771,7 +2762,7 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>109</v>
@@ -2899,7 +2890,7 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>144</v>
@@ -2931,7 +2922,7 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>149</v>
@@ -2963,7 +2954,7 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>109</v>
@@ -3059,7 +3050,7 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>109</v>
@@ -3094,7 +3085,7 @@
         <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>170</v>
@@ -3126,7 +3117,7 @@
         <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>174</v>
@@ -3158,7 +3149,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>178</v>
@@ -3190,7 +3181,7 @@
         <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>182</v>
@@ -3222,7 +3213,7 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>186</v>
@@ -3254,7 +3245,7 @@
         <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>191</v>
@@ -3283,7 +3274,7 @@
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>109</v>
@@ -3496,10 +3487,10 @@
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>210</v>
@@ -3531,7 +3522,7 @@
         <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>213</v>
@@ -3563,7 +3554,7 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>216</v>
@@ -3595,7 +3586,7 @@
         <v>218</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>219</v>
@@ -3656,7 +3647,7 @@
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>109</v>
@@ -3691,7 +3682,7 @@
         <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>228</v>
@@ -3720,10 +3711,10 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>231</v>
@@ -3737,7 +3728,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>232</v>
@@ -3784,7 +3775,7 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>109</v>
@@ -3816,7 +3807,7 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>109</v>
@@ -3848,7 +3839,7 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>109</v>
@@ -3880,7 +3871,7 @@
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>108</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>109</v>
@@ -3944,7 +3935,7 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>109</v>
@@ -3976,7 +3967,7 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>131</v>
@@ -4008,10 +3999,10 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>258</v>
@@ -4043,7 +4034,7 @@
         <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>261</v>
@@ -4072,10 +4063,10 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>109</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>264</v>
@@ -4104,10 +4095,10 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>109</v>
+        <v>149</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>267</v>
@@ -4139,7 +4130,7 @@
         <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>270</v>
@@ -4168,10 +4159,10 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>190</v>
+        <v>89</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>149</v>
+        <v>109</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>273</v>
@@ -4200,10 +4191,10 @@
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>83</v>
+        <v>190</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>109</v>
+        <v>144</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>276</v>
@@ -4267,7 +4258,7 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>282</v>
@@ -4299,7 +4290,7 @@
         <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>285</v>
@@ -4443,7 +4434,7 @@
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>290</v>
@@ -4478,7 +4469,7 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>294</v>
@@ -4507,10 +4498,10 @@
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>297</v>
@@ -4542,7 +4533,7 @@
         <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>300</v>
@@ -4574,7 +4565,7 @@
         <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>303</v>
@@ -4603,10 +4594,10 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>306</v>
@@ -4638,7 +4629,7 @@
         <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>309</v>
@@ -4667,10 +4658,10 @@
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>312</v>
@@ -4716,7 +4707,7 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>316</v>
@@ -4734,7 +4725,7 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>318</v>
@@ -4763,7 +4754,7 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>90</v>
@@ -4795,10 +4786,10 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>324</v>
@@ -4827,10 +4818,10 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>327</v>
@@ -4859,10 +4850,10 @@
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>330</v>
@@ -4891,7 +4882,7 @@
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>109</v>
@@ -4955,7 +4946,7 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>71</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>109</v>
@@ -4987,7 +4978,7 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>109</v>
@@ -5019,7 +5010,7 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>109</v>
@@ -5051,7 +5042,7 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>109</v>
@@ -5083,7 +5074,7 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>109</v>
@@ -5118,7 +5109,7 @@
         <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>354</v>
@@ -5147,7 +5138,7 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>131</v>
@@ -5179,10 +5170,10 @@
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>108</v>
+        <v>89</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>360</v>
@@ -5211,7 +5202,7 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>109</v>
@@ -5243,10 +5234,10 @@
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>131</v>
+        <v>144</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>366</v>
@@ -5275,10 +5266,10 @@
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>149</v>
+        <v>131</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>369</v>
@@ -5307,7 +5298,7 @@
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H29" s="2" t="s">
         <v>131</v>
@@ -5342,7 +5333,7 @@
         <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>375</v>
@@ -5374,7 +5365,7 @@
         <v>71</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>378</v>
@@ -5423,7 +5414,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5488,7 +5479,7 @@
         <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>290</v>
@@ -5497,7 +5488,7 @@
         <v>381</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -5529,7 +5520,7 @@
         <v>384</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -5555,13 +5546,13 @@
         <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>387</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -5593,7 +5584,7 @@
         <v>389</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -5616,16 +5607,16 @@
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>392</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -5657,7 +5648,7 @@
         <v>395</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -5689,7 +5680,7 @@
         <v>398</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -5712,16 +5703,16 @@
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>401</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -5744,16 +5735,16 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>404</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -5761,7 +5752,7 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>405</v>
@@ -5776,16 +5767,16 @@
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>144</v>
+        <v>131</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>407</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -5808,16 +5799,16 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>131</v>
+        <v>149</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>410</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -5840,16 +5831,16 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>413</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -5872,16 +5863,16 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>416</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -5913,7 +5904,7 @@
         <v>420</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -5936,16 +5927,16 @@
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>149</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>423</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -5968,16 +5959,16 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>426</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -6000,16 +5991,16 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>429</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -6032,16 +6023,16 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>432</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -6067,13 +6058,13 @@
         <v>78</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>435</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -6096,7 +6087,7 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>203</v>
@@ -6105,7 +6096,7 @@
         <v>438</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -6137,7 +6128,7 @@
         <v>441</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -6163,13 +6154,13 @@
         <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>444</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -6192,16 +6183,16 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>447</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -6227,13 +6218,13 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>149</v>
+        <v>203</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>450</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -6259,13 +6250,13 @@
         <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>453</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -6297,7 +6288,7 @@
         <v>456</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -6329,7 +6320,7 @@
         <v>460</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -6361,7 +6352,7 @@
         <v>464</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -6384,7 +6375,7 @@
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>218</v>
+        <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>459</v>
@@ -6393,43 +6384,11 @@
         <v>467</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6460,7 +6419,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6527,22 +6485,22 @@
         <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>472</v>
+        <v>468</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>290</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>473</v>
+        <v>469</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -6553,28 +6511,28 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>475</v>
+        <v>471</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>476</v>
+        <v>472</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -6585,13 +6543,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>477</v>
+        <v>473</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>478</v>
+        <v>474</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -6600,13 +6558,13 @@
         <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>479</v>
+        <v>475</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -6617,13 +6575,13 @@
         <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>480</v>
+        <v>476</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -6632,13 +6590,13 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -6649,28 +6607,28 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>483</v>
+        <v>479</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>484</v>
+        <v>480</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>485</v>
+        <v>481</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -6681,28 +6639,28 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>486</v>
+        <v>482</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>487</v>
+        <v>483</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>131</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>488</v>
+        <v>484</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -6713,28 +6671,28 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>489</v>
+        <v>485</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>490</v>
+        <v>486</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>109</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>491</v>
+        <v>487</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -6745,13 +6703,13 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>492</v>
+        <v>488</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>493</v>
+        <v>489</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
@@ -6763,10 +6721,10 @@
         <v>203</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>494</v>
+        <v>490</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -6777,28 +6735,28 @@
         <v>111</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>496</v>
+        <v>492</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>497</v>
+        <v>493</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -6806,31 +6764,31 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>498</v>
+        <v>494</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>108</v>
+        <v>218</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>149</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>500</v>
+        <v>496</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -6841,28 +6799,28 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>501</v>
+        <v>497</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>502</v>
+        <v>498</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>503</v>
+        <v>499</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -6873,28 +6831,28 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>504</v>
+        <v>500</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>505</v>
+        <v>501</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>506</v>
+        <v>502</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -6905,28 +6863,28 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>507</v>
+        <v>503</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>508</v>
+        <v>504</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>203</v>
+        <v>144</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>509</v>
+        <v>505</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -6937,28 +6895,28 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>511</v>
+        <v>507</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>203</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>512</v>
+        <v>508</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -6969,13 +6927,13 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>513</v>
+        <v>509</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>514</v>
+        <v>510</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -6984,13 +6942,13 @@
         <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>515</v>
+        <v>511</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -7001,28 +6959,28 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>516</v>
+        <v>512</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>517</v>
+        <v>513</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>218</v>
+        <v>114</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>518</v>
+        <v>419</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:10">
@@ -7033,28 +6991,28 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>108</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>419</v>
+        <v>517</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
+        <v>518</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="19" spans="1:10">
@@ -7065,28 +7023,28 @@
         <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>523</v>
+        <v>519</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>524</v>
+        <v>520</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>525</v>
+        <v>521</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20" spans="1:10">
@@ -7097,28 +7055,28 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>522</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>527</v>
+        <v>523</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>419</v>
+        <v>203</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>524</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="21" spans="1:10">
@@ -7129,28 +7087,28 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>525</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>530</v>
+        <v>526</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>419</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>527</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="22" spans="1:10">
@@ -7161,28 +7119,28 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>533</v>
+        <v>529</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>534</v>
+        <v>530</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="23" spans="1:10">
@@ -7193,13 +7151,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>535</v>
+        <v>531</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -7208,13 +7166,13 @@
         <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="24" spans="1:10">
@@ -7225,28 +7183,28 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>459</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="25" spans="1:10">
@@ -7257,13 +7215,13 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -7272,13 +7230,13 @@
         <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="1:10">
@@ -7289,28 +7247,28 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>419</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="27" spans="1:10">
@@ -7321,13 +7279,13 @@
         <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -7336,13 +7294,13 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="28" spans="1:10">
@@ -7353,13 +7311,13 @@
         <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
@@ -7368,13 +7326,13 @@
         <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>470</v>
+        <v>533</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="29" spans="1:10">
@@ -7385,13 +7343,13 @@
         <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>554</v>
+        <v>551</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -7400,13 +7358,13 @@
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>459</v>
+        <v>419</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="30" spans="1:10">
@@ -7417,13 +7375,13 @@
         <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
@@ -7432,13 +7390,13 @@
         <v>463</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>559</v>
+        <v>556</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
     <row r="31" spans="1:10">
@@ -7449,28 +7407,28 @@
         <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>560</v>
+        <v>557</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>561</v>
+        <v>558</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>108</v>
+        <v>114</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -248,7 +248,7 @@
     <t>103</t>
   </si>
   <si>
-    <t>26조 8075억 1513만</t>
+    <t>26조 9119억 7254만</t>
   </si>
   <si>
     <t>2</t>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 1815억 3519만</t>
+    <t>11조 2700억 9574만</t>
   </si>
   <si>
     <t>7</t>
@@ -398,7 +398,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>5조 3918억 8444만</t>
+    <t>5조 4012억 9996만</t>
   </si>
   <si>
     <t>12</t>
@@ -485,6 +485,18 @@
     <t>18</t>
   </si>
   <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>3조 7004억 1459만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>강철고튠데</t>
   </si>
   <si>
@@ -494,7 +506,7 @@
     <t>3조 6838억 5909만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -506,18 +518,6 @@
     <t>3조 5006억 2017만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>3조 3744억 7808만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -941,22 +941,22 @@
     <t>8조 9505억 9058만</t>
   </si>
   <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>7조 3300억 8082만</t>
+  </si>
+  <si>
     <t>캐서린</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
   </si>
   <si>
-    <t>6조 9080억 4196만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>6조 7437억 3524만</t>
+    <t>7조 1227억 6786만</t>
   </si>
   <si>
     <t>슈웃</t>
@@ -977,6 +977,15 @@
     <t>5조 7053억 1061만</t>
   </si>
   <si>
+    <t>강린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>5조 4481억 4781만</t>
+  </si>
+  <si>
     <t>임나연</t>
   </si>
   <si>
@@ -995,15 +1004,6 @@
     <t>5조 890억 5092만</t>
   </si>
   <si>
-    <t>강린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>5조 52억 9592만</t>
-  </si>
-  <si>
     <t>YAMAMOTO</t>
   </si>
   <si>
@@ -1127,7 +1127,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
   </si>
   <si>
-    <t>2조 384억 459만</t>
+    <t>2조 396억 1026만</t>
   </si>
   <si>
     <t>하숑</t>
@@ -1436,7 +1436,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AD%EB%A2%B0</t>
   </si>
   <si>
-    <t>81조 4222억 6140만</t>
+    <t>85조 3854억 539만</t>
   </si>
   <si>
     <t>쭈딘</t>
@@ -1445,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
   </si>
   <si>
-    <t>45조 2123억 4090만</t>
+    <t>45조 8192억 145만</t>
   </si>
   <si>
     <t>퀸이</t>
@@ -1454,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%80%B8%EC%9D%B4</t>
   </si>
   <si>
-    <t>27조 5175억 5855만</t>
+    <t>30조 2336억 978만</t>
   </si>
   <si>
     <t>나는숭이</t>
@@ -1490,7 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3조 6596억 204만</t>
+    <t>3조 6602억 6322만</t>
   </si>
   <si>
     <t>꾜뀨</t>
@@ -1592,7 +1592,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
   </si>
   <si>
-    <t>5406억 10만</t>
+    <t>5468억 3111만</t>
   </si>
   <si>
     <t>난뭉</t>
@@ -1631,7 +1631,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>3568억 9779만</t>
+    <t>3684억 9629만</t>
   </si>
   <si>
     <t>해피킹</t>
@@ -1640,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
   </si>
   <si>
-    <t>3286억 7173만</t>
+    <t>3324억 9307만</t>
   </si>
   <si>
     <t>쌀유건</t>
@@ -2954,7 +2954,7 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>109</v>
@@ -2986,10 +2986,10 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>109</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>158</v>
@@ -3021,7 +3021,7 @@
         <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>109</v>
+        <v>131</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>162</v>
@@ -4594,7 +4594,7 @@
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>84</v>
@@ -4626,7 +4626,7 @@
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>71</v>
+        <v>83</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>84</v>
@@ -4722,7 +4722,7 @@
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>84</v>
@@ -4757,7 +4757,7 @@
         <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>90</v>
+        <v>84</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>321</v>
@@ -4786,10 +4786,10 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>324</v>
@@ -4821,7 +4821,7 @@
         <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>109</v>
+        <v>84</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>327</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -16,7 +16,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$29</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Kali!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">숑숑!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">쌈뽕!$A$1:$J$30</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1598" uniqueCount="560">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1608" uniqueCount="562">
   <si>
     <t>guild_name</t>
   </si>
@@ -245,27 +245,30 @@
     <t>섀도어</t>
   </si>
   <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>27조 6177억 2269만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>큐샤프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>26조 9119억 7254만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>큐샤프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>N</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
     <t>20조 8772억 7416만</t>
   </si>
   <si>
@@ -290,6 +293,21 @@
     <t>4</t>
   </si>
   <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>13조 6370억 3703만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
     <t>야가다</t>
   </si>
   <si>
@@ -305,21 +323,6 @@
     <t>13조 2229억 5022만</t>
   </si>
   <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>13조 1760억 5067만</t>
-  </si>
-  <si>
     <t>6</t>
   </si>
   <si>
@@ -329,7 +332,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 2700억 9574만</t>
+    <t>11조 8860억 6865만</t>
   </si>
   <si>
     <t>7</t>
@@ -341,12 +344,39 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 2859억 1203만</t>
+    <t>7조 2979억 3452만</t>
   </si>
   <si>
     <t>8</t>
   </si>
   <si>
+    <t>양정팔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
+  </si>
+  <si>
+    <t>6조 8187억 7629만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>굴러가는일상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>6조 7155억 1566만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>반도</t>
   </si>
   <si>
@@ -359,25 +389,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>6조 3772억 4815만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>굴러가는일상</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
-  </si>
-  <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6조 3436억 8307만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>6조 3933억 9368만</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>포스코퓨처엠</t>
@@ -386,10 +401,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>6조 1164억 6608만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>6조 3741억 1635만</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>우후</t>
@@ -401,7 +416,7 @@
     <t>5조 4012억 9996만</t>
   </si>
   <si>
-    <t>12</t>
+    <t>13</t>
   </si>
   <si>
     <t>흑두부</t>
@@ -410,10 +425,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 7515억 6288만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>4조 7743억 4977만</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -428,7 +443,7 @@
     <t>4조 3985억 226만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>15</t>
   </si>
   <si>
     <t>므고</t>
@@ -437,10 +452,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 1902억 7508만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>4조 2481억 8993만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>4조 170억 8605만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -452,7 +479,22 @@
     <t>3조 9403억 5517만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>18</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>3조 8421억 7386만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -461,112 +503,100 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
   </si>
   <si>
+    <t>3조 7729억 7800만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
+    <t>강철고튠데</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
+  </si>
+  <si>
+    <t>3조 6838억 5909만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>3조 5719억 4137만</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>3조 1414억 4138만</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>덕르코프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
+  </si>
+  <si>
+    <t>2조 7766억 2978만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 7026억 5570만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>2조 4292억 9347만</t>
+  </si>
+  <si>
+    <t>26</t>
+  </si>
+  <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
     <t>97</t>
   </si>
   <si>
-    <t>3조 7729억 7800만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 7652억 4400만</t>
-  </si>
-  <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>3조 7004억 1459만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>3조 6838억 5909만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>3조 5006억 2017만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>3조 1414억 4138만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>덕르코프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
-  </si>
-  <si>
-    <t>2조 7711억 1811만</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 7026억 5570만</t>
-  </si>
-  <si>
-    <t>24</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
-  </si>
-  <si>
     <t>2조 3877억 7093만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>27</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -578,7 +608,7 @@
     <t>2조 2114억 104만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>28</t>
   </si>
   <si>
     <t>여눈</t>
@@ -590,22 +620,7 @@
     <t>2조 1697억 686만</t>
   </si>
   <si>
-    <t>27</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>2조 1168억 8492만</t>
-  </si>
-  <si>
-    <t>28</t>
+    <t>29</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -617,7 +632,7 @@
     <t>2조 663억 1201만</t>
   </si>
   <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>데드캣</t>
@@ -626,778 +641,787 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 200억 173만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>욤지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%A4%EC%A7%80</t>
+    <t>2조 222억 6041만</t>
+  </si>
+  <si>
+    <t>윤기종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
+  </si>
+  <si>
+    <t>57조 2819억 9392만</t>
+  </si>
+  <si>
+    <t>니니니닉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
+  </si>
+  <si>
+    <t>19조 9704억 4578만</t>
+  </si>
+  <si>
+    <t>태태아방</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
+  </si>
+  <si>
+    <t>13조 4687억 3647만</t>
+  </si>
+  <si>
+    <t>뤄드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
+  </si>
+  <si>
+    <t>10조 5089억 5342만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>10조 411억 1296만</t>
+  </si>
+  <si>
+    <t>롱노즈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
+  </si>
+  <si>
+    <t>9조 3375억 9613만</t>
+  </si>
+  <si>
+    <t>주요엘농산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
+  </si>
+  <si>
+    <t>7조 6065억 9341만</t>
+  </si>
+  <si>
+    <t>뱀맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>6조 7803억 2245만</t>
+  </si>
+  <si>
+    <t>삼치김치찜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%EA%B9%80%EC%B9%98%EC%B0%9C</t>
+  </si>
+  <si>
+    <t>6조 6403억 9033만</t>
+  </si>
+  <si>
+    <t>AI루미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>6조 143억 8054만</t>
+  </si>
+  <si>
+    <t>IMABORNHATER</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
+  </si>
+  <si>
+    <t>5조 9309억 2620만</t>
+  </si>
+  <si>
+    <t>조지선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5조 8459억 2046만</t>
+  </si>
+  <si>
+    <t>사당행</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
+  </si>
+  <si>
+    <t>5조 6060억 9236만</t>
+  </si>
+  <si>
+    <t>약한디</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EB%94%94</t>
+  </si>
+  <si>
+    <t>5조 4820억 4885만</t>
+  </si>
+  <si>
+    <t>지안히</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%88%ED%9E%88</t>
+  </si>
+  <si>
+    <t>4조 6846억 5194만</t>
+  </si>
+  <si>
+    <t>전통한우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%86%B5%ED%95%9C%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>4조 5715억 369만</t>
+  </si>
+  <si>
+    <t>올망건빵</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%A7%9D%EA%B1%B4%EB%B9%B5</t>
+  </si>
+  <si>
+    <t>4조 3253억 2975만</t>
+  </si>
+  <si>
+    <t>거푸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
+  </si>
+  <si>
+    <t>4조 2064억 6211만</t>
+  </si>
+  <si>
+    <t>Pixy</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Pixy</t>
+  </si>
+  <si>
+    <t>4조 348억 5847만</t>
+  </si>
+  <si>
+    <t>겨농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
+  </si>
+  <si>
+    <t>3조 9000억 3764만</t>
+  </si>
+  <si>
+    <t>임태호랑나비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%ED%83%9C%ED%98%B8%EB%9E%91%EB%82%98%EB%B9%84</t>
+  </si>
+  <si>
+    <t>3조 4977억 6457만</t>
+  </si>
+  <si>
+    <t>석종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
+  </si>
+  <si>
+    <t>3조 4662억 3545만</t>
+  </si>
+  <si>
+    <t>채빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>2조 8616억 7425만</t>
+  </si>
+  <si>
+    <t>히미노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 6652억 3232만</t>
+  </si>
+  <si>
+    <t>코코호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
+  </si>
+  <si>
+    <t>2조 5001억 7365만</t>
+  </si>
+  <si>
+    <t>홍이수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
+  </si>
+  <si>
+    <t>2조 2068억 3894만</t>
+  </si>
+  <si>
+    <t>킴머웅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%A8%B8%EC%9B%85</t>
+  </si>
+  <si>
+    <t>2조 755억 5068만</t>
+  </si>
+  <si>
+    <t>kingsister</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=kingsister</t>
+  </si>
+  <si>
+    <t>2조 382억 7025만</t>
+  </si>
+  <si>
+    <t>반음</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%9D%8C</t>
+  </si>
+  <si>
+    <t>1조 3764억 3946만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>44조 7381억 1722만</t>
+  </si>
+  <si>
+    <t>소독약</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
+  </si>
+  <si>
+    <t>18조 1784억 9444만</t>
+  </si>
+  <si>
+    <t>주존사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
+  </si>
+  <si>
+    <t>16조 3199억 8725만</t>
+  </si>
+  <si>
+    <t>파산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
+  </si>
+  <si>
+    <t>11조 5169억 397만</t>
+  </si>
+  <si>
+    <t>휘정</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
+  </si>
+  <si>
+    <t>9조 8695억 5615만</t>
+  </si>
+  <si>
+    <t>무피</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
+  </si>
+  <si>
+    <t>8조 9505억 9058만</t>
+  </si>
+  <si>
+    <t>캐서린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>8조 344억 1922만</t>
+  </si>
+  <si>
+    <t>슈웃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
+  </si>
+  <si>
+    <t>6조 5129억 7882만</t>
+  </si>
+  <si>
+    <t>빡박이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 8291억 4708만</t>
+  </si>
+  <si>
+    <t>졸귀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
+  </si>
+  <si>
+    <t>5조 5167억 8565만</t>
+  </si>
+  <si>
+    <t>강린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>5조 4481억 4781만</t>
+  </si>
+  <si>
+    <t>임나연</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
+  </si>
+  <si>
+    <t>5조 3919억 5884만</t>
+  </si>
+  <si>
+    <t>YAMAMOTO</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
+  </si>
+  <si>
+    <t>4조 2509억 6170만</t>
+  </si>
+  <si>
+    <t>스파토이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>4조 891억 6456만</t>
+  </si>
+  <si>
+    <t>Rania</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Rania</t>
+  </si>
+  <si>
+    <t>3조 9985억 2480만</t>
+  </si>
+  <si>
+    <t>픽홀로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>3조 9076억 9715만</t>
+  </si>
+  <si>
+    <t>미진생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
+  </si>
+  <si>
+    <t>3조 5562억 5051만</t>
+  </si>
+  <si>
+    <t>베르1</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
+  </si>
+  <si>
+    <t>3조 2871억 9875만</t>
+  </si>
+  <si>
+    <t>쟈라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>3조 2359억 4543만</t>
+  </si>
+  <si>
+    <t>쟁반짜장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>3조 1243억 7529만</t>
+  </si>
+  <si>
+    <t>바세린</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
+  </si>
+  <si>
+    <t>2조 9237억 864만</t>
+  </si>
+  <si>
+    <t>Uhani</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
+  </si>
+  <si>
+    <t>2조 8490억 4859만</t>
+  </si>
+  <si>
+    <t>가이아의격노</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
+  </si>
+  <si>
+    <t>2조 7761억 3919만</t>
+  </si>
+  <si>
+    <t>깅궁둥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
+  </si>
+  <si>
+    <t>2조 7659억 4400만</t>
+  </si>
+  <si>
+    <t>별렉스b</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
+  </si>
+  <si>
+    <t>2조 6673억 8923만</t>
+  </si>
+  <si>
+    <t>양설유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>2조 396억 1026만</t>
+  </si>
+  <si>
+    <t>하숑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
+  </si>
+  <si>
+    <t>2조 392억 3691만</t>
+  </si>
+  <si>
+    <t>potato</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=potato</t>
+  </si>
+  <si>
+    <t>1조 4832억 5664만</t>
+  </si>
+  <si>
+    <t>양산호수공원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
+  </si>
+  <si>
+    <t>1조 4432억 963만</t>
+  </si>
+  <si>
+    <t>도레스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>1조 3209억 8583만</t>
+  </si>
+  <si>
+    <t>깔개73호</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
+  </si>
+  <si>
+    <t>87조 807억 3622만</t>
+  </si>
+  <si>
+    <t>다정파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>50조 1289억 7645만</t>
+  </si>
+  <si>
+    <t>천상의빛</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
+  </si>
+  <si>
+    <t>12조 8245억 7751만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>6조 8086억 9144만</t>
+  </si>
+  <si>
+    <t>남과장</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
+  </si>
+  <si>
+    <t>5조 9233억 2118만</t>
+  </si>
+  <si>
+    <t>분함</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
+  </si>
+  <si>
+    <t>3조 7213억 2312만</t>
+  </si>
+  <si>
+    <t>숭이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>3조 1138억 667만</t>
+  </si>
+  <si>
+    <t>늑멍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
+  </si>
+  <si>
+    <t>2조 7760억 1995만</t>
+  </si>
+  <si>
+    <t>기초수급좌파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>2조 6547억 3128만</t>
+  </si>
+  <si>
+    <t>춘봉박2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
+  </si>
+  <si>
+    <t>1조 8178억 7559만</t>
+  </si>
+  <si>
+    <t>갓라딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
+  </si>
+  <si>
+    <t>1조 7674억 4038만</t>
+  </si>
+  <si>
+    <t>건브</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
+  </si>
+  <si>
+    <t>1조 6925억 7061만</t>
+  </si>
+  <si>
+    <t>망치든여자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>1조 4931억 4618만</t>
+  </si>
+  <si>
+    <t>나폴리맛동산</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
+  </si>
+  <si>
+    <t>1조 4816억 777만</t>
+  </si>
+  <si>
+    <t>독고패</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
+  </si>
+  <si>
+    <t>1조 2671억 4754만</t>
+  </si>
+  <si>
+    <t>선빵쳐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
+  </si>
+  <si>
+    <t>1조 2350억 6030만</t>
+  </si>
+  <si>
+    <t>마도훈이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 1997억 6801만</t>
+  </si>
+  <si>
+    <t>힐링완이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
   </si>
   <si>
     <t>96</t>
   </si>
   <si>
-    <t>1조 2511억 5308만</t>
-  </si>
-  <si>
-    <t>윤기종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EA%B8%B0%EC%A2%85</t>
-  </si>
-  <si>
-    <t>56조 9456억 9229만</t>
-  </si>
-  <si>
-    <t>니니니닉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%88%EB%8B%88%EB%8B%88%EB%8B%89</t>
-  </si>
-  <si>
-    <t>19조 1873억 9519만</t>
-  </si>
-  <si>
-    <t>태태아방</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%ED%83%9C%EC%95%84%EB%B0%A9</t>
-  </si>
-  <si>
-    <t>13조 4687억 3647만</t>
-  </si>
-  <si>
-    <t>뤄드</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A4%84%EB%93%9C</t>
-  </si>
-  <si>
-    <t>10조 5089억 5342만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EC%82%90%EC%95%84</t>
-  </si>
-  <si>
-    <t>비숍</t>
-  </si>
-  <si>
-    <t>10조 411억 1296만</t>
-  </si>
-  <si>
-    <t>롱노즈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A1%B1%EB%85%B8%EC%A6%88</t>
-  </si>
-  <si>
-    <t>9조 3375억 9613만</t>
-  </si>
-  <si>
-    <t>주요엘농산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%9A%94%EC%97%98%EB%86%8D%EC%82%B0</t>
-  </si>
-  <si>
-    <t>7조 6065억 9341만</t>
-  </si>
-  <si>
-    <t>뱀맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B1%80%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>6조 7803억 2245만</t>
-  </si>
-  <si>
-    <t>삼치김치찜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%BC%EC%B9%98%EA%B9%80%EC%B9%98%EC%B0%9C</t>
-  </si>
-  <si>
-    <t>6조 6403억 9033만</t>
-  </si>
-  <si>
-    <t>AI루미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=AI%EB%A3%A8%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>6조 143억 8054만</t>
-  </si>
-  <si>
-    <t>조지선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%A7%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>5조 8459억 2046만</t>
-  </si>
-  <si>
-    <t>IMABORNHATER</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=IMABORNHATER</t>
-  </si>
-  <si>
-    <t>5조 6292억 9178만</t>
-  </si>
-  <si>
-    <t>사당행</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%8B%B9%ED%96%89</t>
-  </si>
-  <si>
-    <t>5조 5692억 1059만</t>
-  </si>
-  <si>
-    <t>약한디</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BD%ED%95%9C%EB%94%94</t>
-  </si>
-  <si>
-    <t>5조 4820억 4885만</t>
-  </si>
-  <si>
-    <t>지안히</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%EC%95%88%ED%9E%88</t>
-  </si>
-  <si>
-    <t>4조 4230억 6755만</t>
-  </si>
-  <si>
-    <t>올망건빵</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%AC%EB%A7%9D%EA%B1%B4%EB%B9%B5</t>
-  </si>
-  <si>
-    <t>4조 3253억 2975만</t>
-  </si>
-  <si>
-    <t>거푸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%ED%91%B8</t>
-  </si>
-  <si>
-    <t>4조 843억 3028만</t>
-  </si>
-  <si>
-    <t>겨농</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%A8%EB%86%8D</t>
-  </si>
-  <si>
-    <t>3조 9000억 3764만</t>
-  </si>
-  <si>
-    <t>전통한우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%84%ED%86%B5%ED%95%9C%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>3조 8267억 3011만</t>
-  </si>
-  <si>
-    <t>석종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9D%EC%A2%85</t>
-  </si>
-  <si>
-    <t>3조 4662억 3545만</t>
-  </si>
-  <si>
-    <t>Pixy</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Pixy</t>
-  </si>
-  <si>
-    <t>3조 435억 6193만</t>
-  </si>
-  <si>
-    <t>채빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>2조 8616억 7425만</t>
-  </si>
-  <si>
-    <t>히미노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EB%AF%B8%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 6103억 6339만</t>
-  </si>
-  <si>
-    <t>코코호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%ED%98%B8</t>
-  </si>
-  <si>
-    <t>2조 5001억 7365만</t>
-  </si>
-  <si>
-    <t>홍이수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EC%9D%B4%EC%88%98</t>
-  </si>
-  <si>
-    <t>2조 2068억 3894만</t>
-  </si>
-  <si>
-    <t>킴머웅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B4%EB%A8%B8%EC%9B%85</t>
-  </si>
-  <si>
-    <t>2조 755억 5068만</t>
-  </si>
-  <si>
-    <t>kingsister</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=kingsister</t>
-  </si>
-  <si>
-    <t>2조 382억 7025만</t>
-  </si>
-  <si>
-    <t>반음</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%9D%8C</t>
-  </si>
-  <si>
-    <t>1조 3764억 3946만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%91%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>41조 7037억 5060만</t>
-  </si>
-  <si>
-    <t>소독약</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EB%8F%85%EC%95%BD</t>
-  </si>
-  <si>
-    <t>18조 1571억 312만</t>
-  </si>
-  <si>
-    <t>주존사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A3%BC%EC%A1%B4%EC%82%AC</t>
-  </si>
-  <si>
-    <t>16조 2347억 4300만</t>
-  </si>
-  <si>
-    <t>휘정</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9C%98%EC%A0%95</t>
-  </si>
-  <si>
-    <t>9조 8695억 5615만</t>
-  </si>
-  <si>
-    <t>무피</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%ED%94%BC</t>
-  </si>
-  <si>
-    <t>8조 9505억 9058만</t>
-  </si>
-  <si>
-    <t>파산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%82%B0</t>
-  </si>
-  <si>
-    <t>7조 3300억 8082만</t>
-  </si>
-  <si>
-    <t>캐서린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BA%90%EC%84%9C%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>7조 1227억 6786만</t>
-  </si>
-  <si>
-    <t>슈웃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%9B%83</t>
-  </si>
-  <si>
-    <t>6조 125억 9034만</t>
-  </si>
-  <si>
-    <t>빡박이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EB%B0%95%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>5조 7053억 1061만</t>
-  </si>
-  <si>
-    <t>강린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>5조 4481억 4781만</t>
-  </si>
-  <si>
-    <t>임나연</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%84%EB%82%98%EC%97%B0</t>
-  </si>
-  <si>
-    <t>5조 3772억 2631만</t>
-  </si>
-  <si>
-    <t>졸귀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B8%EA%B7%80</t>
-  </si>
-  <si>
-    <t>5조 890억 5092만</t>
-  </si>
-  <si>
-    <t>YAMAMOTO</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=YAMAMOTO</t>
-  </si>
-  <si>
-    <t>4조 2509억 6170만</t>
-  </si>
-  <si>
-    <t>스파토이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%ED%8C%8C%ED%86%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 891억 6456만</t>
-  </si>
-  <si>
-    <t>Rania</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Rania</t>
-  </si>
-  <si>
-    <t>3조 9985억 2480만</t>
-  </si>
-  <si>
-    <t>픽홀로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%BD%ED%99%80%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>3조 5392억 5846만</t>
-  </si>
-  <si>
-    <t>미진생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%B8%EC%A7%84%EC%83%9D</t>
-  </si>
-  <si>
-    <t>3조 5115억 5642만</t>
-  </si>
-  <si>
-    <t>베르1</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%A0%EB%A5%B41</t>
-  </si>
-  <si>
-    <t>3조 2821억 7435만</t>
-  </si>
-  <si>
-    <t>쟈라</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%88%EB%9D%BC</t>
-  </si>
-  <si>
-    <t>3조 2359억 4543만</t>
-  </si>
-  <si>
-    <t>쟁반짜장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9F%81%EB%B0%98%EC%A7%9C%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>3조 431억 2870만</t>
-  </si>
-  <si>
-    <t>바세린</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%94%EC%84%B8%EB%A6%B0</t>
-  </si>
-  <si>
-    <t>2조 9237억 864만</t>
-  </si>
-  <si>
-    <t>Uhani</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Uhani</t>
-  </si>
-  <si>
-    <t>2조 8490억 4859만</t>
-  </si>
-  <si>
-    <t>깅궁둥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EA%B6%81%EB%91%A5</t>
-  </si>
-  <si>
-    <t>2조 7659억 4400만</t>
-  </si>
-  <si>
-    <t>가이아의격노</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%EC%9D%B4%EC%95%84%EC%9D%98%EA%B2%A9%EB%85%B8</t>
-  </si>
-  <si>
-    <t>2조 7515억 4604만</t>
-  </si>
-  <si>
-    <t>별렉스b</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%84%EB%A0%89%EC%8A%A4b</t>
-  </si>
-  <si>
-    <t>2조 6151억 9678만</t>
-  </si>
-  <si>
-    <t>양설유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%84%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>2조 396억 1026만</t>
-  </si>
-  <si>
-    <t>하숑</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EC%88%91</t>
-  </si>
-  <si>
-    <t>2조 367억 9637만</t>
-  </si>
-  <si>
-    <t>potato</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=potato</t>
-  </si>
-  <si>
-    <t>1조 4832억 5664만</t>
-  </si>
-  <si>
-    <t>양산호수공원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%82%B0%ED%98%B8%EC%88%98%EA%B3%B5%EC%9B%90</t>
-  </si>
-  <si>
-    <t>1조 4231억 8184만</t>
-  </si>
-  <si>
-    <t>도레스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%A0%88%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>1조 3209억 8583만</t>
-  </si>
-  <si>
-    <t>깔개73호</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B9%94%EA%B0%9C73%ED%98%B8</t>
-  </si>
-  <si>
-    <t>85조 3099억 6271만</t>
-  </si>
-  <si>
-    <t>다정파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%A0%95%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>50조 1289억 7645만</t>
-  </si>
-  <si>
-    <t>천상의빛</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%9C%EC%83%81%EC%9D%98%EB%B9%9B</t>
-  </si>
-  <si>
-    <t>12조 4236억 3512만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%EC%A0%95%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>6조 7713억 5577만</t>
-  </si>
-  <si>
-    <t>남과장</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%EA%B3%BC%EC%9E%A5</t>
-  </si>
-  <si>
-    <t>5조 9233억 2118만</t>
-  </si>
-  <si>
-    <t>분함</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%84%ED%95%A8</t>
-  </si>
-  <si>
-    <t>3조 7213억 2312만</t>
-  </si>
-  <si>
-    <t>숭이잉</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%AD%EC%9D%B4%EC%9E%89</t>
-  </si>
-  <si>
-    <t>3조 1138억 667만</t>
-  </si>
-  <si>
-    <t>늑멍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8A%91%EB%A9%8D</t>
-  </si>
-  <si>
-    <t>2조 7760억 1995만</t>
-  </si>
-  <si>
-    <t>기초수급좌파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EC%B4%88%EC%88%98%EA%B8%89%EC%A2%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>2조 6547억 3128만</t>
-  </si>
-  <si>
-    <t>춘봉박2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B6%98%EB%B4%89%EB%B0%952</t>
-  </si>
-  <si>
-    <t>1조 7858억 5017만</t>
-  </si>
-  <si>
-    <t>갓라딘</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%9D%BC%EB%94%98</t>
-  </si>
-  <si>
-    <t>1조 7674억 4038만</t>
-  </si>
-  <si>
-    <t>건브</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B4%EB%B8%8C</t>
-  </si>
-  <si>
-    <t>1조 5546억 3661만</t>
-  </si>
-  <si>
-    <t>나폴리맛동산</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%98%ED%8F%B4%EB%A6%AC%EB%A7%9B%EB%8F%99%EC%82%B0</t>
-  </si>
-  <si>
-    <t>1조 4816억 777만</t>
-  </si>
-  <si>
-    <t>망치든여자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EB%93%A0%EC%97%AC%EC%9E%90</t>
+    <t>1조 1855억 5213만</t>
+  </si>
+  <si>
+    <t>I비숍I</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
+  </si>
+  <si>
+    <t>1조 1523억 9005만</t>
+  </si>
+  <si>
+    <t>어허오빠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
+  </si>
+  <si>
+    <t>1조 869억 2663만</t>
+  </si>
+  <si>
+    <t>고지혈증</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
+  </si>
+  <si>
+    <t>1조 222억 16만</t>
+  </si>
+  <si>
+    <t>남편이니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>9131억 5573만</t>
+  </si>
+  <si>
+    <t>왕구링</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
+  </si>
+  <si>
+    <t>8755억 696만</t>
+  </si>
+  <si>
+    <t>망치균이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>8492억 8216만</t>
+  </si>
+  <si>
+    <t>만능도끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
+  </si>
+  <si>
+    <t>7786억 4492만</t>
+  </si>
+  <si>
+    <t>후돌돌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
+  </si>
+  <si>
+    <t>5637억 6502만</t>
+  </si>
+  <si>
+    <t>제육아저씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
   </si>
   <si>
     <t>94</t>
   </si>
   <si>
-    <t>1조 3828억 2857만</t>
-  </si>
-  <si>
-    <t>독고패</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%85%EA%B3%A0%ED%8C%A8</t>
-  </si>
-  <si>
-    <t>1조 2671억 4754만</t>
-  </si>
-  <si>
-    <t>선빵쳐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%B9%B5%EC%B3%90</t>
-  </si>
-  <si>
-    <t>1조 2334억 7944만</t>
-  </si>
-  <si>
-    <t>힐링완이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9E%90%EB%A7%81%EC%99%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 1855억 5213만</t>
-  </si>
-  <si>
-    <t>I비숍I</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=I%EB%B9%84%EC%88%8DI</t>
-  </si>
-  <si>
-    <t>1조 1523억 9005만</t>
-  </si>
-  <si>
-    <t>마도훈이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%88%EB%8F%84%ED%9B%88%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 1260억 4093만</t>
-  </si>
-  <si>
-    <t>어허오빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%B4%ED%97%88%EC%98%A4%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>1조 568억 2998만</t>
-  </si>
-  <si>
-    <t>고지혈증</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EC%A7%80%ED%98%88%EC%A6%9D</t>
-  </si>
-  <si>
-    <t>1조 28억 9591만</t>
-  </si>
-  <si>
-    <t>왕구링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EA%B5%AC%EB%A7%81</t>
-  </si>
-  <si>
-    <t>8755억 696만</t>
-  </si>
-  <si>
-    <t>남편이니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%A8%ED%8E%B8%EC%9D%B4%EB%8B%88</t>
-  </si>
-  <si>
-    <t>8720억 7180만</t>
-  </si>
-  <si>
-    <t>망치균이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%98%EA%B7%A0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>8492억 8216만</t>
-  </si>
-  <si>
-    <t>만능도끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EB%8A%A5%EB%8F%84%EB%81%BC</t>
-  </si>
-  <si>
-    <t>7521억 8497만</t>
-  </si>
-  <si>
-    <t>후돌돌</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9B%84%EB%8F%8C%EB%8F%8C</t>
-  </si>
-  <si>
-    <t>5587억 2994만</t>
+    <t>5448억 8989만</t>
   </si>
   <si>
     <t>이선호에용</t>
@@ -1406,30 +1430,18 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%84%A0%ED%98%B8%EC%97%90%EC%9A%A9</t>
   </si>
   <si>
+    <t>3748억 1851만</t>
+  </si>
+  <si>
+    <t>굴화주민</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
+  </si>
+  <si>
     <t>93</t>
   </si>
   <si>
-    <t>3552억 3651만</t>
-  </si>
-  <si>
-    <t>제육아저씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%9C%A1%EC%95%84%EC%A0%80%EC%94%A8</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>3416억 9933만</t>
-  </si>
-  <si>
-    <t>굴화주민</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%ED%99%94%EC%A3%BC%EB%AF%BC</t>
-  </si>
-  <si>
     <t>2813억 8310만</t>
   </si>
   <si>
@@ -1445,7 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%88%EB%94%98</t>
   </si>
   <si>
-    <t>45조 8192억 145만</t>
+    <t>46조 315억 4321만</t>
   </si>
   <si>
     <t>퀸이</t>
@@ -1472,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%BC%EC%BA%AC%EC%95%99</t>
   </si>
   <si>
-    <t>5조 4765억 1534만</t>
+    <t>5조 7368억 4268만</t>
   </si>
   <si>
     <t>용두산</t>
@@ -1481,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%A9%EB%91%90%EC%82%B0</t>
   </si>
   <si>
-    <t>3조 8492억 7706만</t>
+    <t>3조 9409억 439만</t>
   </si>
   <si>
     <t>형뱁새</t>
@@ -1490,7 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%95%EB%B1%81%EC%83%88</t>
   </si>
   <si>
-    <t>3조 6602억 6322만</t>
+    <t>3조 6783억 2318만</t>
   </si>
   <si>
     <t>꾜뀨</t>
@@ -1499,7 +1511,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%9C%EB%80%A8</t>
   </si>
   <si>
-    <t>1조 7824억 4059만</t>
+    <t>2조 2078억 4397만</t>
+  </si>
+  <si>
+    <t>수컹수컹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
+  </si>
+  <si>
+    <t>1조 7975억 322만</t>
   </si>
   <si>
     <t>팽됴리</t>
@@ -1511,13 +1532,13 @@
     <t>1조 7090억 4670만</t>
   </si>
   <si>
-    <t>수컹수컹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%BB%B9%EC%88%98%EC%BB%B9</t>
-  </si>
-  <si>
-    <t>1조 6673억 9108만</t>
+    <t>점검중임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
+  </si>
+  <si>
+    <t>1조 2020억 7404만</t>
   </si>
   <si>
     <t>비비보람</t>
@@ -1526,16 +1547,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B9%84%EB%B3%B4%EB%9E%8C</t>
   </si>
   <si>
-    <t>1조 1038억 8919만</t>
-  </si>
-  <si>
-    <t>점검중임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%90%EA%B2%80%EC%A4%91%EC%9E%84</t>
-  </si>
-  <si>
-    <t>1조 798억 2267만</t>
+    <t>1조 1068억 1092만</t>
   </si>
   <si>
     <t>장헌</t>
@@ -1544,7 +1556,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%A5%ED%97%8C</t>
   </si>
   <si>
-    <t>9049억 6777만</t>
+    <t>9327억 2983만</t>
   </si>
   <si>
     <t>메쓰가키</t>
@@ -1565,6 +1577,15 @@
     <t>6609억 5361만</t>
   </si>
   <si>
+    <t>다시스타투</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
+  </si>
+  <si>
+    <t>5760억 6702만</t>
+  </si>
+  <si>
     <t>곰굼곰</t>
   </si>
   <si>
@@ -1574,25 +1595,13 @@
     <t>5587억 3185만</t>
   </si>
   <si>
-    <t>다시스타투</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A4%EC%8B%9C%EC%8A%A4%ED%83%80%ED%88%AC</t>
-  </si>
-  <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>5571억 6081만</t>
-  </si>
-  <si>
     <t>뿌뿝</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%BF%9D</t>
   </si>
   <si>
-    <t>5468억 3111만</t>
+    <t>5517억 4759만</t>
   </si>
   <si>
     <t>난뭉</t>
@@ -1619,7 +1628,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%8C%EC%B9%A0</t>
   </si>
   <si>
-    <t>4224억 6620만</t>
+    <t>4337억 2967만</t>
   </si>
   <si>
     <t>박오팔</t>
@@ -1631,7 +1640,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>3684억 9629만</t>
+    <t>3922억 3947만</t>
   </si>
   <si>
     <t>해피킹</t>
@@ -1640,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%82%B9</t>
   </si>
   <si>
-    <t>3324억 9307만</t>
+    <t>3340억 8661만</t>
   </si>
   <si>
     <t>쌀유건</t>
@@ -1649,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%9C%A0%EA%B1%B4</t>
   </si>
   <si>
-    <t>3069억 4515만</t>
+    <t>3103억 8335만</t>
   </si>
   <si>
     <t>문현준2</t>
@@ -1661,22 +1670,31 @@
     <t>2637억 6649만</t>
   </si>
   <si>
+    <t>쌀코볼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
+  </si>
+  <si>
+    <t>2573억 7355만</t>
+  </si>
+  <si>
+    <t>팔라완</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
+  </si>
+  <si>
+    <t>2421억 4612만</t>
+  </si>
+  <si>
     <t>정다몽</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%95%EB%8B%A4%EB%AA%BD</t>
   </si>
   <si>
-    <t>2379억 9792만</t>
-  </si>
-  <si>
-    <t>쌀코볼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8C%80%EC%BD%94%EB%B3%BC</t>
-  </si>
-  <si>
-    <t>2240억 760만</t>
+    <t>2385억 4381만</t>
   </si>
   <si>
     <t>해피퀸</t>
@@ -1685,19 +1703,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%B4%ED%94%BC%ED%80%B8</t>
   </si>
   <si>
-    <t>2152억 5744만</t>
-  </si>
-  <si>
-    <t>팔라완</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8C%94%EB%9D%BC%EC%99%84</t>
-  </si>
-  <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1898억 5109만</t>
+    <t>2214억 282만</t>
   </si>
   <si>
     <t>왕필</t>
@@ -1706,7 +1712,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%99%95%ED%95%84</t>
   </si>
   <si>
-    <t>1845억 8958만</t>
+    <t>1916억 8771만</t>
   </si>
 </sst>
 </file>
@@ -2445,10 +2451,10 @@
         <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2459,28 +2465,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2491,25 +2497,25 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>91</v>
@@ -2541,10 +2547,10 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2555,28 +2561,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2587,28 +2593,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2619,28 +2625,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>108</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2651,28 +2657,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>115</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2683,28 +2689,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="D11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>118</v>
       </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2715,28 +2721,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2747,28 +2753,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>114</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2779,25 +2785,25 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>132</v>
@@ -2826,13 +2832,13 @@
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2843,16 +2849,16 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -2861,10 +2867,10 @@
         <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2875,25 +2881,25 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>145</v>
@@ -2922,13 +2928,13 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2939,25 +2945,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>154</v>
@@ -2986,10 +2992,10 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>158</v>
@@ -3018,10 +3024,10 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>71</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>162</v>
@@ -3050,10 +3056,10 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>166</v>
@@ -3082,10 +3088,10 @@
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>170</v>
@@ -3117,7 +3123,7 @@
         <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>174</v>
@@ -3149,7 +3155,7 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>85</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>178</v>
@@ -3178,13 +3184,13 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>78</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3195,16 +3201,16 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -3213,10 +3219,10 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>149</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3227,28 +3233,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>190</v>
+        <v>78</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3259,28 +3265,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>109</v>
+        <v>153</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3291,28 +3297,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3323,25 +3329,25 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>203</v>
+        <v>119</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>204</v>
@@ -3390,7 +3396,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J29"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3458,7 +3464,7 @@
         <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>207</v>
@@ -3487,10 +3493,10 @@
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>210</v>
@@ -3504,7 +3510,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>211</v>
@@ -3522,7 +3528,7 @@
         <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>213</v>
@@ -3536,7 +3542,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>214</v>
@@ -3554,7 +3560,7 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>216</v>
@@ -3586,7 +3592,7 @@
         <v>218</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>219</v>
@@ -3600,7 +3606,7 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
         <v>220</v>
@@ -3618,7 +3624,7 @@
         <v>78</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>222</v>
@@ -3632,7 +3638,7 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>223</v>
@@ -3647,10 +3653,10 @@
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>225</v>
@@ -3664,7 +3670,7 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
         <v>226</v>
@@ -3682,7 +3688,7 @@
         <v>78</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>228</v>
@@ -3696,7 +3702,7 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>229</v>
@@ -3711,10 +3717,10 @@
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>231</v>
@@ -3728,7 +3734,7 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>232</v>
@@ -3746,7 +3752,7 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>234</v>
@@ -3760,7 +3766,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>235</v>
@@ -3775,10 +3781,10 @@
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>237</v>
@@ -3792,7 +3798,7 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>238</v>
@@ -3807,10 +3813,10 @@
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>240</v>
@@ -3824,7 +3830,7 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
         <v>241</v>
@@ -3839,10 +3845,10 @@
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>243</v>
@@ -3871,10 +3877,10 @@
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>246</v>
@@ -3888,7 +3894,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>247</v>
@@ -3906,7 +3912,7 @@
         <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>249</v>
@@ -3920,7 +3926,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>250</v>
@@ -3935,10 +3941,10 @@
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>252</v>
@@ -3967,10 +3973,10 @@
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>95</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>131</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>255</v>
@@ -3984,7 +3990,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>256</v>
@@ -3999,10 +4005,10 @@
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>90</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>109</v>
+        <v>136</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>258</v>
@@ -4031,10 +4037,10 @@
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>131</v>
+        <v>153</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>261</v>
@@ -4063,10 +4069,10 @@
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>114</v>
+        <v>84</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>264</v>
@@ -4095,10 +4101,10 @@
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>267</v>
@@ -4127,10 +4133,10 @@
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>84</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>270</v>
@@ -4159,10 +4165,10 @@
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>89</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>273</v>
@@ -4191,10 +4197,10 @@
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>190</v>
+        <v>95</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>119</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>276</v>
@@ -4223,10 +4229,10 @@
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>71</v>
+        <v>182</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>131</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>279</v>
@@ -4240,7 +4246,7 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>280</v>
@@ -4258,7 +4264,7 @@
         <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>282</v>
@@ -4272,7 +4278,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>283</v>
@@ -4287,10 +4293,10 @@
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>190</v>
+        <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>285</v>
@@ -4304,7 +4310,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>286</v>
@@ -4319,10 +4325,10 @@
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>203</v>
+        <v>153</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>288</v>
@@ -4331,8 +4337,40 @@
         <v>34</v>
       </c>
     </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="B30" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="I30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="J30" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J29"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4362,6 +4400,7 @@
     <hyperlink ref="E27" r:id="rId26"/>
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
+    <hyperlink ref="E30" r:id="rId29"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4428,19 +4467,19 @@
         <v>42</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>290</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4454,13 +4493,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -4469,10 +4508,10 @@
         <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4483,28 +4522,28 @@
         <v>35</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4515,28 +4554,28 @@
         <v>35</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>78</v>
+        <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4550,25 +4589,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4579,16 +4618,16 @@
         <v>35</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
@@ -4597,10 +4636,10 @@
         <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4611,28 +4650,28 @@
         <v>35</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4643,28 +4682,28 @@
         <v>35</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4675,28 +4714,28 @@
         <v>35</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>190</v>
+        <v>182</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4707,28 +4746,28 @@
         <v>35</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>84</v>
+        <v>96</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4739,28 +4778,28 @@
         <v>35</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4771,16 +4810,16 @@
         <v>35</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
@@ -4789,10 +4828,10 @@
         <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4803,16 +4842,16 @@
         <v>35</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
@@ -4821,10 +4860,10 @@
         <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4838,13 +4877,13 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
@@ -4853,10 +4892,10 @@
         <v>78</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4867,16 +4906,16 @@
         <v>35</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -4885,10 +4924,10 @@
         <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4899,28 +4938,28 @@
         <v>35</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4934,25 +4973,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4963,28 +5002,28 @@
         <v>35</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4998,25 +5037,25 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5030,25 +5069,25 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5062,25 +5101,25 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5094,13 +5133,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -5109,10 +5148,10 @@
         <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5126,25 +5165,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5158,25 +5197,25 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>89</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5190,25 +5229,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5219,16 +5258,16 @@
         <v>35</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -5237,10 +5276,10 @@
         <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5251,28 +5290,28 @@
         <v>35</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5283,28 +5322,28 @@
         <v>35</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5315,16 +5354,16 @@
         <v>35</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
@@ -5333,10 +5372,10 @@
         <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5347,16 +5386,16 @@
         <v>35</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
@@ -5365,10 +5404,10 @@
         <v>71</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5467,25 +5506,25 @@
         <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>290</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -5499,13 +5538,13 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
@@ -5517,7 +5556,7 @@
         <v>72</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -5528,16 +5567,16 @@
         <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -5546,10 +5585,10 @@
         <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -5560,7 +5599,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>51</v>
@@ -5569,7 +5608,7 @@
         <v>51</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>70</v>
@@ -5578,10 +5617,10 @@
         <v>218</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -5595,25 +5634,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -5624,16 +5663,16 @@
         <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
@@ -5642,10 +5681,10 @@
         <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -5656,16 +5695,16 @@
         <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
@@ -5674,10 +5713,10 @@
         <v>78</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -5688,28 +5727,28 @@
         <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -5720,16 +5759,16 @@
         <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
@@ -5738,10 +5777,10 @@
         <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -5752,16 +5791,16 @@
         <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
@@ -5770,10 +5809,10 @@
         <v>71</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -5784,28 +5823,28 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>108</v>
+        <v>118</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -5816,28 +5855,28 @@
         <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -5848,28 +5887,28 @@
         <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>114</v>
+        <v>71</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>149</v>
+        <v>418</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -5883,25 +5922,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>71</v>
+        <v>113</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>419</v>
+        <v>153</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -5912,28 +5951,28 @@
         <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -5944,16 +5983,16 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
@@ -5962,10 +6001,10 @@
         <v>71</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -5979,25 +6018,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -6008,28 +6047,28 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>434</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -6043,25 +6082,25 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>78</v>
+        <v>218</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -6075,13 +6114,13 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
@@ -6090,10 +6129,10 @@
         <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -6107,13 +6146,13 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
@@ -6122,10 +6161,10 @@
         <v>218</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -6139,25 +6178,25 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -6171,25 +6210,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -6203,13 +6242,13 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -6218,10 +6257,10 @@
         <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -6235,13 +6274,13 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
@@ -6250,10 +6289,10 @@
         <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -6264,16 +6303,16 @@
         <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
@@ -6282,10 +6321,10 @@
         <v>218</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -6296,28 +6335,28 @@
         <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -6328,28 +6367,28 @@
         <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="H29" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="I29" s="2" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -6360,28 +6399,28 @@
         <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -6485,19 +6524,19 @@
         <v>59</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>290</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>34</v>
@@ -6511,25 +6550,25 @@
         <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>72</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>34</v>
@@ -6540,16 +6579,16 @@
         <v>52</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>77</v>
@@ -6558,10 +6597,10 @@
         <v>71</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>34</v>
@@ -6572,16 +6611,16 @@
         <v>52</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>77</v>
@@ -6590,10 +6629,10 @@
         <v>71</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>34</v>
@@ -6607,25 +6646,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>34</v>
@@ -6636,28 +6675,28 @@
         <v>52</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>131</v>
+        <v>136</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>34</v>
@@ -6668,28 +6707,28 @@
         <v>52</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>109</v>
+        <v>119</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>34</v>
@@ -6700,16 +6739,16 @@
         <v>52</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>77</v>
@@ -6718,10 +6757,10 @@
         <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>34</v>
@@ -6732,28 +6771,28 @@
         <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>114</v>
+        <v>218</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>34</v>
@@ -6764,28 +6803,28 @@
         <v>52</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>218</v>
+        <v>113</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>34</v>
@@ -6796,28 +6835,28 @@
         <v>52</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>34</v>
@@ -6828,28 +6867,28 @@
         <v>52</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>71</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>34</v>
@@ -6860,28 +6899,28 @@
         <v>52</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>34</v>
@@ -6895,25 +6934,25 @@
         <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>34</v>
@@ -6924,16 +6963,16 @@
         <v>52</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>77</v>
@@ -6942,10 +6981,10 @@
         <v>78</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>187</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>34</v>
@@ -6956,28 +6995,28 @@
         <v>52</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>114</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>34</v>
@@ -6991,25 +7030,25 @@
         <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>517</v>
+        <v>463</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>34</v>
@@ -7020,16 +7059,16 @@
         <v>52</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>77</v>
@@ -7038,10 +7077,10 @@
         <v>218</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>34</v>
@@ -7055,13 +7094,13 @@
         <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>77</v>
@@ -7070,10 +7109,10 @@
         <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>203</v>
+        <v>434</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>34</v>
@@ -7087,25 +7126,25 @@
         <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>34</v>
@@ -7119,25 +7158,25 @@
         <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>517</v>
+        <v>418</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>34</v>
@@ -7151,13 +7190,13 @@
         <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>77</v>
@@ -7166,10 +7205,10 @@
         <v>218</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>34</v>
@@ -7183,25 +7222,25 @@
         <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>459</v>
+        <v>470</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>34</v>
@@ -7215,13 +7254,13 @@
         <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>77</v>
@@ -7230,10 +7269,10 @@
         <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>34</v>
@@ -7247,25 +7286,25 @@
         <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>419</v>
+        <v>463</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>34</v>
@@ -7276,28 +7315,28 @@
         <v>52</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>34</v>
@@ -7308,28 +7347,28 @@
         <v>52</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>78</v>
+        <v>462</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>34</v>
@@ -7340,16 +7379,16 @@
         <v>52</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>77</v>
@@ -7358,10 +7397,10 @@
         <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>419</v>
+        <v>536</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>34</v>
@@ -7372,28 +7411,28 @@
         <v>52</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="H30" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="I30" s="2" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>34</v>
@@ -7404,28 +7443,28 @@
         <v>52</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>555</v>
+        <v>536</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>34</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="558">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="557">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>383</t>
+    <t>389</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>205조 1988억 390만</t>
+    <t>207조 5902억 4049만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.23</t>
+    <t>2026.04.24</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,13 +113,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>382</t>
+    <t>371</t>
   </si>
   <si>
     <t>12위</t>
   </si>
   <si>
-    <t>205조 6317억 2381만</t>
+    <t>221조 1165억 324만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -137,13 +137,13 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>377</t>
+    <t>378</t>
   </si>
   <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>210조 447억 676만</t>
+    <t>215조 1007억 2305만</t>
   </si>
   <si>
     <t>보보네</t>
@@ -158,7 +158,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>385</t>
+    <t>384</t>
   </si>
   <si>
     <t>8위</t>
@@ -167,7 +167,7 @@
     <t>Lv.6</t>
   </si>
   <si>
-    <t>203조 9317억 4680만</t>
+    <t>211조 114억 3427만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -185,7 +185,7 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>381</t>
+    <t>376</t>
   </si>
   <si>
     <t>16위</t>
@@ -194,7 +194,7 @@
     <t>25명</t>
   </si>
   <si>
-    <t>207조 2928억 6383만</t>
+    <t>216조 1259억 6407만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -278,25 +278,28 @@
     <t>다크나이트</t>
   </si>
   <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>18조 9253억 9203만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
     <t>101</t>
   </si>
   <si>
-    <t>18조 9253억 9203만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>13조 6857억 1215만</t>
+    <t>13조 9322억 7271만</t>
   </si>
   <si>
     <t>5</t>
@@ -311,9 +314,6 @@
     <t>보우마스터</t>
   </si>
   <si>
-    <t>102</t>
-  </si>
-  <si>
     <t>13조 2229억 5022만</t>
   </si>
   <si>
@@ -326,7 +326,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 9024억 8753만</t>
+    <t>11조 9918억 5094만</t>
   </si>
   <si>
     <t>7</t>
@@ -338,7 +338,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 3060억 3289만</t>
+    <t>7조 6289억 5284만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +350,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>6조 9166억 3772만</t>
+    <t>7조 551억 4048만</t>
   </si>
   <si>
     <t>9</t>
@@ -371,6 +371,21 @@
     <t>10</t>
   </si>
   <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 4404억 299만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>반도</t>
   </si>
   <si>
@@ -380,24 +395,9 @@
     <t>나이트로드</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
     <t>6조 4098억 9503만</t>
   </si>
   <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>6조 3741억 1635만</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
@@ -419,12 +419,24 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 7743억 4977만</t>
+    <t>4조 9320억 5638만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>4조 4924억 651만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -437,18 +449,6 @@
     <t>4조 3985억 226만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4조 3196억 9131만</t>
-  </si>
-  <si>
     <t>16</t>
   </si>
   <si>
@@ -458,7 +458,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 203억 9184만</t>
+    <t>4조 253억 5355만</t>
   </si>
   <si>
     <t>17</t>
@@ -470,7 +470,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>3조 9403억 5517만</t>
+    <t>4조 51억 9443만</t>
   </si>
   <si>
     <t>18</t>
@@ -485,31 +485,31 @@
     <t>98</t>
   </si>
   <si>
-    <t>3조 8421억 7386만</t>
+    <t>3조 9719억 6394만</t>
   </si>
   <si>
     <t>19</t>
   </si>
   <si>
+    <t>꾸르꾸르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>3조 9234억 6313만</t>
+  </si>
+  <si>
+    <t>20</t>
+  </si>
+  <si>
     <t>아르젠타</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
   </si>
   <si>
-    <t>3조 8160억 9740만</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>꾸르꾸르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>3조 6883억 4554만</t>
+    <t>3조 8330억 4982만</t>
   </si>
   <si>
     <t>21</t>
@@ -533,7 +533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 1414억 4138만</t>
+    <t>3조 2913억 5806만</t>
   </si>
   <si>
     <t>23</t>
@@ -545,12 +545,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 8575억 4038만</t>
+    <t>2조 9098억 6694만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>제스프리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 7544억 4887만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>여븨</t>
   </si>
   <si>
@@ -560,7 +572,7 @@
     <t>2조 7026억 5570만</t>
   </si>
   <si>
-    <t>25</t>
+    <t>26</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -572,7 +584,7 @@
     <t>2조 5587억 7219만</t>
   </si>
   <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>불보독지</t>
@@ -587,7 +599,7 @@
     <t>2조 4292억 9347만</t>
   </si>
   <si>
-    <t>27</t>
+    <t>28</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -602,18 +614,6 @@
     <t>2조 3877억 7093만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>제스프리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 2116억 3503만</t>
-  </si>
-  <si>
     <t>29</t>
   </si>
   <si>
@@ -635,7 +635,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 239억 9809만</t>
+    <t>2조 246억 6143만</t>
+  </si>
+  <si>
+    <t>그때</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C</t>
+  </si>
+  <si>
+    <t>26조 1587억 7806만</t>
   </si>
   <si>
     <t>시명</t>
@@ -662,16 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%A3%BC%EC%86%8C%EC%A3%BC%ED%95%B4</t>
   </si>
   <si>
-    <t>13조 9071억 1442만</t>
-  </si>
-  <si>
-    <t>그때</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C</t>
-  </si>
-  <si>
-    <t>13조 4968억 5171만</t>
+    <t>14조 1626억 126만</t>
   </si>
   <si>
     <t>메소가져와</t>
@@ -707,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
   </si>
   <si>
-    <t>9조 9217억 9789만</t>
+    <t>9조 9319억 1963만</t>
   </si>
   <si>
     <t>vander</t>
@@ -719,6 +719,15 @@
     <t>7조 3095억 176만</t>
   </si>
   <si>
+    <t>무신사할배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>7조 1991억 7101만</t>
+  </si>
+  <si>
     <t>코코연구가2</t>
   </si>
   <si>
@@ -728,13 +737,13 @@
     <t>7조 1647억 6150만</t>
   </si>
   <si>
-    <t>무신사할배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>7조 1377억 4510만</t>
+    <t>인큐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
+  </si>
+  <si>
+    <t>6조 6139억 5179만</t>
   </si>
   <si>
     <t>겜삭</t>
@@ -746,22 +755,22 @@
     <t>6조 4368억 8326만</t>
   </si>
   <si>
-    <t>인큐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
-  </si>
-  <si>
-    <t>6조 2468억 9008만</t>
-  </si>
-  <si>
     <t>효율</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>5조 6638억 3694만</t>
+    <t>6조 2617억 9292만</t>
+  </si>
+  <si>
+    <t>체르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>5조 7041억 7803만</t>
   </si>
   <si>
     <t>운스</t>
@@ -773,15 +782,6 @@
     <t>5조 3995억 859만</t>
   </si>
   <si>
-    <t>체르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>5조 3341억 6432만</t>
-  </si>
-  <si>
     <t>종구왕</t>
   </si>
   <si>
@@ -791,6 +791,21 @@
     <t>5조 1747억 7650만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5조 1487억 699만</t>
+  </si>
+  <si>
+    <t>킹돔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
+  </si>
+  <si>
+    <t>4조 7682억 1823만</t>
+  </si>
+  <si>
     <t>yawaka</t>
   </si>
   <si>
@@ -800,19 +815,13 @@
     <t>4조 6053억 1917만</t>
   </si>
   <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>4조 4670억 5550만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>4조 3945억 2653만</t>
+    <t>신창섭신창섭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
+  </si>
+  <si>
+    <t>4조 2636억 9300만</t>
   </si>
   <si>
     <t>쨍쭝</t>
@@ -821,16 +830,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
   </si>
   <si>
-    <t>4조 2619억 3510만</t>
-  </si>
-  <si>
-    <t>신창섭신창섭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
-  </si>
-  <si>
-    <t>4조 2414억 7747만</t>
+    <t>4조 2636억 9296만</t>
   </si>
   <si>
     <t>코코연구가</t>
@@ -839,7 +839,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%80</t>
   </si>
   <si>
-    <t>4조 528억 7053만</t>
+    <t>4조 687억 9536만</t>
   </si>
   <si>
     <t>이빛낭</t>
@@ -857,7 +857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
   </si>
   <si>
-    <t>3조 8296억 9352만</t>
+    <t>3조 8450억 300만</t>
   </si>
   <si>
     <t>아율마더</t>
@@ -884,7 +884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
   </si>
   <si>
-    <t>3조 2621억 9839만</t>
+    <t>3조 2882억 3017만</t>
   </si>
   <si>
     <t>네그로니</t>
@@ -902,7 +902,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>2조 6990억 7349만</t>
+    <t>2조 7199억 7442만</t>
   </si>
   <si>
     <t>31</t>
@@ -929,7 +929,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%ED%97%88%ED%97%88%ED%97%9D</t>
   </si>
   <si>
-    <t>54조 3540억 9701만</t>
+    <t>55조 2538억 4998만</t>
   </si>
   <si>
     <t>최형사</t>
@@ -938,7 +938,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>25조 1024억 644만</t>
+    <t>25조 1887억 2988만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -965,7 +965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%ED%8D%BC%EC%95%A4%ED%8A%B8</t>
   </si>
   <si>
-    <t>9조 1378억 3801만</t>
+    <t>10조 3167억 1702만</t>
   </si>
   <si>
     <t>쎄도어</t>
@@ -974,7 +974,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8E%84%EB%8F%84%EC%96%B4</t>
   </si>
   <si>
-    <t>6조 2548억 9749만</t>
+    <t>6조 6751억 1083만</t>
+  </si>
+  <si>
+    <t>스응로</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
+  </si>
+  <si>
+    <t>6조 681억 2449만</t>
   </si>
   <si>
     <t>토하루</t>
@@ -983,16 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>5조 9417억 9532만</t>
-  </si>
-  <si>
-    <t>스응로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>5조 9175억 1426만</t>
+    <t>5조 9475억 2302만</t>
   </si>
   <si>
     <t>머겸</t>
@@ -1001,7 +1001,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
   </si>
   <si>
-    <t>5조 5809억 4264만</t>
+    <t>5조 6148억 9060만</t>
+  </si>
+  <si>
+    <t>사본</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
+  </si>
+  <si>
+    <t>5조 3378억 677만</t>
+  </si>
+  <si>
+    <t>abba</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=abba</t>
+  </si>
+  <si>
+    <t>5조 3165억 8775만</t>
   </si>
   <si>
     <t>불소그리스</t>
@@ -1019,7 +1037,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
   </si>
   <si>
-    <t>5조 1728억 6421만</t>
+    <t>5조 1748억 1712만</t>
   </si>
   <si>
     <t>류작</t>
@@ -1031,31 +1049,31 @@
     <t>5조 620억 7034만</t>
   </si>
   <si>
-    <t>abba</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=abba</t>
-  </si>
-  <si>
-    <t>4조 9633억 8081만</t>
-  </si>
-  <si>
-    <t>사본</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
-  </si>
-  <si>
-    <t>4조 8876억 2632만</t>
-  </si>
-  <si>
     <t>인천왕김치언</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
   </si>
   <si>
-    <t>4조 4803억 3145만</t>
+    <t>4조 6789억 8381만</t>
+  </si>
+  <si>
+    <t>윤서u</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
+  </si>
+  <si>
+    <t>4조 3620억 4589만</t>
+  </si>
+  <si>
+    <t>라마킴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
+  </si>
+  <si>
+    <t>4조 3539억 9042만</t>
   </si>
   <si>
     <t>조애니</t>
@@ -1064,25 +1082,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>4조 2092억 5719만</t>
-  </si>
-  <si>
-    <t>윤서u</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
-  </si>
-  <si>
-    <t>4조 1091억 8912만</t>
-  </si>
-  <si>
-    <t>라마킴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
-  </si>
-  <si>
-    <t>3조 8546억 528만</t>
+    <t>4조 2224억 2444만</t>
   </si>
   <si>
     <t>민수심심해</t>
@@ -1100,13 +1100,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>2조 9909억 766만</t>
+    <t>3조 177억 1423만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
   </si>
   <si>
-    <t>2조 8130억 9081만</t>
+    <t>3조 162억 8011만</t>
+  </si>
+  <si>
+    <t>오로치재림</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A1%9C%EC%B9%98%EC%9E%AC%EB%A6%BC</t>
+  </si>
+  <si>
+    <t>2조 7001억 961만</t>
   </si>
   <si>
     <t>승우아빠</t>
@@ -1118,15 +1127,6 @@
     <t>2조 4614억 2347만</t>
   </si>
   <si>
-    <t>오로치재림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A1%9C%EC%B9%98%EC%9E%AC%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>2조 4277억 5163만</t>
-  </si>
-  <si>
     <t>토리꼬리</t>
   </si>
   <si>
@@ -1136,22 +1136,22 @@
     <t>2조 1948억 4810만</t>
   </si>
   <si>
+    <t>문범주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>2조 917억 2418만</t>
+  </si>
+  <si>
     <t>박띵수</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2조 322억 7428만</t>
-  </si>
-  <si>
-    <t>문범주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>2조 300억 5486만</t>
+    <t>2조 398억 219만</t>
   </si>
   <si>
     <t>토리츄</t>
@@ -1169,7 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1조 5067억 6485만</t>
+    <t>1조 5227억 3222만</t>
   </si>
   <si>
     <t>wheesung</t>
@@ -1181,7 +1181,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>2771억 3138만</t>
+    <t>3047억 2423만</t>
   </si>
   <si>
     <t>zl존율율</t>
@@ -1190,10 +1190,10 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>91</t>
-  </si>
-  <si>
-    <t>1798억 5020만</t>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2089억 8071만</t>
   </si>
   <si>
     <t>픅픅</t>
@@ -1202,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
   </si>
   <si>
-    <t>93조 1245억 946만</t>
+    <t>94조 7926억 5567만</t>
   </si>
   <si>
     <t>끝까지힘내자</t>
@@ -1211,7 +1211,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
   </si>
   <si>
-    <t>22조 7569억 4339만</t>
+    <t>26조 5985억 9095만</t>
   </si>
   <si>
     <t>티종</t>
@@ -1232,7 +1232,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
   </si>
   <si>
-    <t>15조 8932억 5887만</t>
+    <t>16조 1125억 2547만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Edom</t>
@@ -1250,6 +1250,15 @@
     <t>7조 842억 6155만</t>
   </si>
   <si>
+    <t>이은제리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>5조 1219억 3069만</t>
+  </si>
+  <si>
     <t>긍궁</t>
   </si>
   <si>
@@ -1259,15 +1268,6 @@
     <t>4조 8275억 1868만</t>
   </si>
   <si>
-    <t>이은제리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>4조 4398억 2320만</t>
-  </si>
-  <si>
     <t>청아씨</t>
   </si>
   <si>
@@ -1292,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
   </si>
   <si>
-    <t>1조 8726억 7611만</t>
+    <t>1조 8729억 5747만</t>
   </si>
   <si>
     <t>반존대</t>
@@ -1322,7 +1322,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>1조 1367억 4377만</t>
+    <t>1조 1570억 9979만</t>
   </si>
   <si>
     <t>망친인생</t>
@@ -1331,7 +1331,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
   </si>
   <si>
-    <t>1조 827억 8602만</t>
+    <t>1조 1022억 2525만</t>
   </si>
   <si>
     <t>서리밍</t>
@@ -1349,7 +1349,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>7668억 4832만</t>
+    <t>8180억 7160만</t>
+  </si>
+  <si>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>7030억 1149만</t>
   </si>
   <si>
     <t>채류진</t>
@@ -1361,6 +1370,15 @@
     <t>6951억 6322만</t>
   </si>
   <si>
+    <t>낀조</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
+  </si>
+  <si>
+    <t>6854억 8392만</t>
+  </si>
+  <si>
     <t>몽샐</t>
   </si>
   <si>
@@ -1370,24 +1388,6 @@
     <t>6831억 1781만</t>
   </si>
   <si>
-    <t>낀조</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
-  </si>
-  <si>
-    <t>6698억 561만</t>
-  </si>
-  <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>6662억 2467만</t>
-  </si>
-  <si>
     <t>달려봐</t>
   </si>
   <si>
@@ -1412,7 +1412,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
   </si>
   <si>
-    <t>5075억 5081만</t>
+    <t>5083억 3073만</t>
   </si>
   <si>
     <t>유해화학물질</t>
@@ -1421,7 +1421,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>4887억 6014만</t>
+    <t>4934억 8056만</t>
+  </si>
+  <si>
+    <t>ENNOY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
+  </si>
+  <si>
+    <t>4539억 8947만</t>
   </si>
   <si>
     <t>쓱싹대선</t>
@@ -1430,16 +1439,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
   </si>
   <si>
-    <t>4422억 4940만</t>
-  </si>
-  <si>
-    <t>ENNOY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
-  </si>
-  <si>
-    <t>4367억 2728만</t>
+    <t>4429억 5201만</t>
   </si>
   <si>
     <t>dvzve</t>
@@ -1457,9 +1457,6 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
     <t>2343억 7259만</t>
   </si>
   <si>
@@ -1472,7 +1469,7 @@
     <t>89</t>
   </si>
   <si>
-    <t>811억 8677만</t>
+    <t>824억 2840만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1484,7 +1481,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>92조 952억 6819만</t>
+    <t>97조 1374억 8843만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1493,7 +1490,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
   </si>
   <si>
-    <t>50조 7576억 1214만</t>
+    <t>51조 9010억 5267만</t>
+  </si>
+  <si>
+    <t>드뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>7조 6372억 7446만</t>
   </si>
   <si>
     <t>덥쳐보니형수</t>
@@ -1502,16 +1508,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
   </si>
   <si>
-    <t>7조 5732억 165만</t>
-  </si>
-  <si>
-    <t>드뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>6조 7959억 4328만</t>
+    <t>7조 6059억 6913만</t>
   </si>
   <si>
     <t>갈맄</t>
@@ -1520,7 +1517,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
   </si>
   <si>
-    <t>6조 6586억 1908만</t>
+    <t>6조 7032억 8917만</t>
   </si>
   <si>
     <t>푸장님</t>
@@ -1529,13 +1526,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EC%9E%A5%EB%8B%98</t>
   </si>
   <si>
-    <t>5조 3161억 4030만</t>
+    <t>5조 4312억 1005만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
   </si>
   <si>
-    <t>5조 2339억 6780만</t>
+    <t>5조 2602억 1932만</t>
   </si>
   <si>
     <t>꾸린이</t>
@@ -1544,7 +1541,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>4조 4970억 6622만</t>
+    <t>4조 8805억 3032만</t>
   </si>
   <si>
     <t>한반</t>
@@ -1553,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 7240억 6872만</t>
+    <t>3조 7477억 843만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1571,7 +1568,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
   </si>
   <si>
-    <t>2조 6643억 7087만</t>
+    <t>2조 8671억 4632만</t>
   </si>
   <si>
     <t>4033</t>
@@ -1580,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=4033</t>
   </si>
   <si>
-    <t>2조 3908억 5090만</t>
+    <t>2조 6047억 9633만</t>
   </si>
   <si>
     <t>세넬</t>
@@ -1589,7 +1586,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>1조 9840억 9989만</t>
+    <t>2조 598억 7312만</t>
+  </si>
+  <si>
+    <t>기뜩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
+  </si>
+  <si>
+    <t>1조 9439억 2961만</t>
   </si>
   <si>
     <t>도밥</t>
@@ -1616,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
   </si>
   <si>
-    <t>1조 7123억 5669만</t>
+    <t>1조 7155억 5729만</t>
   </si>
   <si>
     <t>관둬</t>
@@ -1637,22 +1643,13 @@
     <t>1조 5445억 3805만</t>
   </si>
   <si>
-    <t>기뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>1조 3998억 886만</t>
-  </si>
-  <si>
     <t>챙날</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
   </si>
   <si>
-    <t>1조 1824억 4236만</t>
+    <t>1조 2513억 4514만</t>
   </si>
   <si>
     <t>지히메</t>
@@ -1661,7 +1658,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
   </si>
   <si>
-    <t>9897억 341만</t>
+    <t>1조 194억 2600만</t>
   </si>
   <si>
     <t>홍루이</t>
@@ -1679,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
   </si>
   <si>
-    <t>6008억 9829만</t>
+    <t>6268억 6837만</t>
   </si>
   <si>
     <t>안마시술소</t>
@@ -1688,7 +1685,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
   </si>
   <si>
-    <t>5718억 3409만</t>
+    <t>6168억 2560만</t>
   </si>
   <si>
     <t>성현이여</t>
@@ -1700,7 +1697,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>1995억 5215만</t>
+    <t>2001억 1798만</t>
   </si>
 </sst>
 </file>
@@ -2501,10 +2498,10 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2515,25 +2512,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>95</v>
@@ -2597,7 +2594,7 @@
         <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>103</v>
@@ -2629,7 +2626,7 @@
         <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>107</v>
@@ -2661,7 +2658,7 @@
         <v>111</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>112</v>
@@ -2690,13 +2687,13 @@
         <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="H11" s="2" t="s">
+      <c r="I11" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2707,25 +2704,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>122</v>
@@ -2757,7 +2754,7 @@
         <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>126</v>
@@ -2789,7 +2786,7 @@
         <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>130</v>
@@ -2818,13 +2815,13 @@
         <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2835,25 +2832,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>139</v>
@@ -2885,7 +2882,7 @@
         <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>143</v>
@@ -2917,7 +2914,7 @@
         <v>69</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>147</v>
@@ -2978,10 +2975,10 @@
         <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>156</v>
@@ -3010,10 +3007,10 @@
         <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>160</v>
@@ -3042,10 +3039,10 @@
         <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H22" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>117</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>164</v>
@@ -3077,7 +3074,7 @@
         <v>111</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>168</v>
@@ -3109,7 +3106,7 @@
         <v>69</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>172</v>
@@ -3138,10 +3135,10 @@
         <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>83</v>
+        <v>151</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>176</v>
@@ -3170,10 +3167,10 @@
         <v>75</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>93</v>
+        <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>180</v>
@@ -3202,13 +3199,13 @@
         <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3219,28 +3216,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G28" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="F28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
       <c r="H28" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>190</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3251,25 +3248,25 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>151</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3333,7 +3330,7 @@
         <v>76</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>202</v>
@@ -3450,7 +3447,7 @@
         <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>205</v>
@@ -3479,10 +3476,10 @@
         <v>75</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>208</v>
@@ -3511,10 +3508,10 @@
         <v>75</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>211</v>
@@ -3543,10 +3540,10 @@
         <v>75</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>214</v>
@@ -3560,7 +3557,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>215</v>
@@ -3578,7 +3575,7 @@
         <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>217</v>
@@ -3610,7 +3607,7 @@
         <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>220</v>
@@ -3642,7 +3639,7 @@
         <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
@@ -3674,7 +3671,7 @@
         <v>69</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
@@ -3735,7 +3732,7 @@
         <v>75</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>88</v>
+        <v>121</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>83</v>
@@ -3752,7 +3749,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>233</v>
@@ -3767,10 +3764,10 @@
         <v>75</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>116</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3799,10 +3796,10 @@
         <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
@@ -3831,10 +3828,10 @@
         <v>75</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>83</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
@@ -3866,7 +3863,7 @@
         <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3880,7 +3877,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>245</v>
@@ -3895,7 +3892,7 @@
         <v>75</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>111</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>83</v>
@@ -3927,10 +3924,10 @@
         <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>250</v>
@@ -3962,7 +3959,7 @@
         <v>88</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>253</v>
@@ -3979,25 +3976,25 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>254</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>254</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>255</v>
-      </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>188</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>83</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4011,13 +4008,13 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>257</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>75</v>
@@ -4026,10 +4023,10 @@
         <v>69</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4043,22 +4040,22 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>32</v>
+        <v>259</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>32</v>
+        <v>259</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>260</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>68</v>
+        <v>75</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>184</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>261</v>
@@ -4087,10 +4084,10 @@
         <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>111</v>
+        <v>121</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>264</v>
@@ -4119,10 +4116,10 @@
         <v>75</v>
       </c>
       <c r="G23" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H23" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>83</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>267</v>
@@ -4154,7 +4151,7 @@
         <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>270</v>
@@ -4183,10 +4180,10 @@
         <v>75</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>273</v>
@@ -4218,7 +4215,7 @@
         <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>276</v>
@@ -4250,7 +4247,7 @@
         <v>111</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>279</v>
@@ -4264,7 +4261,7 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>280</v>
@@ -4282,7 +4279,7 @@
         <v>88</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4296,7 +4293,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>283</v>
@@ -4314,7 +4311,7 @@
         <v>111</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>285</v>
@@ -4346,7 +4343,7 @@
         <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>288</v>
@@ -4378,7 +4375,7 @@
         <v>111</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>291</v>
@@ -4560,7 +4557,7 @@
         <v>69</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>303</v>
@@ -4592,7 +4589,7 @@
         <v>76</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>306</v>
@@ -4624,7 +4621,7 @@
         <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>309</v>
@@ -4638,7 +4635,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>310</v>
@@ -4656,7 +4653,7 @@
         <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>312</v>
@@ -4688,7 +4685,7 @@
         <v>69</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>315</v>
@@ -4717,7 +4714,7 @@
         <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>188</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>83</v>
@@ -4749,10 +4746,10 @@
         <v>75</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>184</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>321</v>
@@ -4784,7 +4781,7 @@
         <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>324</v>
@@ -4816,7 +4813,7 @@
         <v>111</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>327</v>
@@ -4830,7 +4827,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>328</v>
@@ -4848,7 +4845,7 @@
         <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>330</v>
@@ -4877,10 +4874,10 @@
         <v>75</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>333</v>
@@ -4912,7 +4909,7 @@
         <v>69</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>336</v>
@@ -4941,10 +4938,10 @@
         <v>75</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>339</v>
@@ -4958,7 +4955,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>340</v>
@@ -4976,7 +4973,7 @@
         <v>69</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>342</v>
@@ -5005,10 +5002,10 @@
         <v>75</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>345</v>
@@ -5037,10 +5034,10 @@
         <v>75</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>348</v>
@@ -5069,10 +5066,10 @@
         <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>116</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>351</v>
@@ -5104,7 +5101,7 @@
         <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>354</v>
@@ -5136,7 +5133,7 @@
         <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>357</v>
@@ -5197,10 +5194,10 @@
         <v>75</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>362</v>
@@ -5229,10 +5226,10 @@
         <v>75</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>365</v>
@@ -5264,7 +5261,7 @@
         <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>368</v>
@@ -5293,10 +5290,10 @@
         <v>75</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>151</v>
+        <v>116</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>371</v>
@@ -5325,10 +5322,10 @@
         <v>75</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>69</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>151</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>374</v>
@@ -5342,7 +5339,7 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>375</v>
@@ -5360,7 +5357,7 @@
         <v>76</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>377</v>
@@ -5374,7 +5371,7 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>378</v>
@@ -5421,7 +5418,7 @@
         <v>75</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="H30" s="2" t="s">
         <v>383</v>
@@ -5636,7 +5633,7 @@
         <v>397</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>398</v>
@@ -5668,7 +5665,7 @@
         <v>76</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>401</v>
@@ -5682,7 +5679,7 @@
         <v>40</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>48</v>
@@ -5700,7 +5697,7 @@
         <v>69</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>403</v>
@@ -5732,7 +5729,7 @@
         <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>406</v>
@@ -5761,10 +5758,10 @@
         <v>75</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>134</v>
+        <v>193</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>409</v>
@@ -5793,10 +5790,10 @@
         <v>75</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>189</v>
+        <v>138</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>412</v>
@@ -5828,7 +5825,7 @@
         <v>69</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>415</v>
@@ -5874,7 +5871,7 @@
         <v>40</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>419</v>
@@ -5892,7 +5889,7 @@
         <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>421</v>
@@ -5924,7 +5921,7 @@
         <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>424</v>
@@ -5956,7 +5953,7 @@
         <v>295</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>427</v>
@@ -6002,7 +5999,7 @@
         <v>40</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>432</v>
@@ -6020,7 +6017,7 @@
         <v>397</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>434</v>
@@ -6113,10 +6110,10 @@
         <v>75</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>430</v>
+        <v>296</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>443</v>
@@ -6145,10 +6142,10 @@
         <v>75</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>69</v>
+        <v>111</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>446</v>
@@ -6180,7 +6177,7 @@
         <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>296</v>
+        <v>430</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>449</v>
@@ -6209,10 +6206,10 @@
         <v>75</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>296</v>
+        <v>383</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>452</v>
@@ -6372,7 +6369,7 @@
         <v>69</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>430</v>
+        <v>296</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>467</v>
@@ -6386,7 +6383,7 @@
         <v>40</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>468</v>
@@ -6404,7 +6401,7 @@
         <v>69</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>383</v>
+        <v>430</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>470</v>
@@ -6418,7 +6415,7 @@
         <v>40</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>471</v>
@@ -6468,10 +6465,10 @@
         <v>69</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>476</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>477</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6485,13 +6482,13 @@
         <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>75</v>
@@ -6500,10 +6497,10 @@
         <v>295</v>
       </c>
       <c r="H31" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>480</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>481</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6602,13 +6599,13 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>483</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>75</v>
@@ -6617,10 +6614,10 @@
         <v>69</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6634,13 +6631,13 @@
         <v>72</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>487</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>75</v>
@@ -6652,7 +6649,7 @@
         <v>70</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6666,25 +6663,25 @@
         <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6698,25 +6695,25 @@
         <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6727,16 +6724,16 @@
         <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>75</v>
@@ -6745,10 +6742,10 @@
         <v>397</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6762,13 +6759,13 @@
         <v>96</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>75</v>
@@ -6777,10 +6774,10 @@
         <v>88</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6800,7 +6797,7 @@
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>68</v>
@@ -6809,10 +6806,10 @@
         <v>69</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6826,13 +6823,13 @@
         <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>75</v>
@@ -6841,10 +6838,10 @@
         <v>69</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6858,25 +6855,25 @@
         <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6890,13 +6887,13 @@
         <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>75</v>
@@ -6905,10 +6902,10 @@
         <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6919,16 +6916,16 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>75</v>
@@ -6937,10 +6934,10 @@
         <v>69</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6954,13 +6951,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>75</v>
@@ -6972,7 +6969,7 @@
         <v>151</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6986,13 +6983,13 @@
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>518</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>519</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>75</v>
@@ -7001,10 +6998,10 @@
         <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7018,13 +7015,13 @@
         <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>75</v>
@@ -7033,10 +7030,10 @@
         <v>69</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>151</v>
+        <v>138</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7047,16 +7044,16 @@
         <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>524</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>525</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>75</v>
@@ -7065,10 +7062,10 @@
         <v>69</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>189</v>
+        <v>151</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7082,13 +7079,13 @@
         <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>75</v>
@@ -7097,10 +7094,10 @@
         <v>69</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7114,25 +7111,25 @@
         <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7146,25 +7143,25 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7178,25 +7175,25 @@
         <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7210,13 +7207,13 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>539</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>540</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>75</v>
@@ -7225,10 +7222,10 @@
         <v>69</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7242,13 +7239,13 @@
         <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>542</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>543</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>75</v>
@@ -7260,7 +7257,7 @@
         <v>430</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7274,13 +7271,13 @@
         <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>75</v>
@@ -7289,10 +7286,10 @@
         <v>69</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>430</v>
+        <v>193</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7306,13 +7303,13 @@
         <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>75</v>
@@ -7324,7 +7321,7 @@
         <v>430</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7338,13 +7335,13 @@
         <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>75</v>
@@ -7353,10 +7350,10 @@
         <v>69</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>430</v>
+        <v>193</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7370,13 +7367,13 @@
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>554</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>554</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>555</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>75</v>
@@ -7385,10 +7382,10 @@
         <v>69</v>
       </c>
       <c r="H26" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>556</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>557</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -10,24 +10,24 @@
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
     <sheet name="GDRAGON" sheetId="3" r:id="rId3"/>
-    <sheet name="청정원" sheetId="4" r:id="rId4"/>
-    <sheet name="Kaia" sheetId="5" r:id="rId5"/>
+    <sheet name="Kaia" sheetId="4" r:id="rId4"/>
+    <sheet name="청정원" sheetId="5" r:id="rId5"/>
     <sheet name="블루스2기" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GDRAGON!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GDRAGON!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Kaia!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">블루스2기!$A$1:$J$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Kaia!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">블루스2기!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">청정원!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">청정원!$A$1:$J$30</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1587" uniqueCount="557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="555">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>389</t>
+    <t>388</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>207조 5902억 4049만</t>
+    <t>209조 35억 7298만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.24</t>
+    <t>2026.04.25</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,13 +113,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>371</t>
+    <t>373</t>
   </si>
   <si>
     <t>12위</t>
   </si>
   <si>
-    <t>221조 1165억 324만</t>
+    <t>223조 4583억 5357만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -128,6 +128,33 @@
     <t>법칙교주</t>
   </si>
   <si>
+    <t>Kaia</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=Kaia</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>368</t>
+  </si>
+  <si>
+    <t>8위</t>
+  </si>
+  <si>
+    <t>Lv.6</t>
+  </si>
+  <si>
+    <t>229조 4115억 3015만</t>
+  </si>
+  <si>
+    <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
+  </si>
+  <si>
+    <t>Edom</t>
+  </si>
+  <si>
     <t>청정원</t>
   </si>
   <si>
@@ -137,45 +164,24 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>378</t>
+    <t>433</t>
+  </si>
+  <si>
+    <t>15위</t>
   </si>
   <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>215조 1007억 2305만</t>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>163조 1060억 6518만</t>
   </si>
   <si>
     <t>보보네</t>
   </si>
   <si>
-    <t>Kaia</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=Kaia</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>384</t>
-  </si>
-  <si>
-    <t>8위</t>
-  </si>
-  <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>211조 114억 3427만</t>
-  </si>
-  <si>
-    <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
-  </si>
-  <si>
-    <t>Edom</t>
-  </si>
-  <si>
     <t>블루스2기</t>
   </si>
   <si>
@@ -185,16 +191,16 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>376</t>
+    <t>374</t>
   </si>
   <si>
     <t>16위</t>
   </si>
   <si>
-    <t>25명</t>
-  </si>
-  <si>
-    <t>216조 1259억 6407만</t>
+    <t>26명</t>
+  </si>
+  <si>
+    <t>222조 9070억 5974만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -242,7 +248,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 4446억 2204만</t>
+    <t>28조 5981억 2484만</t>
   </si>
   <si>
     <t>2</t>
@@ -338,7 +344,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6289억 5284만</t>
+    <t>7조 6510억 5207만</t>
   </si>
   <si>
     <t>8</t>
@@ -350,7 +356,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 551억 4048만</t>
+    <t>7조 2489억 9522만</t>
   </si>
   <si>
     <t>9</t>
@@ -371,31 +377,31 @@
     <t>10</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 4940억 3502만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>6조 4404억 299만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>6조 4098억 9503만</t>
+    <t>6조 4649억 8468만</t>
   </si>
   <si>
     <t>12</t>
@@ -419,7 +425,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 9320억 5638만</t>
+    <t>4조 9811억 5357만</t>
   </si>
   <si>
     <t>14</t>
@@ -431,12 +437,27 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>4조 4924억 651만</t>
+    <t>4조 5621억 2305만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 4977억 2832만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
     <t>뻥뻥</t>
   </si>
   <si>
@@ -449,7 +470,19 @@
     <t>4조 3985억 226만</t>
   </si>
   <si>
-    <t>16</t>
+    <t>17</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
+  </si>
+  <si>
+    <t>4조 645억 8550만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -461,7 +494,7 @@
     <t>4조 253억 5355만</t>
   </si>
   <si>
-    <t>17</t>
+    <t>19</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -473,22 +506,7 @@
     <t>4조 51억 9443만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>3조 9719억 6394만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -500,18 +518,6 @@
     <t>3조 9234억 6313만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>3조 8330억 4982만</t>
-  </si>
-  <si>
     <t>21</t>
   </si>
   <si>
@@ -533,7 +539,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 2913억 5806만</t>
+    <t>3조 3151억 5874만</t>
   </si>
   <si>
     <t>23</t>
@@ -569,7 +575,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 7026억 5570만</t>
+    <t>2조 7249억 3293만</t>
   </si>
   <si>
     <t>26</t>
@@ -611,7 +617,7 @@
     <t>97</t>
   </si>
   <si>
-    <t>2조 3877억 7093만</t>
+    <t>2조 3986억 360만</t>
   </si>
   <si>
     <t>29</t>
@@ -635,7 +641,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 246억 6143만</t>
+    <t>2조 267억 9109만</t>
   </si>
   <si>
     <t>그때</t>
@@ -680,7 +686,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
   </si>
   <si>
-    <t>11조 5373억 1141만</t>
+    <t>11조 9477억 4717만</t>
   </si>
   <si>
     <t>호댕</t>
@@ -716,7 +722,7 @@
     <t>https://mgf.gg/contents/character.php?n=vander</t>
   </si>
   <si>
-    <t>7조 3095억 176만</t>
+    <t>7조 5964억 4776만</t>
   </si>
   <si>
     <t>무신사할배</t>
@@ -725,7 +731,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
   </si>
   <si>
-    <t>7조 1991억 7101만</t>
+    <t>7조 2292억 3002만</t>
   </si>
   <si>
     <t>코코연구가2</t>
@@ -746,15 +752,6 @@
     <t>6조 6139억 5179만</t>
   </si>
   <si>
-    <t>겜삭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B2%9C%EC%82%AD</t>
-  </si>
-  <si>
-    <t>6조 4368억 8326만</t>
-  </si>
-  <si>
     <t>효율</t>
   </si>
   <si>
@@ -773,6 +770,12 @@
     <t>5조 7041억 7803만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5조 5623억 7979만</t>
+  </si>
+  <si>
     <t>운스</t>
   </si>
   <si>
@@ -791,10 +794,13 @@
     <t>5조 1747억 7650만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5조 1487억 699만</t>
+    <t>yawaka</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=yawaka</t>
+  </si>
+  <si>
+    <t>5조 1220억 1649만</t>
   </si>
   <si>
     <t>킹돔</t>
@@ -803,16 +809,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
   </si>
   <si>
-    <t>4조 7682억 1823만</t>
-  </si>
-  <si>
-    <t>yawaka</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=yawaka</t>
-  </si>
-  <si>
-    <t>4조 6053억 1917만</t>
+    <t>4조 8578억 9887만</t>
   </si>
   <si>
     <t>신창섭신창섭</t>
@@ -821,7 +818,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
   </si>
   <si>
-    <t>4조 2636억 9300만</t>
+    <t>4조 2844억 5069만</t>
   </si>
   <si>
     <t>쨍쭝</t>
@@ -830,7 +827,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
   </si>
   <si>
-    <t>4조 2636억 9296만</t>
+    <t>4조 2648억 6791만</t>
   </si>
   <si>
     <t>코코연구가</t>
@@ -857,7 +854,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
   </si>
   <si>
-    <t>3조 8450억 300만</t>
+    <t>3조 8610억 8084만</t>
+  </si>
+  <si>
+    <t>쫑쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
+  </si>
+  <si>
+    <t>3조 5417억 9898만</t>
   </si>
   <si>
     <t>아율마더</t>
@@ -875,16 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 4341억 8486만</t>
-  </si>
-  <si>
-    <t>쫑쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 2882억 3017만</t>
+    <t>3조 5160억 9701만</t>
   </si>
   <si>
     <t>네그로니</t>
@@ -902,10 +899,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>2조 7199억 7442만</t>
-  </si>
-  <si>
-    <t>31</t>
+    <t>2조 9261억 9591만</t>
   </si>
   <si>
     <t>맨셸리</t>
@@ -920,16 +914,289 @@
     <t>95</t>
   </si>
   <si>
-    <t>3980억 4063만</t>
-  </si>
-  <si>
-    <t>크허허헝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%AC%ED%97%88%ED%97%88%ED%97%9D</t>
-  </si>
-  <si>
-    <t>55조 2538억 4998만</t>
+    <t>4126억 8648만</t>
+  </si>
+  <si>
+    <t>픅픅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>109조 2069억 804만</t>
+  </si>
+  <si>
+    <t>끝까지힘내자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
+  </si>
+  <si>
+    <t>28조 7737억 4151만</t>
+  </si>
+  <si>
+    <t>티종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>20조 2481억 75만</t>
+  </si>
+  <si>
+    <t>호뤼뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>16조 2450억 4454만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Edom</t>
+  </si>
+  <si>
+    <t>15조 5459억 9071만</t>
+  </si>
+  <si>
+    <t>야생봄이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7조 5964억 2954만</t>
+  </si>
+  <si>
+    <t>이은제리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>5조 2754억 9069만</t>
+  </si>
+  <si>
+    <t>긍궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
+  </si>
+  <si>
+    <t>4조 8275억 1868만</t>
+  </si>
+  <si>
+    <t>청아씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
+  </si>
+  <si>
+    <t>4조 2370억 3027만</t>
+  </si>
+  <si>
+    <t>KR#9SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>2조 2309억 3914만</t>
+  </si>
+  <si>
+    <t>민규짱짱맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>2조 1417억 9083만</t>
+  </si>
+  <si>
+    <t>반존대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>1조 4439억 4725만</t>
+  </si>
+  <si>
+    <t>츠키유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 2120억 6313만</t>
+  </si>
+  <si>
+    <t>봉찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>1조 1570억 9979만</t>
+  </si>
+  <si>
+    <t>망친인생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
+  </si>
+  <si>
+    <t>1조 1229억 2741만</t>
+  </si>
+  <si>
+    <t>서리밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A6%AC%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>8821억 1213만</t>
+  </si>
+  <si>
+    <t>매력적수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
+  </si>
+  <si>
+    <t>8569억 5829만</t>
+  </si>
+  <si>
+    <t>채류진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
+  </si>
+  <si>
+    <t>7850억 3909만</t>
+  </si>
+  <si>
+    <t>낀조</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
+  </si>
+  <si>
+    <t>7742억 71만</t>
+  </si>
+  <si>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>7413억 4454만</t>
+  </si>
+  <si>
+    <t>몽샐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
+  </si>
+  <si>
+    <t>6831억 1781만</t>
+  </si>
+  <si>
+    <t>달려봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
+  </si>
+  <si>
+    <t>6409억 6907만</t>
+  </si>
+  <si>
+    <t>공또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
+  </si>
+  <si>
+    <t>5766억 521만</t>
+  </si>
+  <si>
+    <t>닝갠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
+  </si>
+  <si>
+    <t>5518억 7119만</t>
+  </si>
+  <si>
+    <t>유해화학물질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
+  </si>
+  <si>
+    <t>4947억 1587만</t>
+  </si>
+  <si>
+    <t>ENNOY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
+  </si>
+  <si>
+    <t>4628억 6007만</t>
+  </si>
+  <si>
+    <t>쓱싹대선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>4536억 1944만</t>
+  </si>
+  <si>
+    <t>dvzve</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
+  </si>
+  <si>
+    <t>4049억 4975만</t>
+  </si>
+  <si>
+    <t>쨍꿍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
+  </si>
+  <si>
+    <t>92</t>
+  </si>
+  <si>
+    <t>2545억 1384만</t>
+  </si>
+  <si>
+    <t>희야미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EC%95%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>957억 9083만</t>
   </si>
   <si>
     <t>최형사</t>
@@ -938,7 +1205,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>25조 1887억 2988만</t>
+    <t>25조 4870억 1271만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -968,6 +1235,15 @@
     <t>10조 3167억 1702만</t>
   </si>
   <si>
+    <t>토하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>6조 7800억 6733만</t>
+  </si>
+  <si>
     <t>쎄도어</t>
   </si>
   <si>
@@ -986,13 +1262,13 @@
     <t>6조 681억 2449만</t>
   </si>
   <si>
-    <t>토하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>5조 9475억 2302만</t>
+    <t>abba</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=abba</t>
+  </si>
+  <si>
+    <t>5조 8087억 8308만</t>
   </si>
   <si>
     <t>머겸</t>
@@ -1001,7 +1277,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
   </si>
   <si>
-    <t>5조 6148억 9060만</t>
+    <t>5조 6791억 2548만</t>
+  </si>
+  <si>
+    <t>류작</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%EC%9E%91</t>
+  </si>
+  <si>
+    <t>5조 5381억 9279만</t>
   </si>
   <si>
     <t>사본</t>
@@ -1010,16 +1295,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
   </si>
   <si>
-    <t>5조 3378억 677만</t>
-  </si>
-  <si>
-    <t>abba</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=abba</t>
-  </si>
-  <si>
-    <t>5조 3165억 8775만</t>
+    <t>5조 4714억 7611만</t>
+  </si>
+  <si>
+    <t>표창넣을게</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
+  </si>
+  <si>
+    <t>5조 3095억 3817만</t>
   </si>
   <si>
     <t>불소그리스</t>
@@ -1031,24 +1316,6 @@
     <t>5조 1920억 8892만</t>
   </si>
   <si>
-    <t>표창넣을게</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
-  </si>
-  <si>
-    <t>5조 1748억 1712만</t>
-  </si>
-  <si>
-    <t>류작</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%EC%9E%91</t>
-  </si>
-  <si>
-    <t>5조 620억 7034만</t>
-  </si>
-  <si>
     <t>인천왕김치언</t>
   </si>
   <si>
@@ -1082,7 +1349,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>4조 2224억 2444만</t>
+    <t>4조 2482억 848만</t>
   </si>
   <si>
     <t>민수심심해</t>
@@ -1094,19 +1361,19 @@
     <t>3조 2698억 7360만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
+  </si>
+  <si>
+    <t>3조 1115억 3156만</t>
+  </si>
+  <si>
     <t>뜨루뜨루</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>3조 177억 1423만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
-  </si>
-  <si>
-    <t>3조 162억 8011만</t>
+    <t>3조 978억 1632만</t>
   </si>
   <si>
     <t>오로치재림</t>
@@ -1124,7 +1391,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%9A%B0%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>2조 4614억 2347만</t>
+    <t>2조 5431억 52만</t>
+  </si>
+  <si>
+    <t>문범주</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>2조 2568억 4452만</t>
   </si>
   <si>
     <t>토리꼬리</t>
@@ -1136,22 +1412,22 @@
     <t>2조 1948억 4810만</t>
   </si>
   <si>
-    <t>문범주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>2조 917억 2418만</t>
-  </si>
-  <si>
     <t>박띵수</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2조 398억 219만</t>
+    <t>2조 1501억 8610만</t>
+  </si>
+  <si>
+    <t>사이비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>1조 7905억 7734만</t>
   </si>
   <si>
     <t>토리츄</t>
@@ -1163,15 +1439,6 @@
     <t>1조 6139억 2384만</t>
   </si>
   <si>
-    <t>사이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>1조 5227억 3222만</t>
-  </si>
-  <si>
     <t>wheesung</t>
   </si>
   <si>
@@ -1190,286 +1457,7 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>2089억 8071만</t>
-  </si>
-  <si>
-    <t>픅픅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
-  </si>
-  <si>
-    <t>94조 7926억 5567만</t>
-  </si>
-  <si>
-    <t>끝까지힘내자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
-  </si>
-  <si>
-    <t>26조 5985억 9095만</t>
-  </si>
-  <si>
-    <t>티종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>20조 2481억 75만</t>
-  </si>
-  <si>
-    <t>호뤼뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>16조 1125억 2547만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Edom</t>
-  </si>
-  <si>
-    <t>15조 673억 264만</t>
-  </si>
-  <si>
-    <t>야생봄이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7조 842억 6155만</t>
-  </si>
-  <si>
-    <t>이은제리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5조 1219억 3069만</t>
-  </si>
-  <si>
-    <t>긍궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
-  </si>
-  <si>
-    <t>4조 8275억 1868만</t>
-  </si>
-  <si>
-    <t>청아씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
-  </si>
-  <si>
-    <t>4조 1319억 6921만</t>
-  </si>
-  <si>
-    <t>KR#9SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>1조 9670억 3733만</t>
-  </si>
-  <si>
-    <t>민규짱짱맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>1조 8729억 5747만</t>
-  </si>
-  <si>
-    <t>반존대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>1조 4439억 4725만</t>
-  </si>
-  <si>
-    <t>츠키유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 1813억 7829만</t>
-  </si>
-  <si>
-    <t>봉찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 1570억 9979만</t>
-  </si>
-  <si>
-    <t>망친인생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
-  </si>
-  <si>
-    <t>1조 1022억 2525만</t>
-  </si>
-  <si>
-    <t>서리밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A6%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>8821억 1213만</t>
-  </si>
-  <si>
-    <t>매력적수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>8180억 7160만</t>
-  </si>
-  <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>7030억 1149만</t>
-  </si>
-  <si>
-    <t>채류진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
-  </si>
-  <si>
-    <t>6951억 6322만</t>
-  </si>
-  <si>
-    <t>낀조</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
-  </si>
-  <si>
-    <t>6854억 8392만</t>
-  </si>
-  <si>
-    <t>몽샐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
-  </si>
-  <si>
-    <t>6831억 1781만</t>
-  </si>
-  <si>
-    <t>달려봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
-  </si>
-  <si>
-    <t>6409억 6907만</t>
-  </si>
-  <si>
-    <t>공또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
-  </si>
-  <si>
-    <t>5735억 39만</t>
-  </si>
-  <si>
-    <t>닝갠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
-  </si>
-  <si>
-    <t>5083억 3073만</t>
-  </si>
-  <si>
-    <t>유해화학물질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
-  </si>
-  <si>
-    <t>4934억 8056만</t>
-  </si>
-  <si>
-    <t>ENNOY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
-  </si>
-  <si>
-    <t>4539억 8947만</t>
-  </si>
-  <si>
-    <t>쓱싹대선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>4429억 5201만</t>
-  </si>
-  <si>
-    <t>dvzve</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
-  </si>
-  <si>
-    <t>4049억 4975만</t>
-  </si>
-  <si>
-    <t>쨍꿍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
-  </si>
-  <si>
-    <t>2343억 7259만</t>
-  </si>
-  <si>
-    <t>희야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>89</t>
-  </si>
-  <si>
-    <t>824억 2840만</t>
+    <t>2102억 3861만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1478,10 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
   </si>
   <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>97조 1374억 8843만</t>
+    <t>99조 6383억 6250만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1490,7 +1475,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
   </si>
   <si>
-    <t>51조 9010억 5267만</t>
+    <t>53조 6569억 4127만</t>
+  </si>
+  <si>
+    <t>덥쳐보니형수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
+  </si>
+  <si>
+    <t>7조 6392억 1498만</t>
   </si>
   <si>
     <t>드뚜</t>
@@ -1502,22 +1496,13 @@
     <t>7조 6372억 7446만</t>
   </si>
   <si>
-    <t>덥쳐보니형수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
-  </si>
-  <si>
-    <t>7조 6059억 6913만</t>
-  </si>
-  <si>
     <t>갈맄</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
   </si>
   <si>
-    <t>6조 7032억 8917만</t>
+    <t>6조 7202억 9097만</t>
   </si>
   <si>
     <t>푸장님</t>
@@ -1526,7 +1511,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EC%9E%A5%EB%8B%98</t>
   </si>
   <si>
-    <t>5조 4312억 1005만</t>
+    <t>5조 6013억 4338만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
@@ -1550,7 +1535,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 7477억 843만</t>
+    <t>3조 7574억 4399만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1559,7 +1544,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%83%A5%EC%93%B0</t>
   </si>
   <si>
-    <t>3조 4142억 2146만</t>
+    <t>3조 7462억 216만</t>
   </si>
   <si>
     <t>침착맨84</t>
@@ -1568,7 +1553,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
   </si>
   <si>
-    <t>2조 8671억 4632만</t>
+    <t>2조 8726억 6261만</t>
   </si>
   <si>
     <t>4033</t>
@@ -1586,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>2조 598억 7312만</t>
+    <t>2조 3288억 1656만</t>
   </si>
   <si>
     <t>기뜩</t>
@@ -1595,7 +1580,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
   </si>
   <si>
-    <t>1조 9439억 2961만</t>
+    <t>1조 9538억 955만</t>
+  </si>
+  <si>
+    <t>리토비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1조 7947억 3068만</t>
   </si>
   <si>
     <t>도밥</t>
@@ -1607,22 +1601,13 @@
     <t>1조 7811억 3646만</t>
   </si>
   <si>
-    <t>리토비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1조 7312억 3157만</t>
-  </si>
-  <si>
     <t>하흙</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
   </si>
   <si>
-    <t>1조 7155억 5729만</t>
+    <t>1조 7166억 7192만</t>
   </si>
   <si>
     <t>관둬</t>
@@ -1631,7 +1616,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
   </si>
   <si>
-    <t>1조 6332억 2171만</t>
+    <t>1조 7154억 1776만</t>
   </si>
   <si>
     <t>라미낭</t>
@@ -1640,7 +1625,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%AF%B8%EB%82%AD</t>
   </si>
   <si>
-    <t>1조 5445억 3805만</t>
+    <t>1조 5723억 8649만</t>
+  </si>
+  <si>
+    <t>야햐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
+  </si>
+  <si>
+    <t>1조 3600억 752만</t>
   </si>
   <si>
     <t>챙날</t>
@@ -1649,7 +1643,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
   </si>
   <si>
-    <t>1조 2513억 4514만</t>
+    <t>1조 3088억 8479만</t>
   </si>
   <si>
     <t>지히메</t>
@@ -1658,7 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
   </si>
   <si>
-    <t>1조 194억 2600만</t>
+    <t>1조 277억 877만</t>
   </si>
   <si>
     <t>홍루이</t>
@@ -1667,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%A3%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>8109억 8697만</t>
+    <t>9477억 2262만</t>
   </si>
   <si>
     <t>이완근</t>
@@ -1676,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
   </si>
   <si>
-    <t>6268억 6837만</t>
+    <t>6790억 5324만</t>
   </si>
   <si>
     <t>안마시술소</t>
@@ -1697,7 +1691,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>2001억 1798만</t>
+    <t>2139억 4828만</t>
   </si>
 </sst>
 </file>
@@ -2219,20 +2213,22 @@
         <v>36</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="K4" s="2"/>
+        <v>39</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>40</v>
+      </c>
       <c r="L4" s="2" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2240,40 +2236,38 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>20</v>
+        <v>48</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>47</v>
-      </c>
+        <v>49</v>
+      </c>
+      <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2281,40 +2275,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="L6" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2352,28 +2346,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2384,7 +2378,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2393,19 +2387,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2416,28 +2410,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2448,28 +2442,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2480,28 +2474,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2512,28 +2506,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2544,28 +2538,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2576,28 +2570,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2608,28 +2602,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2640,28 +2634,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2672,28 +2666,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>69</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2704,28 +2698,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="I12" s="2" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2736,28 +2730,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2768,28 +2762,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2800,28 +2794,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2832,28 +2826,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2864,28 +2858,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>116</v>
+        <v>145</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2896,28 +2890,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>116</v>
-      </c>
       <c r="I18" s="2" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2928,28 +2922,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2960,28 +2954,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2992,28 +2986,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>151</v>
+        <v>119</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3024,28 +3018,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3056,28 +3050,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3088,28 +3082,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3120,28 +3114,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3152,28 +3146,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3184,28 +3178,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3216,28 +3210,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3248,28 +3242,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3280,28 +3274,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3312,28 +3306,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3379,7 +3373,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J32"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3397,28 +3391,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3429,28 +3423,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3461,28 +3455,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3493,28 +3487,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3525,28 +3519,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="I5" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3557,28 +3551,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3589,28 +3583,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3621,28 +3615,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3653,28 +3647,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3685,28 +3679,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3717,28 +3711,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3749,28 +3743,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3781,28 +3775,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3813,28 +3807,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3845,28 +3839,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>76</v>
+        <v>90</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3877,28 +3871,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>245</v>
+        <v>32</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>88</v>
+        <v>190</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3909,28 +3903,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3941,28 +3935,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3973,28 +3967,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>32</v>
+        <v>255</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>255</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>188</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -4005,28 +3999,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4037,28 +4031,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4069,28 +4063,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>89</v>
+        <v>119</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4101,28 +4095,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4133,28 +4127,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>96</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4165,28 +4159,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4197,28 +4191,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>69</v>
+        <v>113</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4229,28 +4223,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4261,28 +4255,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4293,28 +4287,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4325,28 +4319,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4357,67 +4351,35 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>111</v>
+        <v>293</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="32" spans="1:10">
-      <c r="A32" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="E32" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G32" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="H32" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I32" s="2" t="s">
-        <v>297</v>
-      </c>
-      <c r="J32" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J32"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4449,7 +4411,6 @@
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
     <hyperlink ref="E31" r:id="rId30"/>
-    <hyperlink ref="E32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4462,8 +4423,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="3" width="12.7109375" customWidth="1"/>
-    <col min="4" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
@@ -4475,28 +4435,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4507,28 +4467,28 @@
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4539,28 +4499,28 @@
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4571,25 +4531,25 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H4" s="2" t="s">
-        <v>83</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>306</v>
@@ -4603,7 +4563,7 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>307</v>
@@ -4615,13 +4575,13 @@
         <v>308</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>309</v>
@@ -4635,28 +4595,28 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4667,28 +4627,28 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4699,28 +4659,28 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4731,28 +4691,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4763,28 +4723,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4795,28 +4755,28 @@
         <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4827,28 +4787,28 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4859,28 +4819,28 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>333</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4891,28 +4851,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>334</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>335</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>336</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4923,25 +4883,25 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>337</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>338</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>339</v>
@@ -4955,7 +4915,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>340</v>
@@ -4967,13 +4927,13 @@
         <v>341</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>69</v>
+        <v>305</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>89</v>
+        <v>195</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>342</v>
@@ -4987,7 +4947,7 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>343</v>
@@ -4999,13 +4959,13 @@
         <v>344</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>88</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>116</v>
+        <v>195</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>345</v>
@@ -5019,7 +4979,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>346</v>
@@ -5031,13 +4991,13 @@
         <v>347</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>89</v>
+        <v>294</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>348</v>
@@ -5051,7 +5011,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>349</v>
@@ -5063,13 +5023,13 @@
         <v>350</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>116</v>
+        <v>338</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>351</v>
@@ -5083,7 +5043,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>352</v>
@@ -5095,13 +5055,13 @@
         <v>353</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>116</v>
+        <v>338</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>354</v>
@@ -5115,7 +5075,7 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>355</v>
@@ -5127,13 +5087,13 @@
         <v>356</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>357</v>
@@ -5147,28 +5107,28 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>39</v>
+        <v>358</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>39</v>
+        <v>358</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>68</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>295</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5179,28 +5139,28 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5211,28 +5171,28 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>111</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>138</v>
+        <v>294</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5243,28 +5203,28 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>116</v>
+        <v>338</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5275,28 +5235,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>111</v>
+        <v>78</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>116</v>
+        <v>294</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5307,28 +5267,28 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5339,28 +5299,28 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5371,28 +5331,28 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>295</v>
+        <v>113</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>151</v>
+        <v>294</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5403,28 +5363,28 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>121</v>
+        <v>71</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5435,28 +5395,28 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5502,12 +5462,13 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
-    <col min="3" max="4" width="15.7109375" customWidth="1"/>
+    <col min="3" max="3" width="12.7109375" customWidth="1"/>
+    <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
     <col min="9" max="9" width="17.7109375" customWidth="1"/>
@@ -5519,28 +5480,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5548,31 +5509,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5580,31 +5541,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5612,28 +5573,28 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>397</v>
+        <v>90</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>398</v>
@@ -5644,10 +5605,10 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>399</v>
@@ -5659,13 +5620,13 @@
         <v>400</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>401</v>
@@ -5676,31 +5637,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5708,31 +5669,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>116</v>
+        <v>91</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5740,31 +5701,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>190</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>193</v>
+        <v>85</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5772,31 +5733,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>138</v>
+        <v>91</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5804,31 +5765,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>138</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5836,31 +5797,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>151</v>
+        <v>91</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5868,31 +5829,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5900,31 +5861,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5932,31 +5893,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>295</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>193</v>
+        <v>91</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5964,28 +5925,28 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>430</v>
+        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>431</v>
@@ -5996,10 +5957,10 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>432</v>
@@ -6011,13 +5972,13 @@
         <v>433</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>397</v>
+        <v>90</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>193</v>
+        <v>119</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>434</v>
@@ -6028,10 +5989,10 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>435</v>
@@ -6043,13 +6004,13 @@
         <v>436</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>430</v>
+        <v>91</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>437</v>
@@ -6060,10 +6021,10 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>438</v>
@@ -6075,13 +6036,13 @@
         <v>439</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>296</v>
+        <v>119</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>440</v>
@@ -6092,10 +6053,10 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>441</v>
@@ -6107,13 +6068,13 @@
         <v>442</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>296</v>
+        <v>119</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>443</v>
@@ -6124,31 +6085,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>444</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6156,31 +6117,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>447</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>448</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>449</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6188,31 +6149,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>450</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>451</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>383</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>452</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6220,31 +6181,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>453</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>454</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>455</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6252,31 +6213,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>456</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>458</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6284,31 +6245,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>459</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>460</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>461</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6316,31 +6277,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>462</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>463</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>464</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6348,31 +6309,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>465</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>466</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>467</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6380,31 +6341,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>468</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>469</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>430</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>470</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6412,28 +6373,28 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>473</v>
@@ -6444,10 +6405,10 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>474</v>
@@ -6459,13 +6420,13 @@
         <v>475</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>476</v>
@@ -6474,40 +6435,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>478</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6538,7 +6467,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6546,7 +6474,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -6564,28 +6492,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6593,31 +6521,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>481</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>482</v>
+        <v>478</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>483</v>
+        <v>298</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>484</v>
+        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6625,31 +6553,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="H3" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="I3" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6657,31 +6585,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>488</v>
+        <v>483</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>489</v>
+        <v>484</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>397</v>
+        <v>118</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>490</v>
+        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6689,31 +6617,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>491</v>
+        <v>486</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>492</v>
+        <v>487</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>121</v>
+        <v>305</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>493</v>
+        <v>488</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6721,31 +6649,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>397</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
       <c r="I6" s="2" t="s">
-        <v>496</v>
+        <v>491</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6753,31 +6681,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>498</v>
+        <v>493</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>499</v>
+        <v>494</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6785,31 +6713,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>501</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6817,31 +6745,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>502</v>
+        <v>497</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>504</v>
+        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6849,31 +6777,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>506</v>
+        <v>501</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>507</v>
+        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6881,31 +6809,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>508</v>
+        <v>503</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>509</v>
+        <v>504</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>510</v>
+        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6913,31 +6841,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>511</v>
+        <v>506</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>512</v>
+        <v>507</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>513</v>
+        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6945,31 +6873,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>514</v>
+        <v>509</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>515</v>
+        <v>510</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>516</v>
+        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6977,31 +6905,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>517</v>
+        <v>512</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>518</v>
+        <v>513</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>519</v>
+        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -7009,31 +6937,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>520</v>
+        <v>515</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>521</v>
+        <v>516</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>138</v>
+        <v>145</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>522</v>
+        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -7041,31 +6969,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>523</v>
+        <v>518</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>524</v>
+        <v>519</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>525</v>
+        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7073,31 +7001,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>526</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>193</v>
-      </c>
       <c r="I17" s="2" t="s">
-        <v>528</v>
+        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7105,31 +7033,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>529</v>
+        <v>524</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>530</v>
+        <v>525</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>531</v>
+        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7137,31 +7065,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>533</v>
+        <v>528</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>534</v>
+        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7169,31 +7097,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>535</v>
+        <v>530</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>537</v>
+        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7201,31 +7129,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>538</v>
+        <v>533</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>539</v>
+        <v>534</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>69</v>
+        <v>293</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>193</v>
+        <v>140</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>540</v>
+        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7233,31 +7161,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>541</v>
+        <v>536</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>542</v>
+        <v>537</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>430</v>
+        <v>195</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>543</v>
+        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7265,31 +7193,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>544</v>
+        <v>539</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>545</v>
+        <v>540</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>69</v>
+        <v>84</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>546</v>
+        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7297,31 +7225,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>547</v>
+        <v>542</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>548</v>
+        <v>543</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>430</v>
+        <v>195</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>549</v>
+        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7329,31 +7257,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>550</v>
+        <v>545</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>551</v>
+        <v>546</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>69</v>
+        <v>78</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>193</v>
+        <v>338</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>552</v>
+        <v>547</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7361,38 +7289,70 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="J26" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="B27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>553</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>553</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="F26" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>555</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>556</v>
-      </c>
-      <c r="J26" s="2" t="s">
+      <c r="J27" s="2" t="s">
         <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J26"/>
+  <autoFilter ref="A1:J27"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -7419,6 +7379,7 @@
     <hyperlink ref="E24" r:id="rId23"/>
     <hyperlink ref="E25" r:id="rId24"/>
     <hyperlink ref="E26" r:id="rId25"/>
+    <hyperlink ref="E27" r:id="rId26"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="555">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="554">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>388</t>
+    <t>394</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>209조 35억 7298만</t>
+    <t>210조 1486억 3414만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.25</t>
+    <t>2026.04.26</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,13 +113,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>373</t>
+    <t>376</t>
   </si>
   <si>
     <t>12위</t>
   </si>
   <si>
-    <t>223조 4583억 5357만</t>
+    <t>226조 5971억 2413만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -143,10 +143,10 @@
     <t>8위</t>
   </si>
   <si>
-    <t>Lv.6</t>
-  </si>
-  <si>
-    <t>229조 4115억 3015만</t>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>231조 6968억 1979만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -164,19 +164,16 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>433</t>
+    <t>435</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
     <t>29명</t>
   </si>
   <si>
-    <t>163조 1060억 6518만</t>
+    <t>163조 6861억 8247만</t>
   </si>
   <si>
     <t>보보네</t>
@@ -191,16 +188,16 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>374</t>
-  </si>
-  <si>
-    <t>16위</t>
+    <t>375</t>
+  </si>
+  <si>
+    <t>17위</t>
   </si>
   <si>
     <t>26명</t>
   </si>
   <si>
-    <t>222조 9070억 5974만</t>
+    <t>227조 4118억 971만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -248,7 +245,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 5981억 2484만</t>
+    <t>28조 7523억 2933만</t>
   </si>
   <si>
     <t>2</t>
@@ -344,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6510억 5207만</t>
+    <t>7조 6716억 4082만</t>
   </si>
   <si>
     <t>8</t>
@@ -356,12 +353,30 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 2489억 9522만</t>
+    <t>7조 3311억 6274만</t>
   </si>
   <si>
     <t>9</t>
   </si>
   <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>6조 8265억 4136만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -374,24 +389,6 @@
     <t>6조 7155억 1566만</t>
   </si>
   <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>6조 4940억 3502만</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
@@ -431,6 +428,21 @@
     <t>14</t>
   </si>
   <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>99</t>
+  </si>
+  <si>
+    <t>4조 6273억 4164만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
@@ -440,7 +452,7 @@
     <t>4조 5621억 2305만</t>
   </si>
   <si>
-    <t>15</t>
+    <t>16</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -452,37 +464,34 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 4977억 2832만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>99</t>
-  </si>
-  <si>
-    <t>4조 3985억 226만</t>
+    <t>4조 5139억 1714만</t>
   </si>
   <si>
     <t>17</t>
   </si>
   <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>4조 3613억 1130만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>4조 645억 8550만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>4조 768억 9265만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -491,19 +500,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 253억 5355만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 51억 9443만</t>
+    <t>4조 366억 9775만</t>
   </si>
   <si>
     <t>20</t>
@@ -515,7 +512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9234억 6313만</t>
+    <t>3조 9589억 1764만</t>
   </si>
   <si>
     <t>21</t>
@@ -539,7 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 3151억 5874만</t>
+    <t>3조 3304억 6250만</t>
   </si>
   <si>
     <t>23</t>
@@ -551,7 +548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 9098억 6694만</t>
+    <t>2조 9156억 802만</t>
   </si>
   <si>
     <t>24</t>
@@ -593,6 +590,18 @@
     <t>27</t>
   </si>
   <si>
+    <t>자유이용껀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+  </si>
+  <si>
+    <t>2조 4519억 4405만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
     <t>불보독지</t>
   </si>
   <si>
@@ -605,457 +614,454 @@
     <t>2조 4292억 9347만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>자유이용껀</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
+    <t>29</t>
+  </si>
+  <si>
+    <t>여눈</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
+  </si>
+  <si>
+    <t>2조 3292억 507만</t>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>2조 275억 8658만</t>
+  </si>
+  <si>
+    <t>그때</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C</t>
+  </si>
+  <si>
+    <t>26조 1587억 7806만</t>
+  </si>
+  <si>
+    <t>시명</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%AA%85</t>
+  </si>
+  <si>
+    <t>20조 9060억 3624만</t>
+  </si>
+  <si>
+    <t>소주소주해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%A3%BC%EC%86%8C%EC%A3%BC%ED%95%B4</t>
+  </si>
+  <si>
+    <t>14조 3697억 2920만</t>
+  </si>
+  <si>
+    <t>v번개의신v</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=v%EB%B2%88%EA%B0%9C%EC%9D%98%EC%8B%A0v</t>
+  </si>
+  <si>
+    <t>14조 2286억 8809만</t>
+  </si>
+  <si>
+    <t>메소가져와</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
+  </si>
+  <si>
+    <t>12조 8520억 5517만</t>
+  </si>
+  <si>
+    <t>엔도르시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EB%8F%84%EB%A5%B4%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>12조 5594억 1545만</t>
+  </si>
+  <si>
+    <t>호댕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%8C%95</t>
+  </si>
+  <si>
+    <t>11조 683억 25만</t>
+  </si>
+  <si>
+    <t>르밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>9조 9521억 6334만</t>
+  </si>
+  <si>
+    <t>vander</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=vander</t>
+  </si>
+  <si>
+    <t>7조 6700억 9729만</t>
+  </si>
+  <si>
+    <t>무신사할배</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
+  </si>
+  <si>
+    <t>7조 2672억 7779만</t>
+  </si>
+  <si>
+    <t>코코연구가2</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%802</t>
+  </si>
+  <si>
+    <t>7조 1647억 6150만</t>
+  </si>
+  <si>
+    <t>인큐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
+  </si>
+  <si>
+    <t>6조 6139억 5179만</t>
+  </si>
+  <si>
+    <t>효율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>6조 2617억 9292만</t>
+  </si>
+  <si>
+    <t>종구왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
+  </si>
+  <si>
+    <t>5조 8246억 875만</t>
+  </si>
+  <si>
+    <t>체르</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
+  </si>
+  <si>
+    <t>5조 7041억 7803만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>5조 6392억 7905만</t>
+  </si>
+  <si>
+    <t>운스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>5조 3995억 859만</t>
+  </si>
+  <si>
+    <t>yawaka</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=yawaka</t>
+  </si>
+  <si>
+    <t>5조 1220억 1649만</t>
+  </si>
+  <si>
+    <t>킹돔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
+  </si>
+  <si>
+    <t>5조 1064억 7414만</t>
+  </si>
+  <si>
+    <t>신창섭신창섭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
+  </si>
+  <si>
+    <t>4조 4970억 9776만</t>
+  </si>
+  <si>
+    <t>쨍쭝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
+  </si>
+  <si>
+    <t>4조 3407억 5801만</t>
+  </si>
+  <si>
+    <t>요계</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
+  </si>
+  <si>
+    <t>4조 3163억 8988만</t>
+  </si>
+  <si>
+    <t>코코연구가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%80</t>
+  </si>
+  <si>
+    <t>4조 1336억 3721만</t>
+  </si>
+  <si>
+    <t>이빛낭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
+  </si>
+  <si>
+    <t>3조 9593억 1941만</t>
+  </si>
+  <si>
+    <t>쫑쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
+  </si>
+  <si>
+    <t>3조 5908억 3222만</t>
+  </si>
+  <si>
+    <t>13미니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
+  </si>
+  <si>
+    <t>3조 5349억 5464만</t>
+  </si>
+  <si>
+    <t>아율마더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
+  </si>
+  <si>
+    <t>3조 5299억 4117만</t>
+  </si>
+  <si>
+    <t>아율파더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
+  </si>
+  <si>
+    <t>3조 7억 3896만</t>
+  </si>
+  <si>
+    <t>네그로니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>2조 9606억 9107만</t>
+  </si>
+  <si>
+    <t>맨셸리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%EC%85%B8%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>96</t>
+  </si>
+  <si>
+    <t>4177억 9177만</t>
+  </si>
+  <si>
+    <t>픅픅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>109조 5488억 1465만</t>
+  </si>
+  <si>
+    <t>끝까지힘내자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
+  </si>
+  <si>
+    <t>28조 7737억 4151만</t>
+  </si>
+  <si>
+    <t>티종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>20조 2481억 75만</t>
+  </si>
+  <si>
+    <t>호뤼뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>17조 1007억 1083만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Edom</t>
+  </si>
+  <si>
+    <t>15조 5459억 9071만</t>
+  </si>
+  <si>
+    <t>야생봄이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>7조 5964억 2954만</t>
+  </si>
+  <si>
+    <t>이은제리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>5조 5591억 9272만</t>
+  </si>
+  <si>
+    <t>긍궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
+  </si>
+  <si>
+    <t>4조 8275억 1868만</t>
+  </si>
+  <si>
+    <t>청아씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
+  </si>
+  <si>
+    <t>4조 5491억 3270만</t>
+  </si>
+  <si>
+    <t>KR#9SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>2조 2395억 6058만</t>
+  </si>
+  <si>
+    <t>민규짱짱맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
   </si>
   <si>
     <t>97</t>
   </si>
   <si>
-    <t>2조 3986억 360만</t>
-  </si>
-  <si>
-    <t>29</t>
-  </si>
-  <si>
-    <t>여눈</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%88%88</t>
-  </si>
-  <si>
-    <t>2조 1697억 686만</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>2조 267억 9109만</t>
-  </si>
-  <si>
-    <t>그때</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C</t>
-  </si>
-  <si>
-    <t>26조 1587억 7806만</t>
-  </si>
-  <si>
-    <t>시명</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%AA%85</t>
-  </si>
-  <si>
-    <t>20조 9060억 3624만</t>
-  </si>
-  <si>
-    <t>v번개의신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B2%88%EA%B0%9C%EC%9D%98%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>14조 2286억 8809만</t>
-  </si>
-  <si>
-    <t>소주소주해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%A3%BC%EC%86%8C%EC%A3%BC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>14조 1626억 126만</t>
-  </si>
-  <si>
-    <t>메소가져와</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
-  </si>
-  <si>
-    <t>11조 9477억 4717만</t>
-  </si>
-  <si>
-    <t>호댕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%8C%95</t>
-  </si>
-  <si>
-    <t>11조 683억 25만</t>
-  </si>
-  <si>
-    <t>엔도르시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EB%8F%84%EB%A5%B4%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>11조 414억 1562만</t>
-  </si>
-  <si>
-    <t>르밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>9조 9319억 1963만</t>
-  </si>
-  <si>
-    <t>vander</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=vander</t>
-  </si>
-  <si>
-    <t>7조 5964억 4776만</t>
-  </si>
-  <si>
-    <t>무신사할배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>7조 2292억 3002만</t>
-  </si>
-  <si>
-    <t>코코연구가2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%802</t>
-  </si>
-  <si>
-    <t>7조 1647억 6150만</t>
-  </si>
-  <si>
-    <t>인큐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
-  </si>
-  <si>
-    <t>6조 6139억 5179만</t>
-  </si>
-  <si>
-    <t>효율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>6조 2617억 9292만</t>
-  </si>
-  <si>
-    <t>체르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>5조 7041억 7803만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5조 5623억 7979만</t>
-  </si>
-  <si>
-    <t>운스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>5조 3995억 859만</t>
-  </si>
-  <si>
-    <t>종구왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
-  </si>
-  <si>
-    <t>5조 1747억 7650만</t>
-  </si>
-  <si>
-    <t>yawaka</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=yawaka</t>
-  </si>
-  <si>
-    <t>5조 1220억 1649만</t>
-  </si>
-  <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>4조 8578억 9887만</t>
-  </si>
-  <si>
-    <t>신창섭신창섭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
-  </si>
-  <si>
-    <t>4조 2844억 5069만</t>
-  </si>
-  <si>
-    <t>쨍쭝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
-  </si>
-  <si>
-    <t>4조 2648억 6791만</t>
-  </si>
-  <si>
-    <t>코코연구가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%80</t>
-  </si>
-  <si>
-    <t>4조 687억 9536만</t>
-  </si>
-  <si>
-    <t>이빛낭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
-  </si>
-  <si>
-    <t>3조 9593억 1941만</t>
-  </si>
-  <si>
-    <t>요계</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
-  </si>
-  <si>
-    <t>3조 8610억 8084만</t>
-  </si>
-  <si>
-    <t>쫑쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 5417억 9898만</t>
-  </si>
-  <si>
-    <t>아율마더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
-  </si>
-  <si>
-    <t>3조 5299억 4117만</t>
-  </si>
-  <si>
-    <t>13미니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>3조 5160억 9701만</t>
-  </si>
-  <si>
-    <t>네그로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>2조 9606억 9107만</t>
-  </si>
-  <si>
-    <t>아율파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>2조 9261억 9591만</t>
-  </si>
-  <si>
-    <t>맨셸리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%EC%85%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
+    <t>2조 1911억 950만</t>
+  </si>
+  <si>
+    <t>반존대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>1조 4439억 4725만</t>
+  </si>
+  <si>
+    <t>망친인생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
+  </si>
+  <si>
+    <t>1조 3836억 7406만</t>
+  </si>
+  <si>
+    <t>츠키유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 2129억 4255만</t>
+  </si>
+  <si>
+    <t>봉찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>1조 1570억 9979만</t>
+  </si>
+  <si>
+    <t>매력적수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
     <t>95</t>
   </si>
   <si>
-    <t>4126억 8648만</t>
-  </si>
-  <si>
-    <t>픅픅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>109조 2069억 804만</t>
-  </si>
-  <si>
-    <t>끝까지힘내자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
-  </si>
-  <si>
-    <t>28조 7737억 4151만</t>
-  </si>
-  <si>
-    <t>티종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>20조 2481억 75만</t>
-  </si>
-  <si>
-    <t>호뤼뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>16조 2450억 4454만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Edom</t>
-  </si>
-  <si>
-    <t>15조 5459억 9071만</t>
-  </si>
-  <si>
-    <t>야생봄이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>7조 5964억 2954만</t>
-  </si>
-  <si>
-    <t>이은제리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5조 2754억 9069만</t>
-  </si>
-  <si>
-    <t>긍궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
-  </si>
-  <si>
-    <t>4조 8275억 1868만</t>
-  </si>
-  <si>
-    <t>청아씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
-  </si>
-  <si>
-    <t>4조 2370억 3027만</t>
-  </si>
-  <si>
-    <t>KR#9SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>2조 2309억 3914만</t>
-  </si>
-  <si>
-    <t>민규짱짱맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>2조 1417억 9083만</t>
-  </si>
-  <si>
-    <t>반존대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>1조 4439억 4725만</t>
-  </si>
-  <si>
-    <t>츠키유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 2120억 6313만</t>
-  </si>
-  <si>
-    <t>봉찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>96</t>
-  </si>
-  <si>
-    <t>1조 1570억 9979만</t>
-  </si>
-  <si>
-    <t>망친인생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
-  </si>
-  <si>
-    <t>1조 1229억 2741만</t>
+    <t>8837억 9841만</t>
   </si>
   <si>
     <t>서리밍</t>
@@ -1067,13 +1073,13 @@
     <t>8821억 1213만</t>
   </si>
   <si>
-    <t>매력적수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>8569억 5829만</t>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>8518억 2808만</t>
   </si>
   <si>
     <t>채류진</t>
@@ -1091,16 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
   </si>
   <si>
-    <t>7742억 71만</t>
-  </si>
-  <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>7413억 4454만</t>
+    <t>7758억 7795만</t>
   </si>
   <si>
     <t>몽샐</t>
@@ -1121,6 +1118,15 @@
     <t>6409억 6907만</t>
   </si>
   <si>
+    <t>닝갠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
+  </si>
+  <si>
+    <t>5880억 2541만</t>
+  </si>
+  <si>
     <t>공또</t>
   </si>
   <si>
@@ -1130,22 +1136,13 @@
     <t>5766억 521만</t>
   </si>
   <si>
-    <t>닝갠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
-  </si>
-  <si>
-    <t>5518억 7119만</t>
-  </si>
-  <si>
     <t>유해화학물질</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>4947억 1587만</t>
+    <t>4972억 2319만</t>
   </si>
   <si>
     <t>ENNOY</t>
@@ -1154,7 +1151,16 @@
     <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
   </si>
   <si>
-    <t>4628억 6007만</t>
+    <t>4937억 3767만</t>
+  </si>
+  <si>
+    <t>dvzve</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
+  </si>
+  <si>
+    <t>4734억 5258만</t>
   </si>
   <si>
     <t>쓱싹대선</t>
@@ -1163,16 +1169,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
   </si>
   <si>
-    <t>4536억 1944만</t>
-  </si>
-  <si>
-    <t>dvzve</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
-  </si>
-  <si>
-    <t>4049억 4975만</t>
+    <t>4543억 3198만</t>
   </si>
   <si>
     <t>쨍꿍</t>
@@ -1184,7 +1181,7 @@
     <t>92</t>
   </si>
   <si>
-    <t>2545억 1384만</t>
+    <t>2771억 238만</t>
   </si>
   <si>
     <t>희야미</t>
@@ -1205,7 +1202,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>25조 4870억 1271만</t>
+    <t>25조 5460억 364만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -1259,7 +1256,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
   </si>
   <si>
-    <t>6조 681억 2449만</t>
+    <t>6조 752억 346만</t>
   </si>
   <si>
     <t>abba</t>
@@ -1295,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
   </si>
   <si>
-    <t>5조 4714억 7611만</t>
+    <t>5조 4775억 559만</t>
   </si>
   <si>
     <t>표창넣을게</t>
@@ -1331,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
   </si>
   <si>
-    <t>4조 3620억 4589만</t>
+    <t>4조 4648억 4958만</t>
   </si>
   <si>
     <t>라마킴</t>
@@ -1340,7 +1337,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
   </si>
   <si>
-    <t>4조 3539억 9042만</t>
+    <t>4조 3545억 1322만</t>
   </si>
   <si>
     <t>조애니</t>
@@ -1364,7 +1361,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
   </si>
   <si>
-    <t>3조 1115억 3156만</t>
+    <t>3조 1197억 2050만</t>
   </si>
   <si>
     <t>뜨루뜨루</t>
@@ -1373,7 +1370,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>3조 978억 1632만</t>
+    <t>3조 1010억 221만</t>
   </si>
   <si>
     <t>오로치재림</t>
@@ -1382,7 +1379,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A1%9C%EC%B9%98%EC%9E%AC%EB%A6%BC</t>
   </si>
   <si>
-    <t>2조 7001억 961만</t>
+    <t>2조 8213억 1978만</t>
   </si>
   <si>
     <t>승우아빠</t>
@@ -1391,7 +1388,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%9A%B0%EC%95%84%EB%B9%A0</t>
   </si>
   <si>
-    <t>2조 5431억 52만</t>
+    <t>2조 7947억 5414만</t>
   </si>
   <si>
     <t>문범주</t>
@@ -1427,7 +1424,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1조 7905억 7734만</t>
+    <t>1조 8067억 6708만</t>
   </si>
   <si>
     <t>토리츄</t>
@@ -1457,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>2102억 3861만</t>
+    <t>2145억 167만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1466,7 +1463,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
   </si>
   <si>
-    <t>99조 6383억 6250만</t>
+    <t>100조 1466억 8081만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1475,7 +1472,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
   </si>
   <si>
-    <t>53조 6569억 4127만</t>
+    <t>57조 951억 6777만</t>
   </si>
   <si>
     <t>덥쳐보니형수</t>
@@ -1484,7 +1481,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
   </si>
   <si>
-    <t>7조 6392억 1498만</t>
+    <t>7조 6789억 4859만</t>
   </si>
   <si>
     <t>드뚜</t>
@@ -1517,7 +1514,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
   </si>
   <si>
-    <t>5조 2602억 1932만</t>
+    <t>5조 3472억 665만</t>
   </si>
   <si>
     <t>꾸린이</t>
@@ -1535,7 +1532,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 7574억 4399만</t>
+    <t>3조 7617억 7502만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1553,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
   </si>
   <si>
-    <t>2조 8726억 6261만</t>
+    <t>3조 473억 2990만</t>
   </si>
   <si>
     <t>4033</t>
@@ -1562,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=4033</t>
   </si>
   <si>
-    <t>2조 6047억 9633만</t>
+    <t>2조 6523억 1165만</t>
   </si>
   <si>
     <t>세넬</t>
@@ -1571,7 +1568,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>2조 3288억 1656만</t>
+    <t>2조 3321억 4829만</t>
   </si>
   <si>
     <t>기뜩</t>
@@ -1580,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
   </si>
   <si>
-    <t>1조 9538억 955만</t>
+    <t>2조 580억 6432만</t>
   </si>
   <si>
     <t>리토비</t>
@@ -1607,7 +1604,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
   </si>
   <si>
-    <t>1조 7166억 7192만</t>
+    <t>1조 7224억 2791만</t>
   </si>
   <si>
     <t>관둬</t>
@@ -1634,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
   </si>
   <si>
-    <t>1조 3600억 752만</t>
+    <t>1조 3735억 703만</t>
   </si>
   <si>
     <t>챙날</t>
@@ -1679,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
   </si>
   <si>
-    <t>6168억 2560만</t>
+    <t>6227억 5652만</t>
   </si>
   <si>
     <t>성현이여</t>
@@ -1691,7 +1688,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>2139억 4828만</t>
+    <t>2207억 9854만</t>
   </si>
 </sst>
 </file>
@@ -2257,17 +2254,17 @@
         <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="I5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>48</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2275,40 +2272,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>52</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>58</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>59</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2346,28 +2343,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2378,7 +2375,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>23</v>
@@ -2387,19 +2384,19 @@
         <v>23</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>72</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>73</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -2410,28 +2407,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="C3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="D3" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="I3" s="2" t="s">
         <v>79</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2442,28 +2439,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="H4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>85</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>86</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2474,28 +2471,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>92</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2506,28 +2503,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2538,28 +2535,28 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>79</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>101</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2570,28 +2567,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="D8" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>104</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>105</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2602,28 +2599,28 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>108</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>109</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2634,25 +2631,25 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>112</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
+      <c r="H10" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>114</v>
@@ -2678,16 +2675,16 @@
         <v>117</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>119</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>120</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2698,28 +2695,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2730,28 +2727,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>126</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2762,28 +2759,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>129</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>131</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2794,25 +2791,25 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>136</v>
@@ -2838,16 +2835,16 @@
         <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>113</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>140</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>141</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2858,28 +2855,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>142</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>145</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2890,28 +2887,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>148</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>149</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>150</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2922,28 +2919,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>152</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>153</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>154</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2954,28 +2951,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>154</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>155</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="D20" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>156</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>157</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>158</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2986,28 +2983,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>159</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>162</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3018,28 +3015,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>165</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>166</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3050,28 +3047,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>169</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3082,28 +3079,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>172</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>173</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3114,28 +3111,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>177</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>178</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3146,28 +3143,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>180</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>182</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3178,28 +3175,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>185</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>186</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3210,28 +3207,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>188</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>189</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3242,28 +3239,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>194</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3274,28 +3271,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>197</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>198</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>200</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3306,28 +3303,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>201</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>202</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>204</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3391,28 +3388,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3423,28 +3420,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>205</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3455,28 +3452,28 @@
         <v>25</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>208</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>210</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3487,28 +3484,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>213</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3519,28 +3516,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>214</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>216</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3551,28 +3548,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>217</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>219</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3583,28 +3580,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>222</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3615,28 +3612,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>223</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3647,28 +3644,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>228</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3679,28 +3676,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>229</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3714,25 +3711,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>234</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3743,28 +3740,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>235</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3775,28 +3772,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="E13" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>240</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3807,28 +3804,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3839,28 +3836,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>246</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3874,25 +3871,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>32</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>248</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3903,28 +3900,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>249</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3935,28 +3932,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="E18" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3967,28 +3964,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>255</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="E19" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3999,28 +3996,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>258</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>260</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4031,28 +4028,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>260</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>261</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="E21" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4063,28 +4060,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>266</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4095,28 +4092,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>267</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>267</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4127,28 +4124,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="E24" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>272</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4159,28 +4156,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>272</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>273</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>273</v>
-      </c>
-      <c r="E25" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4191,28 +4188,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>276</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>278</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4223,28 +4220,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="E27" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>279</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>279</v>
-      </c>
-      <c r="E27" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4255,28 +4252,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E28" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="E28" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>284</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4287,28 +4284,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="E29" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>285</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4319,28 +4316,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E30" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="E30" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4351,28 +4348,28 @@
         <v>25</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="H31" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -4426,7 +4423,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4435,28 +4432,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4467,28 +4464,28 @@
         <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4499,28 +4496,28 @@
         <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>300</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4531,28 +4528,28 @@
         <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4563,28 +4560,28 @@
         <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4595,7 +4592,7 @@
         <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>41</v>
@@ -4604,19 +4601,19 @@
         <v>41</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="G6" s="2" t="s">
-        <v>71</v>
-      </c>
       <c r="H6" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4627,28 +4624,28 @@
         <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="D7" s="2" t="s">
-        <v>312</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4659,28 +4656,28 @@
         <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>315</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4691,28 +4688,28 @@
         <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>318</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4723,28 +4720,28 @@
         <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>321</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4758,25 +4755,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="D11" s="2" t="s">
-        <v>324</v>
-      </c>
-      <c r="E11" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>326</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4787,28 +4784,28 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>326</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>327</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="I12" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>329</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4819,28 +4816,28 @@
         <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>331</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>332</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4851,28 +4848,28 @@
         <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>334</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>335</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4883,28 +4880,28 @@
         <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>337</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>339</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4918,25 +4915,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="E16" s="2" t="s">
-        <v>341</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>342</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4947,28 +4944,28 @@
         <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>343</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>344</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>345</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4979,28 +4976,28 @@
         <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>346</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>347</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>348</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5011,28 +5008,28 @@
         <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>349</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5043,28 +5040,28 @@
         <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>352</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5075,28 +5072,28 @@
         <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>355</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>356</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>357</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5107,28 +5104,28 @@
         <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>359</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>360</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5139,28 +5136,28 @@
         <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>362</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>363</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5171,28 +5168,28 @@
         <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>364</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>365</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>366</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5203,28 +5200,28 @@
         <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>367</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>368</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>369</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5235,28 +5232,28 @@
         <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>370</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>372</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5267,28 +5264,28 @@
         <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>374</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>375</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5299,28 +5296,28 @@
         <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>376</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>377</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>378</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5331,28 +5328,28 @@
         <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>378</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>379</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5363,28 +5360,28 @@
         <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5395,28 +5392,28 @@
         <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>388</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>389</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5480,28 +5477,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5512,28 +5509,28 @@
         <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>389</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5544,28 +5541,28 @@
         <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>393</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>394</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>395</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5576,28 +5573,28 @@
         <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>395</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>397</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>398</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5608,28 +5605,28 @@
         <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>399</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>400</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>401</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5640,28 +5637,28 @@
         <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>402</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>403</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>404</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5672,28 +5669,28 @@
         <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>406</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>407</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5704,28 +5701,28 @@
         <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>408</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>409</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>410</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5736,28 +5733,28 @@
         <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>411</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>412</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>413</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5768,28 +5765,28 @@
         <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>414</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>415</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>416</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5803,25 +5800,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>419</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5832,28 +5829,28 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>419</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>420</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>421</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>422</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5864,28 +5861,28 @@
         <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>423</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>424</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>425</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5896,28 +5893,28 @@
         <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>427</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>428</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5928,28 +5925,28 @@
         <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>429</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>431</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5963,25 +5960,25 @@
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>431</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>432</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>433</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>434</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5992,28 +5989,28 @@
         <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>435</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>436</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>437</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6024,28 +6021,28 @@
         <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>438</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>439</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>440</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6056,28 +6053,28 @@
         <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>440</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>441</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6088,28 +6085,28 @@
         <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6120,28 +6117,28 @@
         <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>446</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>447</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>448</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6152,28 +6149,28 @@
         <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>449</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>450</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>451</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6184,28 +6181,28 @@
         <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>452</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>453</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>454</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6216,28 +6213,28 @@
         <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>455</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>456</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>457</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6248,28 +6245,28 @@
         <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>458</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>459</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>460</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6280,28 +6277,28 @@
         <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>461</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>462</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>463</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6312,28 +6309,28 @@
         <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>463</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>464</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>465</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>466</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6344,28 +6341,28 @@
         <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>466</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>467</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6376,28 +6373,28 @@
         <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H29" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H29" s="2" t="s">
+      <c r="I29" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6408,28 +6405,28 @@
         <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>474</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>384</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6483,7 +6480,7 @@
     <col min="4" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -6492,28 +6489,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>66</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>67</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6521,31 +6518,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6553,31 +6550,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>481</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>482</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6585,31 +6582,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6617,31 +6614,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6649,31 +6646,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>305</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6681,31 +6678,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6713,31 +6710,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6745,31 +6742,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6777,31 +6774,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6809,31 +6806,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6841,31 +6838,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6873,31 +6870,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6905,31 +6902,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6937,31 +6934,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6969,31 +6966,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7001,31 +6998,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7033,31 +7030,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7065,31 +7062,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7097,31 +7094,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7129,31 +7126,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7161,31 +7158,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7193,31 +7190,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7225,31 +7222,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7257,31 +7254,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7289,31 +7286,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7321,31 +7318,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H27" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="F27" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="H27" s="2" t="s">
+      <c r="I27" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -15,7 +15,7 @@
     <sheet name="블루스2기" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GDRAGON!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GDRAGON!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Kaia!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">블루스2기!$A$1:$J$27</definedName>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="551">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>394</t>
+    <t>388</t>
   </si>
   <si>
     <t>13위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>210조 1486억 3414만</t>
+    <t>220조 3391억 950만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.26</t>
+    <t>2026.04.27</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,13 +113,16 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>376</t>
-  </si>
-  <si>
-    <t>12위</t>
-  </si>
-  <si>
-    <t>226조 5971억 2413만</t>
+    <t>389</t>
+  </si>
+  <si>
+    <t>11위</t>
+  </si>
+  <si>
+    <t>29명</t>
+  </si>
+  <si>
+    <t>218조 3079억 2710만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -137,7 +140,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>368</t>
+    <t>363</t>
   </si>
   <si>
     <t>8위</t>
@@ -146,7 +149,7 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>231조 6968억 1979만</t>
+    <t>241조 9907억 228만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -164,16 +167,13 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>435</t>
+    <t>440</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>29명</t>
-  </si>
-  <si>
-    <t>163조 6861억 8247만</t>
+    <t>168조 7434억 6773만</t>
   </si>
   <si>
     <t>보보네</t>
@@ -188,16 +188,16 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>375</t>
-  </si>
-  <si>
-    <t>17위</t>
+    <t>366</t>
+  </si>
+  <si>
+    <t>16위</t>
   </si>
   <si>
     <t>26명</t>
   </si>
   <si>
-    <t>227조 4118억 971만</t>
+    <t>239조 2396억 7777만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -245,21 +245,39 @@
     <t>104</t>
   </si>
   <si>
-    <t>28조 7523억 2933만</t>
+    <t>31조 4685억 9720만</t>
   </si>
   <si>
     <t>2</t>
   </si>
   <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>21조 8866억 2814만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
     <t>큐샤프</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>신궁</t>
   </si>
   <si>
@@ -269,24 +287,6 @@
     <t>20조 8772억 7416만</t>
   </si>
   <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>18조 9253억 9203만</t>
-  </si>
-  <si>
     <t>4</t>
   </si>
   <si>
@@ -302,7 +302,7 @@
     <t>101</t>
   </si>
   <si>
-    <t>13조 9322억 7271만</t>
+    <t>14조 8623억 2147만</t>
   </si>
   <si>
     <t>5</t>
@@ -341,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6716억 4082만</t>
+    <t>7조 6801억 1998만</t>
   </si>
   <si>
     <t>8</t>
@@ -353,7 +353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 3311억 6274만</t>
+    <t>7조 5286억 8021만</t>
   </si>
   <si>
     <t>9</t>
@@ -371,7 +371,7 @@
     <t>100</t>
   </si>
   <si>
-    <t>6조 8265억 4136만</t>
+    <t>7조 1219억 6098만</t>
   </si>
   <si>
     <t>10</t>
@@ -392,6 +392,18 @@
     <t>11</t>
   </si>
   <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>6조 5215억 1858만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
     <t>포스코퓨처엠</t>
   </si>
   <si>
@@ -401,31 +413,58 @@
     <t>6조 4649억 8468만</t>
   </si>
   <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>5조 4515억 8769만</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
+    <t>므고</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>5조 2258억 7841만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
     <t>흑두부</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>4조 9811억 5357만</t>
-  </si>
-  <si>
-    <t>14</t>
+    <t>5조 339억 2537만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 7304억 2040만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>4조 6479억 5302만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -440,67 +479,28 @@
     <t>4조 6273억 4164만</t>
   </si>
   <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>므고</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
-  </si>
-  <si>
-    <t>4조 5621억 2305만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 5139억 1714만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 3613억 1130만</t>
-  </si>
-  <si>
     <t>18</t>
   </si>
   <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>4조 1571억 2932만</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
     <t>비스밤</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
-    <t>4조 768억 9265만</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>4조 366억 9775만</t>
+    <t>4조 1213억 1333만</t>
   </si>
   <si>
     <t>20</t>
@@ -512,7 +512,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9589억 1764만</t>
+    <t>3조 9882억 292만</t>
   </si>
   <si>
     <t>21</t>
@@ -536,7 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 3304억 6250만</t>
+    <t>3조 4067억 1103만</t>
   </si>
   <si>
     <t>23</t>
@@ -548,12 +548,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 9156억 802만</t>
+    <t>2조 9483억 6909만</t>
   </si>
   <si>
     <t>24</t>
   </si>
   <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>2조 8743억 5331만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>제스프리</t>
   </si>
   <si>
@@ -563,18 +575,6 @@
     <t>2조 7544억 4887만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 7249억 3293만</t>
-  </si>
-  <si>
     <t>26</t>
   </si>
   <si>
@@ -662,16 +662,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%A3%BC%EC%86%8C%EC%A3%BC%ED%95%B4</t>
   </si>
   <si>
-    <t>14조 3697억 2920만</t>
-  </si>
-  <si>
-    <t>v번개의신v</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=v%EB%B2%88%EA%B0%9C%EC%9D%98%EC%8B%A0v</t>
-  </si>
-  <si>
-    <t>14조 2286억 8809만</t>
+    <t>16조 151억 105만</t>
   </si>
   <si>
     <t>메소가져와</t>
@@ -707,7 +698,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
   </si>
   <si>
-    <t>9조 9521억 6334만</t>
+    <t>10조 8125억 3069만</t>
   </si>
   <si>
     <t>vander</t>
@@ -716,7 +707,7 @@
     <t>https://mgf.gg/contents/character.php?n=vander</t>
   </si>
   <si>
-    <t>7조 6700억 9729만</t>
+    <t>7조 6777억 2935만</t>
   </si>
   <si>
     <t>무신사할배</t>
@@ -725,7 +716,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
   </si>
   <si>
-    <t>7조 2672억 7779만</t>
+    <t>7조 4497억 2175만</t>
   </si>
   <si>
     <t>코코연구가2</t>
@@ -752,7 +743,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>6조 2617억 9292만</t>
+    <t>6조 4121억 6745만</t>
   </si>
   <si>
     <t>종구왕</t>
@@ -761,7 +752,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
   </si>
   <si>
-    <t>5조 8246억 875만</t>
+    <t>5조 9723억 677만</t>
   </si>
   <si>
     <t>체르</t>
@@ -779,6 +770,15 @@
     <t>5조 6392억 7905만</t>
   </si>
   <si>
+    <t>킹돔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
+  </si>
+  <si>
+    <t>5조 4328억 6429만</t>
+  </si>
+  <si>
     <t>운스</t>
   </si>
   <si>
@@ -797,22 +797,13 @@
     <t>5조 1220억 1649만</t>
   </si>
   <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>5조 1064억 7414만</t>
-  </si>
-  <si>
     <t>신창섭신창섭</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
   </si>
   <si>
-    <t>4조 4970억 9776만</t>
+    <t>4조 7212억 1448만</t>
   </si>
   <si>
     <t>쨍쭝</t>
@@ -821,7 +812,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
   </si>
   <si>
-    <t>4조 3407억 5801만</t>
+    <t>4조 6059억 5811만</t>
   </si>
   <si>
     <t>요계</t>
@@ -830,7 +821,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
   </si>
   <si>
-    <t>4조 3163억 8988만</t>
+    <t>4조 3600억 6827만</t>
   </si>
   <si>
     <t>코코연구가</t>
@@ -857,7 +848,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
   </si>
   <si>
-    <t>3조 5908억 3222만</t>
+    <t>3조 6391억 1926만</t>
   </si>
   <si>
     <t>13미니</t>
@@ -866,7 +857,7 @@
     <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 5349억 5464만</t>
+    <t>3조 5571억 4495만</t>
   </si>
   <si>
     <t>아율마더</t>
@@ -875,7 +866,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
   </si>
   <si>
-    <t>3조 5299억 4117만</t>
+    <t>3조 5389억 2913만</t>
   </si>
   <si>
     <t>아율파더</t>
@@ -884,7 +875,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>3조 7억 3896만</t>
+    <t>3조 1546억 9866만</t>
   </si>
   <si>
     <t>네그로니</t>
@@ -893,7 +884,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>2조 9606억 9107만</t>
+    <t>3조 1502억 5777만</t>
   </si>
   <si>
     <t>맨셸리</t>
@@ -908,7 +899,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>4177억 9177만</t>
+    <t>5268억 7773만</t>
   </si>
   <si>
     <t>픅픅</t>
@@ -920,7 +911,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>109조 5488억 1465만</t>
+    <t>111조 24억 8369만</t>
   </si>
   <si>
     <t>끝까지힘내자</t>
@@ -929,7 +920,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
   </si>
   <si>
-    <t>28조 7737억 4151만</t>
+    <t>34조 5879억 2379만</t>
   </si>
   <si>
     <t>티종</t>
@@ -956,7 +947,7 @@
     <t>https://mgf.gg/contents/character.php?n=Edom</t>
   </si>
   <si>
-    <t>15조 5459억 9071만</t>
+    <t>15조 7765억 9880만</t>
   </si>
   <si>
     <t>야생봄이</t>
@@ -974,7 +965,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>5조 5591억 9272만</t>
+    <t>5조 7731억 2999만</t>
   </si>
   <si>
     <t>긍궁</t>
@@ -983,7 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
   </si>
   <si>
-    <t>4조 8275억 1868만</t>
+    <t>5조 3816억 2633만</t>
   </si>
   <si>
     <t>청아씨</t>
@@ -992,7 +983,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
   </si>
   <si>
-    <t>4조 5491억 3270만</t>
+    <t>4조 7061억 5379만</t>
+  </si>
+  <si>
+    <t>민규짱짱맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>2조 4760억 4834만</t>
   </si>
   <si>
     <t>KR#9SQP2LGG2B</t>
@@ -1001,28 +1001,28 @@
     <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
   </si>
   <si>
-    <t>2조 2395억 6058만</t>
-  </si>
-  <si>
-    <t>민규짱짱맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
+    <t>2조 3172억 7325만</t>
+  </si>
+  <si>
+    <t>츠키유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>1조 5958억 6891만</t>
+  </si>
+  <si>
+    <t>반존대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
   </si>
   <si>
     <t>97</t>
   </si>
   <si>
-    <t>2조 1911억 950만</t>
-  </si>
-  <si>
-    <t>반존대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>1조 4439억 4725만</t>
+    <t>1조 5527억 6976만</t>
   </si>
   <si>
     <t>망친인생</t>
@@ -1031,16 +1031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
   </si>
   <si>
-    <t>1조 3836억 7406만</t>
-  </si>
-  <si>
-    <t>츠키유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 2129억 4255만</t>
+    <t>1조 4888억 5491만</t>
   </si>
   <si>
     <t>봉찬</t>
@@ -1061,7 +1052,7 @@
     <t>95</t>
   </si>
   <si>
-    <t>8837억 9841만</t>
+    <t>9122억 2811만</t>
   </si>
   <si>
     <t>서리밍</t>
@@ -1082,13 +1073,22 @@
     <t>8518억 2808만</t>
   </si>
   <si>
+    <t>달려봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
+  </si>
+  <si>
+    <t>8324억 8049만</t>
+  </si>
+  <si>
     <t>채류진</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
   </si>
   <si>
-    <t>7850억 3909만</t>
+    <t>7937억 1939만</t>
   </si>
   <si>
     <t>낀조</t>
@@ -1097,7 +1097,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
   </si>
   <si>
-    <t>7758억 7795만</t>
+    <t>7811억 4055만</t>
   </si>
   <si>
     <t>몽샐</t>
@@ -1106,16 +1106,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
   </si>
   <si>
-    <t>6831억 1781만</t>
-  </si>
-  <si>
-    <t>달려봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
-  </si>
-  <si>
-    <t>6409억 6907만</t>
+    <t>6873억 8645만</t>
   </si>
   <si>
     <t>닝갠</t>
@@ -1124,7 +1115,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
   </si>
   <si>
-    <t>5880억 2541만</t>
+    <t>6023억 1234만</t>
   </si>
   <si>
     <t>공또</t>
@@ -1133,7 +1124,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
   </si>
   <si>
-    <t>5766억 521만</t>
+    <t>5821억 9376만</t>
   </si>
   <si>
     <t>유해화학물질</t>
@@ -1142,7 +1133,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>4972억 2319만</t>
+    <t>5018억 2431만</t>
   </si>
   <si>
     <t>ENNOY</t>
@@ -1151,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
   </si>
   <si>
-    <t>4937억 3767만</t>
+    <t>4943억 6783만</t>
   </si>
   <si>
     <t>dvzve</t>
@@ -1169,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
   </si>
   <si>
-    <t>4543억 3198만</t>
+    <t>4560억 4237만</t>
   </si>
   <si>
     <t>쨍꿍</t>
@@ -1193,7 +1184,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>957억 9083만</t>
+    <t>1014억 3891만</t>
   </si>
   <si>
     <t>최형사</t>
@@ -1202,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>25조 5460억 364만</t>
+    <t>27조 7146억 2441만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -1238,7 +1229,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
   </si>
   <si>
-    <t>6조 7800억 6733만</t>
+    <t>7조 9938억 907만</t>
   </si>
   <si>
     <t>쎄도어</t>
@@ -1256,7 +1247,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
   </si>
   <si>
-    <t>6조 752억 346만</t>
+    <t>6조 1219억 9639만</t>
+  </si>
+  <si>
+    <t>머겸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
+  </si>
+  <si>
+    <t>6조 231억 823만</t>
   </si>
   <si>
     <t>abba</t>
@@ -1268,15 +1268,6 @@
     <t>5조 8087억 8308만</t>
   </si>
   <si>
-    <t>머겸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
-  </si>
-  <si>
-    <t>5조 6791억 2548만</t>
-  </si>
-  <si>
     <t>류작</t>
   </si>
   <si>
@@ -1292,7 +1283,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
   </si>
   <si>
-    <t>5조 4775억 559만</t>
+    <t>5조 5132억 7176만</t>
   </si>
   <si>
     <t>표창넣을게</t>
@@ -1301,7 +1292,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
   </si>
   <si>
-    <t>5조 3095억 3817만</t>
+    <t>5조 3365억 1499만</t>
   </si>
   <si>
     <t>불소그리스</t>
@@ -1313,22 +1304,22 @@
     <t>5조 1920억 8892만</t>
   </si>
   <si>
+    <t>윤서u</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
+  </si>
+  <si>
+    <t>4조 7654억 1939만</t>
+  </si>
+  <si>
     <t>인천왕김치언</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
   </si>
   <si>
-    <t>4조 6789억 8381만</t>
-  </si>
-  <si>
-    <t>윤서u</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
-  </si>
-  <si>
-    <t>4조 4648억 4958만</t>
+    <t>4조 7507억 1614만</t>
   </si>
   <si>
     <t>라마킴</t>
@@ -1337,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
   </si>
   <si>
-    <t>4조 3545억 1322만</t>
+    <t>4조 4769억 7439만</t>
   </si>
   <si>
     <t>조애니</t>
@@ -1358,19 +1349,19 @@
     <t>3조 2698억 7360만</t>
   </si>
   <si>
+    <t>뜨루뜨루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>3조 1816억 894만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
   </si>
   <si>
-    <t>3조 1197억 2050만</t>
-  </si>
-  <si>
-    <t>뜨루뜨루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>3조 1010억 221만</t>
+    <t>3조 1472억 4695만</t>
   </si>
   <si>
     <t>오로치재림</t>
@@ -1379,7 +1370,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A1%9C%EC%B9%98%EC%9E%AC%EB%A6%BC</t>
   </si>
   <si>
-    <t>2조 8213억 1978만</t>
+    <t>3조 240억 6770만</t>
   </si>
   <si>
     <t>승우아빠</t>
@@ -1397,7 +1388,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>2조 2568억 4452만</t>
+    <t>2조 2639억 1395만</t>
+  </si>
+  <si>
+    <t>박띵수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
+  </si>
+  <si>
+    <t>2조 2300억 7595만</t>
   </si>
   <si>
     <t>토리꼬리</t>
@@ -1409,22 +1409,13 @@
     <t>2조 1948억 4810만</t>
   </si>
   <si>
-    <t>박띵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>2조 1501억 8610만</t>
-  </si>
-  <si>
     <t>사이비숍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>1조 8067억 6708만</t>
+    <t>1조 9854억 9439만</t>
   </si>
   <si>
     <t>토리츄</t>
@@ -1445,7 +1436,7 @@
     <t>94</t>
   </si>
   <si>
-    <t>3047억 2423만</t>
+    <t>4494억 8136만</t>
   </si>
   <si>
     <t>zl존율율</t>
@@ -1454,7 +1445,7 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>2145억 167만</t>
+    <t>2198억 1763만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1463,7 +1454,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
   </si>
   <si>
-    <t>100조 1466억 8081만</t>
+    <t>108조 4948억 4009만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1472,7 +1463,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
   </si>
   <si>
-    <t>57조 951억 6777만</t>
+    <t>57조 3025억 6856만</t>
   </si>
   <si>
     <t>덥쳐보니형수</t>
@@ -1481,7 +1472,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
   </si>
   <si>
-    <t>7조 6789억 4859만</t>
+    <t>7조 8360억 4690만</t>
   </si>
   <si>
     <t>드뚜</t>
@@ -1499,7 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
   </si>
   <si>
-    <t>6조 7202억 9097만</t>
+    <t>6조 7244억 4168만</t>
   </si>
   <si>
     <t>푸장님</t>
@@ -1508,22 +1499,22 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EC%9E%A5%EB%8B%98</t>
   </si>
   <si>
-    <t>5조 6013억 4338만</t>
+    <t>6조 2486억 8797만</t>
+  </si>
+  <si>
+    <t>꾸린이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6조 399억 1655만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
   </si>
   <si>
-    <t>5조 3472억 665만</t>
-  </si>
-  <si>
-    <t>꾸린이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>4조 8805억 3032만</t>
+    <t>5조 8642억 6997만</t>
   </si>
   <si>
     <t>한반</t>
@@ -1532,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 7617억 7502만</t>
+    <t>3조 7700억 4471만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1559,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=4033</t>
   </si>
   <si>
-    <t>2조 6523억 1165만</t>
+    <t>2조 8376억 1733만</t>
   </si>
   <si>
     <t>세넬</t>
@@ -1568,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>2조 3321억 4829만</t>
+    <t>2조 4353억 249만</t>
   </si>
   <si>
     <t>기뜩</t>
@@ -1577,7 +1568,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
   </si>
   <si>
-    <t>2조 580억 6432만</t>
+    <t>2조 785억 9293만</t>
+  </si>
+  <si>
+    <t>관둬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
+  </si>
+  <si>
+    <t>1조 8398억 6283만</t>
+  </si>
+  <si>
+    <t>하흙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
+  </si>
+  <si>
+    <t>1조 7950억 5457만</t>
   </si>
   <si>
     <t>리토비</t>
@@ -1598,31 +1607,13 @@
     <t>1조 7811억 3646만</t>
   </si>
   <si>
-    <t>하흙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
-  </si>
-  <si>
-    <t>1조 7224억 2791만</t>
-  </si>
-  <si>
-    <t>관둬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
-  </si>
-  <si>
-    <t>1조 7154억 1776만</t>
-  </si>
-  <si>
     <t>라미낭</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%AF%B8%EB%82%AD</t>
   </si>
   <si>
-    <t>1조 5723억 8649만</t>
+    <t>1조 6431억 3517만</t>
   </si>
   <si>
     <t>야햐</t>
@@ -1631,7 +1622,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
   </si>
   <si>
-    <t>1조 3735억 703만</t>
+    <t>1조 4802억 9569만</t>
   </si>
   <si>
     <t>챙날</t>
@@ -1640,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
   </si>
   <si>
-    <t>1조 3088억 8479만</t>
+    <t>1조 3174억 6688만</t>
   </si>
   <si>
     <t>지히메</t>
@@ -1649,7 +1640,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
   </si>
   <si>
-    <t>1조 277억 877만</t>
+    <t>1조 356억 5788만</t>
   </si>
   <si>
     <t>홍루이</t>
@@ -1688,7 +1679,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>2207억 9854만</t>
+    <t>2396억 6940만</t>
   </si>
 </sst>
 </file>
@@ -2175,16 +2166,16 @@
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2192,40 +2183,40 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2233,31 +2224,31 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>47</v>
+        <v>30</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>48</v>
@@ -2293,7 +2284,7 @@
         <v>54</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>55</v>
@@ -2521,7 +2512,7 @@
         <v>95</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>96</v>
@@ -2550,10 +2541,10 @@
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>100</v>
@@ -2710,7 +2701,7 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>113</v>
@@ -2742,7 +2733,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>113</v>
@@ -2774,10 +2765,10 @@
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -2806,13 +2797,13 @@
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="H15" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>135</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2823,25 +2814,25 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="H16" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>140</v>
@@ -2870,13 +2861,13 @@
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>144</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2887,25 +2878,25 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>149</v>
@@ -2934,10 +2925,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -2966,10 +2957,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>157</v>
@@ -3065,7 +3056,7 @@
         <v>118</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>169</v>
@@ -3097,7 +3088,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>173</v>
@@ -3126,10 +3117,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>144</v>
+        <v>90</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>177</v>
@@ -3158,10 +3149,10 @@
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>90</v>
+        <v>139</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>181</v>
@@ -3225,7 +3216,7 @@
         <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>189</v>
@@ -3257,7 +3248,7 @@
         <v>193</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3289,7 +3280,7 @@
         <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>198</v>
@@ -3318,7 +3309,7 @@
         <v>76</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H31" s="2" t="s">
         <v>113</v>
@@ -3370,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J31"/>
+  <dimension ref="A1:J30"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3438,7 +3429,7 @@
         <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>205</v>
@@ -3470,7 +3461,7 @@
         <v>70</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>208</v>
@@ -3502,7 +3493,7 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>211</v>
@@ -3531,7 +3522,7 @@
         <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>78</v>
@@ -3563,10 +3554,10 @@
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>217</v>
@@ -3595,7 +3586,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>84</v>
@@ -3630,7 +3621,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
@@ -3659,10 +3650,10 @@
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>226</v>
@@ -3691,10 +3682,10 @@
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
@@ -3723,10 +3714,10 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>112</v>
+        <v>89</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3755,7 +3746,7 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>90</v>
@@ -3787,7 +3778,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>90</v>
@@ -3819,10 +3810,10 @@
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>77</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>241</v>
@@ -3854,7 +3845,7 @@
         <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>244</v>
@@ -3868,28 +3859,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>245</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>84</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3903,22 +3894,22 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>247</v>
       </c>
       <c r="E17" s="2" t="s">
         <v>248</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>249</v>
@@ -3932,7 +3923,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>250</v>
@@ -3950,7 +3941,7 @@
         <v>118</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>252</v>
@@ -4011,10 +4002,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>258</v>
@@ -4043,7 +4034,7 @@
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>90</v>
@@ -4075,10 +4066,10 @@
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>264</v>
@@ -4107,10 +4098,10 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>84</v>
+        <v>113</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>267</v>
@@ -4139,10 +4130,10 @@
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>95</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>270</v>
@@ -4171,7 +4162,7 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>95</v>
+        <v>118</v>
       </c>
       <c r="H25" s="2" t="s">
         <v>90</v>
@@ -4203,7 +4194,7 @@
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>89</v>
       </c>
       <c r="H26" s="2" t="s">
         <v>90</v>
@@ -4235,10 +4226,10 @@
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>89</v>
+        <v>118</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>279</v>
@@ -4270,7 +4261,7 @@
         <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>113</v>
+        <v>148</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4302,7 +4293,7 @@
         <v>118</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>135</v>
+        <v>90</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>285</v>
@@ -4331,52 +4322,20 @@
         <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>118</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>90</v>
+        <v>289</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="31" spans="1:10">
-      <c r="A31" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>290</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>292</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="J31" s="2" t="s">
-        <v>24</v>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A1:J31"/>
+  <autoFilter ref="A1:J30"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -4407,7 +4366,6 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
-    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -4423,7 +4381,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="18.7109375" customWidth="1"/>
+    <col min="9" max="9" width="17.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4461,31 +4419,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>294</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>296</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4493,31 +4451,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4525,31 +4483,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>90</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4557,31 +4515,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4589,19 +4547,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -4613,7 +4571,7 @@
         <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4621,31 +4579,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4653,19 +4611,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
@@ -4674,10 +4632,10 @@
         <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4685,19 +4643,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -4706,10 +4664,10 @@
         <v>89</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4717,19 +4675,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
@@ -4741,7 +4699,7 @@
         <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4749,31 +4707,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>118</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4781,31 +4739,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>327</v>
+        <v>148</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4813,31 +4771,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>89</v>
+        <v>288</v>
       </c>
       <c r="H13" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>327</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4845,31 +4803,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>303</v>
+        <v>89</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4877,31 +4835,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4909,19 +4867,19 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
@@ -4930,10 +4888,10 @@
         <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4941,19 +4899,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -4962,10 +4920,10 @@
         <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4973,19 +4931,19 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
@@ -4994,10 +4952,10 @@
         <v>118</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -5005,31 +4963,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5037,31 +4995,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>292</v>
+        <v>340</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5069,19 +5027,19 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
@@ -5090,10 +5048,10 @@
         <v>118</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5101,31 +5059,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>343</v>
+        <v>289</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5133,19 +5091,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
@@ -5154,10 +5112,10 @@
         <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5165,19 +5123,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -5186,10 +5144,10 @@
         <v>118</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5197,19 +5155,19 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
@@ -5218,10 +5176,10 @@
         <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5229,31 +5187,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5261,19 +5219,19 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -5282,10 +5240,10 @@
         <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5293,19 +5251,19 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
@@ -5314,10 +5272,10 @@
         <v>118</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5325,19 +5283,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
@@ -5346,10 +5304,10 @@
         <v>70</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5357,19 +5315,19 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
@@ -5378,10 +5336,10 @@
         <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5389,31 +5347,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>199</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>385</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>385</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>387</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5506,19 +5464,19 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>76</v>
@@ -5527,10 +5485,10 @@
         <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5538,31 +5496,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5570,19 +5528,19 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -5591,10 +5549,10 @@
         <v>89</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5602,19 +5560,19 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
@@ -5626,7 +5584,7 @@
         <v>90</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5634,19 +5592,19 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
@@ -5658,7 +5616,7 @@
         <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5666,19 +5624,19 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
@@ -5690,7 +5648,7 @@
         <v>90</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5698,19 +5656,19 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>76</v>
@@ -5719,10 +5677,10 @@
         <v>193</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5730,19 +5688,19 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>76</v>
@@ -5751,10 +5709,10 @@
         <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5762,19 +5720,19 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
@@ -5783,10 +5741,10 @@
         <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5794,31 +5752,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>90</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5826,19 +5784,19 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
@@ -5850,7 +5808,7 @@
         <v>113</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5858,19 +5816,19 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -5882,7 +5840,7 @@
         <v>90</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5890,19 +5848,19 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
@@ -5914,7 +5872,7 @@
         <v>90</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5922,31 +5880,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>70</v>
+        <v>89</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5954,31 +5912,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>431</v>
+        <v>428</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>432</v>
+        <v>429</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>113</v>
+        <v>90</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5986,19 +5944,19 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>435</v>
+        <v>432</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -6010,7 +5968,7 @@
         <v>90</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6018,31 +5976,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>437</v>
+        <v>434</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>438</v>
+        <v>435</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>439</v>
+        <v>436</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6050,19 +6008,19 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>440</v>
+        <v>437</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>441</v>
+        <v>438</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
@@ -6074,7 +6032,7 @@
         <v>90</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6082,31 +6040,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>49</v>
+        <v>440</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>49</v>
+        <v>440</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>443</v>
+        <v>441</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>291</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6114,31 +6072,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>445</v>
+        <v>49</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>445</v>
+        <v>49</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>446</v>
+        <v>443</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>70</v>
+        <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6146,19 +6104,19 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>449</v>
+        <v>446</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -6167,10 +6125,10 @@
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6178,19 +6136,19 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>452</v>
+        <v>449</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
@@ -6202,7 +6160,7 @@
         <v>113</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6210,19 +6168,19 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -6234,7 +6192,7 @@
         <v>113</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6242,31 +6200,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>113</v>
+        <v>139</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6274,31 +6232,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>460</v>
+        <v>457</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>118</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>144</v>
+        <v>113</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6306,31 +6264,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>464</v>
+        <v>461</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>465</v>
+        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6338,31 +6296,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>186</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>468</v>
+        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6370,19 +6328,19 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>190</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>470</v>
+        <v>467</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>76</v>
@@ -6391,10 +6349,10 @@
         <v>112</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>471</v>
+        <v>468</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>472</v>
+        <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6402,31 +6360,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>473</v>
+        <v>470</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>474</v>
+        <v>471</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>475</v>
+        <v>472</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6524,13 +6482,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>477</v>
+        <v>474</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>76</v>
@@ -6539,10 +6497,10 @@
         <v>70</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>478</v>
+        <v>475</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6556,25 +6514,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>479</v>
+        <v>476</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>480</v>
+        <v>477</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>481</v>
+        <v>478</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6588,13 +6546,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>482</v>
+        <v>479</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -6606,7 +6564,7 @@
         <v>113</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>484</v>
+        <v>481</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6620,25 +6578,25 @@
         <v>86</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>485</v>
+        <v>482</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>486</v>
+        <v>483</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>487</v>
+        <v>484</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6652,25 +6610,25 @@
         <v>92</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6684,13 +6642,13 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>492</v>
+        <v>489</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
@@ -6699,10 +6657,10 @@
         <v>89</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>493</v>
+        <v>490</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6716,25 +6674,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>491</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>491</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6748,16 +6706,16 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>58</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>496</v>
+        <v>58</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>70</v>
@@ -6766,7 +6724,7 @@
         <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6780,13 +6738,13 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>500</v>
+        <v>497</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
@@ -6798,7 +6756,7 @@
         <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>501</v>
+        <v>498</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6812,25 +6770,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>502</v>
+        <v>499</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>503</v>
+        <v>500</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6844,13 +6802,13 @@
         <v>120</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>505</v>
+        <v>502</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>506</v>
+        <v>503</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
@@ -6859,10 +6817,10 @@
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>507</v>
+        <v>504</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6876,25 +6834,25 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>508</v>
+        <v>505</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>509</v>
+        <v>506</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>507</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6908,13 +6866,13 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>512</v>
+        <v>509</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
@@ -6923,10 +6881,10 @@
         <v>118</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>510</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6940,13 +6898,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>514</v>
+        <v>511</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>515</v>
+        <v>512</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
@@ -6955,10 +6913,10 @@
         <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>135</v>
+        <v>148</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>513</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6969,28 +6927,28 @@
         <v>50</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>517</v>
+        <v>514</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>516</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7004,13 +6962,13 @@
         <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>517</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>521</v>
+        <v>518</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -7019,10 +6977,10 @@
         <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>519</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7033,16 +6991,16 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>520</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>524</v>
+        <v>521</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
@@ -7051,10 +7009,10 @@
         <v>70</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>327</v>
+        <v>139</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7068,25 +7026,25 @@
         <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>528</v>
+        <v>525</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7100,13 +7058,13 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
@@ -7115,10 +7073,10 @@
         <v>118</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>531</v>
+        <v>528</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7132,25 +7090,25 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7164,13 +7122,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>535</v>
+        <v>532</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -7179,10 +7137,10 @@
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>327</v>
+        <v>139</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>534</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7196,25 +7154,25 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>538</v>
+        <v>535</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>536</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>540</v>
+        <v>537</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7228,13 +7186,13 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -7243,10 +7201,10 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7260,25 +7218,25 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>544</v>
+        <v>541</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>545</v>
+        <v>542</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>292</v>
+        <v>330</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>543</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7292,13 +7250,13 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>544</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>545</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
@@ -7307,10 +7265,10 @@
         <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7324,13 +7282,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -7339,10 +7297,10 @@
         <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>552</v>
+        <v>549</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>553</v>
+        <v>550</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -20,14 +20,14 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Kaia!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">블루스2기!$A$1:$J$27</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">청정원!$A$1:$J$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">청정원!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="551">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="554">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,10 +80,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>388</t>
-  </si>
-  <si>
-    <t>13위</t>
+    <t>391</t>
+  </si>
+  <si>
+    <t>14위</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>220조 3391억 950만</t>
+    <t>227조 2799억 3680만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.27</t>
+    <t>2026.04.28</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,7 +113,7 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>389</t>
+    <t>393</t>
   </si>
   <si>
     <t>11위</t>
@@ -122,7 +122,7 @@
     <t>29명</t>
   </si>
   <si>
-    <t>218조 3079억 2710만</t>
+    <t>224조 4597억 7214만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -140,16 +140,16 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>363</t>
-  </si>
-  <si>
-    <t>8위</t>
+    <t>364</t>
+  </si>
+  <si>
+    <t>9위</t>
   </si>
   <si>
     <t>Lv.7</t>
   </si>
   <si>
-    <t>241조 9907억 228만</t>
+    <t>252조 4414억 5065만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -167,13 +167,13 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>440</t>
+    <t>430</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>168조 7434억 6773만</t>
+    <t>179조 7720억 3255만</t>
   </si>
   <si>
     <t>보보네</t>
@@ -188,7 +188,7 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>366</t>
+    <t>375</t>
   </si>
   <si>
     <t>16위</t>
@@ -197,7 +197,7 @@
     <t>26명</t>
   </si>
   <si>
-    <t>239조 2396억 7777만</t>
+    <t>238조 6651억 3670만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -245,7 +245,7 @@
     <t>104</t>
   </si>
   <si>
-    <t>31조 4685억 9720만</t>
+    <t>33조 6514억 3727만</t>
   </si>
   <si>
     <t>2</t>
@@ -266,7 +266,7 @@
     <t>102</t>
   </si>
   <si>
-    <t>21조 8866억 2814만</t>
+    <t>22조 7632억 1918만</t>
   </si>
   <si>
     <t>3</t>
@@ -281,42 +281,42 @@
     <t>신궁</t>
   </si>
   <si>
+    <t>20조 8772억 7416만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>14조 8623억 2147만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
     <t>103</t>
   </si>
   <si>
-    <t>20조 8772억 7416만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>14조 8623억 2147만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
     <t>13조 2229억 5022만</t>
   </si>
   <si>
@@ -329,7 +329,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>11조 9918억 5094만</t>
+    <t>12조 6451억 9325만</t>
   </si>
   <si>
     <t>7</t>
@@ -341,7 +341,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>7조 6801억 1998만</t>
+    <t>8조 3818억 1066만</t>
   </si>
   <si>
     <t>8</t>
@@ -353,7 +353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 5286억 8021만</t>
+    <t>7조 8622억 22만</t>
   </si>
   <si>
     <t>9</t>
@@ -377,6 +377,18 @@
     <t>10</t>
   </si>
   <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>6조 8249억 4902만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -389,7 +401,7 @@
     <t>6조 7155억 1566만</t>
   </si>
   <si>
-    <t>11</t>
+    <t>12</t>
   </si>
   <si>
     <t>우후</t>
@@ -398,19 +410,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>6조 5215억 1858만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>6조 4649억 8468만</t>
+    <t>6조 6454억 425만</t>
   </si>
   <si>
     <t>13</t>
@@ -422,22 +422,46 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>5조 2258억 7841만</t>
+    <t>5조 2326억 4158만</t>
   </si>
   <si>
     <t>14</t>
   </si>
   <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>5조 1150억 4755만</t>
+  </si>
+  <si>
+    <t>15</t>
+  </si>
+  <si>
     <t>흑두부</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
   </si>
   <si>
-    <t>5조 339억 2537만</t>
-  </si>
-  <si>
-    <t>15</t>
+    <t>5조 582억 6768만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>4조 8881억 6806만</t>
+  </si>
+  <si>
+    <t>17</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -449,37 +473,25 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 7304억 2040만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 6479억 5302만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+    <t>4조 8235억 7398만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>비스밤</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
   </si>
   <si>
     <t>99</t>
   </si>
   <si>
-    <t>4조 6273억 4164만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>4조 7975억 1419만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -491,18 +503,6 @@
     <t>4조 1571억 2932만</t>
   </si>
   <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>비스밤</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EC%8A%A4%EB%B0%A4</t>
-  </si>
-  <si>
-    <t>4조 1213억 1333만</t>
-  </si>
-  <si>
     <t>20</t>
   </si>
   <si>
@@ -536,7 +536,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 4067억 1103만</t>
+    <t>3조 4647억 3569만</t>
   </si>
   <si>
     <t>23</t>
@@ -548,7 +548,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>2조 9483억 6909만</t>
+    <t>3조 477억 3365만</t>
   </si>
   <si>
     <t>24</t>
@@ -560,7 +560,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 8743억 5331만</t>
+    <t>2조 8934억 4065만</t>
   </si>
   <si>
     <t>25</t>
@@ -635,7 +635,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 275억 8658만</t>
+    <t>2조 317억 2232만</t>
   </si>
   <si>
     <t>그때</t>
@@ -671,7 +671,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
   </si>
   <si>
-    <t>12조 8520억 5517만</t>
+    <t>14조 579억 6513만</t>
   </si>
   <si>
     <t>엔도르시</t>
@@ -689,7 +689,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%8C%95</t>
   </si>
   <si>
-    <t>11조 683억 25만</t>
+    <t>11조 9726억 8823만</t>
   </si>
   <si>
     <t>르밥</t>
@@ -707,7 +707,16 @@
     <t>https://mgf.gg/contents/character.php?n=vander</t>
   </si>
   <si>
-    <t>7조 6777억 2935만</t>
+    <t>8조 1696억 1376만</t>
+  </si>
+  <si>
+    <t>인큐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
+  </si>
+  <si>
+    <t>7조 7524억 313만</t>
   </si>
   <si>
     <t>무신사할배</t>
@@ -716,7 +725,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
   </si>
   <si>
-    <t>7조 4497억 2175만</t>
+    <t>7조 6111억 5399만</t>
   </si>
   <si>
     <t>코코연구가2</t>
@@ -728,15 +737,6 @@
     <t>7조 1647억 6150만</t>
   </si>
   <si>
-    <t>인큐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
-  </si>
-  <si>
-    <t>6조 6139억 5179만</t>
-  </si>
-  <si>
     <t>효율</t>
   </si>
   <si>
@@ -746,13 +746,28 @@
     <t>6조 4121억 6745만</t>
   </si>
   <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
+  </si>
+  <si>
+    <t>6조 1521억 414만</t>
+  </si>
+  <si>
     <t>종구왕</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
   </si>
   <si>
-    <t>5조 9723억 677만</t>
+    <t>6조 849억 4745만</t>
+  </si>
+  <si>
+    <t>킹돔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
+  </si>
+  <si>
+    <t>5조 9751억 7788만</t>
   </si>
   <si>
     <t>체르</t>
@@ -761,22 +776,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
   </si>
   <si>
-    <t>5조 7041억 7803만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>5조 6392억 7905만</t>
-  </si>
-  <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>5조 4328억 6429만</t>
+    <t>5조 8172억 6200만</t>
   </si>
   <si>
     <t>운스</t>
@@ -797,13 +797,22 @@
     <t>5조 1220억 1649만</t>
   </si>
   <si>
+    <t>요계</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
+  </si>
+  <si>
+    <t>4조 7700억 7705만</t>
+  </si>
+  <si>
     <t>신창섭신창섭</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
   </si>
   <si>
-    <t>4조 7212억 1448만</t>
+    <t>4조 7374억 5013만</t>
   </si>
   <si>
     <t>쨍쭝</t>
@@ -815,15 +824,6 @@
     <t>4조 6059억 5811만</t>
   </si>
   <si>
-    <t>요계</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
-  </si>
-  <si>
-    <t>4조 3600억 6827만</t>
-  </si>
-  <si>
     <t>코코연구가</t>
   </si>
   <si>
@@ -839,7 +839,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
   </si>
   <si>
-    <t>3조 9593억 1941만</t>
+    <t>3조 9744억 1139만</t>
+  </si>
+  <si>
+    <t>아율마더</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
+  </si>
+  <si>
+    <t>3조 8704억 5050만</t>
   </si>
   <si>
     <t>쫑쓰</t>
@@ -848,7 +857,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
   </si>
   <si>
-    <t>3조 6391억 1926만</t>
+    <t>3조 7518억 3557만</t>
   </si>
   <si>
     <t>13미니</t>
@@ -857,16 +866,16 @@
     <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 5571억 4495만</t>
-  </si>
-  <si>
-    <t>아율마더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
-  </si>
-  <si>
-    <t>3조 5389억 2913만</t>
+    <t>3조 5760억 9647만</t>
+  </si>
+  <si>
+    <t>네그로니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
+  </si>
+  <si>
+    <t>3조 2114억 6233만</t>
   </si>
   <si>
     <t>아율파더</t>
@@ -878,15 +887,6 @@
     <t>3조 1546억 9866만</t>
   </si>
   <si>
-    <t>네그로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>3조 1502억 5777만</t>
-  </si>
-  <si>
     <t>맨셸리</t>
   </si>
   <si>
@@ -899,7 +899,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>5268억 7773만</t>
+    <t>5300억 6333만</t>
   </si>
   <si>
     <t>픅픅</t>
@@ -911,7 +911,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>111조 24억 8369만</t>
+    <t>111조 3804억 4966만</t>
   </si>
   <si>
     <t>끝까지힘내자</t>
@@ -923,6 +923,15 @@
     <t>34조 5879억 2379만</t>
   </si>
   <si>
+    <t>호뤼뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>21조 7497억 3722만</t>
+  </si>
+  <si>
     <t>티종</t>
   </si>
   <si>
@@ -935,19 +944,10 @@
     <t>20조 2481억 75만</t>
   </si>
   <si>
-    <t>호뤼뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>17조 1007억 1083만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=Edom</t>
   </si>
   <si>
-    <t>15조 7765억 9880만</t>
+    <t>19조 7796억 4086만</t>
   </si>
   <si>
     <t>야생봄이</t>
@@ -956,7 +956,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>7조 5964억 2954만</t>
+    <t>7조 8148억 5346만</t>
+  </si>
+  <si>
+    <t>긍궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
+  </si>
+  <si>
+    <t>5조 7907억 8522만</t>
   </si>
   <si>
     <t>이은제리</t>
@@ -965,16 +974,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
   </si>
   <si>
-    <t>5조 7731억 2999만</t>
-  </si>
-  <si>
-    <t>긍궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
-  </si>
-  <si>
-    <t>5조 3816억 2633만</t>
+    <t>5조 7826억 3445만</t>
   </si>
   <si>
     <t>청아씨</t>
@@ -983,7 +983,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
   </si>
   <si>
-    <t>4조 7061억 5379만</t>
+    <t>4조 7751억 9312만</t>
   </si>
   <si>
     <t>민규짱짱맨</t>
@@ -992,7 +992,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
   </si>
   <si>
-    <t>2조 4760억 4834만</t>
+    <t>2조 5903억 4540만</t>
   </si>
   <si>
     <t>KR#9SQP2LGG2B</t>
@@ -1001,7 +1001,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
   </si>
   <si>
-    <t>2조 3172억 7325만</t>
+    <t>2조 3424억 4435만</t>
   </si>
   <si>
     <t>츠키유</t>
@@ -1010,7 +1010,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
   </si>
   <si>
-    <t>1조 5958억 6891만</t>
+    <t>1조 8559억 7520만</t>
   </si>
   <si>
     <t>반존대</t>
@@ -1031,7 +1031,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
   </si>
   <si>
-    <t>1조 4888억 5491만</t>
+    <t>1조 5143억 1900만</t>
   </si>
   <si>
     <t>봉찬</t>
@@ -1040,7 +1040,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
   </si>
   <si>
-    <t>1조 1570억 9979만</t>
+    <t>1조 1978억 4287만</t>
   </si>
   <si>
     <t>매력적수달</t>
@@ -1052,7 +1052,25 @@
     <t>95</t>
   </si>
   <si>
-    <t>9122억 2811만</t>
+    <t>9292억 4251만</t>
+  </si>
+  <si>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>9036억 1989만</t>
+  </si>
+  <si>
+    <t>달려봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
+  </si>
+  <si>
+    <t>8860억 8843만</t>
   </si>
   <si>
     <t>서리밍</t>
@@ -1064,31 +1082,13 @@
     <t>8821억 1213만</t>
   </si>
   <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>8518억 2808만</t>
-  </si>
-  <si>
-    <t>달려봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
-  </si>
-  <si>
-    <t>8324억 8049만</t>
-  </si>
-  <si>
     <t>채류진</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
   </si>
   <si>
-    <t>7937억 1939만</t>
+    <t>8093억 8552만</t>
   </si>
   <si>
     <t>낀조</t>
@@ -1106,7 +1106,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
   </si>
   <si>
-    <t>6873억 8645만</t>
+    <t>7442억 2872만</t>
+  </si>
+  <si>
+    <t>공또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
+  </si>
+  <si>
+    <t>6140억 9930만</t>
   </si>
   <si>
     <t>닝갠</t>
@@ -1118,22 +1127,13 @@
     <t>6023억 1234만</t>
   </si>
   <si>
-    <t>공또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
-  </si>
-  <si>
-    <t>5821억 9376만</t>
-  </si>
-  <si>
     <t>유해화학물질</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>5018억 2431만</t>
+    <t>5063억 1252만</t>
   </si>
   <si>
     <t>ENNOY</t>
@@ -1142,7 +1142,7 @@
     <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
   </si>
   <si>
-    <t>4943억 6783만</t>
+    <t>4958억 6854만</t>
   </si>
   <si>
     <t>dvzve</t>
@@ -1160,7 +1160,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
   </si>
   <si>
-    <t>4560억 4237만</t>
+    <t>4720억 3106만</t>
   </si>
   <si>
     <t>쨍꿍</t>
@@ -1193,7 +1193,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>27조 7146억 2441만</t>
+    <t>28조 3742억 466만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -1211,7 +1211,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%A4%EB%AF%B8</t>
   </si>
   <si>
-    <t>13조 4229억 1475만</t>
+    <t>15조 7855억 8875만</t>
+  </si>
+  <si>
+    <t>토하루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>10조 9001억 8560만</t>
   </si>
   <si>
     <t>슈퍼앤트</t>
@@ -1223,15 +1232,6 @@
     <t>10조 3167억 1702만</t>
   </si>
   <si>
-    <t>토하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>7조 9938억 907만</t>
-  </si>
-  <si>
     <t>쎄도어</t>
   </si>
   <si>
@@ -1241,6 +1241,15 @@
     <t>6조 6751억 1083만</t>
   </si>
   <si>
+    <t>머겸</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
+  </si>
+  <si>
+    <t>6조 1927억 8768만</t>
+  </si>
+  <si>
     <t>스응로</t>
   </si>
   <si>
@@ -1250,22 +1259,31 @@
     <t>6조 1219억 9639만</t>
   </si>
   <si>
-    <t>머겸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
-  </si>
-  <si>
-    <t>6조 231억 823만</t>
-  </si>
-  <si>
     <t>abba</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=abba</t>
   </si>
   <si>
-    <t>5조 8087억 8308만</t>
+    <t>6조 781억 970만</t>
+  </si>
+  <si>
+    <t>사본</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
+  </si>
+  <si>
+    <t>5조 6970억 5560만</t>
+  </si>
+  <si>
+    <t>표창넣을게</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
+  </si>
+  <si>
+    <t>5조 5434억 156만</t>
   </si>
   <si>
     <t>류작</t>
@@ -1277,24 +1295,6 @@
     <t>5조 5381억 9279만</t>
   </si>
   <si>
-    <t>사본</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
-  </si>
-  <si>
-    <t>5조 5132억 7176만</t>
-  </si>
-  <si>
-    <t>표창넣을게</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
-  </si>
-  <si>
-    <t>5조 3365억 1499만</t>
-  </si>
-  <si>
     <t>불소그리스</t>
   </si>
   <si>
@@ -1304,22 +1304,22 @@
     <t>5조 1920억 8892만</t>
   </si>
   <si>
+    <t>인천왕김치언</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
+  </si>
+  <si>
+    <t>5조 1147억 9352만</t>
+  </si>
+  <si>
     <t>윤서u</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
   </si>
   <si>
-    <t>4조 7654억 1939만</t>
-  </si>
-  <si>
-    <t>인천왕김치언</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
-  </si>
-  <si>
-    <t>4조 7507억 1614만</t>
+    <t>4조 8058억 3000만</t>
   </si>
   <si>
     <t>라마킴</t>
@@ -1328,7 +1328,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
   </si>
   <si>
-    <t>4조 4769억 7439만</t>
+    <t>4조 6323억 7544만</t>
   </si>
   <si>
     <t>조애니</t>
@@ -1337,7 +1337,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>4조 2482억 848만</t>
+    <t>4조 3628억 3463만</t>
+  </si>
+  <si>
+    <t>뜨루뜨루</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
+  </si>
+  <si>
+    <t>3조 4281억 950만</t>
   </si>
   <si>
     <t>민수심심해</t>
@@ -1349,19 +1358,10 @@
     <t>3조 2698억 7360만</t>
   </si>
   <si>
-    <t>뜨루뜨루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>3조 1816억 894만</t>
-  </si>
-  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
   </si>
   <si>
-    <t>3조 1472억 4695만</t>
+    <t>3조 2498억 755만</t>
   </si>
   <si>
     <t>오로치재림</t>
@@ -1373,6 +1373,15 @@
     <t>3조 240억 6770만</t>
   </si>
   <si>
+    <t>우현이심심해</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%98%84%EC%9D%B4%EC%8B%AC%EC%8B%AC%ED%95%B4</t>
+  </si>
+  <si>
+    <t>2조 8248억 2319만</t>
+  </si>
+  <si>
     <t>승우아빠</t>
   </si>
   <si>
@@ -1388,7 +1397,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
   </si>
   <si>
-    <t>2조 2639억 1395만</t>
+    <t>2조 4228억 8783만</t>
   </si>
   <si>
     <t>박띵수</t>
@@ -1397,7 +1406,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
   </si>
   <si>
-    <t>2조 2300억 7595만</t>
+    <t>2조 2360억 4439만</t>
+  </si>
+  <si>
+    <t>사이비숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
+  </si>
+  <si>
+    <t>2조 2323억 1749만</t>
   </si>
   <si>
     <t>토리꼬리</t>
@@ -1409,15 +1427,6 @@
     <t>2조 1948억 4810만</t>
   </si>
   <si>
-    <t>사이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>1조 9854억 9439만</t>
-  </si>
-  <si>
     <t>토리츄</t>
   </si>
   <si>
@@ -1445,7 +1454,10 @@
     <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
   </si>
   <si>
-    <t>2198억 1763만</t>
+    <t>93</t>
+  </si>
+  <si>
+    <t>2299억 1025만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1454,7 +1466,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
   </si>
   <si>
-    <t>108조 4948억 4009만</t>
+    <t>109조 9399억 3466만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1472,7 +1484,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
   </si>
   <si>
-    <t>7조 8360억 4690만</t>
+    <t>8조 1072억 6227만</t>
   </si>
   <si>
     <t>드뚜</t>
@@ -1481,7 +1493,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
   </si>
   <si>
-    <t>7조 6372억 7446만</t>
+    <t>7조 8611억 4894만</t>
   </si>
   <si>
     <t>갈맄</t>
@@ -1490,16 +1502,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
   </si>
   <si>
-    <t>6조 7244억 4168만</t>
-  </si>
-  <si>
-    <t>푸장님</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%B8%EC%9E%A5%EB%8B%98</t>
-  </si>
-  <si>
-    <t>6조 2486억 8797만</t>
+    <t>6조 7304억 8108만</t>
   </si>
   <si>
     <t>꾸린이</t>
@@ -1514,7 +1517,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
   </si>
   <si>
-    <t>5조 8642억 6997만</t>
+    <t>6조 357억 1773만</t>
   </si>
   <si>
     <t>한반</t>
@@ -1523,7 +1526,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 7700억 4471만</t>
+    <t>3조 8083억 2799만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1544,13 +1547,22 @@
     <t>3조 473억 2990만</t>
   </si>
   <si>
+    <t>한맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>2조 8862억 6125만</t>
+  </si>
+  <si>
     <t>4033</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=4033</t>
   </si>
   <si>
-    <t>2조 8376억 1733만</t>
+    <t>2조 8491억 4117만</t>
   </si>
   <si>
     <t>세넬</t>
@@ -1559,7 +1571,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>2조 4353억 249만</t>
+    <t>2조 5303억 5623만</t>
   </si>
   <si>
     <t>기뜩</t>
@@ -1571,31 +1583,31 @@
     <t>2조 785억 9293만</t>
   </si>
   <si>
+    <t>리토비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1조 9788억 8836만</t>
+  </si>
+  <si>
+    <t>하흙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
+  </si>
+  <si>
+    <t>1조 9233억 4396만</t>
+  </si>
+  <si>
     <t>관둬</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
   </si>
   <si>
-    <t>1조 8398억 6283만</t>
-  </si>
-  <si>
-    <t>하흙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
-  </si>
-  <si>
-    <t>1조 7950억 5457만</t>
-  </si>
-  <si>
-    <t>리토비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1조 7947억 3068만</t>
+    <t>1조 8526억 7735만</t>
   </si>
   <si>
     <t>도밥</t>
@@ -1622,7 +1634,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
   </si>
   <si>
-    <t>1조 4802억 9569만</t>
+    <t>1조 5099억 7477만</t>
   </si>
   <si>
     <t>챙날</t>
@@ -1640,7 +1652,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
   </si>
   <si>
-    <t>1조 356억 5788만</t>
+    <t>1조 455억 4916만</t>
   </si>
   <si>
     <t>홍루이</t>
@@ -1649,7 +1661,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%A3%A8%EC%9D%B4</t>
   </si>
   <si>
-    <t>9477억 2262만</t>
+    <t>1조 240억 3361만</t>
   </si>
   <si>
     <t>이완근</t>
@@ -1658,7 +1670,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
   </si>
   <si>
-    <t>6790억 5324만</t>
+    <t>7227억 7441만</t>
   </si>
   <si>
     <t>안마시술소</t>
@@ -1667,16 +1679,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
   </si>
   <si>
-    <t>6227억 5652만</t>
+    <t>6632억 4562만</t>
   </si>
   <si>
     <t>성현이여</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%ED%98%84%EC%9D%B4%EC%97%AC</t>
-  </si>
-  <si>
-    <t>93</t>
   </si>
   <si>
     <t>2396억 6940만</t>
@@ -2248,7 +2257,7 @@
         <v>39</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>48</v>
@@ -2448,10 +2457,10 @@
         <v>83</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>84</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>85</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2462,28 +2471,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="H5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>90</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>91</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2494,25 +2503,25 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>96</v>
@@ -2544,7 +2553,7 @@
         <v>77</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>100</v>
@@ -2573,10 +2582,10 @@
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H8" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>104</v>
@@ -2605,10 +2614,10 @@
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H9" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>108</v>
@@ -2669,13 +2678,13 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>118</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>119</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2686,25 +2695,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="D12" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>123</v>
@@ -2733,7 +2742,7 @@
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H13" s="2" t="s">
         <v>113</v>
@@ -2768,7 +2777,7 @@
         <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>131</v>
@@ -2797,7 +2806,7 @@
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>113</v>
@@ -2829,13 +2838,13 @@
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H16" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>139</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2846,16 +2855,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="E17" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -2867,7 +2876,7 @@
         <v>113</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2878,28 +2887,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>148</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>149</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2910,25 +2919,25 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="2" t="s">
         <v>152</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>153</v>
@@ -2957,10 +2966,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>148</v>
+        <v>113</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>157</v>
@@ -3053,10 +3062,10 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>169</v>
@@ -3088,7 +3097,7 @@
         <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>173</v>
@@ -3120,7 +3129,7 @@
         <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>177</v>
@@ -3152,7 +3161,7 @@
         <v>83</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>181</v>
@@ -3181,7 +3190,7 @@
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>113</v>
@@ -3216,7 +3225,7 @@
         <v>70</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>189</v>
@@ -3248,7 +3257,7 @@
         <v>193</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>194</v>
@@ -3280,7 +3289,7 @@
         <v>70</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>198</v>
@@ -3490,7 +3499,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>78</v>
@@ -3507,7 +3516,7 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>212</v>
@@ -3539,7 +3548,7 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>215</v>
@@ -3554,7 +3563,7 @@
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H6" s="2" t="s">
         <v>78</v>
@@ -3589,7 +3598,7 @@
         <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>84</v>
+        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>220</v>
@@ -3621,7 +3630,7 @@
         <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>223</v>
@@ -3650,7 +3659,7 @@
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>78</v>
@@ -3682,10 +3691,10 @@
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>112</v>
+        <v>122</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>229</v>
@@ -3714,10 +3723,10 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>232</v>
@@ -3731,7 +3740,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>233</v>
@@ -3746,10 +3755,10 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>235</v>
@@ -3781,7 +3790,7 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>238</v>
@@ -3798,25 +3807,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>239</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3830,25 +3839,25 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>242</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3862,19 +3871,19 @@
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>33</v>
+        <v>244</v>
       </c>
       <c r="E16" s="2" t="s">
         <v>245</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
         <v>78</v>
@@ -3891,7 +3900,7 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>247</v>
@@ -3906,7 +3915,7 @@
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>78</v>
@@ -3923,7 +3932,7 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>250</v>
@@ -3938,7 +3947,7 @@
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H18" s="2" t="s">
         <v>78</v>
@@ -3955,7 +3964,7 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>253</v>
@@ -3970,10 +3979,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>255</v>
@@ -4002,10 +4011,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>112</v>
+        <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>258</v>
@@ -4034,10 +4043,10 @@
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>261</v>
@@ -4066,10 +4075,10 @@
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>78</v>
+        <v>89</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>264</v>
@@ -4098,10 +4107,10 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>267</v>
@@ -4130,10 +4139,10 @@
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>270</v>
@@ -4162,10 +4171,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>273</v>
@@ -4194,10 +4203,10 @@
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H26" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>276</v>
@@ -4226,10 +4235,10 @@
         <v>76</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>279</v>
@@ -4258,10 +4267,10 @@
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>148</v>
+        <v>89</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>282</v>
@@ -4290,10 +4299,10 @@
         <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>90</v>
+        <v>152</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>285</v>
@@ -4381,7 +4390,7 @@
     <col min="3" max="4" width="15.7109375" customWidth="1"/>
     <col min="5" max="5" width="50.7109375" customWidth="1"/>
     <col min="6" max="8" width="12.7109375" customWidth="1"/>
-    <col min="9" max="9" width="17.7109375" customWidth="1"/>
+    <col min="9" max="9" width="18.7109375" customWidth="1"/>
     <col min="10" max="10" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4501,13 +4510,13 @@
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4518,25 +4527,25 @@
         <v>34</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>83</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>304</v>
@@ -4550,7 +4559,7 @@
         <v>34</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>42</v>
@@ -4568,7 +4577,7 @@
         <v>70</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>306</v>
@@ -4629,10 +4638,10 @@
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>312</v>
@@ -4661,10 +4670,10 @@
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>315</v>
@@ -4725,10 +4734,10 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>321</v>
@@ -4742,7 +4751,7 @@
         <v>34</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>322</v>
@@ -4760,7 +4769,7 @@
         <v>83</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>324</v>
@@ -4792,7 +4801,7 @@
         <v>288</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>327</v>
@@ -4821,7 +4830,7 @@
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H14" s="2" t="s">
         <v>330</v>
@@ -4853,7 +4862,7 @@
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H15" s="2" t="s">
         <v>330</v>
@@ -4888,7 +4897,7 @@
         <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>289</v>
+        <v>330</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>337</v>
@@ -4902,7 +4911,7 @@
         <v>34</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>338</v>
@@ -4934,7 +4943,7 @@
         <v>34</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>342</v>
@@ -4949,10 +4958,10 @@
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>118</v>
+        <v>83</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>330</v>
+        <v>289</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>344</v>
@@ -4966,7 +4975,7 @@
         <v>34</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>345</v>
@@ -4981,10 +4990,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>289</v>
+        <v>340</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>347</v>
@@ -5013,10 +5022,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>340</v>
+        <v>330</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>350</v>
@@ -5045,7 +5054,7 @@
         <v>76</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>289</v>
@@ -5077,7 +5086,7 @@
         <v>76</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H22" s="2" t="s">
         <v>289</v>
@@ -5141,7 +5150,7 @@
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>289</v>
@@ -5173,10 +5182,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>340</v>
+        <v>289</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>365</v>
@@ -5269,7 +5278,7 @@
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>340</v>
@@ -5417,7 +5426,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -5546,7 +5555,7 @@
         <v>76</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>78</v>
@@ -5563,7 +5572,7 @@
         <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
         <v>395</v>
@@ -5578,10 +5587,10 @@
         <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>118</v>
+        <v>88</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>90</v>
+        <v>78</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>397</v>
@@ -5595,7 +5604,7 @@
         <v>43</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>398</v>
@@ -5610,10 +5619,10 @@
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="H6" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>400</v>
@@ -5645,7 +5654,7 @@
         <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>403</v>
@@ -5674,10 +5683,10 @@
         <v>76</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>193</v>
+        <v>70</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>78</v>
+        <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>406</v>
@@ -5706,10 +5715,10 @@
         <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>193</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>113</v>
+        <v>78</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>409</v>
@@ -5741,7 +5750,7 @@
         <v>70</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>412</v>
@@ -5770,10 +5779,10 @@
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>415</v>
@@ -5787,7 +5796,7 @@
         <v>43</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>416</v>
@@ -5802,10 +5811,10 @@
         <v>76</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>418</v>
@@ -5834,10 +5843,10 @@
         <v>76</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>421</v>
@@ -5866,10 +5875,10 @@
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>424</v>
@@ -5898,10 +5907,10 @@
         <v>76</v>
       </c>
       <c r="G15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>113</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>427</v>
@@ -5930,10 +5939,10 @@
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>88</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>430</v>
@@ -5947,7 +5956,7 @@
         <v>43</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>431</v>
@@ -5962,10 +5971,10 @@
         <v>76</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>433</v>
@@ -5979,7 +5988,7 @@
         <v>43</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>434</v>
@@ -6011,7 +6020,7 @@
         <v>43</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>437</v>
@@ -6026,10 +6035,10 @@
         <v>76</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>439</v>
@@ -6058,10 +6067,10 @@
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>113</v>
+        <v>89</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>442</v>
@@ -6093,7 +6102,7 @@
         <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>444</v>
@@ -6154,7 +6163,7 @@
         <v>76</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
         <v>113</v>
@@ -6186,7 +6195,7 @@
         <v>76</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H24" s="2" t="s">
         <v>113</v>
@@ -6218,10 +6227,10 @@
         <v>76</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>122</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>139</v>
+        <v>113</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>456</v>
@@ -6250,10 +6259,10 @@
         <v>76</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>118</v>
+        <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>113</v>
+        <v>147</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>459</v>
@@ -6285,7 +6294,7 @@
         <v>288</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>462</v>
@@ -6314,10 +6323,10 @@
         <v>76</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>83</v>
+        <v>122</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>330</v>
+        <v>113</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>465</v>
@@ -6346,13 +6355,13 @@
         <v>76</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="H29" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>468</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>469</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6366,22 +6375,22 @@
         <v>195</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>470</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>380</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>472</v>
@@ -6390,8 +6399,40 @@
         <v>24</v>
       </c>
     </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="B31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="E31" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="F31" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="I31" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="J31" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J30"/>
+  <autoFilter ref="A1:J31"/>
   <hyperlinks>
     <hyperlink ref="E2" r:id="rId1"/>
     <hyperlink ref="E3" r:id="rId2"/>
@@ -6422,6 +6463,7 @@
     <hyperlink ref="E28" r:id="rId27"/>
     <hyperlink ref="E29" r:id="rId28"/>
     <hyperlink ref="E30" r:id="rId29"/>
+    <hyperlink ref="E31" r:id="rId30"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -6482,13 +6524,13 @@
         <v>67</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>76</v>
@@ -6500,7 +6542,7 @@
         <v>293</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6514,13 +6556,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>76</v>
@@ -6532,7 +6574,7 @@
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6546,13 +6588,13 @@
         <v>80</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>76</v>
@@ -6564,7 +6606,7 @@
         <v>113</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6575,28 +6617,28 @@
         <v>50</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H5" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6607,28 +6649,28 @@
         <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6642,25 +6684,25 @@
         <v>97</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>89</v>
+        <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6674,16 +6716,16 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>491</v>
+        <v>58</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>491</v>
+        <v>58</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>70</v>
@@ -6692,7 +6734,7 @@
         <v>113</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6706,25 +6748,25 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>58</v>
+        <v>497</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>58</v>
+        <v>497</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>112</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6738,25 +6780,25 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>112</v>
+        <v>83</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>113</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6770,25 +6812,25 @@
         <v>115</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>83</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>113</v>
+        <v>152</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6799,16 +6841,16 @@
         <v>50</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>76</v>
@@ -6817,10 +6859,10 @@
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6834,13 +6876,13 @@
         <v>124</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>76</v>
@@ -6849,10 +6891,10 @@
         <v>83</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6866,25 +6908,25 @@
         <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6898,13 +6940,13 @@
         <v>132</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>76</v>
@@ -6913,10 +6955,10 @@
         <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6930,25 +6972,25 @@
         <v>136</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>77</v>
+        <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6959,16 +7001,16 @@
         <v>50</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>76</v>
@@ -6977,10 +7019,10 @@
         <v>70</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -6991,28 +7033,28 @@
         <v>50</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>77</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7023,16 +7065,16 @@
         <v>50</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>76</v>
@@ -7041,10 +7083,10 @@
         <v>70</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7058,25 +7100,25 @@
         <v>154</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>76</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="H20" s="2" t="s">
         <v>330</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7090,13 +7132,13 @@
         <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>76</v>
@@ -7105,10 +7147,10 @@
         <v>288</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7122,13 +7164,13 @@
         <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>76</v>
@@ -7137,10 +7179,10 @@
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>139</v>
+        <v>147</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7154,13 +7196,13 @@
         <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>76</v>
@@ -7172,7 +7214,7 @@
         <v>289</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7186,13 +7228,13 @@
         <v>170</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>76</v>
@@ -7204,7 +7246,7 @@
         <v>330</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7218,13 +7260,13 @@
         <v>174</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>76</v>
@@ -7236,7 +7278,7 @@
         <v>330</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7250,13 +7292,13 @@
         <v>178</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>76</v>
@@ -7268,7 +7310,7 @@
         <v>330</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7282,13 +7324,13 @@
         <v>182</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>76</v>
@@ -7297,10 +7339,10 @@
         <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>549</v>
+        <v>471</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="554">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="553">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,10 +80,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>391</t>
-  </si>
-  <si>
-    <t>14위</t>
+    <t>353</t>
+  </si>
+  <si>
+    <t>11위</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>227조 2799억 3680만</t>
+    <t>272조 1350억 3602만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.28</t>
+    <t>2026.04.29</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,16 +113,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>393</t>
-  </si>
-  <si>
-    <t>11위</t>
+    <t>387</t>
   </si>
   <si>
     <t>29명</t>
   </si>
   <si>
-    <t>224조 4597억 7214만</t>
+    <t>229조 2783억 7318만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -140,7 +137,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>364</t>
+    <t>361</t>
   </si>
   <si>
     <t>9위</t>
@@ -149,7 +146,7 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>252조 4414억 5065만</t>
+    <t>259조 5318억 7205만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -167,13 +164,13 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>430</t>
+    <t>425</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>179조 7720억 3255만</t>
+    <t>184조 4870억 6757만</t>
   </si>
   <si>
     <t>보보네</t>
@@ -188,7 +185,7 @@
     <t>Scania 28</t>
   </si>
   <si>
-    <t>375</t>
+    <t>370</t>
   </si>
   <si>
     <t>16위</t>
@@ -197,7 +194,7 @@
     <t>26명</t>
   </si>
   <si>
-    <t>238조 6651억 3670만</t>
+    <t>246조 4081억 6436만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -233,6 +230,27 @@
     <t>1</t>
   </si>
   <si>
+    <t>울힝</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B8%ED%9E%9D</t>
+  </si>
+  <si>
+    <t>N</t>
+  </si>
+  <si>
+    <t>아크메이지(썬,콜)</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>46조 8814억 2450만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
   </si>
   <si>
@@ -242,13 +260,10 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>33조 6514억 3727만</t>
-  </si>
-  <si>
-    <t>2</t>
+    <t>33조 9446억 6489만</t>
+  </si>
+  <si>
+    <t>3</t>
   </si>
   <si>
     <t>킹몬</t>
@@ -257,9 +272,6 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
   </si>
   <si>
-    <t>N</t>
-  </si>
-  <si>
     <t>다크나이트</t>
   </si>
   <si>
@@ -269,7 +281,7 @@
     <t>22조 7632억 1918만</t>
   </si>
   <si>
-    <t>3</t>
+    <t>4</t>
   </si>
   <si>
     <t>큐샤프</t>
@@ -284,7 +296,7 @@
     <t>20조 8772억 7416만</t>
   </si>
   <si>
-    <t>4</t>
+    <t>5</t>
   </si>
   <si>
     <t>엘라임</t>
@@ -299,10 +311,10 @@
     <t>101</t>
   </si>
   <si>
-    <t>14조 8623억 2147만</t>
-  </si>
-  <si>
-    <t>5</t>
+    <t>15조 4304억 3522만</t>
+  </si>
+  <si>
+    <t>6</t>
   </si>
   <si>
     <t>야가다</t>
@@ -320,7 +332,7 @@
     <t>13조 2229억 5022만</t>
   </si>
   <si>
-    <t>6</t>
+    <t>7</t>
   </si>
   <si>
     <t>단풍카우</t>
@@ -329,10 +341,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
   </si>
   <si>
-    <t>12조 6451억 9325만</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>12조 7144억 1150만</t>
+  </si>
+  <si>
+    <t>8</t>
   </si>
   <si>
     <t>아르미느</t>
@@ -344,7 +356,7 @@
     <t>8조 3818억 1066만</t>
   </si>
   <si>
-    <t>8</t>
+    <t>9</t>
   </si>
   <si>
     <t>양정팔</t>
@@ -353,10 +365,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 8622억 22만</t>
-  </si>
-  <si>
-    <t>9</t>
+    <t>7조 8716억 4430만</t>
+  </si>
+  <si>
+    <t>10</t>
   </si>
   <si>
     <t>반도</t>
@@ -371,10 +383,10 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 1219억 6098만</t>
-  </si>
-  <si>
-    <t>10</t>
+    <t>7조 1271억 2840만</t>
+  </si>
+  <si>
+    <t>11</t>
   </si>
   <si>
     <t>포스코퓨처엠</t>
@@ -383,10 +395,10 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
   </si>
   <si>
-    <t>6조 8249억 4902만</t>
-  </si>
-  <si>
-    <t>11</t>
+    <t>6조 9200억 704만</t>
+  </si>
+  <si>
+    <t>12</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -395,13 +407,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>아크메이지(썬,콜)</t>
-  </si>
-  <si>
-    <t>6조 7155억 1566만</t>
-  </si>
-  <si>
-    <t>12</t>
+    <t>6조 7222억 597만</t>
+  </si>
+  <si>
+    <t>13</t>
   </si>
   <si>
     <t>우후</t>
@@ -410,10 +419,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
   </si>
   <si>
-    <t>6조 6454억 425만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>6조 6544억 7794만</t>
+  </si>
+  <si>
+    <t>14</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
+    <t>5조 3631억 9121만</t>
+  </si>
+  <si>
+    <t>15</t>
   </si>
   <si>
     <t>므고</t>
@@ -425,7 +446,7 @@
     <t>5조 2326억 4158만</t>
   </si>
   <si>
-    <t>14</t>
+    <t>16</t>
   </si>
   <si>
     <t>뻥뻥</t>
@@ -434,22 +455,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
   </si>
   <si>
-    <t>5조 1150억 4755만</t>
-  </si>
-  <si>
-    <t>15</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>5조 582억 6768만</t>
-  </si>
-  <si>
-    <t>16</t>
+    <t>5조 2009억 8901만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>아르젠타</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
+  </si>
+  <si>
+    <t>98</t>
+  </si>
+  <si>
+    <t>4조 9510억 5146만</t>
+  </si>
+  <si>
+    <t>18</t>
   </si>
   <si>
     <t>KR#TAKIN9CP37</t>
@@ -458,25 +482,10 @@
     <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
   </si>
   <si>
-    <t>4조 8881억 6806만</t>
-  </si>
-  <si>
-    <t>17</t>
-  </si>
-  <si>
-    <t>아르젠타</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EC%A0%A0%ED%83%80</t>
-  </si>
-  <si>
-    <t>98</t>
-  </si>
-  <si>
-    <t>4조 8235억 7398만</t>
-  </si>
-  <si>
-    <t>18</t>
+    <t>4조 9299억 7891만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -491,7 +500,7 @@
     <t>4조 7975억 1419만</t>
   </si>
   <si>
-    <t>19</t>
+    <t>20</t>
   </si>
   <si>
     <t>쭌파파</t>
@@ -500,10 +509,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
   </si>
   <si>
-    <t>4조 1571억 2932만</t>
-  </si>
-  <si>
-    <t>20</t>
+    <t>4조 1586억 2443만</t>
+  </si>
+  <si>
+    <t>21</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -512,19 +521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>3조 9882억 292만</t>
-  </si>
-  <si>
-    <t>21</t>
-  </si>
-  <si>
-    <t>강철고튠데</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%95%EC%B2%A0%EA%B3%A0%ED%8A%A0%EB%8D%B0</t>
-  </si>
-  <si>
-    <t>3조 6838억 5909만</t>
+    <t>4조 16억 1372만</t>
   </si>
   <si>
     <t>22</t>
@@ -548,7 +545,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EB%A5%B4%EC%BD%94%ED%94%84</t>
   </si>
   <si>
-    <t>3조 477억 3365만</t>
+    <t>3조 488억 9661만</t>
   </si>
   <si>
     <t>24</t>
@@ -635,7 +632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 317억 2232만</t>
+    <t>2조 570억 4078만</t>
   </si>
   <si>
     <t>그때</t>
@@ -671,7 +668,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
   </si>
   <si>
-    <t>14조 579억 6513만</t>
+    <t>14조 5449억 423만</t>
+  </si>
+  <si>
+    <t>르밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>13조 2237억 9181만</t>
   </si>
   <si>
     <t>엔도르시</t>
@@ -692,22 +698,13 @@
     <t>11조 9726억 8823만</t>
   </si>
   <si>
-    <t>르밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>10조 8125억 3069만</t>
-  </si>
-  <si>
     <t>vander</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=vander</t>
   </si>
   <si>
-    <t>8조 1696억 1376만</t>
+    <t>8조 1744억 2670만</t>
   </si>
   <si>
     <t>인큐</t>
@@ -737,6 +734,15 @@
     <t>7조 1647억 6150만</t>
   </si>
   <si>
+    <t>종구왕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
+  </si>
+  <si>
+    <t>6조 5149억 9088만</t>
+  </si>
+  <si>
     <t>효율</t>
   </si>
   <si>
@@ -746,28 +752,28 @@
     <t>6조 4121억 6745만</t>
   </si>
   <si>
+    <t>킹돔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
+  </si>
+  <si>
+    <t>6조 2561억 8768만</t>
+  </si>
+  <si>
+    <t>운스</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
+  </si>
+  <si>
+    <t>6조 1925억 5745만</t>
+  </si>
+  <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
   </si>
   <si>
-    <t>6조 1521억 414만</t>
-  </si>
-  <si>
-    <t>종구왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
-  </si>
-  <si>
-    <t>6조 849억 4745만</t>
-  </si>
-  <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>5조 9751억 7788만</t>
+    <t>6조 1702억 7857만</t>
   </si>
   <si>
     <t>체르</t>
@@ -776,16 +782,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
   </si>
   <si>
-    <t>5조 8172억 6200만</t>
-  </si>
-  <si>
-    <t>운스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>5조 3995억 859만</t>
+    <t>5조 8351억 7849만</t>
   </si>
   <si>
     <t>yawaka</t>
@@ -803,7 +800,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
   </si>
   <si>
-    <t>4조 7700억 7705만</t>
+    <t>4조 8736억 465만</t>
   </si>
   <si>
     <t>신창섭신창섭</t>
@@ -839,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
   </si>
   <si>
-    <t>3조 9744억 1139만</t>
+    <t>3조 9851억 1092만</t>
   </si>
   <si>
     <t>아율마더</t>
@@ -857,7 +854,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
   </si>
   <si>
-    <t>3조 7518억 3557만</t>
+    <t>3조 7663억 4816만</t>
   </si>
   <si>
     <t>13미니</t>
@@ -866,7 +863,7 @@
     <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 5760억 9647만</t>
+    <t>3조 6574억 242만</t>
   </si>
   <si>
     <t>네그로니</t>
@@ -875,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 2114억 6233만</t>
+    <t>3조 3312억 948만</t>
   </si>
   <si>
     <t>아율파더</t>
@@ -884,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>3조 1546억 9866만</t>
+    <t>3조 1614억 1528만</t>
   </si>
   <si>
     <t>맨셸리</t>
@@ -899,7 +896,7 @@
     <t>96</t>
   </si>
   <si>
-    <t>5300억 6333만</t>
+    <t>5689억 4875만</t>
   </si>
   <si>
     <t>픅픅</t>
@@ -911,7 +908,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>111조 3804억 4966만</t>
+    <t>114조 3933억 1142만</t>
   </si>
   <si>
     <t>끝까지힘내자</t>
@@ -929,7 +926,13 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
   </si>
   <si>
-    <t>21조 7497억 3722만</t>
+    <t>22조 3217억 2205만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Edom</t>
+  </si>
+  <si>
+    <t>20조 5824억 4828만</t>
   </si>
   <si>
     <t>티종</t>
@@ -944,19 +947,22 @@
     <t>20조 2481억 75만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=Edom</t>
-  </si>
-  <si>
-    <t>19조 7796억 4086만</t>
-  </si>
-  <si>
     <t>야생봄이</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
   </si>
   <si>
-    <t>7조 8148억 5346만</t>
+    <t>9조 5092억 2050만</t>
+  </si>
+  <si>
+    <t>이은제리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>6조 2702억 6723만</t>
   </si>
   <si>
     <t>긍궁</t>
@@ -965,16 +971,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
   </si>
   <si>
-    <t>5조 7907억 8522만</t>
-  </si>
-  <si>
-    <t>이은제리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>5조 7826억 3445만</t>
+    <t>5조 7959억 4437만</t>
   </si>
   <si>
     <t>청아씨</t>
@@ -983,7 +980,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
   </si>
   <si>
-    <t>4조 7751억 9312만</t>
+    <t>4조 8340억 1193만</t>
   </si>
   <si>
     <t>민규짱짱맨</t>
@@ -1001,7 +998,7 @@
     <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
   </si>
   <si>
-    <t>2조 3424억 4435만</t>
+    <t>2조 3974억 3623만</t>
   </si>
   <si>
     <t>츠키유</t>
@@ -1031,7 +1028,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
   </si>
   <si>
-    <t>1조 5143억 1900만</t>
+    <t>1조 5380억 968만</t>
   </si>
   <si>
     <t>봉찬</t>
@@ -1043,34 +1040,34 @@
     <t>1조 1978억 4287만</t>
   </si>
   <si>
+    <t>달려봐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
+  </si>
+  <si>
+    <t>95</t>
+  </si>
+  <si>
+    <t>9903억 8990만</t>
+  </si>
+  <si>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>9564억 1089만</t>
+  </si>
+  <si>
     <t>매력적수달</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
-    <t>95</t>
-  </si>
-  <si>
-    <t>9292억 4251만</t>
-  </si>
-  <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>9036억 1989만</t>
-  </si>
-  <si>
-    <t>달려봐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
-  </si>
-  <si>
-    <t>8860억 8843만</t>
+    <t>9490억 4143만</t>
   </si>
   <si>
     <t>서리밍</t>
@@ -1082,6 +1079,15 @@
     <t>8821억 1213만</t>
   </si>
   <si>
+    <t>몽샐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
+  </si>
+  <si>
+    <t>8309억 7303만</t>
+  </si>
+  <si>
     <t>채류진</t>
   </si>
   <si>
@@ -1097,16 +1103,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
   </si>
   <si>
-    <t>7811억 4055만</t>
-  </si>
-  <si>
-    <t>몽샐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
-  </si>
-  <si>
-    <t>7442억 2872만</t>
+    <t>7874억 4930만</t>
   </si>
   <si>
     <t>공또</t>
@@ -1115,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
   </si>
   <si>
-    <t>6140억 9930만</t>
+    <t>6454억 2708만</t>
   </si>
   <si>
     <t>닝갠</t>
@@ -1124,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
   </si>
   <si>
-    <t>6023억 1234만</t>
+    <t>6027억 8867만</t>
   </si>
   <si>
     <t>유해화학물질</t>
@@ -1133,7 +1130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>5063억 1252만</t>
+    <t>5479억 115만</t>
   </si>
   <si>
     <t>ENNOY</t>
@@ -1142,7 +1139,16 @@
     <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
   </si>
   <si>
-    <t>4958억 6854만</t>
+    <t>5064억 4730만</t>
+  </si>
+  <si>
+    <t>쓱싹대선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>4962억 2217만</t>
   </si>
   <si>
     <t>dvzve</t>
@@ -1154,15 +1160,6 @@
     <t>4734억 5258만</t>
   </si>
   <si>
-    <t>쓱싹대선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>4720억 3106만</t>
-  </si>
-  <si>
     <t>쨍꿍</t>
   </si>
   <si>
@@ -1193,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>28조 3742억 466만</t>
+    <t>28조 6482억 6125만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -1232,6 +1229,15 @@
     <t>10조 3167억 1702만</t>
   </si>
   <si>
+    <t>술라이만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EB%9D%BC%EC%9D%B4%EB%A7%8C</t>
+  </si>
+  <si>
+    <t>7조 2013억 3063만</t>
+  </si>
+  <si>
     <t>쎄도어</t>
   </si>
   <si>
@@ -1247,7 +1253,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
   </si>
   <si>
-    <t>6조 1927억 8768만</t>
+    <t>6조 2723억 7081만</t>
   </si>
   <si>
     <t>스응로</t>
@@ -1256,7 +1262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
   </si>
   <si>
-    <t>6조 1219억 9639만</t>
+    <t>6조 1334억 3836만</t>
   </si>
   <si>
     <t>abba</t>
@@ -1274,16 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
   </si>
   <si>
-    <t>5조 6970억 5560만</t>
-  </si>
-  <si>
-    <t>표창넣을게</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%91%9C%EC%B0%BD%EB%84%A3%EC%9D%84%EA%B2%8C</t>
-  </si>
-  <si>
-    <t>5조 5434억 156만</t>
+    <t>5조 8869억 8233만</t>
   </si>
   <si>
     <t>류작</t>
@@ -1301,7 +1298,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EC%86%8C%EA%B7%B8%EB%A6%AC%EC%8A%A4</t>
   </si>
   <si>
-    <t>5조 1920억 8892만</t>
+    <t>5조 1945억 4963만</t>
   </si>
   <si>
     <t>인천왕김치언</t>
@@ -1310,7 +1307,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
   </si>
   <si>
-    <t>5조 1147억 9352만</t>
+    <t>5조 1292억 641만</t>
   </si>
   <si>
     <t>윤서u</t>
@@ -1319,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
   </si>
   <si>
-    <t>4조 8058억 3000만</t>
+    <t>4조 8860억 260만</t>
   </si>
   <si>
     <t>라마킴</t>
@@ -1328,7 +1325,16 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
   </si>
   <si>
-    <t>4조 6323억 7544만</t>
+    <t>4조 8215억 9223만</t>
+  </si>
+  <si>
+    <t>거북이와토끼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%B6%81%EC%9D%B4%EC%99%80%ED%86%A0%EB%81%BC</t>
+  </si>
+  <si>
+    <t>4조 3678억 4529만</t>
   </si>
   <si>
     <t>조애니</t>
@@ -1337,7 +1343,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
   </si>
   <si>
-    <t>4조 3628억 3463만</t>
+    <t>4조 3649억 1632만</t>
   </si>
   <si>
     <t>뜨루뜨루</t>
@@ -1346,7 +1352,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>3조 4281억 950만</t>
+    <t>3조 4331억 9118만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
+  </si>
+  <si>
+    <t>3조 2759억 3119만</t>
   </si>
   <si>
     <t>민수심심해</t>
@@ -1358,12 +1370,6 @@
     <t>3조 2698억 7360만</t>
   </si>
   <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
-  </si>
-  <si>
-    <t>3조 2498억 755만</t>
-  </si>
-  <si>
     <t>오로치재림</t>
   </si>
   <si>
@@ -1400,22 +1406,13 @@
     <t>2조 4228억 8783만</t>
   </si>
   <si>
-    <t>박띵수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%95%EB%9D%B5%EC%88%98</t>
-  </si>
-  <si>
-    <t>2조 2360억 4439만</t>
-  </si>
-  <si>
     <t>사이비숍</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
   </si>
   <si>
-    <t>2조 2323억 1749만</t>
+    <t>2조 2415억 9856만</t>
   </si>
   <si>
     <t>토리꼬리</t>
@@ -1424,7 +1421,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EA%BC%AC%EB%A6%AC</t>
   </si>
   <si>
-    <t>2조 1948억 4810만</t>
+    <t>2조 2304억 8571만</t>
   </si>
   <si>
     <t>토리츄</t>
@@ -1457,7 +1454,7 @@
     <t>93</t>
   </si>
   <si>
-    <t>2299억 1025만</t>
+    <t>2357억 3820만</t>
   </si>
   <si>
     <t>모데쓰</t>
@@ -1466,7 +1463,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
   </si>
   <si>
-    <t>109조 9399억 3466만</t>
+    <t>116조 7878억 4427만</t>
   </si>
   <si>
     <t>잉잉기</t>
@@ -1493,7 +1490,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
   </si>
   <si>
-    <t>7조 8611억 4894만</t>
+    <t>7조 8674억 3607만</t>
   </si>
   <si>
     <t>갈맄</t>
@@ -1502,7 +1499,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
   </si>
   <si>
-    <t>6조 7304억 8108만</t>
+    <t>6조 7374억 6694만</t>
   </si>
   <si>
     <t>꾸린이</t>
@@ -1511,7 +1508,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
   </si>
   <si>
-    <t>6조 399억 1655만</t>
+    <t>6조 438억 2757만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
@@ -1526,7 +1523,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
   </si>
   <si>
-    <t>3조 8083억 2799만</t>
+    <t>3조 8691억 3586만</t>
   </si>
   <si>
     <t>하냥쓰</t>
@@ -1553,7 +1550,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
   </si>
   <si>
-    <t>2조 8862억 6125만</t>
+    <t>3조 451억 503만</t>
   </si>
   <si>
     <t>4033</t>
@@ -1562,7 +1559,7 @@
     <t>https://mgf.gg/contents/character.php?n=4033</t>
   </si>
   <si>
-    <t>2조 8491억 4117만</t>
+    <t>2조 9263억 2132만</t>
   </si>
   <si>
     <t>세넬</t>
@@ -1571,7 +1568,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
   </si>
   <si>
-    <t>2조 5303억 5623만</t>
+    <t>2조 7827억 5300만</t>
   </si>
   <si>
     <t>기뜩</t>
@@ -1580,7 +1577,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
   </si>
   <si>
-    <t>2조 785억 9293만</t>
+    <t>2조 1440억 3699만</t>
   </si>
   <si>
     <t>리토비</t>
@@ -1592,6 +1589,15 @@
     <t>1조 9788억 8836만</t>
   </si>
   <si>
+    <t>도밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>1조 9524억 3673만</t>
+  </si>
+  <si>
     <t>하흙</t>
   </si>
   <si>
@@ -1607,16 +1613,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
   </si>
   <si>
-    <t>1조 8526억 7735만</t>
-  </si>
-  <si>
-    <t>도밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>1조 7811억 3646만</t>
+    <t>1조 8698억 9121만</t>
   </si>
   <si>
     <t>라미낭</t>
@@ -1634,7 +1631,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
   </si>
   <si>
-    <t>1조 5099억 7477만</t>
+    <t>1조 5217억 8894만</t>
   </si>
   <si>
     <t>챙날</t>
@@ -1652,7 +1649,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
   </si>
   <si>
-    <t>1조 455억 4916만</t>
+    <t>1조 1638억 9885만</t>
   </si>
   <si>
     <t>홍루이</t>
@@ -1670,7 +1667,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
   </si>
   <si>
-    <t>7227억 7441만</t>
+    <t>7235억 3050만</t>
   </si>
   <si>
     <t>안마시술소</t>
@@ -1679,7 +1676,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
   </si>
   <si>
-    <t>6632억 4562만</t>
+    <t>6649억 2292만</t>
   </si>
   <si>
     <t>성현이여</t>
@@ -2169,22 +2166,22 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>19</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>32</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2192,40 +2189,40 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>35</v>
-      </c>
       <c r="C4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="K4" s="2" t="s">
+      <c r="L4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="L4" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2233,38 +2230,38 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="B5" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>44</v>
-      </c>
       <c r="C5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="G5" s="2" t="s">
-        <v>47</v>
-      </c>
       <c r="H5" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="K5" s="2"/>
       <c r="L5" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2272,40 +2269,40 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>51</v>
-      </c>
       <c r="C6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F6" s="2" t="s">
+      <c r="G6" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="G6" s="2" t="s">
+      <c r="H6" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="H6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="I6" s="2" t="s">
+      <c r="J6" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="K6" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>57</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>58</v>
       </c>
       <c r="M6" s="2" t="s">
         <v>24</v>
@@ -2343,28 +2340,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -2375,13 +2372,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>23</v>
-      </c>
       <c r="D2" s="2" t="s">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>68</v>
@@ -2410,25 +2407,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="G3" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="H3" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>77</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>79</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2439,28 +2436,28 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="H4" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
+      <c r="I4" s="2" t="s">
         <v>83</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>84</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -2471,28 +2468,28 @@
         <v>13</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>88</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>90</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -2503,28 +2500,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>92</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="H6" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
+      <c r="I6" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>96</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -2535,25 +2532,25 @@
         <v>13</v>
       </c>
       <c r="B7" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="H7" s="2" t="s">
         <v>99</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>100</v>
@@ -2579,13 +2576,13 @@
         <v>103</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>104</v>
@@ -2611,13 +2608,13 @@
         <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>88</v>
+        <v>92</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>108</v>
@@ -2643,16 +2640,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2663,25 +2660,25 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="H11" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>89</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>118</v>
@@ -2707,16 +2704,16 @@
         <v>121</v>
       </c>
       <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G12" s="2" t="s">
+      <c r="H12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>122</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>123</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2727,28 +2724,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>124</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>126</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2759,28 +2756,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="D14" s="2" t="s">
+        <v>128</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>129</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>131</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2791,28 +2788,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>135</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2823,28 +2820,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="C16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="D16" s="2" t="s">
+        <v>136</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2855,28 +2852,28 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C17" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="D17" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>143</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2887,28 +2884,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="D18" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H18" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="2" t="s">
+      <c r="I18" s="2" t="s">
         <v>147</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2919,28 +2916,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="C19" s="2" t="s">
         <v>149</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="D19" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>151</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>153</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2951,28 +2948,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="C20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="E20" s="2" t="s">
-        <v>156</v>
-      </c>
       <c r="F20" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>113</v>
+        <v>155</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2983,28 +2980,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
+        <v>157</v>
+      </c>
+      <c r="C21" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="D21" s="2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>159</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>160</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3015,28 +3012,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
+        <v>161</v>
+      </c>
+      <c r="C22" s="2" t="s">
         <v>162</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="D22" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>164</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3047,28 +3044,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>168</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>169</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3079,28 +3076,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="C24" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="D24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>172</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>173</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3111,28 +3108,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
+        <v>173</v>
+      </c>
+      <c r="C25" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="D25" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>176</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>177</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3143,28 +3140,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="C26" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="D26" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>180</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>181</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3175,28 +3172,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C27" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="D27" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>183</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>184</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>185</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3207,28 +3204,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C28" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="D28" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>188</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>189</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3239,28 +3236,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="C29" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="D29" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="2" t="s">
+      <c r="H29" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3271,28 +3268,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="D30" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H30" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3303,28 +3300,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C31" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="D31" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>200</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H31" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I31" s="2" t="s">
         <v>201</v>
-      </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>202</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3388,28 +3385,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -3420,28 +3417,28 @@
         <v>25</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>203</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>204</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>205</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3455,25 +3452,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3484,28 +3481,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>210</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3516,28 +3513,28 @@
         <v>25</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>213</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3548,28 +3545,28 @@
         <v>25</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>215</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>216</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3580,28 +3577,28 @@
         <v>25</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>219</v>
-      </c>
       <c r="F7" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3615,25 +3612,25 @@
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>221</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3647,25 +3644,25 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>224</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>225</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3679,25 +3676,25 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>227</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3708,28 +3705,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>230</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>230</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>231</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3743,25 +3740,25 @@
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>233</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>233</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3772,28 +3769,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>236</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>237</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3804,13 +3801,13 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>33</v>
+        <v>238</v>
       </c>
       <c r="E14" s="2" t="s">
         <v>239</v>
@@ -3819,10 +3816,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>193</v>
+        <v>87</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>78</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>240</v>
@@ -3836,7 +3833,7 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>241</v>
@@ -3848,13 +3845,13 @@
         <v>242</v>
       </c>
       <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="G15" s="2" t="s">
-        <v>88</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>243</v>
@@ -3868,7 +3865,7 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>244</v>
@@ -3880,13 +3877,13 @@
         <v>245</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>246</v>
@@ -3900,28 +3897,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>247</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3932,28 +3929,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>250</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>251</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>252</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3964,28 +3961,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>253</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3996,28 +3993,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>256</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>256</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>257</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>258</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4028,28 +4025,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>259</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>259</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4060,28 +4057,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>262</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>262</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>263</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>264</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4092,28 +4089,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>264</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>265</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>265</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4124,28 +4121,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>94</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>270</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4156,28 +4153,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>271</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4188,28 +4185,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>274</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>275</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>276</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4220,28 +4217,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -4252,28 +4249,28 @@
         <v>25</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>280</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>282</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -4284,28 +4281,28 @@
         <v>25</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>283</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -4316,28 +4313,28 @@
         <v>25</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>286</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
+      <c r="H30" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>289</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>290</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -4399,28 +4396,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -4428,31 +4425,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>290</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>291</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>293</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>294</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -4460,31 +4457,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>295</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -4492,31 +4489,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>298</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -4524,31 +4521,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>301</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>304</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -4556,31 +4553,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>42</v>
+        <v>302</v>
       </c>
       <c r="E6" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -4588,31 +4585,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>307</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -4620,31 +4617,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>310</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -4652,31 +4649,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>313</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -4684,31 +4681,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>316</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -4716,31 +4713,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>319</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>320</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>321</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -4748,31 +4745,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -4780,31 +4777,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>325</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>326</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>327</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -4812,31 +4809,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>328</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H14" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H14" s="2" t="s">
+      <c r="I14" s="2" t="s">
         <v>330</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>331</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4844,31 +4841,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>332</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>333</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>334</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -4876,31 +4873,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>335</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>336</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>337</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -4908,31 +4905,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>338</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
+      <c r="I17" s="2" t="s">
         <v>340</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>341</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -4940,31 +4937,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>343</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>344</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -4972,31 +4969,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>346</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>347</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -5004,31 +5001,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>348</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>349</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>350</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -5036,31 +5033,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>351</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>352</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>353</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -5068,31 +5065,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>354</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -5100,31 +5097,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>357</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="F23" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>340</v>
+        <v>288</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -5132,31 +5129,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>360</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>361</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>362</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -5164,31 +5161,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>362</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>363</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>364</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>365</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -5196,31 +5193,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>366</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>367</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>368</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -5228,31 +5225,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>368</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>369</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>370</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>371</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -5260,31 +5257,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>372</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>373</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>340</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>374</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -5292,31 +5289,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>374</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>375</v>
-      </c>
-      <c r="E29" s="2" t="s">
-        <v>376</v>
-      </c>
       <c r="F29" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -5324,31 +5321,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>378</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>380</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>381</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -5356,31 +5353,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>382</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>384</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>385</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -5444,28 +5441,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -5473,31 +5470,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>386</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -5505,31 +5502,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="E3" s="2" t="s">
+      <c r="F3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>390</v>
-      </c>
-      <c r="F3" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>391</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -5537,31 +5534,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>392</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>393</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>394</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -5569,31 +5566,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>395</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>396</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>397</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -5601,31 +5598,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>397</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>398</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>399</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>400</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -5633,31 +5630,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>401</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>402</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>403</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -5665,31 +5662,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>404</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>405</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>406</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -5697,31 +5694,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>408</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>409</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -5729,31 +5726,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>412</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -5761,31 +5758,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>413</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>414</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>415</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -5793,31 +5790,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>416</v>
-      </c>
-      <c r="E12" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="F12" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>89</v>
+        <v>117</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -5825,31 +5822,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>419</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>420</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>421</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -5857,31 +5854,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>423</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>424</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -5889,31 +5886,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>426</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>427</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -5921,31 +5918,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>428</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>429</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>430</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -5953,31 +5950,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>432</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>433</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -5985,31 +5982,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>433</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>434</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>435</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>436</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -6017,31 +6014,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>436</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>437</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -6049,31 +6046,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>440</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>441</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>442</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6081,31 +6078,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E21" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="F21" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -6113,31 +6110,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>445</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>446</v>
-      </c>
       <c r="F22" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>113</v>
+        <v>93</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -6145,31 +6142,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>448</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>449</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>450</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -6177,31 +6174,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>451</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -6209,31 +6206,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>455</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>456</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -6241,31 +6238,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>457</v>
-      </c>
-      <c r="E26" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="F26" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -6273,31 +6270,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>461</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>462</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -6305,31 +6302,31 @@
     </row>
     <row r="28" spans="1:10">
       <c r="A28" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="C28" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="E28" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="D28" s="2" t="s">
-        <v>463</v>
-      </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G28" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H28" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I28" s="2" t="s">
         <v>464</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G28" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H28" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I28" s="2" t="s">
-        <v>465</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -6337,31 +6334,31 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>465</v>
+      </c>
+      <c r="E29" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="D29" s="2" t="s">
-        <v>466</v>
-      </c>
-      <c r="E29" s="2" t="s">
+      <c r="F29" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G29" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H29" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I29" s="2" t="s">
         <v>467</v>
-      </c>
-      <c r="F29" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G29" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H29" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I29" s="2" t="s">
-        <v>468</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -6369,31 +6366,31 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="C30" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>468</v>
+      </c>
+      <c r="E30" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>469</v>
-      </c>
-      <c r="E30" s="2" t="s">
+      <c r="F30" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G30" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H30" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="F30" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G30" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H30" s="2" t="s">
+      <c r="I30" s="2" t="s">
         <v>471</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>472</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6401,31 +6398,31 @@
     </row>
     <row r="31" spans="1:10">
       <c r="A31" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="D31" s="2" t="s">
-        <v>473</v>
-      </c>
-      <c r="E31" s="2" t="s">
+      <c r="F31" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G31" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H31" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="F31" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G31" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H31" s="2" t="s">
+      <c r="I31" s="2" t="s">
         <v>475</v>
-      </c>
-      <c r="I31" s="2" t="s">
-        <v>476</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6489,28 +6486,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>65</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>66</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>12</v>
@@ -6518,31 +6515,31 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>292</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>478</v>
-      </c>
-      <c r="F2" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>479</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6550,31 +6547,31 @@
     </row>
     <row r="3" spans="1:10">
       <c r="A3" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>480</v>
       </c>
-      <c r="D3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>481</v>
-      </c>
       <c r="F3" s="2" t="s">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>83</v>
+        <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>71</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6582,31 +6579,31 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="E4" s="2" t="s">
         <v>483</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="E4" s="2" t="s">
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>484</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>485</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6614,31 +6611,31 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>486</v>
       </c>
-      <c r="D5" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I5" s="2" t="s">
         <v>487</v>
-      </c>
-      <c r="F5" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>488</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6646,31 +6643,31 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>304</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I6" s="2" t="s">
         <v>490</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>303</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>491</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6678,31 +6675,31 @@
     </row>
     <row r="7" spans="1:10">
       <c r="A7" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G7" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6710,31 +6707,31 @@
     </row>
     <row r="8" spans="1:10">
       <c r="A8" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>101</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>495</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>496</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6742,31 +6739,31 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>497</v>
-      </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I9" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6774,31 +6771,31 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>500</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I10" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="F10" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="I10" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6806,31 +6803,31 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="E11" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>503</v>
-      </c>
-      <c r="E11" s="2" t="s">
+      <c r="F11" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="F11" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6838,31 +6835,31 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>119</v>
       </c>
       <c r="C12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>506</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6870,31 +6867,31 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>509</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I13" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="F13" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6902,31 +6899,31 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="E14" s="2" t="s">
+      <c r="F14" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>513</v>
-      </c>
-      <c r="F14" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G14" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H14" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>514</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6934,31 +6931,31 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>155</v>
+      </c>
+      <c r="I15" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6966,31 +6963,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="E16" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>518</v>
-      </c>
-      <c r="E16" s="2" t="s">
+      <c r="F16" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I16" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="F16" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G16" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H16" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I16" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -6998,31 +6995,31 @@
     </row>
     <row r="17" spans="1:10">
       <c r="A17" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="E17" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="E17" s="2" t="s">
+      <c r="F17" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G17" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="F17" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G17" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H17" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I17" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7030,31 +7027,31 @@
     </row>
     <row r="18" spans="1:10">
       <c r="A18" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="E18" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>524</v>
-      </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G18" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H18" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I18" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="F18" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G18" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H18" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I18" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7062,31 +7059,31 @@
     </row>
     <row r="19" spans="1:10">
       <c r="A19" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="E19" s="2" t="s">
         <v>527</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>527</v>
-      </c>
-      <c r="E19" s="2" t="s">
+      <c r="F19" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G19" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H19" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I19" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="F19" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I19" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7094,31 +7091,31 @@
     </row>
     <row r="20" spans="1:10">
       <c r="A20" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>531</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>122</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>532</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7126,31 +7123,31 @@
     </row>
     <row r="21" spans="1:10">
       <c r="A21" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="E21" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>533</v>
-      </c>
-      <c r="E21" s="2" t="s">
+      <c r="F21" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G21" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H21" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I21" s="2" t="s">
         <v>534</v>
-      </c>
-      <c r="F21" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G21" s="2" t="s">
-        <v>288</v>
-      </c>
-      <c r="H21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I21" s="2" t="s">
-        <v>535</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7158,31 +7155,31 @@
     </row>
     <row r="22" spans="1:10">
       <c r="A22" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="E22" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>536</v>
-      </c>
-      <c r="E22" s="2" t="s">
+      <c r="F22" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H22" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I22" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F22" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="I22" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7190,31 +7187,31 @@
     </row>
     <row r="23" spans="1:10">
       <c r="A23" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="E23" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="H23" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I23" s="2" t="s">
         <v>540</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="H23" s="2" t="s">
-        <v>289</v>
-      </c>
-      <c r="I23" s="2" t="s">
-        <v>541</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7222,31 +7219,31 @@
     </row>
     <row r="24" spans="1:10">
       <c r="A24" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="E24" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>542</v>
-      </c>
-      <c r="E24" s="2" t="s">
+      <c r="F24" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G24" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H24" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I24" s="2" t="s">
         <v>543</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H24" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I24" s="2" t="s">
-        <v>544</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7254,31 +7251,31 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="E25" s="2" t="s">
         <v>545</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="E25" s="2" t="s">
+      <c r="F25" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="H25" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I25" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="F25" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G25" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="H25" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I25" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7286,31 +7283,31 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="E26" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>548</v>
-      </c>
-      <c r="E26" s="2" t="s">
+      <c r="F26" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G26" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="I26" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="F26" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G26" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H26" s="2" t="s">
-        <v>330</v>
-      </c>
-      <c r="I26" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7318,31 +7315,31 @@
     </row>
     <row r="27" spans="1:10">
       <c r="A27" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="E27" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>551</v>
-      </c>
-      <c r="E27" s="2" t="s">
+      <c r="F27" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G27" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H27" s="2" t="s">
+        <v>470</v>
+      </c>
+      <c r="I27" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="F27" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="G27" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H27" s="2" t="s">
-        <v>471</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="553">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="552">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,7 +80,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>353</t>
+    <t>354</t>
   </si>
   <si>
     <t>11위</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>272조 1350억 3602만</t>
+    <t>274조 9424억 2503만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,7 +101,7 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.29</t>
+    <t>2026.04.30</t>
   </si>
   <si>
     <t>GDRAGON</t>
@@ -113,13 +113,13 @@
     <t>Scania 3</t>
   </si>
   <si>
-    <t>387</t>
+    <t>388</t>
   </si>
   <si>
     <t>29명</t>
   </si>
   <si>
-    <t>229조 2783억 7318만</t>
+    <t>230조 657억 3592만</t>
   </si>
   <si>
     <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
@@ -137,7 +137,7 @@
     <t>Scania 31</t>
   </si>
   <si>
-    <t>361</t>
+    <t>362</t>
   </si>
   <si>
     <t>9위</t>
@@ -146,7 +146,7 @@
     <t>Lv.7</t>
   </si>
   <si>
-    <t>259조 5318억 7205만</t>
+    <t>261조 3622억 7812만</t>
   </si>
   <si>
     <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
@@ -164,37 +164,37 @@
     <t>Scania 8</t>
   </si>
   <si>
-    <t>425</t>
+    <t>422</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>188조 65억 5176만</t>
+  </si>
+  <si>
+    <t>보보네</t>
+  </si>
+  <si>
+    <t>블루스2기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A3%A8%EC%8A%A42%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>Scania 28</t>
+  </si>
+  <si>
+    <t>366</t>
   </si>
   <si>
     <t>15위</t>
   </si>
   <si>
-    <t>184조 4870억 6757만</t>
-  </si>
-  <si>
-    <t>보보네</t>
-  </si>
-  <si>
-    <t>블루스2기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A3%A8%EC%8A%A42%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>370</t>
-  </si>
-  <si>
-    <t>16위</t>
-  </si>
-  <si>
     <t>26명</t>
   </si>
   <si>
-    <t>246조 4081억 6436만</t>
+    <t>255조 8569억 5430만</t>
   </si>
   <si>
     <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
@@ -260,7 +260,7 @@
     <t>섀도어</t>
   </si>
   <si>
-    <t>33조 9446억 6489만</t>
+    <t>35조 863억 7090만</t>
   </si>
   <si>
     <t>3</t>
@@ -353,7 +353,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
   </si>
   <si>
-    <t>8조 3818억 1066만</t>
+    <t>8조 4042억 1015만</t>
   </si>
   <si>
     <t>9</t>
@@ -365,12 +365,24 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
   </si>
   <si>
-    <t>7조 8716억 4430만</t>
+    <t>7조 9691억 6815만</t>
   </si>
   <si>
     <t>10</t>
   </si>
   <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>7조 4061억 9856만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
     <t>반도</t>
   </si>
   <si>
@@ -383,24 +395,24 @@
     <t>100</t>
   </si>
   <si>
-    <t>7조 1271억 2840만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>6조 9200억 704만</t>
+    <t>7조 1350억 9675만</t>
   </si>
   <si>
     <t>12</t>
   </si>
   <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>7조 117억 2611만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
     <t>굴러가는일상</t>
   </si>
   <si>
@@ -410,18 +422,6 @@
     <t>6조 7222억 597만</t>
   </si>
   <si>
-    <t>13</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>6조 6544억 7794만</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -443,7 +443,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>5조 2326억 4158만</t>
+    <t>5조 2445억 5234만</t>
   </si>
   <si>
     <t>16</t>
@@ -470,7 +470,7 @@
     <t>98</t>
   </si>
   <si>
-    <t>4조 9510억 5146만</t>
+    <t>4조 9725억 1519만</t>
   </si>
   <si>
     <t>18</t>
@@ -521,7 +521,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>4조 16억 1372만</t>
+    <t>4조 476억 6532만</t>
   </si>
   <si>
     <t>22</t>
@@ -533,7 +533,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
   </si>
   <si>
-    <t>3조 4647억 3569만</t>
+    <t>3조 4803억 5459만</t>
   </si>
   <si>
     <t>23</t>
@@ -551,16 +551,28 @@
     <t>24</t>
   </si>
   <si>
+    <t>플로우00</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
+  </si>
+  <si>
+    <t>3조 265억 4028만</t>
+  </si>
+  <si>
+    <t>25</t>
+  </si>
+  <si>
     <t>여븨</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
   </si>
   <si>
-    <t>2조 8934억 4065만</t>
-  </si>
-  <si>
-    <t>25</t>
+    <t>2조 9622억 15만</t>
+  </si>
+  <si>
+    <t>26</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -572,18 +584,6 @@
     <t>2조 7544억 4887만</t>
   </si>
   <si>
-    <t>26</t>
-  </si>
-  <si>
-    <t>플로우00</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%8C%EB%A1%9C%EC%9A%B000</t>
-  </si>
-  <si>
-    <t>2조 5587억 7219만</t>
-  </si>
-  <si>
     <t>27</t>
   </si>
   <si>
@@ -593,7 +593,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9E%90%EC%9C%A0%EC%9D%B4%EC%9A%A9%EA%BB%80</t>
   </si>
   <si>
-    <t>2조 4519억 4405만</t>
+    <t>2조 4532억 9685만</t>
   </si>
   <si>
     <t>28</t>
@@ -632,7 +632,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
   </si>
   <si>
-    <t>2조 570억 4078만</t>
+    <t>2조 1184억 6702만</t>
   </si>
   <si>
     <t>그때</t>
@@ -650,7 +650,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%AA%85</t>
   </si>
   <si>
-    <t>20조 9060억 3624만</t>
+    <t>21조 1050억 8450만</t>
   </si>
   <si>
     <t>소주소주해</t>
@@ -677,7 +677,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
   </si>
   <si>
-    <t>13조 2237억 9181만</t>
+    <t>13조 6524억 9699만</t>
   </si>
   <si>
     <t>엔도르시</t>
@@ -758,7 +758,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
   </si>
   <si>
-    <t>6조 2561억 8768만</t>
+    <t>6조 2688억 7451만</t>
   </si>
   <si>
     <t>운스</t>
@@ -767,13 +767,13 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
   </si>
   <si>
-    <t>6조 1925억 5745만</t>
+    <t>6조 2302억 5225만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
   </si>
   <si>
-    <t>6조 1702억 7857만</t>
+    <t>6조 1807억 8625만</t>
   </si>
   <si>
     <t>체르</t>
@@ -836,7 +836,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
   </si>
   <si>
-    <t>3조 9851억 1092만</t>
+    <t>3조 9942억 9579만</t>
   </si>
   <si>
     <t>아율마더</t>
@@ -845,7 +845,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
   </si>
   <si>
-    <t>3조 8704억 5050만</t>
+    <t>3조 9404억 5955만</t>
   </si>
   <si>
     <t>쫑쓰</t>
@@ -872,7 +872,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
   </si>
   <si>
-    <t>3조 3312억 948만</t>
+    <t>3조 3363억 9901만</t>
   </si>
   <si>
     <t>아율파더</t>
@@ -881,7 +881,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
   </si>
   <si>
-    <t>3조 1614억 1528만</t>
+    <t>3조 1954억 4437만</t>
   </si>
   <si>
     <t>맨셸리</t>
@@ -908,7 +908,7 @@
     <t>105</t>
   </si>
   <si>
-    <t>114조 3933억 1142만</t>
+    <t>114조 4499억 3097만</t>
   </si>
   <si>
     <t>끝까지힘내자</t>
@@ -926,7 +926,7 @@
     <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
   </si>
   <si>
-    <t>22조 3217억 2205만</t>
+    <t>22조 6677억 7988만</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=Edom</t>
@@ -944,7 +944,7 @@
     <t>팔라딘</t>
   </si>
   <si>
-    <t>20조 2481억 75만</t>
+    <t>20조 2902억 1410만</t>
   </si>
   <si>
     <t>야생봄이</t>
@@ -956,6 +956,15 @@
     <t>9조 5092억 2050만</t>
   </si>
   <si>
+    <t>긍궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
+  </si>
+  <si>
+    <t>7조 243억 2592만</t>
+  </si>
+  <si>
     <t>이은제리</t>
   </si>
   <si>
@@ -965,15 +974,6 @@
     <t>6조 2702억 6723만</t>
   </si>
   <si>
-    <t>긍궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
-  </si>
-  <si>
-    <t>5조 7959억 4437만</t>
-  </si>
-  <si>
     <t>청아씨</t>
   </si>
   <si>
@@ -1010,6 +1010,15 @@
     <t>1조 8559억 7520만</t>
   </si>
   <si>
+    <t>망친인생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
+  </si>
+  <si>
+    <t>1조 6185억 7611만</t>
+  </si>
+  <si>
     <t>반존대</t>
   </si>
   <si>
@@ -1022,15 +1031,6 @@
     <t>1조 5527억 6976만</t>
   </si>
   <si>
-    <t>망친인생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
-  </si>
-  <si>
-    <t>1조 5380억 968만</t>
-  </si>
-  <si>
     <t>봉찬</t>
   </si>
   <si>
@@ -1079,6 +1079,15 @@
     <t>8821억 1213만</t>
   </si>
   <si>
+    <t>채류진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
+  </si>
+  <si>
+    <t>8679억 2319만</t>
+  </si>
+  <si>
     <t>몽샐</t>
   </si>
   <si>
@@ -1088,22 +1097,13 @@
     <t>8309억 7303만</t>
   </si>
   <si>
-    <t>채류진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8093억 8552만</t>
-  </si>
-  <si>
     <t>낀조</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
   </si>
   <si>
-    <t>7874억 4930만</t>
+    <t>7964억 3324만</t>
   </si>
   <si>
     <t>공또</t>
@@ -1112,7 +1112,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
   </si>
   <si>
-    <t>6454억 2708만</t>
+    <t>6544억 6271만</t>
   </si>
   <si>
     <t>닝갠</t>
@@ -1121,7 +1121,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
   </si>
   <si>
-    <t>6027억 8867만</t>
+    <t>6033억 3397만</t>
   </si>
   <si>
     <t>유해화학물질</t>
@@ -1130,7 +1130,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
   </si>
   <si>
-    <t>5479억 115만</t>
+    <t>5629억 5975만</t>
   </si>
   <si>
     <t>ENNOY</t>
@@ -1139,7 +1139,7 @@
     <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
   </si>
   <si>
-    <t>5064억 4730만</t>
+    <t>5078억 8037만</t>
   </si>
   <si>
     <t>쓱싹대선</t>
@@ -1166,10 +1166,10 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
   </si>
   <si>
-    <t>92</t>
-  </si>
-  <si>
-    <t>2771억 238만</t>
+    <t>93</t>
+  </si>
+  <si>
+    <t>3047억 4490만</t>
   </si>
   <si>
     <t>희야미</t>
@@ -1181,7 +1181,7 @@
     <t>90</t>
   </si>
   <si>
-    <t>1014억 3891만</t>
+    <t>1125억 6555만</t>
   </si>
   <si>
     <t>최형사</t>
@@ -1190,7 +1190,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
   </si>
   <si>
-    <t>28조 6482억 6125만</t>
+    <t>28조 7582억 7650만</t>
   </si>
   <si>
     <t>멀링</t>
@@ -1199,7 +1199,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%EB%A7%81</t>
   </si>
   <si>
-    <t>18조 4699억 1040만</t>
+    <t>18조 5085억 1921만</t>
   </si>
   <si>
     <t>오오미</t>
@@ -1208,7 +1208,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%A4%EB%AF%B8</t>
   </si>
   <si>
-    <t>15조 7855억 8875만</t>
+    <t>16조 9791억 9376만</t>
   </si>
   <si>
     <t>토하루</t>
@@ -1229,6 +1229,15 @@
     <t>10조 3167억 1702만</t>
   </si>
   <si>
+    <t>쎄도어</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8E%84%EB%8F%84%EC%96%B4</t>
+  </si>
+  <si>
+    <t>8조 1239억 9013만</t>
+  </si>
+  <si>
     <t>술라이만</t>
   </si>
   <si>
@@ -1238,15 +1247,6 @@
     <t>7조 2013억 3063만</t>
   </si>
   <si>
-    <t>쎄도어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8E%84%EB%8F%84%EC%96%B4</t>
-  </si>
-  <si>
-    <t>6조 6751억 1083만</t>
-  </si>
-  <si>
     <t>머겸</t>
   </si>
   <si>
@@ -1262,7 +1262,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
   </si>
   <si>
-    <t>6조 1334억 3836만</t>
+    <t>6조 1434억 6353만</t>
   </si>
   <si>
     <t>abba</t>
@@ -1280,7 +1280,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
   </si>
   <si>
-    <t>5조 8869억 8233만</t>
+    <t>5조 9409억 4714만</t>
   </si>
   <si>
     <t>류작</t>
@@ -1316,7 +1316,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
   </si>
   <si>
-    <t>4조 8860억 260만</t>
+    <t>5조 978억 1644만</t>
   </si>
   <si>
     <t>라마킴</t>
@@ -1328,6 +1328,15 @@
     <t>4조 8215억 9223만</t>
   </si>
   <si>
+    <t>조애니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
+  </si>
+  <si>
+    <t>4조 5474억 6888만</t>
+  </si>
+  <si>
     <t>거북이와토끼</t>
   </si>
   <si>
@@ -1337,13 +1346,10 @@
     <t>4조 3678억 4529만</t>
   </si>
   <si>
-    <t>조애니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>4조 3649억 1632만</t>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
+  </si>
+  <si>
+    <t>3조 4820억 9851만</t>
   </si>
   <si>
     <t>뜨루뜨루</t>
@@ -1352,13 +1358,7 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
   </si>
   <si>
-    <t>3조 4331억 9118만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
-  </si>
-  <si>
-    <t>3조 2759억 3119만</t>
+    <t>3조 4558억 80만</t>
   </si>
   <si>
     <t>민수심심해</t>
@@ -1406,6 +1406,15 @@
     <t>2조 4228억 8783만</t>
   </si>
   <si>
+    <t>토리꼬리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EA%BC%AC%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>2조 2708억 440만</t>
+  </si>
+  <si>
     <t>사이비숍</t>
   </si>
   <si>
@@ -1415,15 +1424,6 @@
     <t>2조 2415억 9856만</t>
   </si>
   <si>
-    <t>토리꼬리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EA%BC%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 2304억 8571만</t>
-  </si>
-  <si>
     <t>토리츄</t>
   </si>
   <si>
@@ -1439,253 +1439,250 @@
     <t>https://mgf.gg/contents/character.php?n=wheesung</t>
   </si>
   <si>
+    <t>4494억 8136만</t>
+  </si>
+  <si>
+    <t>zl존율율</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
+  </si>
+  <si>
+    <t>2366억 6200만</t>
+  </si>
+  <si>
+    <t>모데쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
+  </si>
+  <si>
+    <t>124조 9126억 7268만</t>
+  </si>
+  <si>
+    <t>잉잉기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>58조 725억 552만</t>
+  </si>
+  <si>
+    <t>덥쳐보니형수</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
+  </si>
+  <si>
+    <t>8조 1072억 6227만</t>
+  </si>
+  <si>
+    <t>드뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>7조 8674억 3607만</t>
+  </si>
+  <si>
+    <t>갈맄</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
+  </si>
+  <si>
+    <t>6조 7374억 6694만</t>
+  </si>
+  <si>
+    <t>꾸린이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>6조 858억 6475만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
+  </si>
+  <si>
+    <t>6조 638억 9705만</t>
+  </si>
+  <si>
+    <t>한반</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
+  </si>
+  <si>
+    <t>3조 8720억 6714만</t>
+  </si>
+  <si>
+    <t>하냥쓰</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%83%A5%EC%93%B0</t>
+  </si>
+  <si>
+    <t>3조 7462억 216만</t>
+  </si>
+  <si>
+    <t>침착맨84</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
+  </si>
+  <si>
+    <t>3조 2633억 224만</t>
+  </si>
+  <si>
+    <t>한맹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
+  </si>
+  <si>
+    <t>3조 539억 6371만</t>
+  </si>
+  <si>
+    <t>4033</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=4033</t>
+  </si>
+  <si>
+    <t>2조 9484억 9633만</t>
+  </si>
+  <si>
+    <t>세넬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
+  </si>
+  <si>
+    <t>2조 9064억 9667만</t>
+  </si>
+  <si>
+    <t>기뜩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
+  </si>
+  <si>
+    <t>2조 3365억 6408만</t>
+  </si>
+  <si>
+    <t>리토비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
+  </si>
+  <si>
+    <t>1조 9788억 8836만</t>
+  </si>
+  <si>
+    <t>군적금헌터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EC%A0%81%EA%B8%88%ED%97%8C%ED%84%B0</t>
+  </si>
+  <si>
+    <t>1조 9668억 1214만</t>
+  </si>
+  <si>
+    <t>도밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>1조 9524억 3673만</t>
+  </si>
+  <si>
+    <t>하흙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
+  </si>
+  <si>
+    <t>1조 9233억 4396만</t>
+  </si>
+  <si>
+    <t>라미낭</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%AF%B8%EB%82%AD</t>
+  </si>
+  <si>
+    <t>1조 6431억 3517만</t>
+  </si>
+  <si>
+    <t>야햐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
+  </si>
+  <si>
+    <t>1조 5217억 8894만</t>
+  </si>
+  <si>
+    <t>챙날</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
+  </si>
+  <si>
+    <t>1조 3174억 6688만</t>
+  </si>
+  <si>
+    <t>지히메</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
+  </si>
+  <si>
+    <t>1조 1638억 9885만</t>
+  </si>
+  <si>
+    <t>홍루이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%A3%A8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>1조 240억 3361만</t>
+  </si>
+  <si>
+    <t>이완근</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
+  </si>
+  <si>
+    <t>7235억 3050만</t>
+  </si>
+  <si>
+    <t>안마시술소</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
+  </si>
+  <si>
+    <t>6769억 1596만</t>
+  </si>
+  <si>
+    <t>성현이여</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%ED%98%84%EC%9D%B4%EC%97%AC</t>
+  </si>
+  <si>
     <t>94</t>
   </si>
   <si>
-    <t>4494억 8136만</t>
-  </si>
-  <si>
-    <t>zl존율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>2357억 3820만</t>
-  </si>
-  <si>
-    <t>모데쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
-  </si>
-  <si>
-    <t>116조 7878억 4427만</t>
-  </si>
-  <si>
-    <t>잉잉기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>57조 3025억 6856만</t>
-  </si>
-  <si>
-    <t>덥쳐보니형수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
-  </si>
-  <si>
-    <t>8조 1072억 6227만</t>
-  </si>
-  <si>
-    <t>드뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>7조 8674억 3607만</t>
-  </si>
-  <si>
-    <t>갈맄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
-  </si>
-  <si>
-    <t>6조 7374억 6694만</t>
-  </si>
-  <si>
-    <t>꾸린이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6조 438억 2757만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
-  </si>
-  <si>
-    <t>6조 357억 1773만</t>
-  </si>
-  <si>
-    <t>한반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
-  </si>
-  <si>
-    <t>3조 8691억 3586만</t>
-  </si>
-  <si>
-    <t>하냥쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%83%A5%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 7462억 216만</t>
-  </si>
-  <si>
-    <t>침착맨84</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
-  </si>
-  <si>
-    <t>3조 473억 2990만</t>
-  </si>
-  <si>
-    <t>한맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>3조 451억 503만</t>
-  </si>
-  <si>
-    <t>4033</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=4033</t>
-  </si>
-  <si>
-    <t>2조 9263억 2132만</t>
-  </si>
-  <si>
-    <t>세넬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
-  </si>
-  <si>
-    <t>2조 7827억 5300만</t>
-  </si>
-  <si>
-    <t>기뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>2조 1440억 3699만</t>
-  </si>
-  <si>
-    <t>리토비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1조 9788억 8836만</t>
-  </si>
-  <si>
-    <t>도밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>1조 9524억 3673만</t>
-  </si>
-  <si>
-    <t>하흙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
-  </si>
-  <si>
-    <t>1조 9233억 4396만</t>
-  </si>
-  <si>
-    <t>관둬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B4%80%EB%91%AC</t>
-  </si>
-  <si>
-    <t>1조 8698억 9121만</t>
-  </si>
-  <si>
-    <t>라미낭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%AF%B8%EB%82%AD</t>
-  </si>
-  <si>
-    <t>1조 6431억 3517만</t>
-  </si>
-  <si>
-    <t>야햐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
-  </si>
-  <si>
-    <t>1조 5217억 8894만</t>
-  </si>
-  <si>
-    <t>챙날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
-  </si>
-  <si>
-    <t>1조 3174억 6688만</t>
-  </si>
-  <si>
-    <t>지히메</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
-  </si>
-  <si>
-    <t>1조 1638억 9885만</t>
-  </si>
-  <si>
-    <t>홍루이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%A3%A8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 240억 3361만</t>
-  </si>
-  <si>
-    <t>이완근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>7235억 3050만</t>
-  </si>
-  <si>
-    <t>안마시술소</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
-  </si>
-  <si>
-    <t>6649억 2292만</t>
-  </si>
-  <si>
-    <t>성현이여</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%ED%98%84%EC%9D%B4%EC%97%AC</t>
-  </si>
-  <si>
-    <t>2396억 6940만</t>
+    <t>2482억 7722만</t>
   </si>
 </sst>
 </file>
@@ -2675,13 +2672,13 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="I11" s="2" t="s">
         <v>116</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I11" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2692,25 +2689,25 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
+        <v>117</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="E12" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="F12" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G12" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>120</v>
-      </c>
-      <c r="E12" s="2" t="s">
+      <c r="H12" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="F12" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G12" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>93</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>122</v>
@@ -2739,10 +2736,10 @@
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>70</v>
+        <v>92</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>126</v>
@@ -2771,10 +2768,10 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="I14" s="2" t="s">
         <v>130</v>
@@ -2806,7 +2803,7 @@
         <v>70</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>134</v>
@@ -2870,7 +2867,7 @@
         <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>142</v>
@@ -2934,7 +2931,7 @@
         <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>151</v>
@@ -2998,7 +2995,7 @@
         <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>160</v>
@@ -3030,7 +3027,7 @@
         <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>164</v>
@@ -3123,10 +3120,10 @@
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>76</v>
+        <v>98</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>176</v>
@@ -3155,10 +3152,10 @@
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>146</v>
+        <v>93</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>180</v>
@@ -3187,10 +3184,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>184</v>
@@ -3318,7 +3315,7 @@
         <v>87</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>201</v>
@@ -3467,7 +3464,7 @@
         <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>207</v>
@@ -3563,7 +3560,7 @@
         <v>76</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>216</v>
@@ -3720,7 +3717,7 @@
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>82</v>
@@ -3737,7 +3734,7 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>232</v>
@@ -4040,7 +4037,7 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H21" s="2" t="s">
         <v>82</v>
@@ -4171,7 +4168,7 @@
         <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>272</v>
@@ -4510,7 +4507,7 @@
         <v>87</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>299</v>
@@ -4606,7 +4603,7 @@
         <v>87</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>308</v>
@@ -4635,10 +4632,10 @@
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>311</v>
@@ -4667,10 +4664,10 @@
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>92</v>
+        <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>314</v>
@@ -4702,7 +4699,7 @@
         <v>76</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>317</v>
@@ -4748,7 +4745,7 @@
         <v>33</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>321</v>
@@ -4827,13 +4824,13 @@
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>92</v>
+        <v>304</v>
       </c>
       <c r="H14" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I14" s="2" t="s">
         <v>329</v>
-      </c>
-      <c r="I14" s="2" t="s">
-        <v>330</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -4847,22 +4844,22 @@
         <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>331</v>
-      </c>
-      <c r="E15" s="2" t="s">
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="H15" s="2" t="s">
         <v>332</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>304</v>
-      </c>
-      <c r="H15" s="2" t="s">
-        <v>146</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>333</v>
@@ -4894,7 +4891,7 @@
         <v>76</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>336</v>
@@ -5022,7 +5019,7 @@
         <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>349</v>
@@ -5051,10 +5048,10 @@
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>352</v>
@@ -5083,10 +5080,10 @@
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>288</v>
+        <v>339</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>355</v>
@@ -5523,7 +5520,7 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="I3" s="2" t="s">
         <v>390</v>
@@ -5715,7 +5712,7 @@
         <v>76</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I9" s="2" t="s">
         <v>408</v>
@@ -5793,7 +5790,7 @@
         <v>42</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
         <v>415</v>
@@ -5811,7 +5808,7 @@
         <v>70</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I12" s="2" t="s">
         <v>417</v>
@@ -6003,7 +6000,7 @@
         <v>87</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>117</v>
+        <v>93</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>435</v>
@@ -6035,7 +6032,7 @@
         <v>87</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>93</v>
+        <v>121</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>438</v>
@@ -6052,25 +6049,25 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E20" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>439</v>
-      </c>
-      <c r="E20" s="2" t="s">
+      <c r="F20" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="G20" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="H20" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="I20" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="F20" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G20" s="2" t="s">
-        <v>76</v>
-      </c>
-      <c r="H20" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I20" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -6084,22 +6081,22 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>48</v>
+        <v>441</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>48</v>
+        <v>441</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>442</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>287</v>
+        <v>76</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>443</v>
@@ -6163,7 +6160,7 @@
         <v>76</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>449</v>
@@ -6195,7 +6192,7 @@
         <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I24" s="2" t="s">
         <v>452</v>
@@ -6227,7 +6224,7 @@
         <v>70</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>455</v>
@@ -6259,7 +6256,7 @@
         <v>70</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I26" s="2" t="s">
         <v>458</v>
@@ -6288,10 +6285,10 @@
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>287</v>
+        <v>70</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>146</v>
+        <v>121</v>
       </c>
       <c r="I27" s="2" t="s">
         <v>461</v>
@@ -6320,10 +6317,10 @@
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>70</v>
+        <v>287</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>117</v>
+        <v>146</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>464</v>
@@ -6355,7 +6352,7 @@
         <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>467</v>
@@ -6384,13 +6381,13 @@
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H30" s="2" t="s">
+        <v>339</v>
+      </c>
+      <c r="I30" s="2" t="s">
         <v>470</v>
-      </c>
-      <c r="I30" s="2" t="s">
-        <v>471</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -6404,13 +6401,13 @@
         <v>198</v>
       </c>
       <c r="C31" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="E31" s="2" t="s">
         <v>472</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>472</v>
-      </c>
-      <c r="E31" s="2" t="s">
-        <v>473</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
@@ -6419,10 +6416,10 @@
         <v>287</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>474</v>
+        <v>379</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>475</v>
+        <v>473</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -6521,13 +6518,13 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>476</v>
+        <v>474</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>477</v>
+        <v>475</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
@@ -6539,7 +6536,7 @@
         <v>292</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -6553,13 +6550,13 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>69</v>
@@ -6568,10 +6565,10 @@
         <v>87</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>292</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -6585,25 +6582,25 @@
         <v>78</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>120</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>482</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>482</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="F4" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="I4" s="2" t="s">
-        <v>484</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -6617,13 +6614,13 @@
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
@@ -6632,10 +6629,10 @@
         <v>304</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>487</v>
+        <v>485</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -6649,13 +6646,13 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>488</v>
+        <v>486</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>489</v>
+        <v>487</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
@@ -6667,7 +6664,7 @@
         <v>93</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>490</v>
+        <v>488</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -6681,13 +6678,13 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
@@ -6696,10 +6693,10 @@
         <v>76</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -6719,7 +6716,7 @@
         <v>57</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>75</v>
@@ -6728,10 +6725,10 @@
         <v>76</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -6745,25 +6742,25 @@
         <v>105</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>497</v>
+        <v>495</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="H9" s="2" t="s">
         <v>93</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>498</v>
+        <v>496</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -6777,13 +6774,13 @@
         <v>109</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>499</v>
+        <v>497</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
@@ -6792,10 +6789,10 @@
         <v>87</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -6809,13 +6806,13 @@
         <v>113</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
@@ -6824,10 +6821,10 @@
         <v>76</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>155</v>
+        <v>121</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -6838,16 +6835,16 @@
         <v>49</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
@@ -6856,10 +6853,10 @@
         <v>76</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -6873,13 +6870,13 @@
         <v>123</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>508</v>
+        <v>506</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>509</v>
+        <v>507</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
@@ -6891,7 +6888,7 @@
         <v>155</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>510</v>
+        <v>508</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -6905,13 +6902,13 @@
         <v>127</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>511</v>
+        <v>509</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>512</v>
+        <v>510</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
@@ -6920,10 +6917,10 @@
         <v>70</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>513</v>
+        <v>511</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -6937,13 +6934,13 @@
         <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>514</v>
+        <v>512</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="F15" s="2" t="s">
         <v>69</v>
@@ -6955,7 +6952,7 @@
         <v>155</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -6969,13 +6966,13 @@
         <v>135</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>517</v>
+        <v>515</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>518</v>
+        <v>516</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
@@ -6987,7 +6984,7 @@
         <v>146</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>519</v>
+        <v>517</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -7001,25 +6998,25 @@
         <v>139</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>520</v>
+        <v>518</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>521</v>
+        <v>519</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>76</v>
+        <v>287</v>
       </c>
       <c r="H17" s="2" t="s">
         <v>146</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>522</v>
+        <v>520</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -7033,13 +7030,13 @@
         <v>143</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>523</v>
+        <v>521</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>524</v>
+        <v>522</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
@@ -7051,7 +7048,7 @@
         <v>146</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>525</v>
+        <v>523</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -7065,25 +7062,25 @@
         <v>148</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>526</v>
+        <v>524</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>527</v>
+        <v>525</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="H19" s="2" t="s">
         <v>146</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -7097,13 +7094,13 @@
         <v>152</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>529</v>
+        <v>527</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>530</v>
+        <v>528</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
@@ -7112,10 +7109,10 @@
         <v>70</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -7129,13 +7126,13 @@
         <v>157</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>532</v>
+        <v>530</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
@@ -7147,7 +7144,7 @@
         <v>146</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>534</v>
+        <v>532</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -7161,13 +7158,13 @@
         <v>161</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>535</v>
+        <v>533</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>536</v>
+        <v>534</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
@@ -7179,7 +7176,7 @@
         <v>146</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>537</v>
+        <v>535</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -7193,13 +7190,13 @@
         <v>165</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>539</v>
+        <v>537</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
@@ -7208,10 +7205,10 @@
         <v>81</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>540</v>
+        <v>538</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -7225,13 +7222,13 @@
         <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>541</v>
+        <v>539</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
@@ -7240,10 +7237,10 @@
         <v>76</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -7257,13 +7254,13 @@
         <v>173</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>545</v>
+        <v>543</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
@@ -7272,10 +7269,10 @@
         <v>87</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>546</v>
+        <v>544</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -7289,13 +7286,13 @@
         <v>177</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
@@ -7304,10 +7301,10 @@
         <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -7321,13 +7318,13 @@
         <v>181</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
@@ -7336,10 +7333,10 @@
         <v>76</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>470</v>
+        <v>550</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>

--- a/reports/빅딜/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/빅딜_league_mgf_report.xlsx
@@ -9,25 +9,25 @@
   <sheets>
     <sheet name="guilds" sheetId="1" r:id="rId1"/>
     <sheet name="빅딜" sheetId="2" r:id="rId2"/>
-    <sheet name="GDRAGON" sheetId="3" r:id="rId3"/>
+    <sheet name="넘버원" sheetId="3" r:id="rId3"/>
     <sheet name="Kaia" sheetId="4" r:id="rId4"/>
-    <sheet name="청정원" sheetId="5" r:id="rId5"/>
-    <sheet name="블루스2기" sheetId="6" r:id="rId6"/>
+    <sheet name="풍년순대국밥" sheetId="5" r:id="rId5"/>
+    <sheet name="장비" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">GDRAGON!$A$1:$J$30</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">guilds!$A$1:$M$6</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Kaia!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">블루스2기!$A$1:$J$27</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">Kaia!$A$1:$J$32</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">넘버원!$A$1:$J$31</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">빅딜!$A$1:$J$31</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">청정원!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">장비!$A$1:$J$31</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">풍년순대국밥!$A$1:$J$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1577" uniqueCount="552">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1638" uniqueCount="572">
   <si>
     <t>guild_name</t>
   </si>
@@ -80,10 +80,10 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>354</t>
-  </si>
-  <si>
-    <t>11위</t>
+    <t>355</t>
+  </si>
+  <si>
+    <t>10위</t>
   </si>
   <si>
     <t>Lv.8</t>
@@ -92,7 +92,7 @@
     <t>30명</t>
   </si>
   <si>
-    <t>274조 9424억 2503만</t>
+    <t>381조 9031억 5417만</t>
   </si>
   <si>
     <t>셀린느2군 IN 300위분들 귓문의/혜영,망겜감별사,큐샤프,단풍카우</t>
@@ -101,106 +101,106 @@
     <t>망겜감별사</t>
   </si>
   <si>
-    <t>2026.04.30</t>
-  </si>
-  <si>
-    <t>GDRAGON</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=GDRAGON</t>
-  </si>
-  <si>
-    <t>Scania 3</t>
-  </si>
-  <si>
-    <t>388</t>
+    <t>2026.05.03</t>
+  </si>
+  <si>
+    <t>넘버원</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%84%98%EB%B2%84%EC%9B%90</t>
+  </si>
+  <si>
+    <t>Scania 5</t>
+  </si>
+  <si>
+    <t>372</t>
+  </si>
+  <si>
+    <t>14위</t>
+  </si>
+  <si>
+    <t>Lv.9</t>
+  </si>
+  <si>
+    <t>351조 5943억 9356만</t>
+  </si>
+  <si>
+    <t>안녕하세요. 넘버원 길드입니다. 활발한 활동, 앞으로 상위권을 달려가실 분들 오픈톡 참여 가능하신분들 서아핑 귓말 주세요</t>
+  </si>
+  <si>
+    <t>서아핑</t>
+  </si>
+  <si>
+    <t>Kaia</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=Kaia</t>
+  </si>
+  <si>
+    <t>Scania 31</t>
+  </si>
+  <si>
+    <t>302</t>
+  </si>
+  <si>
+    <t>7위</t>
+  </si>
+  <si>
+    <t>Lv.7</t>
+  </si>
+  <si>
+    <t>561조 656억 7051만</t>
+  </si>
+  <si>
+    <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
+  </si>
+  <si>
+    <t>Edom</t>
+  </si>
+  <si>
+    <t>풍년순대국밥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%ED%92%8D%EB%85%84%EC%88%9C%EB%8C%80%EA%B5%AD%EB%B0%A5</t>
+  </si>
+  <si>
+    <t>Scania 4</t>
+  </si>
+  <si>
+    <t>338</t>
+  </si>
+  <si>
+    <t>432조 1472억 3602만</t>
+  </si>
+  <si>
+    <t>길드가입조건:투력2조이상 (!!!!오픈톡 필수참여!!!!!!!) 길드컨텐츠 열심히 하는분들 환영 입니다. 문의- 망동, 밍츄핑, 갱미킴</t>
+  </si>
+  <si>
+    <t>망동</t>
+  </si>
+  <si>
+    <t>장비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%9E%A5%EB%B9%84</t>
+  </si>
+  <si>
+    <t>Scania 12</t>
+  </si>
+  <si>
+    <t>347</t>
   </si>
   <si>
     <t>29명</t>
   </si>
   <si>
-    <t>230조 657억 3592만</t>
-  </si>
-  <si>
-    <t>자리 없더라도 토벌,대항 점수 기재해서 법칙교주 귓말 주세요 !</t>
-  </si>
-  <si>
-    <t>법칙교주</t>
-  </si>
-  <si>
-    <t>Kaia</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=Kaia</t>
-  </si>
-  <si>
-    <t>Scania 31</t>
-  </si>
-  <si>
-    <t>362</t>
-  </si>
-  <si>
-    <t>9위</t>
-  </si>
-  <si>
-    <t>Lv.7</t>
-  </si>
-  <si>
-    <t>261조 3622억 7812만</t>
-  </si>
-  <si>
-    <t>공동의 노력만이 최고의 성과를 만듭니다.</t>
-  </si>
-  <si>
-    <t>Edom</t>
-  </si>
-  <si>
-    <t>청정원</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EC%B2%AD%EC%A0%95%EC%9B%90</t>
-  </si>
-  <si>
-    <t>Scania 8</t>
-  </si>
-  <si>
-    <t>422</t>
-  </si>
-  <si>
-    <t>14위</t>
-  </si>
-  <si>
-    <t>188조 65억 5176만</t>
-  </si>
-  <si>
-    <t>보보네</t>
-  </si>
-  <si>
-    <t>블루스2기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/guild_info.php?g_name=%EB%B8%94%EB%A3%A8%EC%8A%A42%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>Scania 28</t>
-  </si>
-  <si>
-    <t>366</t>
-  </si>
-  <si>
-    <t>15위</t>
-  </si>
-  <si>
-    <t>26명</t>
-  </si>
-  <si>
-    <t>255조 8569억 5430만</t>
-  </si>
-  <si>
-    <t>매일 접속 필수 / 전투력 1조 이상 / 매주 공헌도 1500 이상 / 오픈채팅 참여 가능</t>
-  </si>
-  <si>
-    <t>첼냥쓰</t>
+    <t>406조 5280억 5291만</t>
+  </si>
+  <si>
+    <t>생존자 구합니다 함께 오래하실분</t>
+  </si>
+  <si>
+    <t>통고</t>
   </si>
   <si>
     <t>member_rank_in_guild</t>
@@ -239,178 +239,196 @@
     <t>N</t>
   </si>
   <si>
+    <t>비숍</t>
+  </si>
+  <si>
+    <t>104</t>
+  </si>
+  <si>
+    <t>69조 2475억 454만</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>킹몬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
+  </si>
+  <si>
+    <t>다크나이트</t>
+  </si>
+  <si>
+    <t>103</t>
+  </si>
+  <si>
+    <t>52조 6919억 3252만</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
+  </si>
+  <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>105</t>
+  </si>
+  <si>
+    <t>39조 2290억 5155만</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>큐샤프</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
+  </si>
+  <si>
+    <t>신궁</t>
+  </si>
+  <si>
+    <t>37조 5330억 7535만</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>엘라임</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
+  </si>
+  <si>
+    <t>히어로</t>
+  </si>
+  <si>
+    <t>102</t>
+  </si>
+  <si>
+    <t>22조 1991억 4843만</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>단풍카우</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
+  </si>
+  <si>
+    <t>15조 1609억 687만</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>야가다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>보우마스터</t>
+  </si>
+  <si>
+    <t>13조 2229억 5022만</t>
+  </si>
+  <si>
+    <t>8</t>
+  </si>
+  <si>
+    <t>아르미느</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
+  </si>
+  <si>
+    <t>10조 4842억 7700만</t>
+  </si>
+  <si>
+    <t>9</t>
+  </si>
+  <si>
+    <t>포스코퓨처엠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
+  </si>
+  <si>
+    <t>섀도어</t>
+  </si>
+  <si>
+    <t>101</t>
+  </si>
+  <si>
+    <t>9조 5916억 8180만</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>양정팔</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
+  </si>
+  <si>
+    <t>9조 1721억 1064만</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>우후</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
+  </si>
+  <si>
+    <t>8조 2972억 3433만</t>
+  </si>
+  <si>
+    <t>12</t>
+  </si>
+  <si>
+    <t>반도</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
+  </si>
+  <si>
+    <t>나이트로드</t>
+  </si>
+  <si>
+    <t>100</t>
+  </si>
+  <si>
+    <t>7조 8230억 2060만</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>흑두부</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
+  </si>
+  <si>
     <t>아크메이지(썬,콜)</t>
   </si>
   <si>
-    <t>104</t>
-  </si>
-  <si>
-    <t>46조 8814억 2450만</t>
-  </si>
-  <si>
-    <t>2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EA%B2%9C%EA%B0%90%EB%B3%84%EC%82%AC</t>
-  </si>
-  <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>섀도어</t>
-  </si>
-  <si>
-    <t>35조 863억 7090만</t>
-  </si>
-  <si>
-    <t>3</t>
-  </si>
-  <si>
-    <t>킹몬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%AA%AC</t>
-  </si>
-  <si>
-    <t>다크나이트</t>
-  </si>
-  <si>
-    <t>102</t>
-  </si>
-  <si>
-    <t>22조 7632억 1918만</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>큐샤프</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%81%90%EC%83%A4%ED%94%84</t>
-  </si>
-  <si>
-    <t>신궁</t>
-  </si>
-  <si>
-    <t>20조 8772억 7416만</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>엘라임</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%98%EB%9D%BC%EC%9E%84</t>
-  </si>
-  <si>
-    <t>히어로</t>
-  </si>
-  <si>
-    <t>101</t>
-  </si>
-  <si>
-    <t>15조 4304억 3522만</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>야가다</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EA%B0%80%EB%8B%A4</t>
-  </si>
-  <si>
-    <t>보우마스터</t>
-  </si>
-  <si>
-    <t>103</t>
-  </si>
-  <si>
-    <t>13조 2229억 5022만</t>
-  </si>
-  <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>단풍카우</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%A8%ED%92%8D%EC%B9%B4%EC%9A%B0</t>
-  </si>
-  <si>
-    <t>12조 7144억 1150만</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>아르미느</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%A5%B4%EB%AF%B8%EB%8A%90</t>
-  </si>
-  <si>
-    <t>8조 4042억 1015만</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>양정팔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%96%91%EC%A0%95%ED%8C%94</t>
-  </si>
-  <si>
-    <t>7조 9691억 6815만</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>포스코퓨처엠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8F%AC%EC%8A%A4%EC%BD%94%ED%93%A8%EC%B2%98%EC%97%A0</t>
-  </si>
-  <si>
-    <t>7조 4061억 9856만</t>
-  </si>
-  <si>
-    <t>11</t>
-  </si>
-  <si>
-    <t>반도</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EB%8F%84</t>
-  </si>
-  <si>
-    <t>나이트로드</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>7조 1350억 9675만</t>
-  </si>
-  <si>
-    <t>12</t>
-  </si>
-  <si>
-    <t>우후</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%9B%84</t>
-  </si>
-  <si>
-    <t>7조 117억 2611만</t>
-  </si>
-  <si>
-    <t>13</t>
+    <t>7조 6231억 8496만</t>
+  </si>
+  <si>
+    <t>14</t>
   </si>
   <si>
     <t>굴러가는일상</t>
@@ -419,46 +437,58 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%B5%B4%EB%9F%AC%EA%B0%80%EB%8A%94%EC%9D%BC%EC%83%81</t>
   </si>
   <si>
-    <t>6조 7222억 597만</t>
-  </si>
-  <si>
-    <t>14</t>
-  </si>
-  <si>
-    <t>흑두부</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%91%EB%91%90%EB%B6%80</t>
-  </si>
-  <si>
-    <t>5조 3631억 9121만</t>
+    <t>7조 5148억 1235만</t>
   </si>
   <si>
     <t>15</t>
   </si>
   <si>
+    <t>KR#TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
+  </si>
+  <si>
+    <t>6조 1489억 7925만</t>
+  </si>
+  <si>
+    <t>16</t>
+  </si>
+  <si>
+    <t>뻥뻥</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
+  </si>
+  <si>
+    <t>6조 188억 8756만</t>
+  </si>
+  <si>
+    <t>17</t>
+  </si>
+  <si>
+    <t>쭌파파</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
+  </si>
+  <si>
+    <t>5조 5412억 1354만</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
     <t>므고</t>
   </si>
   <si>
     <t>https://mgf.gg/contents/character.php?n=%EB%AF%80%EA%B3%A0</t>
   </si>
   <si>
-    <t>5조 2445억 5234만</t>
-  </si>
-  <si>
-    <t>16</t>
-  </si>
-  <si>
-    <t>뻥뻥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%BB%A5%EB%BB%A5</t>
-  </si>
-  <si>
-    <t>5조 2009억 8901만</t>
-  </si>
-  <si>
-    <t>17</t>
+    <t>5조 4279억 7446만</t>
+  </si>
+  <si>
+    <t>19</t>
   </si>
   <si>
     <t>아르젠타</t>
@@ -473,19 +503,31 @@
     <t>4조 9725억 1519만</t>
   </si>
   <si>
-    <t>18</t>
-  </si>
-  <si>
-    <t>KR#TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%23TAKIN9CP37</t>
-  </si>
-  <si>
-    <t>4조 9299억 7891만</t>
-  </si>
-  <si>
-    <t>19</t>
+    <t>20</t>
+  </si>
+  <si>
+    <t>여븨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
+  </si>
+  <si>
+    <t>4조 8791억 7843만</t>
+  </si>
+  <si>
+    <t>21</t>
+  </si>
+  <si>
+    <t>민들레꽃</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
+  </si>
+  <si>
+    <t>4조 8132억 8816만</t>
+  </si>
+  <si>
+    <t>22</t>
   </si>
   <si>
     <t>비스밤</t>
@@ -500,19 +542,7 @@
     <t>4조 7975억 1419만</t>
   </si>
   <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>쭌파파</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AD%8C%ED%8C%8C%ED%8C%8C</t>
-  </si>
-  <si>
-    <t>4조 1586억 2443만</t>
-  </si>
-  <si>
-    <t>21</t>
+    <t>23</t>
   </si>
   <si>
     <t>꾸르꾸르</t>
@@ -521,22 +551,25 @@
     <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A5%B4%EA%BE%B8%EB%A5%B4</t>
   </si>
   <si>
-    <t>4조 476억 6532만</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>민들레꽃</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EB%93%A4%EB%A0%88%EA%BD%83</t>
-  </si>
-  <si>
-    <t>3조 4803억 5459만</t>
-  </si>
-  <si>
-    <t>23</t>
+    <t>4조 5572억 5348만</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>불보독지</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
+  </si>
+  <si>
+    <t>아크메이지(불,독)</t>
+  </si>
+  <si>
+    <t>3조 3228억 3964만</t>
+  </si>
+  <si>
+    <t>25</t>
   </si>
   <si>
     <t>덕르코프</t>
@@ -548,7 +581,7 @@
     <t>3조 488억 9661만</t>
   </si>
   <si>
-    <t>24</t>
+    <t>26</t>
   </si>
   <si>
     <t>플로우00</t>
@@ -560,19 +593,7 @@
     <t>3조 265억 4028만</t>
   </si>
   <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>여븨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%AC%EB%B8%A8</t>
-  </si>
-  <si>
-    <t>2조 9622억 15만</t>
-  </si>
-  <si>
-    <t>26</t>
+    <t>27</t>
   </si>
   <si>
     <t>제스프리</t>
@@ -581,10 +602,22 @@
     <t>https://mgf.gg/contents/character.php?n=%EC%A0%9C%EC%8A%A4%ED%94%84%EB%A6%AC</t>
   </si>
   <si>
-    <t>2조 7544억 4887만</t>
-  </si>
-  <si>
-    <t>27</t>
+    <t>2조 7967억 8402만</t>
+  </si>
+  <si>
+    <t>28</t>
+  </si>
+  <si>
+    <t>데드캣</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
+  </si>
+  <si>
+    <t>2조 4694억 8975만</t>
+  </si>
+  <si>
+    <t>29</t>
   </si>
   <si>
     <t>자유이용껀</t>
@@ -596,22 +629,7 @@
     <t>2조 4532억 9685만</t>
   </si>
   <si>
-    <t>28</t>
-  </si>
-  <si>
-    <t>불보독지</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EB%B3%B4%EB%8F%85%EC%A7%80</t>
-  </si>
-  <si>
-    <t>아크메이지(불,독)</t>
-  </si>
-  <si>
-    <t>2조 4292억 9347만</t>
-  </si>
-  <si>
-    <t>29</t>
+    <t>30</t>
   </si>
   <si>
     <t>여눈</t>
@@ -623,421 +641,424 @@
     <t>2조 3292억 507만</t>
   </si>
   <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>데드캣</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B0%EB%93%9C%EC%BA%A3</t>
-  </si>
-  <si>
-    <t>2조 1184억 6702만</t>
-  </si>
-  <si>
-    <t>그때</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%95%8C</t>
-  </si>
-  <si>
-    <t>26조 1587억 7806만</t>
-  </si>
-  <si>
-    <t>시명</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%9C%EB%AA%85</t>
-  </si>
-  <si>
-    <t>21조 1050억 8450만</t>
-  </si>
-  <si>
-    <t>소주소주해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%86%8C%EC%A3%BC%EC%86%8C%EC%A3%BC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>16조 151억 105만</t>
-  </si>
-  <si>
-    <t>메소가져와</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%94%EC%86%8C%EA%B0%80%EC%A0%B8%EC%99%80</t>
-  </si>
-  <si>
-    <t>14조 5449억 423만</t>
-  </si>
-  <si>
-    <t>르밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%B4%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>13조 6524억 9699만</t>
-  </si>
-  <si>
-    <t>엔도르시</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EB%8F%84%EB%A5%B4%EC%8B%9C</t>
-  </si>
-  <si>
-    <t>12조 5594억 1545만</t>
-  </si>
-  <si>
-    <t>호댕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%8C%95</t>
-  </si>
-  <si>
-    <t>11조 9726억 8823만</t>
-  </si>
-  <si>
-    <t>vander</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=vander</t>
-  </si>
-  <si>
-    <t>8조 1744억 2670만</t>
-  </si>
-  <si>
-    <t>인큐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%ED%81%90</t>
-  </si>
-  <si>
-    <t>7조 7524억 313만</t>
-  </si>
-  <si>
-    <t>무신사할배</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EC%8B%A0%EC%82%AC%ED%95%A0%EB%B0%B0</t>
-  </si>
-  <si>
-    <t>7조 6111억 5399만</t>
-  </si>
-  <si>
-    <t>코코연구가2</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%802</t>
-  </si>
-  <si>
-    <t>7조 1647억 6150만</t>
-  </si>
-  <si>
-    <t>종구왕</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A2%85%EA%B5%AC%EC%99%95</t>
-  </si>
-  <si>
-    <t>6조 5149억 9088만</t>
-  </si>
-  <si>
-    <t>효율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>6조 4121억 6745만</t>
-  </si>
-  <si>
-    <t>킹돔</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%82%B9%EB%8F%94</t>
-  </si>
-  <si>
-    <t>6조 2688억 7451만</t>
-  </si>
-  <si>
-    <t>운스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B4%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>6조 2302억 5225만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B2%95%EC%B9%99%EA%B5%90%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>6조 1807억 8625만</t>
-  </si>
-  <si>
-    <t>체르</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%B4%EB%A5%B4</t>
-  </si>
-  <si>
-    <t>5조 8351억 7849만</t>
-  </si>
-  <si>
-    <t>yawaka</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=yawaka</t>
-  </si>
-  <si>
-    <t>5조 1220억 1649만</t>
-  </si>
-  <si>
-    <t>요계</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%94%EA%B3%84</t>
-  </si>
-  <si>
-    <t>4조 8736억 465만</t>
-  </si>
-  <si>
-    <t>신창섭신창섭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8B%A0%EC%B0%BD%EC%84%AD%EC%8B%A0%EC%B0%BD%EC%84%AD</t>
-  </si>
-  <si>
-    <t>4조 7374억 5013만</t>
-  </si>
-  <si>
-    <t>쨍쭝</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EC%AD%9D</t>
-  </si>
-  <si>
-    <t>4조 6059억 5811만</t>
-  </si>
-  <si>
-    <t>코코연구가</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%BD%94%EC%BD%94%EC%97%B0%EA%B5%AC%EA%B0%80</t>
-  </si>
-  <si>
-    <t>4조 1336억 3721만</t>
-  </si>
-  <si>
-    <t>이빛낭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B9%9B%EB%82%AD</t>
-  </si>
-  <si>
-    <t>3조 9942억 9579만</t>
-  </si>
-  <si>
-    <t>아율마더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%EB%A7%88%EB%8D%94</t>
-  </si>
-  <si>
-    <t>3조 9404억 5955만</t>
-  </si>
-  <si>
-    <t>쫑쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 7663억 4816만</t>
-  </si>
-  <si>
-    <t>13미니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=13%EB%AF%B8%EB%8B%88</t>
-  </si>
-  <si>
-    <t>3조 6574억 242만</t>
-  </si>
-  <si>
-    <t>네그로니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EA%B7%B8%EB%A1%9C%EB%8B%88</t>
-  </si>
-  <si>
-    <t>3조 3363억 9901만</t>
-  </si>
-  <si>
-    <t>아율파더</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EC%9C%A8%ED%8C%8C%EB%8D%94</t>
-  </si>
-  <si>
-    <t>3조 1954억 4437만</t>
-  </si>
-  <si>
-    <t>맨셸리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A8%EC%85%B8%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>비숍</t>
+    <t>퍄요</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8D%84%EC%9A%94</t>
+  </si>
+  <si>
+    <t>45조 5800억 787만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EC%95%84%ED%95%91</t>
+  </si>
+  <si>
+    <t>40조 8781억 6752만</t>
+  </si>
+  <si>
+    <t>한치핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EC%B9%98%ED%95%91</t>
+  </si>
+  <si>
+    <t>28조 1282억 1685만</t>
+  </si>
+  <si>
+    <t>JKBB</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=JKBB</t>
+  </si>
+  <si>
+    <t>24조 7762억 7214만</t>
+  </si>
+  <si>
+    <t>토키공듀</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%82%A4%EA%B3%B5%EB%93%80</t>
+  </si>
+  <si>
+    <t>20조 4705억 5086만</t>
+  </si>
+  <si>
+    <t>윤물</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EB%AC%BC</t>
+  </si>
+  <si>
+    <t>20조 1397억 6644만</t>
+  </si>
+  <si>
+    <t>쫑인이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%AB%91%EC%9D%B8%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>11조 4795억 7314만</t>
+  </si>
+  <si>
+    <t>기망구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%A7%9D%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>10조 7179억 6576만</t>
+  </si>
+  <si>
+    <t>z아시안느z</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=z%EC%95%84%EC%8B%9C%EC%95%88%EB%8A%90z</t>
+  </si>
+  <si>
+    <t>10조 7164억 8855만</t>
+  </si>
+  <si>
+    <t>배디농</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%B0%EB%94%94%EB%86%8D</t>
+  </si>
+  <si>
+    <t>9조 4661억 2177만</t>
+  </si>
+  <si>
+    <t>모사예드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EC%82%AC%EC%98%88%EB%93%9C</t>
+  </si>
+  <si>
+    <t>9조 3198억 2035만</t>
+  </si>
+  <si>
+    <t>감자주인</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%90%EC%9E%90%EC%A3%BC%EC%9D%B8</t>
+  </si>
+  <si>
+    <t>9조 2880억 7590만</t>
+  </si>
+  <si>
+    <t>조승기</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%8A%B9%EA%B8%B0</t>
+  </si>
+  <si>
+    <t>8조 6992억 7707만</t>
+  </si>
+  <si>
+    <t>모덩</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%A9</t>
+  </si>
+  <si>
+    <t>8조 3540억 3806만</t>
+  </si>
+  <si>
+    <t>초바초바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B4%88%EB%B0%94%EC%B4%88%EB%B0%94</t>
+  </si>
+  <si>
+    <t>8조 2821억 2146만</t>
+  </si>
+  <si>
+    <t>디에이치</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%94%94%EC%97%90%EC%9D%B4%EC%B9%98</t>
+  </si>
+  <si>
+    <t>8조 1412억 5582만</t>
+  </si>
+  <si>
+    <t>수오니</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%88%98%EC%98%A4%EB%8B%88</t>
+  </si>
+  <si>
+    <t>7조 6831억 6445만</t>
+  </si>
+  <si>
+    <t>짱개컷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%B1%EA%B0%9C%EC%BB%B7</t>
+  </si>
+  <si>
+    <t>6조 7312억 4127만</t>
+  </si>
+  <si>
+    <t>태추킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%83%9C%EC%B6%94%ED%82%B9</t>
+  </si>
+  <si>
+    <t>6조 5632억 9964만</t>
+  </si>
+  <si>
+    <t>아미핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%84%EB%AF%B8%ED%95%91</t>
+  </si>
+  <si>
+    <t>5조 7653억 2189만</t>
+  </si>
+  <si>
+    <t>옆다방이뿐이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%86%EB%8B%A4%EB%B0%A9%EC%9D%B4%EB%BF%90%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 7527억 8907만</t>
+  </si>
+  <si>
+    <t>렁유진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A0%81%EC%9C%A0%EC%A7%84</t>
+  </si>
+  <si>
+    <t>5조 5518억 220만</t>
+  </si>
+  <si>
+    <t>루야나</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A3%A8%EC%95%BC%EB%82%98</t>
+  </si>
+  <si>
+    <t>5조 5392억 3758만</t>
+  </si>
+  <si>
+    <t>받대리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%9B%EB%8C%80%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>5조 4286억 44만</t>
+  </si>
+  <si>
+    <t>이뱅입니다</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%B1%85%EC%9E%85%EB%8B%88%EB%8B%A4</t>
+  </si>
+  <si>
+    <t>5조 3003억 3460만</t>
+  </si>
+  <si>
+    <t>노가다이씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%85%B8%EA%B0%80%EB%8B%A4%EC%9D%B4%EC%94%A8</t>
+  </si>
+  <si>
+    <t>4조 2027억 9491만</t>
+  </si>
+  <si>
+    <t>지혜혜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%98%9C%ED%98%9C</t>
+  </si>
+  <si>
+    <t>4조 1808억 5965만</t>
+  </si>
+  <si>
+    <t>엄마핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%84%EB%A7%88%ED%95%91</t>
+  </si>
+  <si>
+    <t>3조 9681억 3732만</t>
+  </si>
+  <si>
+    <t>슈종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%EC%A2%85</t>
+  </si>
+  <si>
+    <t>3조 8276억 7768만</t>
+  </si>
+  <si>
+    <t>맹시</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%B9%EC%8B%9C</t>
+  </si>
+  <si>
+    <t>3조 7987억 5434만</t>
+  </si>
+  <si>
+    <t>픅픅</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
+  </si>
+  <si>
+    <t>106</t>
+  </si>
+  <si>
+    <t>258조 5252억 2912만</t>
+  </si>
+  <si>
+    <t>호뤼뤼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
+  </si>
+  <si>
+    <t>68조 6500억 673만</t>
+  </si>
+  <si>
+    <t>끝까지힘내자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
+  </si>
+  <si>
+    <t>66조 576억 8108만</t>
+  </si>
+  <si>
+    <t>티종</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
+  </si>
+  <si>
+    <t>팔라딘</t>
+  </si>
+  <si>
+    <t>49조 4397억 5852만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=Edom</t>
+  </si>
+  <si>
+    <t>36조 7373억 645만</t>
+  </si>
+  <si>
+    <t>야생봄이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>16조 9320억 9469만</t>
+  </si>
+  <si>
+    <t>이은제리</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
+  </si>
+  <si>
+    <t>13조 5548억 927만</t>
+  </si>
+  <si>
+    <t>긍궁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
+  </si>
+  <si>
+    <t>11조 2943억 3190만</t>
+  </si>
+  <si>
+    <t>청아씨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
+  </si>
+  <si>
+    <t>7조 7427억 9482만</t>
+  </si>
+  <si>
+    <t>민규짱짱맨</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
+  </si>
+  <si>
+    <t>3조 8031억 2044만</t>
+  </si>
+  <si>
+    <t>츠키유</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
+  </si>
+  <si>
+    <t>3조 5128억 2785만</t>
+  </si>
+  <si>
+    <t>KR#9SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
+  </si>
+  <si>
+    <t>3조 1378억 5906만</t>
+  </si>
+  <si>
+    <t>망친인생</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
+  </si>
+  <si>
+    <t>1조 9606억 6575만</t>
+  </si>
+  <si>
+    <t>반존대</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
+  </si>
+  <si>
+    <t>1조 5527억 6976만</t>
+  </si>
+  <si>
+    <t>봉찬</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
+  </si>
+  <si>
+    <t>97</t>
+  </si>
+  <si>
+    <t>1조 5391억 2311만</t>
+  </si>
+  <si>
+    <t>매력적수달</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
   </si>
   <si>
     <t>96</t>
   </si>
   <si>
-    <t>5689억 4875만</t>
-  </si>
-  <si>
-    <t>픅픅</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%94%85%ED%94%85</t>
-  </si>
-  <si>
-    <t>105</t>
-  </si>
-  <si>
-    <t>114조 4499억 3097만</t>
-  </si>
-  <si>
-    <t>끝까지힘내자</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%81%9D%EA%B9%8C%EC%A7%80%ED%9E%98%EB%82%B4%EC%9E%90</t>
-  </si>
-  <si>
-    <t>34조 5879억 2379만</t>
-  </si>
-  <si>
-    <t>호뤼뤼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%98%B8%EB%A4%BC%EB%A4%BC</t>
-  </si>
-  <si>
-    <t>22조 6677억 7988만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=Edom</t>
-  </si>
-  <si>
-    <t>20조 5824억 4828만</t>
-  </si>
-  <si>
-    <t>티종</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%8B%B0%EC%A2%85</t>
-  </si>
-  <si>
-    <t>팔라딘</t>
-  </si>
-  <si>
-    <t>20조 2902억 1410만</t>
-  </si>
-  <si>
-    <t>야생봄이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%83%9D%EB%B4%84%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>9조 5092억 2050만</t>
-  </si>
-  <si>
-    <t>긍궁</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%8D%EA%B6%81</t>
-  </si>
-  <si>
-    <t>7조 243억 2592만</t>
-  </si>
-  <si>
-    <t>이은제리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%9D%80%EC%A0%9C%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>6조 2702억 6723만</t>
-  </si>
-  <si>
-    <t>청아씨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%AD%EC%95%84%EC%94%A8</t>
-  </si>
-  <si>
-    <t>4조 8340억 1193만</t>
-  </si>
-  <si>
-    <t>민규짱짱맨</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EA%B7%9C%EC%A7%B1%EC%A7%B1%EB%A7%A8</t>
-  </si>
-  <si>
-    <t>2조 5903억 4540만</t>
-  </si>
-  <si>
-    <t>KR#9SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=KR%239SQP2LGG2B</t>
-  </si>
-  <si>
-    <t>2조 3974억 3623만</t>
-  </si>
-  <si>
-    <t>츠키유</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B8%A0%ED%82%A4%EC%9C%A0</t>
-  </si>
-  <si>
-    <t>1조 8559억 7520만</t>
-  </si>
-  <si>
-    <t>망친인생</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EC%B9%9C%EC%9D%B8%EC%83%9D</t>
-  </si>
-  <si>
-    <t>1조 6185억 7611만</t>
-  </si>
-  <si>
-    <t>반존대</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B0%98%EC%A1%B4%EB%8C%80</t>
-  </si>
-  <si>
-    <t>97</t>
-  </si>
-  <si>
-    <t>1조 5527억 6976만</t>
-  </si>
-  <si>
-    <t>봉찬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B4%89%EC%B0%AC</t>
-  </si>
-  <si>
-    <t>1조 1978억 4287만</t>
+    <t>1조 4782억 3903만</t>
   </si>
   <si>
     <t>달려봐</t>
@@ -1046,643 +1067,682 @@
     <t>https://mgf.gg/contents/character.php?n=%EB%8B%AC%EB%A0%A4%EB%B4%90</t>
   </si>
   <si>
+    <t>1조 4341억 7064만</t>
+  </si>
+  <si>
+    <t>블핑돼</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B8%94%ED%95%91%EB%8F%BC</t>
+  </si>
+  <si>
+    <t>1조 3725억 4078만</t>
+  </si>
+  <si>
+    <t>몽샐</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
+  </si>
+  <si>
+    <t>1조 1943억 8126만</t>
+  </si>
+  <si>
+    <t>델리오</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
+  </si>
+  <si>
+    <t>1조 912억 9773만</t>
+  </si>
+  <si>
+    <t>서리밍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A6%AC%EB%B0%8D</t>
+  </si>
+  <si>
+    <t>9319억 8195만</t>
+  </si>
+  <si>
+    <t>채류진</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
+  </si>
+  <si>
+    <t>9301억 8538만</t>
+  </si>
+  <si>
+    <t>낀조</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
+  </si>
+  <si>
+    <t>8632억 9056만</t>
+  </si>
+  <si>
+    <t>유해화학물질</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
+  </si>
+  <si>
+    <t>8460억 4123만</t>
+  </si>
+  <si>
+    <t>ENNOY</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
+  </si>
+  <si>
+    <t>7740억 8124만</t>
+  </si>
+  <si>
+    <t>dvzve</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
+  </si>
+  <si>
+    <t>7434억 1505만</t>
+  </si>
+  <si>
+    <t>닝갠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
+  </si>
+  <si>
+    <t>7187억 7027만</t>
+  </si>
+  <si>
+    <t>공또</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
+  </si>
+  <si>
+    <t>7175억 1260만</t>
+  </si>
+  <si>
+    <t>쓱싹대선</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
+  </si>
+  <si>
+    <t>5531억 9811만</t>
+  </si>
+  <si>
+    <t>쨍꿍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
+  </si>
+  <si>
+    <t>93</t>
+  </si>
+  <si>
+    <t>3047억 4490만</t>
+  </si>
+  <si>
+    <t>31</t>
+  </si>
+  <si>
+    <t>희야미</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EC%95%BC%EB%AF%B8</t>
+  </si>
+  <si>
+    <t>90</t>
+  </si>
+  <si>
+    <t>1125억 6555만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%9D%EB%8F%99</t>
+  </si>
+  <si>
+    <t>239조 9743억 5025만</t>
+  </si>
+  <si>
+    <t>걀보</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B1%80%EB%B3%B4</t>
+  </si>
+  <si>
+    <t>46조 1417억 1775만</t>
+  </si>
+  <si>
+    <t>밍츄핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B0%8D%EC%B8%84%ED%95%91</t>
+  </si>
+  <si>
+    <t>29조 7687억 6217만</t>
+  </si>
+  <si>
+    <t>랏뚜</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9E%8F%EB%9A%9C</t>
+  </si>
+  <si>
+    <t>8조 7100억 9321만</t>
+  </si>
+  <si>
+    <t>하깁s</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EA%B9%81s</t>
+  </si>
+  <si>
+    <t>7조 3548억 4174만</t>
+  </si>
+  <si>
+    <t>이호은</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%ED%98%B8%EC%9D%80</t>
+  </si>
+  <si>
+    <t>6조 8715억 283만</t>
+  </si>
+  <si>
+    <t>그냐앙</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%B8%EB%83%90%EC%95%99</t>
+  </si>
+  <si>
+    <t>6조 208억 4700만</t>
+  </si>
+  <si>
+    <t>효능</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9A%A8%EB%8A%A5</t>
+  </si>
+  <si>
+    <t>5조 9109억 91만</t>
+  </si>
+  <si>
+    <t>네모수박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%84%A4%EB%AA%A8%EC%88%98%EB%B0%95</t>
+  </si>
+  <si>
+    <t>5조 7949억 6021만</t>
+  </si>
+  <si>
+    <t>님하하하</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8B%98%ED%95%98%ED%95%98%ED%95%98</t>
+  </si>
+  <si>
+    <t>5조 7463억 9554만</t>
+  </si>
+  <si>
+    <t>은디탁</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EB%94%94%ED%83%81</t>
+  </si>
+  <si>
+    <t>5조 6987억 3015만</t>
+  </si>
+  <si>
+    <t>갱미킴</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%B1%EB%AF%B8%ED%82%B4</t>
+  </si>
+  <si>
+    <t>5조 4153억 6820만</t>
+  </si>
+  <si>
+    <t>왕오이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%99%95%EC%98%A4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>5조 1760억 9241만</t>
+  </si>
+  <si>
+    <t>애기이잉</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EA%B8%B0%EC%9D%B4%EC%9E%89</t>
+  </si>
+  <si>
+    <t>4조 8403억 8861만</t>
+  </si>
+  <si>
+    <t>승호숍</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%ED%98%B8%EC%88%8D</t>
+  </si>
+  <si>
+    <t>4조 7981억 8653만</t>
+  </si>
+  <si>
+    <t>뮤료</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AE%A4%EB%A3%8C</t>
+  </si>
+  <si>
+    <t>4조 4030억 1630만</t>
+  </si>
+  <si>
+    <t>늙은마</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8A%99%EC%9D%80%EB%A7%88</t>
+  </si>
+  <si>
+    <t>3조 9998억 3379만</t>
+  </si>
+  <si>
+    <t>야제</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%EC%A0%9C</t>
+  </si>
+  <si>
+    <t>3조 5878억 3689만</t>
+  </si>
+  <si>
+    <t>은수성</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%80%EC%88%98%EC%84%B1</t>
+  </si>
+  <si>
+    <t>3조 5423억 6058만</t>
+  </si>
+  <si>
+    <t>부라</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B6%80%EB%9D%BC</t>
+  </si>
+  <si>
+    <t>3조 3867억 7289만</t>
+  </si>
+  <si>
+    <t>무드등</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B4%EB%93%9C%EB%93%B1</t>
+  </si>
+  <si>
+    <t>2조 9255억 5632만</t>
+  </si>
+  <si>
+    <t>안올드</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EC%98%AC%EB%93%9C</t>
+  </si>
+  <si>
+    <t>2조 6851억 4556만</t>
+  </si>
+  <si>
+    <t>jinajina</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=jinajina</t>
+  </si>
+  <si>
+    <t>2조 4398억 6125만</t>
+  </si>
+  <si>
+    <t>뻑가</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BB%91%EA%B0%80</t>
+  </si>
+  <si>
+    <t>2조 3268억 6934만</t>
+  </si>
+  <si>
+    <t>라이언킹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EC%9D%B4%EC%96%B8%ED%82%B9</t>
+  </si>
+  <si>
+    <t>2조 799억 2881만</t>
+  </si>
+  <si>
+    <t>덕장이다습할</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%8D%95%EC%9E%A5%EC%9D%B4%EB%8B%A4%EC%8A%B5%ED%95%A0</t>
+  </si>
+  <si>
+    <t>2조 494억 4393만</t>
+  </si>
+  <si>
+    <t>뿌베</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%BF%8C%EB%B2%A0</t>
+  </si>
+  <si>
+    <t>2조 76억 6793만</t>
+  </si>
+  <si>
+    <t>근카자</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B7%BC%EC%B9%B4%EC%9E%90</t>
+  </si>
+  <si>
+    <t>1조 7728억 3315만</t>
+  </si>
+  <si>
+    <t>챵술사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B1%B5%EC%88%A0%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1조 6736억 341만</t>
+  </si>
+  <si>
+    <t>켠석</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BC%A0%EC%84%9D</t>
+  </si>
+  <si>
+    <t>1조 6598억 3113만</t>
+  </si>
+  <si>
+    <t>썬콜GG</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%8D%AC%EC%BD%9CGG</t>
+  </si>
+  <si>
+    <t>264조 4315억 7048만</t>
+  </si>
+  <si>
+    <t>헫샷</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%97%AB%EC%83%B7</t>
+  </si>
+  <si>
+    <t>21조 5194억 6878만</t>
+  </si>
+  <si>
+    <t>애승e</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%95%A0%EC%8A%B9e</t>
+  </si>
+  <si>
+    <t>19조 5083억 796만</t>
+  </si>
+  <si>
+    <t>최수박</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%EC%88%98%EB%B0%95</t>
+  </si>
+  <si>
+    <t>17조 922억 5216만</t>
+  </si>
+  <si>
+    <t>리묘남편</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%EB%AC%98%EB%82%A8%ED%8E%B8</t>
+  </si>
+  <si>
+    <t>15조 7087억 6125만</t>
+  </si>
+  <si>
+    <t>얌얌얌얌</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%96%8C%EC%96%8C%EC%96%8C%EC%96%8C</t>
+  </si>
+  <si>
+    <t>7조 8138억 1918만</t>
+  </si>
+  <si>
+    <t>똥쿨래</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%98%A5%EC%BF%A8%EB%9E%98</t>
+  </si>
+  <si>
+    <t>5조 1301억 3375만</t>
+  </si>
+  <si>
+    <t>비버서비</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%84%EB%B2%84%EC%84%9C%EB%B9%84</t>
+  </si>
+  <si>
+    <t>3조 9053억 5508만</t>
+  </si>
+  <si>
+    <t>빡쿠</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%B9%A1%EC%BF%A0</t>
+  </si>
+  <si>
+    <t>3조 8144억 8411만</t>
+  </si>
+  <si>
+    <t>가현우영</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%80%ED%98%84%EC%9A%B0%EC%98%81</t>
+  </si>
+  <si>
+    <t>3조 6212억 5490만</t>
+  </si>
+  <si>
+    <t>샤르체이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%83%A4%EB%A5%B4%EC%B2%B4%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>3조 5808억 7064만</t>
+  </si>
+  <si>
+    <t>이뇽뇽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EB%87%BD%EB%87%BD</t>
+  </si>
+  <si>
+    <t>3조 5275억 6228만</t>
+  </si>
+  <si>
+    <t>링크s</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%A7%81%ED%81%ACs</t>
+  </si>
+  <si>
+    <t>3조 2636억 8249만</t>
+  </si>
+  <si>
+    <t>뚱애옹</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EB%9A%B1%EC%95%A0%EC%98%B9</t>
+  </si>
+  <si>
+    <t>3조 2597억 3065만</t>
+  </si>
+  <si>
+    <t>갓땡이</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%93%EB%95%A1%EC%9D%B4</t>
+  </si>
+  <si>
+    <t>2조 9962억 5487만</t>
+  </si>
+  <si>
+    <t>파워욱상</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%8C%8C%EC%9B%8C%EC%9A%B1%EC%83%81</t>
+  </si>
+  <si>
+    <t>2조 9578억 8832만</t>
+  </si>
+  <si>
+    <t>히운</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%9E%88%EC%9A%B4</t>
+  </si>
+  <si>
+    <t>2조 8388억 4174만</t>
+  </si>
+  <si>
+    <t>차캐핑</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%B0%A8%EC%BA%90%ED%95%91</t>
+  </si>
+  <si>
+    <t>2조 7635억 6457만</t>
+  </si>
+  <si>
+    <t>이체zl</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%B2%B4zl</t>
+  </si>
+  <si>
+    <t>2조 7323억 6324만</t>
+  </si>
+  <si>
+    <t>선리포터</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%84%A0%EB%A6%AC%ED%8F%AC%ED%84%B0</t>
+  </si>
+  <si>
+    <t>2조 7195억 2259만</t>
+  </si>
+  <si>
+    <t>깅밍댕</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B9%85%EB%B0%8D%EB%8C%95</t>
+  </si>
+  <si>
+    <t>2조 3878억 8686만</t>
+  </si>
+  <si>
+    <t>쿰바</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BF%B0%EB%B0%94</t>
+  </si>
+  <si>
+    <t>2조 2405억 565만</t>
+  </si>
+  <si>
+    <t>오류동역</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A5%98%EB%8F%99%EC%97%AD</t>
+  </si>
+  <si>
+    <t>1조 9134억 3462만</t>
+  </si>
+  <si>
+    <t>콜딘</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%BD%9C%EB%94%98</t>
+  </si>
+  <si>
+    <t>1조 8698억 2977만</t>
+  </si>
+  <si>
+    <t>개백수법사</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B0%9C%EB%B0%B1%EC%88%98%EB%B2%95%EC%82%AC</t>
+  </si>
+  <si>
+    <t>1조 7810억 1941만</t>
+  </si>
+  <si>
+    <t>고기천재</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EA%B8%B0%EC%B2%9C%EC%9E%AC</t>
+  </si>
+  <si>
+    <t>1조 4057억 2178만</t>
+  </si>
+  <si>
+    <t>곽봉구</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%BD%EB%B4%89%EA%B5%AC</t>
+  </si>
+  <si>
+    <t>1조 3592억 4892만</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%ED%86%B5%EA%B3%A0</t>
+  </si>
+  <si>
+    <t>1조 1119억 2882만</t>
+  </si>
+  <si>
+    <t>엔룽</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EC%97%94%EB%A3%BD</t>
+  </si>
+  <si>
     <t>95</t>
   </si>
   <si>
-    <t>9903억 8990만</t>
-  </si>
-  <si>
-    <t>델리오</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%B8%EB%A6%AC%EC%98%A4</t>
-  </si>
-  <si>
-    <t>9564억 1089만</t>
-  </si>
-  <si>
-    <t>매력적수달</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A7%A4%EB%A0%A5%EC%A0%81%EC%88%98%EB%8B%AC</t>
-  </si>
-  <si>
-    <t>9490억 4143만</t>
-  </si>
-  <si>
-    <t>서리밍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%9C%EB%A6%AC%EB%B0%8D</t>
-  </si>
-  <si>
-    <t>8821억 1213만</t>
-  </si>
-  <si>
-    <t>채류진</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%84%EB%A5%98%EC%A7%84</t>
-  </si>
-  <si>
-    <t>8679억 2319만</t>
-  </si>
-  <si>
-    <t>몽샐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%BD%EC%83%90</t>
-  </si>
-  <si>
-    <t>8309억 7303만</t>
-  </si>
-  <si>
-    <t>낀조</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%82%80%EC%A1%B0</t>
-  </si>
-  <si>
-    <t>7964억 3324만</t>
-  </si>
-  <si>
-    <t>공또</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B3%B5%EB%98%90</t>
-  </si>
-  <si>
-    <t>6544억 6271만</t>
-  </si>
-  <si>
-    <t>닝갠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8B%9D%EA%B0%A0</t>
-  </si>
-  <si>
-    <t>6033억 3397만</t>
-  </si>
-  <si>
-    <t>유해화학물질</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A0%ED%95%B4%ED%99%94%ED%95%99%EB%AC%BC%EC%A7%88</t>
-  </si>
-  <si>
-    <t>5629억 5975만</t>
-  </si>
-  <si>
-    <t>ENNOY</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=ENNOY</t>
-  </si>
-  <si>
-    <t>5078억 8037만</t>
-  </si>
-  <si>
-    <t>쓱싹대선</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%93%B1%EC%8B%B9%EB%8C%80%EC%84%A0</t>
-  </si>
-  <si>
-    <t>4962억 2217만</t>
-  </si>
-  <si>
-    <t>dvzve</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=dvzve</t>
-  </si>
-  <si>
-    <t>4734억 5258만</t>
-  </si>
-  <si>
-    <t>쨍꿍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A8%8D%EA%BF%8D</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>3047억 4490만</t>
-  </si>
-  <si>
-    <t>희야미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%9D%AC%EC%95%BC%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>1125억 6555만</t>
-  </si>
-  <si>
-    <t>최형사</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B5%9C%ED%98%95%EC%82%AC</t>
-  </si>
-  <si>
-    <t>28조 7582억 7650만</t>
-  </si>
-  <si>
-    <t>멀링</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A9%80%EB%A7%81</t>
-  </si>
-  <si>
-    <t>18조 5085억 1921만</t>
-  </si>
-  <si>
-    <t>오오미</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EC%98%A4%EB%AF%B8</t>
-  </si>
-  <si>
-    <t>16조 9791억 9376만</t>
-  </si>
-  <si>
-    <t>토하루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%ED%95%98%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>10조 9001억 8560만</t>
-  </si>
-  <si>
-    <t>슈퍼앤트</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%88%ED%8D%BC%EC%95%A4%ED%8A%B8</t>
-  </si>
-  <si>
-    <t>10조 3167억 1702만</t>
-  </si>
-  <si>
-    <t>쎄도어</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8E%84%EB%8F%84%EC%96%B4</t>
-  </si>
-  <si>
-    <t>8조 1239억 9013만</t>
-  </si>
-  <si>
-    <t>술라이만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%88%A0%EB%9D%BC%EC%9D%B4%EB%A7%8C</t>
-  </si>
-  <si>
-    <t>7조 2013억 3063만</t>
-  </si>
-  <si>
-    <t>머겸</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A8%B8%EA%B2%B8</t>
-  </si>
-  <si>
-    <t>6조 2723억 7081만</t>
-  </si>
-  <si>
-    <t>스응로</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%A4%EC%9D%91%EB%A1%9C</t>
-  </si>
-  <si>
-    <t>6조 1434억 6353만</t>
-  </si>
-  <si>
-    <t>abba</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=abba</t>
-  </si>
-  <si>
-    <t>6조 781억 970만</t>
-  </si>
-  <si>
-    <t>사본</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EB%B3%B8</t>
-  </si>
-  <si>
-    <t>5조 9409억 4714만</t>
-  </si>
-  <si>
-    <t>류작</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A5%98%EC%9E%91</t>
-  </si>
-  <si>
-    <t>5조 5381억 9279만</t>
-  </si>
-  <si>
-    <t>불소그리스</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B6%88%EC%86%8C%EA%B7%B8%EB%A6%AC%EC%8A%A4</t>
-  </si>
-  <si>
-    <t>5조 1945억 4963만</t>
-  </si>
-  <si>
-    <t>인천왕김치언</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B8%EC%B2%9C%EC%99%95%EA%B9%80%EC%B9%98%EC%96%B8</t>
-  </si>
-  <si>
-    <t>5조 1292억 641만</t>
-  </si>
-  <si>
-    <t>윤서u</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9C%A4%EC%84%9Cu</t>
-  </si>
-  <si>
-    <t>5조 978억 1644만</t>
-  </si>
-  <si>
-    <t>라마킴</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%A7%88%ED%82%B4</t>
-  </si>
-  <si>
-    <t>4조 8215억 9223만</t>
-  </si>
-  <si>
-    <t>조애니</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A1%B0%EC%95%A0%EB%8B%88</t>
-  </si>
-  <si>
-    <t>4조 5474억 6888만</t>
-  </si>
-  <si>
-    <t>거북이와토끼</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B1%B0%EB%B6%81%EC%9D%B4%EC%99%80%ED%86%A0%EB%81%BC</t>
-  </si>
-  <si>
-    <t>4조 3678억 4529만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%B3%B4%EB%B3%B4%EB%84%A4</t>
-  </si>
-  <si>
-    <t>3조 4820억 9851만</t>
-  </si>
-  <si>
-    <t>뜨루뜨루</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9C%A8%EB%A3%A8%EB%9C%A8%EB%A3%A8</t>
-  </si>
-  <si>
-    <t>3조 4558억 80만</t>
-  </si>
-  <si>
-    <t>민수심심해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AF%BC%EC%88%98%EC%8B%AC%EC%8B%AC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>3조 2698억 7360만</t>
-  </si>
-  <si>
-    <t>오로치재림</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%98%A4%EB%A1%9C%EC%B9%98%EC%9E%AC%EB%A6%BC</t>
-  </si>
-  <si>
-    <t>3조 240억 6770만</t>
-  </si>
-  <si>
-    <t>우현이심심해</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9A%B0%ED%98%84%EC%9D%B4%EC%8B%AC%EC%8B%AC%ED%95%B4</t>
-  </si>
-  <si>
-    <t>2조 8248억 2319만</t>
-  </si>
-  <si>
-    <t>승우아빠</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%8A%B9%EC%9A%B0%EC%95%84%EB%B9%A0</t>
-  </si>
-  <si>
-    <t>2조 7947억 5414만</t>
-  </si>
-  <si>
-    <t>문범주</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AC%B8%EB%B2%94%EC%A3%BC</t>
-  </si>
-  <si>
-    <t>2조 4228억 8783만</t>
-  </si>
-  <si>
-    <t>토리꼬리</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EA%BC%AC%EB%A6%AC</t>
-  </si>
-  <si>
-    <t>2조 2708억 440만</t>
-  </si>
-  <si>
-    <t>사이비숍</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%82%AC%EC%9D%B4%EB%B9%84%EC%88%8D</t>
-  </si>
-  <si>
-    <t>2조 2415억 9856만</t>
-  </si>
-  <si>
-    <t>토리츄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%86%A0%EB%A6%AC%EC%B8%84</t>
-  </si>
-  <si>
-    <t>1조 6139억 2384만</t>
-  </si>
-  <si>
-    <t>wheesung</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=wheesung</t>
-  </si>
-  <si>
-    <t>4494억 8136만</t>
-  </si>
-  <si>
-    <t>zl존율율</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=zl%EC%A1%B4%EC%9C%A8%EC%9C%A8</t>
-  </si>
-  <si>
-    <t>2366억 6200만</t>
-  </si>
-  <si>
-    <t>모데쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%AA%A8%EB%8D%B0%EC%93%B0</t>
-  </si>
-  <si>
-    <t>124조 9126억 7268만</t>
-  </si>
-  <si>
-    <t>잉잉기</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9E%89%EC%9E%89%EA%B8%B0</t>
-  </si>
-  <si>
-    <t>58조 725억 552만</t>
-  </si>
-  <si>
-    <t>덥쳐보니형수</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8D%A5%EC%B3%90%EB%B3%B4%EB%8B%88%ED%98%95%EC%88%98</t>
-  </si>
-  <si>
-    <t>8조 1072억 6227만</t>
-  </si>
-  <si>
-    <t>드뚜</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%93%9C%EB%9A%9C</t>
-  </si>
-  <si>
-    <t>7조 8674억 3607만</t>
-  </si>
-  <si>
-    <t>갈맄</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B0%88%EB%A7%84</t>
-  </si>
-  <si>
-    <t>6조 7374억 6694만</t>
-  </si>
-  <si>
-    <t>꾸린이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%BE%B8%EB%A6%B0%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>6조 858억 6475만</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B2%BC%EB%83%A5%EC%93%B0</t>
-  </si>
-  <si>
-    <t>6조 638억 9705만</t>
-  </si>
-  <si>
-    <t>한반</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%B0%98</t>
-  </si>
-  <si>
-    <t>3조 8720억 6714만</t>
-  </si>
-  <si>
-    <t>하냥쓰</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%EB%83%A5%EC%93%B0</t>
-  </si>
-  <si>
-    <t>3조 7462억 216만</t>
-  </si>
-  <si>
-    <t>침착맨84</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B9%A8%EC%B0%A9%EB%A7%A884</t>
-  </si>
-  <si>
-    <t>3조 2633억 224만</t>
-  </si>
-  <si>
-    <t>한맹</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%9C%EB%A7%B9</t>
-  </si>
-  <si>
-    <t>3조 539억 6371만</t>
-  </si>
-  <si>
-    <t>4033</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=4033</t>
-  </si>
-  <si>
-    <t>2조 9484억 9633만</t>
-  </si>
-  <si>
-    <t>세넬</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B8%EB%84%AC</t>
-  </si>
-  <si>
-    <t>2조 9064억 9667만</t>
-  </si>
-  <si>
-    <t>기뜩</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B8%B0%EB%9C%A9</t>
-  </si>
-  <si>
-    <t>2조 3365억 6408만</t>
-  </si>
-  <si>
-    <t>리토비</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%A6%AC%ED%86%A0%EB%B9%84</t>
-  </si>
-  <si>
-    <t>1조 9788억 8836만</t>
-  </si>
-  <si>
-    <t>군적금헌터</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EA%B5%B0%EC%A0%81%EA%B8%88%ED%97%8C%ED%84%B0</t>
-  </si>
-  <si>
-    <t>1조 9668억 1214만</t>
-  </si>
-  <si>
-    <t>도밥</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%8F%84%EB%B0%A5</t>
-  </si>
-  <si>
-    <t>1조 9524억 3673만</t>
-  </si>
-  <si>
-    <t>하흙</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%95%98%ED%9D%99</t>
-  </si>
-  <si>
-    <t>1조 9233억 4396만</t>
-  </si>
-  <si>
-    <t>라미낭</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EB%9D%BC%EB%AF%B8%EB%82%AD</t>
-  </si>
-  <si>
-    <t>1조 6431억 3517만</t>
-  </si>
-  <si>
-    <t>야햐</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%BC%ED%96%90</t>
-  </si>
-  <si>
-    <t>1조 5217억 8894만</t>
-  </si>
-  <si>
-    <t>챙날</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%B1%99%EB%82%A0</t>
-  </si>
-  <si>
-    <t>1조 3174억 6688만</t>
-  </si>
-  <si>
-    <t>지히메</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%A7%80%ED%9E%88%EB%A9%94</t>
-  </si>
-  <si>
-    <t>1조 1638억 9885만</t>
-  </si>
-  <si>
-    <t>홍루이</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%ED%99%8D%EB%A3%A8%EC%9D%B4</t>
-  </si>
-  <si>
-    <t>1조 240억 3361만</t>
-  </si>
-  <si>
-    <t>이완근</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%9D%B4%EC%99%84%EA%B7%BC</t>
-  </si>
-  <si>
-    <t>7235억 3050만</t>
-  </si>
-  <si>
-    <t>안마시술소</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%95%88%EB%A7%88%EC%8B%9C%EC%88%A0%EC%86%8C</t>
-  </si>
-  <si>
-    <t>6769억 1596만</t>
-  </si>
-  <si>
-    <t>성현이여</t>
-  </si>
-  <si>
-    <t>https://mgf.gg/contents/character.php?n=%EC%84%B1%ED%98%84%EC%9D%B4%EC%97%AC</t>
-  </si>
-  <si>
-    <t>94</t>
-  </si>
-  <si>
-    <t>2482억 7722만</t>
+    <t>6692억 2824만</t>
+  </si>
+  <si>
+    <t>고기썬콜GG</t>
+  </si>
+  <si>
+    <t>https://mgf.gg/contents/character.php?n=%EA%B3%A0%EA%B8%B0%EC%8D%AC%EC%BD%9CGG</t>
+  </si>
+  <si>
+    <t>91</t>
+  </si>
+  <si>
+    <t>1121억 8956만</t>
   </si>
 </sst>
 </file>
@@ -2163,22 +2223,22 @@
         <v>28</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>18</v>
+        <v>29</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>19</v>
+        <v>30</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="M3" s="2" t="s">
         <v>24</v>
@@ -2186,40 +2246,40 @@
     </row>
     <row r="4" spans="1:13">
       <c r="A4" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>34</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>24</v>
@@ -2227,28 +2287,28 @@
     </row>
     <row r="5" spans="1:13">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>43</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>42</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>20</v>
@@ -2256,9 +2316,11 @@
       <c r="J5" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="K5" s="2"/>
+      <c r="K5" s="2" t="s">
+        <v>48</v>
+      </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
         <v>24</v>
@@ -2266,28 +2328,28 @@
     </row>
     <row r="6" spans="1:13">
       <c r="A6" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B6" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>50</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>49</v>
       </c>
       <c r="D6" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>53</v>
+        <v>18</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>38</v>
+        <v>19</v>
       </c>
       <c r="I6" s="2" t="s">
         <v>54</v>
@@ -2404,25 +2466,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>23</v>
+        <v>74</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>76</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>71</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -2433,22 +2495,22 @@
         <v>13</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>79</v>
+        <v>23</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>80</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>82</v>
@@ -2544,13 +2606,13 @@
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="I7" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I7" s="2" t="s">
-        <v>100</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -2561,28 +2623,28 @@
         <v>13</v>
       </c>
       <c r="B8" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="F8" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G8" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D8" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="E8" s="2" t="s">
+      <c r="H8" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="I8" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="F8" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G8" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="I8" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -2593,16 +2655,16 @@
         <v>13</v>
       </c>
       <c r="B9" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="D9" s="2" t="s">
+        <v>105</v>
+      </c>
+      <c r="E9" s="2" t="s">
         <v>106</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>107</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
@@ -2614,7 +2676,7 @@
         <v>93</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -2625,28 +2687,28 @@
         <v>13</v>
       </c>
       <c r="B10" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="D10" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E10" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="D10" s="2" t="s">
-        <v>110</v>
-      </c>
-      <c r="E10" s="2" t="s">
+      <c r="F10" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G10" s="2" t="s">
         <v>111</v>
       </c>
-      <c r="F10" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H10" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -2657,28 +2719,28 @@
         <v>13</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -2689,28 +2751,28 @@
         <v>13</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>120</v>
+        <v>92</v>
       </c>
       <c r="H12" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="I12" s="2" t="s">
         <v>121</v>
-      </c>
-      <c r="I12" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -2721,28 +2783,28 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D13" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E13" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="E13" s="2" t="s">
+      <c r="F13" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G13" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="F13" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G13" s="2" t="s">
-        <v>92</v>
-      </c>
       <c r="H13" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -2753,28 +2815,28 @@
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -2785,28 +2847,28 @@
         <v>13</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>70</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -2817,28 +2879,28 @@
         <v>13</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -2849,16 +2911,16 @@
         <v>13</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>69</v>
@@ -2867,10 +2929,10 @@
         <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>121</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -2881,28 +2943,28 @@
         <v>13</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>146</v>
+        <v>112</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -2913,28 +2975,28 @@
         <v>13</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -2945,28 +3007,28 @@
         <v>13</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -2977,28 +3039,28 @@
         <v>13</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -3009,28 +3071,28 @@
         <v>13</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -3041,28 +3103,28 @@
         <v>13</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -3073,28 +3135,28 @@
         <v>13</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -3105,28 +3167,28 @@
         <v>13</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>98</v>
+        <v>178</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>121</v>
+        <v>169</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -3137,28 +3199,28 @@
         <v>13</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>93</v>
+        <v>169</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -3169,28 +3231,28 @@
         <v>13</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>87</v>
+        <v>102</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>24</v>
@@ -3201,28 +3263,28 @@
         <v>13</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>169</v>
       </c>
       <c r="I28" s="2" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J28" s="2" t="s">
         <v>24</v>
@@ -3233,28 +3295,28 @@
         <v>13</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>155</v>
+        <v>126</v>
       </c>
       <c r="I29" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J29" s="2" t="s">
         <v>24</v>
@@ -3265,28 +3327,28 @@
         <v>13</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I30" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="J30" s="2" t="s">
         <v>24</v>
@@ -3297,28 +3359,28 @@
         <v>13</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G31" s="2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>121</v>
+        <v>156</v>
       </c>
       <c r="I31" s="2" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="J31" s="2" t="s">
         <v>24</v>
@@ -3364,7 +3426,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J30"/>
+  <dimension ref="A1:J31"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
@@ -3417,25 +3479,25 @@
         <v>66</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>24</v>
@@ -3449,25 +3511,25 @@
         <v>73</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>205</v>
+        <v>33</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>69</v>
+        <v>81</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>24</v>
@@ -3478,28 +3540,28 @@
         <v>25</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>92</v>
+        <v>125</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>24</v>
@@ -3513,25 +3575,25 @@
         <v>84</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>76</v>
+        <v>131</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="I5" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="J5" s="2" t="s">
         <v>24</v>
@@ -3545,25 +3607,25 @@
         <v>89</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I6" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="J6" s="2" t="s">
         <v>24</v>
@@ -3577,25 +3639,25 @@
         <v>95</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I7" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="J7" s="2" t="s">
         <v>24</v>
@@ -3606,28 +3668,28 @@
         <v>25</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>76</v>
+        <v>111</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
       <c r="I8" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="J8" s="2" t="s">
         <v>24</v>
@@ -3638,28 +3700,28 @@
         <v>25</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>24</v>
@@ -3670,28 +3732,28 @@
         <v>25</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>70</v>
+        <v>102</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I10" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="J10" s="2" t="s">
         <v>24</v>
@@ -3702,28 +3764,28 @@
         <v>25</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>120</v>
+        <v>70</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I11" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="J11" s="2" t="s">
         <v>24</v>
@@ -3734,28 +3796,28 @@
         <v>25</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>92</v>
+        <v>111</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I12" s="2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J12" s="2" t="s">
         <v>24</v>
@@ -3766,28 +3828,28 @@
         <v>25</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I13" s="2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J13" s="2" t="s">
         <v>24</v>
@@ -3798,28 +3860,28 @@
         <v>25</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>87</v>
+        <v>111</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I14" s="2" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J14" s="2" t="s">
         <v>24</v>
@@ -3830,28 +3892,28 @@
         <v>25</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G15" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C15" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E15" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="F15" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="G15" s="2" t="s">
-        <v>76</v>
-      </c>
       <c r="H15" s="2" t="s">
-        <v>82</v>
+        <v>112</v>
       </c>
       <c r="I15" s="2" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="J15" s="2" t="s">
         <v>24</v>
@@ -3862,28 +3924,28 @@
         <v>25</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I16" s="2" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="J16" s="2" t="s">
         <v>24</v>
@@ -3894,28 +3956,28 @@
         <v>25</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>32</v>
+        <v>248</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>192</v>
+        <v>87</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J17" s="2" t="s">
         <v>24</v>
@@ -3926,28 +3988,28 @@
         <v>25</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="F18" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>92</v>
+        <v>131</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>82</v>
+        <v>93</v>
       </c>
       <c r="I18" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="J18" s="2" t="s">
         <v>24</v>
@@ -3958,28 +4020,28 @@
         <v>25</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F19" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>70</v>
+        <v>125</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>24</v>
@@ -3990,28 +4052,28 @@
         <v>25</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>76</v>
+        <v>87</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I20" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="J20" s="2" t="s">
         <v>24</v>
@@ -4022,28 +4084,28 @@
         <v>25</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>120</v>
+        <v>111</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>82</v>
+        <v>126</v>
       </c>
       <c r="I21" s="2" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="J21" s="2" t="s">
         <v>24</v>
@@ -4054,28 +4116,28 @@
         <v>25</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I22" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="J22" s="2" t="s">
         <v>24</v>
@@ -4086,28 +4148,28 @@
         <v>25</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="F23" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>70</v>
+        <v>131</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="I23" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="J23" s="2" t="s">
         <v>24</v>
@@ -4118,28 +4180,28 @@
         <v>25</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="F24" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>98</v>
+        <v>131</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>24</v>
@@ -4150,28 +4212,28 @@
         <v>25</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>70</v>
+        <v>111</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>121</v>
+        <v>112</v>
       </c>
       <c r="I25" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="J25" s="2" t="s">
         <v>24</v>
@@ -4182,28 +4244,28 @@
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>69</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>70</v>
+        <v>76</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>93</v>
+        <v>112</v>
       </c>
       <c r="I26" s="2" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="J26" s="2" t="s">
         <v>24</v>
@@ -4214,28 +4276,28 @@
         <v>25</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E27" s="2" t=